--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
@@ -74,7 +74,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Type the real unit price you found (in the row's currency). It replaces the estimate in Low, High and Working.</t>
+          <t xml:space="preserve">Type the real unit price you found, in CAD. It replaces the estimate in Low, High and Working.</t>
         </r>
       </text>
     </comment>
@@ -88,7 +88,7 @@
     <t xml:space="preserve">07K ZN6 Turbo Swap — Cost Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">CAD, before HST. Low/High = estimate range. WORKING = your actual price where you've entered one, otherwise the midpoint of the estimate. Have = Y lines count $0.</t>
+    <t xml:space="preserve">All prices in CAD (USD × 1.42, GBP × 1.85 at Oct 4, 2026), before HST. Low/High = estimate range. WORKING = your actual price where you've entered one, otherwise the midpoint of the estimate. Have = Y lines count $0.</t>
   </si>
   <si>
     <t xml:space="preserve">Assumptions</t>
@@ -337,7 +337,7 @@
     <t xml:space="preserve">Make?</t>
   </si>
   <si>
-    <t xml:space="preserve">MY unit cost (actual)</t>
+    <t xml:space="preserve">MY unit cost (actual, CAD)</t>
   </si>
   <si>
     <t xml:space="preserve">Ext low (CAD)</t>
@@ -2641,7 +2641,7 @@
     <t xml:space="preserve">9. Filters are on the header row: filter by System, Phase, Source or Status.</t>
   </si>
   <si>
-    <t xml:space="preserve">10. Exchange rates are on the Summary tab (yellow). Update USD and GBP before ordering.</t>
+    <t xml:space="preserve">10. Everything is in CAD. If you find a price in USD or GBP, convert it with the rates on the Summary tab (or change that row's Cur to USD/GBP and type the foreign price).</t>
   </si>
   <si>
     <t xml:space="preserve">Colours: blue = you edit it; yellow = key input; green row = you have it; grey row = excluded; orange row = other gearbox route.</t>
@@ -3491,15 +3491,15 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B15)</f>
-        <v>11997</v>
+        <v>11995</v>
       </c>
       <c r="D15" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B15)</f>
-        <v>23246</v>
+        <v>23250</v>
       </c>
       <c r="E15" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B15)</f>
-        <v>17621.5</v>
+        <v>17622.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3509,15 +3509,15 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B16)</f>
-        <v>1137.6</v>
+        <v>1144</v>
       </c>
       <c r="D16" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B16)</f>
-        <v>2885.8</v>
+        <v>2874</v>
       </c>
       <c r="E16" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B16)</f>
-        <v>2011.7</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3527,15 +3527,15 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B17)</f>
-        <v>2250.52</v>
+        <v>2260</v>
       </c>
       <c r="D17" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B17)</f>
-        <v>5610.85</v>
+        <v>5613</v>
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B17)</f>
-        <v>3930.685</v>
+        <v>3936.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3563,15 +3563,15 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B19)</f>
-        <v>724.2</v>
+        <v>724</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B19)</f>
-        <v>1313.5</v>
+        <v>1315</v>
       </c>
       <c r="E19" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B19)</f>
-        <v>1018.85</v>
+        <v>1019.5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3581,15 +3581,15 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B20)</f>
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D20" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B20)</f>
-        <v>896.6</v>
+        <v>895</v>
       </c>
       <c r="E20" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B20)</f>
-        <v>594.3</v>
+        <v>595</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3599,15 +3599,15 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B21)</f>
-        <v>4922.76</v>
+        <v>4933</v>
       </c>
       <c r="D21" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B21)</f>
-        <v>8526.34</v>
+        <v>8511</v>
       </c>
       <c r="E21" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B21)</f>
-        <v>6724.55</v>
+        <v>6722</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3617,15 +3617,15 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B22)</f>
-        <v>1084.88</v>
+        <v>1078</v>
       </c>
       <c r="D22" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B22)</f>
-        <v>2281.94</v>
+        <v>2305</v>
       </c>
       <c r="E22" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B22)</f>
-        <v>1683.41</v>
+        <v>1691.5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3635,15 +3635,15 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B23)</f>
-        <v>1076.42</v>
+        <v>1083</v>
       </c>
       <c r="D23" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B23)</f>
-        <v>3537.34</v>
+        <v>3553</v>
       </c>
       <c r="E23" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B23)</f>
-        <v>2306.88</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3653,15 +3653,15 @@
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B24)</f>
-        <v>626.58</v>
+        <v>623</v>
       </c>
       <c r="D24" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B24)</f>
-        <v>1342.5</v>
+        <v>1340</v>
       </c>
       <c r="E24" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B24)</f>
-        <v>984.54</v>
+        <v>981.5</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3671,15 +3671,15 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B25)</f>
-        <v>483.6</v>
+        <v>482</v>
       </c>
       <c r="D25" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B25)</f>
-        <v>1002.7</v>
+        <v>1010</v>
       </c>
       <c r="E25" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B25)</f>
-        <v>743.15</v>
+        <v>746</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3689,15 +3689,15 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B26)</f>
-        <v>404.7</v>
+        <v>405</v>
       </c>
       <c r="D26" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B26)</f>
-        <v>886.5</v>
+        <v>885</v>
       </c>
       <c r="E26" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B26)</f>
-        <v>645.6</v>
+        <v>645</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3707,15 +3707,15 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$B$5:$B$233,$B27)</f>
-        <v>367.8</v>
+        <v>370</v>
       </c>
       <c r="D27" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$B$5:$B$233,$B27)</f>
-        <v>925.6</v>
+        <v>925</v>
       </c>
       <c r="E27" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$B$5:$B$233,$B27)</f>
-        <v>646.7</v>
+        <v>647.5</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3774,15 +3774,15 @@
       </c>
       <c r="C32" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$M$5:$M$233,$B32)</f>
-        <v>12018.3</v>
+        <v>12015</v>
       </c>
       <c r="D32" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$M$5:$M$233,$B32)</f>
-        <v>23331.2</v>
+        <v>23335</v>
       </c>
       <c r="E32" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$M$5:$M$233,$B32)</f>
-        <v>17674.75</v>
+        <v>17675</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3792,15 +3792,15 @@
       </c>
       <c r="C33" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$M$5:$M$233,$B33)</f>
-        <v>851.9</v>
+        <v>860</v>
       </c>
       <c r="D33" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$M$5:$M$233,$B33)</f>
-        <v>1941.6</v>
+        <v>1940</v>
       </c>
       <c r="E33" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$M$5:$M$233,$B33)</f>
-        <v>1396.75</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3810,15 +3810,15 @@
       </c>
       <c r="C34" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$M$5:$M$233,$B34)</f>
-        <v>5230.62</v>
+        <v>5242</v>
       </c>
       <c r="D34" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$M$5:$M$233,$B34)</f>
-        <v>12685.89</v>
+        <v>12690</v>
       </c>
       <c r="E34" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$M$5:$M$233,$B34)</f>
-        <v>8958.255</v>
+        <v>8966</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3828,15 +3828,15 @@
       </c>
       <c r="C35" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$M$5:$M$233,$B35)</f>
-        <v>7182.04</v>
+        <v>7190</v>
       </c>
       <c r="D35" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$M$5:$M$233,$B35)</f>
-        <v>14001.98</v>
+        <v>14016</v>
       </c>
       <c r="E35" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$M$5:$M$233,$B35)</f>
-        <v>10592.01</v>
+        <v>10603</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="C36" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$M$5:$M$233,$B36)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="D36" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$M$5:$M$233,$B36)</f>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="E36" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$M$5:$M$233,$B36)</f>
-        <v>290.1</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3895,15 +3895,15 @@
       </c>
       <c r="C40" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$K$5:$K$233,$B40)</f>
-        <v>24583.96</v>
+        <v>24605</v>
       </c>
       <c r="D40" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$K$5:$K$233,$B40)</f>
-        <v>50349.77</v>
+        <v>50361</v>
       </c>
       <c r="E40" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$K$5:$K$233,$B40)</f>
-        <v>37466.865</v>
+        <v>37483</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3913,15 +3913,15 @@
       </c>
       <c r="C41" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$T$5:$T$233,BOM!$K$5:$K$233,$B41)</f>
-        <v>784.1</v>
+        <v>787</v>
       </c>
       <c r="D41" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$U$5:$U$233,BOM!$K$5:$K$233,$B41)</f>
-        <v>2105.9</v>
+        <v>2115</v>
       </c>
       <c r="E41" s="10" t="n">
         <f aca="false">SUMIFS(BOM!$V$5:$V$233,BOM!$K$5:$K$233,$B41)</f>
-        <v>1445</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4016,15 +4016,15 @@
       </c>
       <c r="C48" s="11" t="n">
         <f aca="false">SUM(BOM!$T$5:$T$233)-C47</f>
-        <v>13868.06</v>
+        <v>13892</v>
       </c>
       <c r="D48" s="11" t="n">
         <f aca="false">SUM(BOM!$U$5:$U$233)-D47</f>
-        <v>31455.67</v>
+        <v>31476</v>
       </c>
       <c r="E48" s="11" t="n">
         <f aca="false">SUM(BOM!$V$5:$V$233)-E47</f>
-        <v>22661.865</v>
+        <v>22684</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4052,15 +4052,15 @@
       </c>
       <c r="C50" s="11" t="n">
         <f aca="false">C48-C49</f>
-        <v>13868.06</v>
+        <v>13892</v>
       </c>
       <c r="D50" s="11" t="n">
         <f aca="false">D48-D49</f>
-        <v>31455.67</v>
+        <v>31476</v>
       </c>
       <c r="E50" s="11" t="n">
         <f aca="false">E48-E49</f>
-        <v>22661.865</v>
+        <v>22684</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4070,15 +4070,15 @@
       </c>
       <c r="C51" s="11" t="n">
         <f aca="false">C50*$C$10</f>
-        <v>3467.015</v>
+        <v>3473</v>
       </c>
       <c r="D51" s="11" t="n">
         <f aca="false">D50*$C$10</f>
-        <v>7863.9175</v>
+        <v>7869</v>
       </c>
       <c r="E51" s="11" t="n">
         <f aca="false">E50*$C$10</f>
-        <v>5665.46625</v>
+        <v>5671</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4088,15 +4088,15 @@
       </c>
       <c r="C52" s="11" t="n">
         <f aca="false">C48+C51</f>
-        <v>17335.075</v>
+        <v>17365</v>
       </c>
       <c r="D52" s="11" t="n">
         <f aca="false">D48+D51</f>
-        <v>39319.5875</v>
+        <v>39345</v>
       </c>
       <c r="E52" s="11" t="n">
         <f aca="false">E48+E51</f>
-        <v>28327.33125</v>
+        <v>28355</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4106,15 +4106,15 @@
       </c>
       <c r="C53" s="13" t="n">
         <f aca="false">C47+C52</f>
-        <v>28835.075</v>
+        <v>28865</v>
       </c>
       <c r="D53" s="13" t="n">
         <f aca="false">D47+D52</f>
-        <v>60319.5875</v>
+        <v>60345</v>
       </c>
       <c r="E53" s="13" t="n">
         <f aca="false">E47+E52</f>
-        <v>44577.33125</v>
+        <v>44605</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4465,13 +4465,13 @@
         <v>94</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>300</v>
+        <v>425</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>1150</v>
+        <v>1635</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>43</v>
@@ -4498,15 +4498,15 @@
       <c r="S6" s="21"/>
       <c r="T6" s="22" t="n">
         <f aca="false">IF(AND($O6="Y",$Q6&lt;&gt;"Y",OR($N6="",$N6=Summary!$C$11)),$F6*IF($S6&lt;&gt;"",$S6,$I6)*INDEX(Summary!$C$6:$C$8,MATCH($H6,Summary!$B$6:$B$8,0)),0)</f>
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="U6" s="22" t="n">
         <f aca="false">IF(AND($O6="Y",$Q6&lt;&gt;"Y",OR($N6="",$N6=Summary!$C$11)),$F6*IF($S6&lt;&gt;"",$S6,$J6)*INDEX(Summary!$C$6:$C$8,MATCH($H6,Summary!$B$6:$B$8,0)),0)</f>
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="V6" s="22" t="n">
         <f aca="false">IF(AND($O6="Y",$Q6&lt;&gt;"Y",OR($N6="",$N6=Summary!$C$11)),$F6*IF($S6&lt;&gt;"",$S6,($I6+$J6)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H6,Summary!$B$6:$B$8,0)),0)</f>
-        <v>1029.5</v>
+        <v>1030</v>
       </c>
       <c r="W6" s="16" t="s">
         <v>61</v>
@@ -4609,13 +4609,13 @@
         <v>94</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>43</v>
@@ -4642,15 +4642,15 @@
       <c r="S8" s="21"/>
       <c r="T8" s="22" t="n">
         <f aca="false">IF(AND($O8="Y",$Q8&lt;&gt;"Y",OR($N8="",$N8=Summary!$C$11)),$F8*IF($S8&lt;&gt;"",$S8,$I8)*INDEX(Summary!$C$6:$C$8,MATCH($H8,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U8" s="22" t="n">
         <f aca="false">IF(AND($O8="Y",$Q8&lt;&gt;"Y",OR($N8="",$N8=Summary!$C$11)),$F8*IF($S8&lt;&gt;"",$S8,$J8)*INDEX(Summary!$C$6:$C$8,MATCH($H8,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V8" s="22" t="n">
         <f aca="false">IF(AND($O8="Y",$Q8&lt;&gt;"Y",OR($N8="",$N8=Summary!$C$11)),$F8*IF($S8&lt;&gt;"",$S8,($I8+$J8)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H8,Summary!$B$6:$B$8,0)),0)</f>
-        <v>142</v>
+        <v>142.5</v>
       </c>
       <c r="W8" s="16" t="s">
         <v>109</v>
@@ -4680,13 +4680,13 @@
         <v>94</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J9" s="20" t="n">
-        <v>300</v>
+        <v>425</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>43</v>
@@ -4751,13 +4751,13 @@
         <v>94</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>43</v>
@@ -4784,15 +4784,15 @@
       <c r="S10" s="21"/>
       <c r="T10" s="22" t="n">
         <f aca="false">IF(AND($O10="Y",$Q10&lt;&gt;"Y",OR($N10="",$N10=Summary!$C$11)),$F10*IF($S10&lt;&gt;"",$S10,$I10)*INDEX(Summary!$C$6:$C$8,MATCH($H10,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U10" s="22" t="n">
         <f aca="false">IF(AND($O10="Y",$Q10&lt;&gt;"Y",OR($N10="",$N10=Summary!$C$11)),$F10*IF($S10&lt;&gt;"",$S10,$J10)*INDEX(Summary!$C$6:$C$8,MATCH($H10,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="V10" s="22" t="n">
         <f aca="false">IF(AND($O10="Y",$Q10&lt;&gt;"Y",OR($N10="",$N10=Summary!$C$11)),$F10*IF($S10&lt;&gt;"",$S10,($I10+$J10)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H10,Summary!$B$6:$B$8,0)),0)</f>
-        <v>46.15</v>
+        <v>47.5</v>
       </c>
       <c r="W10" s="16" t="s">
         <v>109</v>
@@ -4820,13 +4820,13 @@
         <v>94</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I11" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J11" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>43</v>
@@ -4853,15 +4853,15 @@
       <c r="S11" s="21"/>
       <c r="T11" s="22" t="n">
         <f aca="false">IF(AND($O11="Y",$Q11&lt;&gt;"Y",OR($N11="",$N11=Summary!$C$11)),$F11*IF($S11&lt;&gt;"",$S11,$I11)*INDEX(Summary!$C$6:$C$8,MATCH($H11,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U11" s="22" t="n">
         <f aca="false">IF(AND($O11="Y",$Q11&lt;&gt;"Y",OR($N11="",$N11=Summary!$C$11)),$F11*IF($S11&lt;&gt;"",$S11,$J11)*INDEX(Summary!$C$6:$C$8,MATCH($H11,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="V11" s="22" t="n">
         <f aca="false">IF(AND($O11="Y",$Q11&lt;&gt;"Y",OR($N11="",$N11=Summary!$C$11)),$F11*IF($S11&lt;&gt;"",$S11,($I11+$J11)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H11,Summary!$B$6:$B$8,0)),0)</f>
-        <v>24.85</v>
+        <v>24.5</v>
       </c>
       <c r="W11" s="16" t="s">
         <v>109</v>
@@ -4889,13 +4889,13 @@
         <v>94</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>43</v>
@@ -4922,15 +4922,15 @@
       <c r="S12" s="21"/>
       <c r="T12" s="22" t="n">
         <f aca="false">IF(AND($O12="Y",$Q12&lt;&gt;"Y",OR($N12="",$N12=Summary!$C$11)),$F12*IF($S12&lt;&gt;"",$S12,$I12)*INDEX(Summary!$C$6:$C$8,MATCH($H12,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="U12" s="22" t="n">
         <f aca="false">IF(AND($O12="Y",$Q12&lt;&gt;"Y",OR($N12="",$N12=Summary!$C$11)),$F12*IF($S12&lt;&gt;"",$S12,$J12)*INDEX(Summary!$C$6:$C$8,MATCH($H12,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V12" s="22" t="n">
         <f aca="false">IF(AND($O12="Y",$Q12&lt;&gt;"Y",OR($N12="",$N12=Summary!$C$11)),$F12*IF($S12&lt;&gt;"",$S12,($I12+$J12)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H12,Summary!$B$6:$B$8,0)),0)</f>
-        <v>53.25</v>
+        <v>52.5</v>
       </c>
       <c r="W12" s="16" t="s">
         <v>109</v>
@@ -4960,13 +4960,13 @@
         <v>131</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>43</v>
@@ -4993,15 +4993,15 @@
       <c r="S13" s="21"/>
       <c r="T13" s="22" t="n">
         <f aca="false">IF(AND($O13="Y",$Q13&lt;&gt;"Y",OR($N13="",$N13=Summary!$C$11)),$F13*IF($S13&lt;&gt;"",$S13,$I13)*INDEX(Summary!$C$6:$C$8,MATCH($H13,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U13" s="22" t="n">
         <f aca="false">IF(AND($O13="Y",$Q13&lt;&gt;"Y",OR($N13="",$N13=Summary!$C$11)),$F13*IF($S13&lt;&gt;"",$S13,$J13)*INDEX(Summary!$C$6:$C$8,MATCH($H13,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V13" s="22" t="n">
         <f aca="false">IF(AND($O13="Y",$Q13&lt;&gt;"Y",OR($N13="",$N13=Summary!$C$11)),$F13*IF($S13&lt;&gt;"",$S13,($I13+$J13)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H13,Summary!$B$6:$B$8,0)),0)</f>
-        <v>39.05</v>
+        <v>37.5</v>
       </c>
       <c r="W13" s="16" t="s">
         <v>109</v>
@@ -5029,13 +5029,13 @@
         <v>131</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>43</v>
@@ -5062,15 +5062,15 @@
       <c r="S14" s="21"/>
       <c r="T14" s="22" t="n">
         <f aca="false">IF(AND($O14="Y",$Q14&lt;&gt;"Y",OR($N14="",$N14=Summary!$C$11)),$F14*IF($S14&lt;&gt;"",$S14,$I14)*INDEX(Summary!$C$6:$C$8,MATCH($H14,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U14" s="22" t="n">
         <f aca="false">IF(AND($O14="Y",$Q14&lt;&gt;"Y",OR($N14="",$N14=Summary!$C$11)),$F14*IF($S14&lt;&gt;"",$S14,$J14)*INDEX(Summary!$C$6:$C$8,MATCH($H14,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="V14" s="22" t="n">
         <f aca="false">IF(AND($O14="Y",$Q14&lt;&gt;"Y",OR($N14="",$N14=Summary!$C$11)),$F14*IF($S14&lt;&gt;"",$S14,($I14+$J14)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H14,Summary!$B$6:$B$8,0)),0)</f>
-        <v>24.85</v>
+        <v>24.5</v>
       </c>
       <c r="W14" s="16" t="s">
         <v>109</v>
@@ -5098,13 +5098,13 @@
         <v>131</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I15" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J15" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>43</v>
@@ -5131,15 +5131,15 @@
       <c r="S15" s="21"/>
       <c r="T15" s="22" t="n">
         <f aca="false">IF(AND($O15="Y",$Q15&lt;&gt;"Y",OR($N15="",$N15=Summary!$C$11)),$F15*IF($S15&lt;&gt;"",$S15,$I15)*INDEX(Summary!$C$6:$C$8,MATCH($H15,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U15" s="22" t="n">
         <f aca="false">IF(AND($O15="Y",$Q15&lt;&gt;"Y",OR($N15="",$N15=Summary!$C$11)),$F15*IF($S15&lt;&gt;"",$S15,$J15)*INDEX(Summary!$C$6:$C$8,MATCH($H15,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="V15" s="22" t="n">
         <f aca="false">IF(AND($O15="Y",$Q15&lt;&gt;"Y",OR($N15="",$N15=Summary!$C$11)),$F15*IF($S15&lt;&gt;"",$S15,($I15+$J15)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H15,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="W15" s="16" t="s">
         <v>109</v>
@@ -5167,13 +5167,13 @@
         <v>94</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>43</v>
@@ -5200,15 +5200,15 @@
       <c r="S16" s="21"/>
       <c r="T16" s="22" t="n">
         <f aca="false">IF(AND($O16="Y",$Q16&lt;&gt;"Y",OR($N16="",$N16=Summary!$C$11)),$F16*IF($S16&lt;&gt;"",$S16,$I16)*INDEX(Summary!$C$6:$C$8,MATCH($H16,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U16" s="22" t="n">
         <f aca="false">IF(AND($O16="Y",$Q16&lt;&gt;"Y",OR($N16="",$N16=Summary!$C$11)),$F16*IF($S16&lt;&gt;"",$S16,$J16)*INDEX(Summary!$C$6:$C$8,MATCH($H16,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="V16" s="22" t="n">
         <f aca="false">IF(AND($O16="Y",$Q16&lt;&gt;"Y",OR($N16="",$N16=Summary!$C$11)),$F16*IF($S16&lt;&gt;"",$S16,($I16+$J16)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H16,Summary!$B$6:$B$8,0)),0)</f>
-        <v>24.85</v>
+        <v>24.5</v>
       </c>
       <c r="W16" s="16" t="s">
         <v>109</v>
@@ -5238,13 +5238,13 @@
         <v>94</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I17" s="20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J17" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>43</v>
@@ -5271,15 +5271,15 @@
       <c r="S17" s="21"/>
       <c r="T17" s="22" t="n">
         <f aca="false">IF(AND($O17="Y",$Q17&lt;&gt;"Y",OR($N17="",$N17=Summary!$C$11)),$F17*IF($S17&lt;&gt;"",$S17,$I17)*INDEX(Summary!$C$6:$C$8,MATCH($H17,Summary!$B$6:$B$8,0)),0)</f>
-        <v>34.08</v>
+        <v>34</v>
       </c>
       <c r="U17" s="22" t="n">
         <f aca="false">IF(AND($O17="Y",$Q17&lt;&gt;"Y",OR($N17="",$N17=Summary!$C$11)),$F17*IF($S17&lt;&gt;"",$S17,$J17)*INDEX(Summary!$C$6:$C$8,MATCH($H17,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V17" s="22" t="n">
         <f aca="false">IF(AND($O17="Y",$Q17&lt;&gt;"Y",OR($N17="",$N17=Summary!$C$11)),$F17*IF($S17&lt;&gt;"",$S17,($I17+$J17)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H17,Summary!$B$6:$B$8,0)),0)</f>
-        <v>52.54</v>
+        <v>52</v>
       </c>
       <c r="W17" s="16" t="s">
         <v>109</v>
@@ -5307,13 +5307,13 @@
         <v>94</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>43</v>
@@ -5340,15 +5340,15 @@
       <c r="S18" s="21"/>
       <c r="T18" s="22" t="n">
         <f aca="false">IF(AND($O18="Y",$Q18&lt;&gt;"Y",OR($N18="",$N18=Summary!$C$11)),$F18*IF($S18&lt;&gt;"",$S18,$I18)*INDEX(Summary!$C$6:$C$8,MATCH($H18,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="U18" s="22" t="n">
         <f aca="false">IF(AND($O18="Y",$Q18&lt;&gt;"Y",OR($N18="",$N18=Summary!$C$11)),$F18*IF($S18&lt;&gt;"",$S18,$J18)*INDEX(Summary!$C$6:$C$8,MATCH($H18,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V18" s="22" t="n">
         <f aca="false">IF(AND($O18="Y",$Q18&lt;&gt;"Y",OR($N18="",$N18=Summary!$C$11)),$F18*IF($S18&lt;&gt;"",$S18,($I18+$J18)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H18,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>127.5</v>
       </c>
       <c r="W18" s="16" t="s">
         <v>109</v>
@@ -5376,13 +5376,13 @@
         <v>94</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I19" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J19" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>43</v>
@@ -5409,15 +5409,15 @@
       <c r="S19" s="21"/>
       <c r="T19" s="22" t="n">
         <f aca="false">IF(AND($O19="Y",$Q19&lt;&gt;"Y",OR($N19="",$N19=Summary!$C$11)),$F19*IF($S19&lt;&gt;"",$S19,$I19)*INDEX(Summary!$C$6:$C$8,MATCH($H19,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U19" s="22" t="n">
         <f aca="false">IF(AND($O19="Y",$Q19&lt;&gt;"Y",OR($N19="",$N19=Summary!$C$11)),$F19*IF($S19&lt;&gt;"",$S19,$J19)*INDEX(Summary!$C$6:$C$8,MATCH($H19,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="V19" s="22" t="n">
         <f aca="false">IF(AND($O19="Y",$Q19&lt;&gt;"Y",OR($N19="",$N19=Summary!$C$11)),$F19*IF($S19&lt;&gt;"",$S19,($I19+$J19)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H19,Summary!$B$6:$B$8,0)),0)</f>
-        <v>46.15</v>
+        <v>47.5</v>
       </c>
       <c r="W19" s="16" t="s">
         <v>109</v>
@@ -5447,13 +5447,13 @@
         <v>150</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I20" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="20" t="n">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>43</v>
@@ -5484,11 +5484,11 @@
       </c>
       <c r="U20" s="22" t="n">
         <f aca="false">IF(AND($O20="Y",$Q20&lt;&gt;"Y",OR($N20="",$N20=Summary!$C$11)),$F20*IF($S20&lt;&gt;"",$S20,$J20)*INDEX(Summary!$C$6:$C$8,MATCH($H20,Summary!$B$6:$B$8,0)),0)</f>
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="V20" s="22" t="n">
         <f aca="false">IF(AND($O20="Y",$Q20&lt;&gt;"Y",OR($N20="",$N20=Summary!$C$11)),$F20*IF($S20&lt;&gt;"",$S20,($I20+$J20)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H20,Summary!$B$6:$B$8,0)),0)</f>
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="W20" s="16" t="s">
         <v>109</v>
@@ -5516,13 +5516,13 @@
         <v>131</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I21" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J21" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>43</v>
@@ -5549,15 +5549,15 @@
       <c r="S21" s="21"/>
       <c r="T21" s="22" t="n">
         <f aca="false">IF(AND($O21="Y",$Q21&lt;&gt;"Y",OR($N21="",$N21=Summary!$C$11)),$F21*IF($S21&lt;&gt;"",$S21,$I21)*INDEX(Summary!$C$6:$C$8,MATCH($H21,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U21" s="22" t="n">
         <f aca="false">IF(AND($O21="Y",$Q21&lt;&gt;"Y",OR($N21="",$N21=Summary!$C$11)),$F21*IF($S21&lt;&gt;"",$S21,$J21)*INDEX(Summary!$C$6:$C$8,MATCH($H21,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V21" s="22" t="n">
         <f aca="false">IF(AND($O21="Y",$Q21&lt;&gt;"Y",OR($N21="",$N21=Summary!$C$11)),$F21*IF($S21&lt;&gt;"",$S21,($I21+$J21)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H21,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>29.5</v>
       </c>
       <c r="W21" s="16" t="s">
         <v>109</v>
@@ -5587,13 +5587,13 @@
         <v>94</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J22" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>43</v>
@@ -5620,15 +5620,15 @@
       <c r="S22" s="21"/>
       <c r="T22" s="22" t="n">
         <f aca="false">IF(AND($O22="Y",$Q22&lt;&gt;"Y",OR($N22="",$N22=Summary!$C$11)),$F22*IF($S22&lt;&gt;"",$S22,$I22)*INDEX(Summary!$C$6:$C$8,MATCH($H22,Summary!$B$6:$B$8,0)),0)</f>
-        <v>22.72</v>
+        <v>22</v>
       </c>
       <c r="U22" s="22" t="n">
         <f aca="false">IF(AND($O22="Y",$Q22&lt;&gt;"Y",OR($N22="",$N22=Summary!$C$11)),$F22*IF($S22&lt;&gt;"",$S22,$J22)*INDEX(Summary!$C$6:$C$8,MATCH($H22,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>40</v>
       </c>
       <c r="V22" s="22" t="n">
         <f aca="false">IF(AND($O22="Y",$Q22&lt;&gt;"Y",OR($N22="",$N22=Summary!$C$11)),$F22*IF($S22&lt;&gt;"",$S22,($I22+$J22)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H22,Summary!$B$6:$B$8,0)),0)</f>
-        <v>32.66</v>
+        <v>31</v>
       </c>
       <c r="W22" s="16" t="s">
         <v>109</v>
@@ -5658,13 +5658,13 @@
         <v>161</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I23" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J23" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>43</v>
@@ -5691,15 +5691,15 @@
       <c r="S23" s="21"/>
       <c r="T23" s="22" t="n">
         <f aca="false">IF(AND($O23="Y",$Q23&lt;&gt;"Y",OR($N23="",$N23=Summary!$C$11)),$F23*IF($S23&lt;&gt;"",$S23,$I23)*INDEX(Summary!$C$6:$C$8,MATCH($H23,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="U23" s="22" t="n">
         <f aca="false">IF(AND($O23="Y",$Q23&lt;&gt;"Y",OR($N23="",$N23=Summary!$C$11)),$F23*IF($S23&lt;&gt;"",$S23,$J23)*INDEX(Summary!$C$6:$C$8,MATCH($H23,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V23" s="22" t="n">
         <f aca="false">IF(AND($O23="Y",$Q23&lt;&gt;"Y",OR($N23="",$N23=Summary!$C$11)),$F23*IF($S23&lt;&gt;"",$S23,($I23+$J23)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H23,Summary!$B$6:$B$8,0)),0)</f>
-        <v>134.9</v>
+        <v>135</v>
       </c>
       <c r="W23" s="16" t="s">
         <v>109</v>
@@ -5729,13 +5729,13 @@
         <v>94</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I24" s="20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>43</v>
@@ -5762,15 +5762,15 @@
       <c r="S24" s="21"/>
       <c r="T24" s="22" t="n">
         <f aca="false">IF(AND($O24="Y",$Q24&lt;&gt;"Y",OR($N24="",$N24=Summary!$C$11)),$F24*IF($S24&lt;&gt;"",$S24,$I24)*INDEX(Summary!$C$6:$C$8,MATCH($H24,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U24" s="22" t="n">
         <f aca="false">IF(AND($O24="Y",$Q24&lt;&gt;"Y",OR($N24="",$N24=Summary!$C$11)),$F24*IF($S24&lt;&gt;"",$S24,$J24)*INDEX(Summary!$C$6:$C$8,MATCH($H24,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V24" s="22" t="n">
         <f aca="false">IF(AND($O24="Y",$Q24&lt;&gt;"Y",OR($N24="",$N24=Summary!$C$11)),$F24*IF($S24&lt;&gt;"",$S24,($I24+$J24)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H24,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="W24" s="16" t="s">
         <v>109</v>
@@ -5800,13 +5800,13 @@
         <v>94</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I25" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J25" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>43</v>
@@ -5833,15 +5833,15 @@
       <c r="S25" s="21"/>
       <c r="T25" s="22" t="n">
         <f aca="false">IF(AND($O25="Y",$Q25&lt;&gt;"Y",OR($N25="",$N25=Summary!$C$11)),$F25*IF($S25&lt;&gt;"",$S25,$I25)*INDEX(Summary!$C$6:$C$8,MATCH($H25,Summary!$B$6:$B$8,0)),0)</f>
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="U25" s="22" t="n">
         <f aca="false">IF(AND($O25="Y",$Q25&lt;&gt;"Y",OR($N25="",$N25=Summary!$C$11)),$F25*IF($S25&lt;&gt;"",$S25,$J25)*INDEX(Summary!$C$6:$C$8,MATCH($H25,Summary!$B$6:$B$8,0)),0)</f>
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="V25" s="22" t="n">
         <f aca="false">IF(AND($O25="Y",$Q25&lt;&gt;"Y",OR($N25="",$N25=Summary!$C$11)),$F25*IF($S25&lt;&gt;"",$S25,($I25+$J25)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H25,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>212.5</v>
       </c>
       <c r="W25" s="16" t="s">
         <v>109</v>
@@ -5871,13 +5871,13 @@
         <v>131</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J26" s="20" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>43</v>
@@ -5904,15 +5904,15 @@
       <c r="S26" s="21"/>
       <c r="T26" s="22" t="n">
         <f aca="false">IF(AND($O26="Y",$Q26&lt;&gt;"Y",OR($N26="",$N26=Summary!$C$11)),$F26*IF($S26&lt;&gt;"",$S26,$I26)*INDEX(Summary!$C$6:$C$8,MATCH($H26,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U26" s="22" t="n">
         <f aca="false">IF(AND($O26="Y",$Q26&lt;&gt;"Y",OR($N26="",$N26=Summary!$C$11)),$F26*IF($S26&lt;&gt;"",$S26,$J26)*INDEX(Summary!$C$6:$C$8,MATCH($H26,Summary!$B$6:$B$8,0)),0)</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="V26" s="22" t="n">
         <f aca="false">IF(AND($O26="Y",$Q26&lt;&gt;"Y",OR($N26="",$N26=Summary!$C$11)),$F26*IF($S26&lt;&gt;"",$S26,($I26+$J26)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H26,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>97.5</v>
       </c>
       <c r="W26" s="16" t="s">
         <v>109</v>
@@ -5942,13 +5942,13 @@
         <v>131</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I27" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J27" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>43</v>
@@ -5975,15 +5975,15 @@
       <c r="S27" s="21"/>
       <c r="T27" s="22" t="n">
         <f aca="false">IF(AND($O27="Y",$Q27&lt;&gt;"Y",OR($N27="",$N27=Summary!$C$11)),$F27*IF($S27&lt;&gt;"",$S27,$I27)*INDEX(Summary!$C$6:$C$8,MATCH($H27,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U27" s="22" t="n">
         <f aca="false">IF(AND($O27="Y",$Q27&lt;&gt;"Y",OR($N27="",$N27=Summary!$C$11)),$F27*IF($S27&lt;&gt;"",$S27,$J27)*INDEX(Summary!$C$6:$C$8,MATCH($H27,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V27" s="22" t="n">
         <f aca="false">IF(AND($O27="Y",$Q27&lt;&gt;"Y",OR($N27="",$N27=Summary!$C$11)),$F27*IF($S27&lt;&gt;"",$S27,($I27+$J27)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H27,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>57.5</v>
       </c>
       <c r="W27" s="16" t="s">
         <v>109</v>
@@ -6013,13 +6013,13 @@
         <v>94</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I28" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J28" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>44</v>
@@ -6084,13 +6084,13 @@
         <v>94</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I29" s="20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J29" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>43</v>
@@ -6117,15 +6117,15 @@
       <c r="S29" s="21"/>
       <c r="T29" s="22" t="n">
         <f aca="false">IF(AND($O29="Y",$Q29&lt;&gt;"Y",OR($N29="",$N29=Summary!$C$11)),$F29*IF($S29&lt;&gt;"",$S29,$I29)*INDEX(Summary!$C$6:$C$8,MATCH($H29,Summary!$B$6:$B$8,0)),0)</f>
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="U29" s="22" t="n">
         <f aca="false">IF(AND($O29="Y",$Q29&lt;&gt;"Y",OR($N29="",$N29=Summary!$C$11)),$F29*IF($S29&lt;&gt;"",$S29,$J29)*INDEX(Summary!$C$6:$C$8,MATCH($H29,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="V29" s="22" t="n">
         <f aca="false">IF(AND($O29="Y",$Q29&lt;&gt;"Y",OR($N29="",$N29=Summary!$C$11)),$F29*IF($S29&lt;&gt;"",$S29,($I29+$J29)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H29,Summary!$B$6:$B$8,0)),0)</f>
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="W29" s="16" t="s">
         <v>109</v>
@@ -6155,13 +6155,13 @@
         <v>94</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I30" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J30" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>43</v>
@@ -6188,15 +6188,15 @@
       <c r="S30" s="21"/>
       <c r="T30" s="22" t="n">
         <f aca="false">IF(AND($O30="Y",$Q30&lt;&gt;"Y",OR($N30="",$N30=Summary!$C$11)),$F30*IF($S30&lt;&gt;"",$S30,$I30)*INDEX(Summary!$C$6:$C$8,MATCH($H30,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U30" s="22" t="n">
         <f aca="false">IF(AND($O30="Y",$Q30&lt;&gt;"Y",OR($N30="",$N30=Summary!$C$11)),$F30*IF($S30&lt;&gt;"",$S30,$J30)*INDEX(Summary!$C$6:$C$8,MATCH($H30,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V30" s="22" t="n">
         <f aca="false">IF(AND($O30="Y",$Q30&lt;&gt;"Y",OR($N30="",$N30=Summary!$C$11)),$F30*IF($S30&lt;&gt;"",$S30,($I30+$J30)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H30,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>112.5</v>
       </c>
       <c r="W30" s="16" t="s">
         <v>109</v>
@@ -6226,13 +6226,13 @@
         <v>94</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I31" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J31" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>43</v>
@@ -6259,15 +6259,15 @@
       <c r="S31" s="21"/>
       <c r="T31" s="22" t="n">
         <f aca="false">IF(AND($O31="Y",$Q31&lt;&gt;"Y",OR($N31="",$N31=Summary!$C$11)),$F31*IF($S31&lt;&gt;"",$S31,$I31)*INDEX(Summary!$C$6:$C$8,MATCH($H31,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="U31" s="22" t="n">
         <f aca="false">IF(AND($O31="Y",$Q31&lt;&gt;"Y",OR($N31="",$N31=Summary!$C$11)),$F31*IF($S31&lt;&gt;"",$S31,$J31)*INDEX(Summary!$C$6:$C$8,MATCH($H31,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V31" s="22" t="n">
         <f aca="false">IF(AND($O31="Y",$Q31&lt;&gt;"Y",OR($N31="",$N31=Summary!$C$11)),$F31*IF($S31&lt;&gt;"",$S31,($I31+$J31)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H31,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>127.5</v>
       </c>
       <c r="W31" s="16" t="s">
         <v>109</v>
@@ -6295,13 +6295,13 @@
         <v>150</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="J32" s="20" t="n">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>43</v>
@@ -6328,15 +6328,15 @@
       <c r="S32" s="21"/>
       <c r="T32" s="22" t="n">
         <f aca="false">IF(AND($O32="Y",$Q32&lt;&gt;"Y",OR($N32="",$N32=Summary!$C$11)),$F32*IF($S32&lt;&gt;"",$S32,$I32)*INDEX(Summary!$C$6:$C$8,MATCH($H32,Summary!$B$6:$B$8,0)),0)</f>
-        <v>255.6</v>
+        <v>255</v>
       </c>
       <c r="U32" s="22" t="n">
         <f aca="false">IF(AND($O32="Y",$Q32&lt;&gt;"Y",OR($N32="",$N32=Summary!$C$11)),$F32*IF($S32&lt;&gt;"",$S32,$J32)*INDEX(Summary!$C$6:$C$8,MATCH($H32,Summary!$B$6:$B$8,0)),0)</f>
-        <v>397.6</v>
+        <v>400</v>
       </c>
       <c r="V32" s="22" t="n">
         <f aca="false">IF(AND($O32="Y",$Q32&lt;&gt;"Y",OR($N32="",$N32=Summary!$C$11)),$F32*IF($S32&lt;&gt;"",$S32,($I32+$J32)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H32,Summary!$B$6:$B$8,0)),0)</f>
-        <v>326.6</v>
+        <v>327.5</v>
       </c>
       <c r="W32" s="16" t="s">
         <v>109</v>
@@ -6366,13 +6366,13 @@
         <v>131</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I33" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J33" s="20" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>43</v>
@@ -6506,13 +6506,13 @@
         <v>94</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I35" s="20" t="n">
-        <v>425</v>
+        <v>605</v>
       </c>
       <c r="J35" s="20" t="n">
-        <v>995</v>
+        <v>1415</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>43</v>
@@ -6541,15 +6541,15 @@
       <c r="S35" s="21"/>
       <c r="T35" s="22" t="n">
         <f aca="false">IF(AND($O35="Y",$Q35&lt;&gt;"Y",OR($N35="",$N35=Summary!$C$11)),$F35*IF($S35&lt;&gt;"",$S35,$I35)*INDEX(Summary!$C$6:$C$8,MATCH($H35,Summary!$B$6:$B$8,0)),0)</f>
-        <v>603.5</v>
+        <v>605</v>
       </c>
       <c r="U35" s="22" t="n">
         <f aca="false">IF(AND($O35="Y",$Q35&lt;&gt;"Y",OR($N35="",$N35=Summary!$C$11)),$F35*IF($S35&lt;&gt;"",$S35,$J35)*INDEX(Summary!$C$6:$C$8,MATCH($H35,Summary!$B$6:$B$8,0)),0)</f>
-        <v>1412.9</v>
+        <v>1415</v>
       </c>
       <c r="V35" s="22" t="n">
         <f aca="false">IF(AND($O35="Y",$Q35&lt;&gt;"Y",OR($N35="",$N35=Summary!$C$11)),$F35*IF($S35&lt;&gt;"",$S35,($I35+$J35)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H35,Summary!$B$6:$B$8,0)),0)</f>
-        <v>1008.2</v>
+        <v>1010</v>
       </c>
       <c r="W35" s="16" t="s">
         <v>210</v>
@@ -6579,13 +6579,13 @@
         <v>94</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="J36" s="20" t="n">
-        <v>350</v>
+        <v>495</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>43</v>
@@ -6614,11 +6614,11 @@
       <c r="S36" s="21"/>
       <c r="T36" s="22" t="n">
         <f aca="false">IF(AND($O36="Y",$Q36&lt;&gt;"Y",OR($N36="",$N36=Summary!$C$11)),$F36*IF($S36&lt;&gt;"",$S36,$I36)*INDEX(Summary!$C$6:$C$8,MATCH($H36,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U36" s="22" t="n">
         <f aca="false">IF(AND($O36="Y",$Q36&lt;&gt;"Y",OR($N36="",$N36=Summary!$C$11)),$F36*IF($S36&lt;&gt;"",$S36,$J36)*INDEX(Summary!$C$6:$C$8,MATCH($H36,Summary!$B$6:$B$8,0)),0)</f>
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="V36" s="22" t="n">
         <f aca="false">IF(AND($O36="Y",$Q36&lt;&gt;"Y",OR($N36="",$N36=Summary!$C$11)),$F36*IF($S36&lt;&gt;"",$S36,($I36+$J36)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H36,Summary!$B$6:$B$8,0)),0)</f>
@@ -6650,13 +6650,13 @@
         <v>94</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I37" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J37" s="20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>43</v>
@@ -6685,15 +6685,15 @@
       <c r="S37" s="21"/>
       <c r="T37" s="22" t="n">
         <f aca="false">IF(AND($O37="Y",$Q37&lt;&gt;"Y",OR($N37="",$N37=Summary!$C$11)),$F37*IF($S37&lt;&gt;"",$S37,$I37)*INDEX(Summary!$C$6:$C$8,MATCH($H37,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="U37" s="22" t="n">
         <f aca="false">IF(AND($O37="Y",$Q37&lt;&gt;"Y",OR($N37="",$N37=Summary!$C$11)),$F37*IF($S37&lt;&gt;"",$S37,$J37)*INDEX(Summary!$C$6:$C$8,MATCH($H37,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V37" s="22" t="n">
         <f aca="false">IF(AND($O37="Y",$Q37&lt;&gt;"Y",OR($N37="",$N37=Summary!$C$11)),$F37*IF($S37&lt;&gt;"",$S37,($I37+$J37)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H37,Summary!$B$6:$B$8,0)),0)</f>
-        <v>53.25</v>
+        <v>52.5</v>
       </c>
       <c r="W37" s="16" t="s">
         <v>109</v>
@@ -6723,13 +6723,13 @@
         <v>94</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>43</v>
@@ -6762,11 +6762,11 @@
       </c>
       <c r="U38" s="22" t="n">
         <f aca="false">IF(AND($O38="Y",$Q38&lt;&gt;"Y",OR($N38="",$N38=Summary!$C$11)),$F38*IF($S38&lt;&gt;"",$S38,$J38)*INDEX(Summary!$C$6:$C$8,MATCH($H38,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V38" s="22" t="n">
         <f aca="false">IF(AND($O38="Y",$Q38&lt;&gt;"Y",OR($N38="",$N38=Summary!$C$11)),$F38*IF($S38&lt;&gt;"",$S38,($I38+$J38)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H38,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>27.5</v>
       </c>
       <c r="W38" s="16" t="s">
         <v>109</v>
@@ -6796,13 +6796,13 @@
         <v>94</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I39" s="20" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="J39" s="20" t="n">
-        <v>300</v>
+        <v>425</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>44</v>
@@ -6831,15 +6831,15 @@
       <c r="S39" s="21"/>
       <c r="T39" s="22" t="n">
         <f aca="false">IF(AND($O39="Y",$Q39&lt;&gt;"Y",OR($N39="",$N39=Summary!$C$11)),$F39*IF($S39&lt;&gt;"",$S39,$I39)*INDEX(Summary!$C$6:$C$8,MATCH($H39,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U39" s="22" t="n">
         <f aca="false">IF(AND($O39="Y",$Q39&lt;&gt;"Y",OR($N39="",$N39=Summary!$C$11)),$F39*IF($S39&lt;&gt;"",$S39,$J39)*INDEX(Summary!$C$6:$C$8,MATCH($H39,Summary!$B$6:$B$8,0)),0)</f>
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="V39" s="22" t="n">
         <f aca="false">IF(AND($O39="Y",$Q39&lt;&gt;"Y",OR($N39="",$N39=Summary!$C$11)),$F39*IF($S39&lt;&gt;"",$S39,($I39+$J39)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H39,Summary!$B$6:$B$8,0)),0)</f>
-        <v>319.5</v>
+        <v>320</v>
       </c>
       <c r="W39" s="16" t="s">
         <v>109</v>
@@ -6871,13 +6871,13 @@
         <v>94</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>43</v>
@@ -6906,15 +6906,15 @@
       <c r="S40" s="21"/>
       <c r="T40" s="22" t="n">
         <f aca="false">IF(AND($O40="Y",$Q40&lt;&gt;"Y",OR($N40="",$N40=Summary!$C$11)),$F40*IF($S40&lt;&gt;"",$S40,$I40)*INDEX(Summary!$C$6:$C$8,MATCH($H40,Summary!$B$6:$B$8,0)),0)</f>
-        <v>11.36</v>
+        <v>12</v>
       </c>
       <c r="U40" s="22" t="n">
         <f aca="false">IF(AND($O40="Y",$Q40&lt;&gt;"Y",OR($N40="",$N40=Summary!$C$11)),$F40*IF($S40&lt;&gt;"",$S40,$J40)*INDEX(Summary!$C$6:$C$8,MATCH($H40,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>28</v>
       </c>
       <c r="V40" s="22" t="n">
         <f aca="false">IF(AND($O40="Y",$Q40&lt;&gt;"Y",OR($N40="",$N40=Summary!$C$11)),$F40*IF($S40&lt;&gt;"",$S40,($I40+$J40)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H40,Summary!$B$6:$B$8,0)),0)</f>
-        <v>19.88</v>
+        <v>20</v>
       </c>
       <c r="W40" s="16" t="s">
         <v>109</v>
@@ -6944,13 +6944,13 @@
         <v>94</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I41" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J41" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>43</v>
@@ -6979,15 +6979,15 @@
       <c r="S41" s="21"/>
       <c r="T41" s="22" t="n">
         <f aca="false">IF(AND($O41="Y",$Q41&lt;&gt;"Y",OR($N41="",$N41=Summary!$C$11)),$F41*IF($S41&lt;&gt;"",$S41,$I41)*INDEX(Summary!$C$6:$C$8,MATCH($H41,Summary!$B$6:$B$8,0)),0)</f>
-        <v>11.36</v>
+        <v>12</v>
       </c>
       <c r="U41" s="22" t="n">
         <f aca="false">IF(AND($O41="Y",$Q41&lt;&gt;"Y",OR($N41="",$N41=Summary!$C$11)),$F41*IF($S41&lt;&gt;"",$S41,$J41)*INDEX(Summary!$C$6:$C$8,MATCH($H41,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>28</v>
       </c>
       <c r="V41" s="22" t="n">
         <f aca="false">IF(AND($O41="Y",$Q41&lt;&gt;"Y",OR($N41="",$N41=Summary!$C$11)),$F41*IF($S41&lt;&gt;"",$S41,($I41+$J41)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H41,Summary!$B$6:$B$8,0)),0)</f>
-        <v>19.88</v>
+        <v>20</v>
       </c>
       <c r="W41" s="16" t="s">
         <v>109</v>
@@ -7015,13 +7015,13 @@
         <v>131</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I42" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>43</v>
@@ -7054,11 +7054,11 @@
       </c>
       <c r="U42" s="22" t="n">
         <f aca="false">IF(AND($O42="Y",$Q42&lt;&gt;"Y",OR($N42="",$N42=Summary!$C$11)),$F42*IF($S42&lt;&gt;"",$S42,$J42)*INDEX(Summary!$C$6:$C$8,MATCH($H42,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V42" s="22" t="n">
         <f aca="false">IF(AND($O42="Y",$Q42&lt;&gt;"Y",OR($N42="",$N42=Summary!$C$11)),$F42*IF($S42&lt;&gt;"",$S42,($I42+$J42)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H42,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>27.5</v>
       </c>
       <c r="W42" s="16" t="s">
         <v>109</v>
@@ -7090,13 +7090,13 @@
         <v>94</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I43" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>43</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="U43" s="22" t="n">
         <f aca="false">IF(AND($O43="Y",$Q43&lt;&gt;"Y",OR($N43="",$N43=Summary!$C$11)),$F43*IF($S43&lt;&gt;"",$S43,$J43)*INDEX(Summary!$C$6:$C$8,MATCH($H43,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="V43" s="22" t="n">
         <f aca="false">IF(AND($O43="Y",$Q43&lt;&gt;"Y",OR($N43="",$N43=Summary!$C$11)),$F43*IF($S43&lt;&gt;"",$S43,($I43+$J43)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H43,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="W43" s="16" t="s">
         <v>109</v>
@@ -7163,13 +7163,13 @@
         <v>94</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I44" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J44" s="20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K44" s="16" t="s">
         <v>43</v>
@@ -7198,15 +7198,15 @@
       <c r="S44" s="21"/>
       <c r="T44" s="22" t="n">
         <f aca="false">IF(AND($O44="Y",$Q44&lt;&gt;"Y",OR($N44="",$N44=Summary!$C$11)),$F44*IF($S44&lt;&gt;"",$S44,$I44)*INDEX(Summary!$C$6:$C$8,MATCH($H44,Summary!$B$6:$B$8,0)),0)</f>
-        <v>22.72</v>
+        <v>24</v>
       </c>
       <c r="U44" s="22" t="n">
         <f aca="false">IF(AND($O44="Y",$Q44&lt;&gt;"Y",OR($N44="",$N44=Summary!$C$11)),$F44*IF($S44&lt;&gt;"",$S44,$J44)*INDEX(Summary!$C$6:$C$8,MATCH($H44,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="V44" s="22" t="n">
         <f aca="false">IF(AND($O44="Y",$Q44&lt;&gt;"Y",OR($N44="",$N44=Summary!$C$11)),$F44*IF($S44&lt;&gt;"",$S44,($I44+$J44)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H44,Summary!$B$6:$B$8,0)),0)</f>
-        <v>39.76</v>
+        <v>40</v>
       </c>
       <c r="W44" s="16" t="s">
         <v>109</v>
@@ -7236,13 +7236,13 @@
         <v>94</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I45" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45" s="20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K45" s="16" t="s">
         <v>43</v>
@@ -7271,15 +7271,15 @@
       <c r="S45" s="21"/>
       <c r="T45" s="22" t="n">
         <f aca="false">IF(AND($O45="Y",$Q45&lt;&gt;"Y",OR($N45="",$N45=Summary!$C$11)),$F45*IF($S45&lt;&gt;"",$S45,$I45)*INDEX(Summary!$C$6:$C$8,MATCH($H45,Summary!$B$6:$B$8,0)),0)</f>
-        <v>22.72</v>
+        <v>24</v>
       </c>
       <c r="U45" s="22" t="n">
         <f aca="false">IF(AND($O45="Y",$Q45&lt;&gt;"Y",OR($N45="",$N45=Summary!$C$11)),$F45*IF($S45&lt;&gt;"",$S45,$J45)*INDEX(Summary!$C$6:$C$8,MATCH($H45,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="V45" s="22" t="n">
         <f aca="false">IF(AND($O45="Y",$Q45&lt;&gt;"Y",OR($N45="",$N45=Summary!$C$11)),$F45*IF($S45&lt;&gt;"",$S45,($I45+$J45)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H45,Summary!$B$6:$B$8,0)),0)</f>
-        <v>39.76</v>
+        <v>40</v>
       </c>
       <c r="W45" s="16" t="s">
         <v>109</v>
@@ -7382,13 +7382,13 @@
         <v>94</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I47" s="20" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="J47" s="20" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="K47" s="16" t="s">
         <v>43</v>
@@ -7455,13 +7455,13 @@
         <v>94</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="J48" s="20" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>43</v>
@@ -7530,13 +7530,13 @@
         <v>150</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I49" s="20" t="n">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="J49" s="20" t="n">
-        <v>726</v>
+        <v>1030</v>
       </c>
       <c r="K49" s="16" t="s">
         <v>43</v>
@@ -7565,15 +7565,15 @@
       <c r="S49" s="21"/>
       <c r="T49" s="22" t="n">
         <f aca="false">IF(AND($O49="Y",$Q49&lt;&gt;"Y",OR($N49="",$N49=Summary!$C$11)),$F49*IF($S49&lt;&gt;"",$S49,$I49)*INDEX(Summary!$C$6:$C$8,MATCH($H49,Summary!$B$6:$B$8,0)),0)</f>
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="U49" s="22" t="n">
         <f aca="false">IF(AND($O49="Y",$Q49&lt;&gt;"Y",OR($N49="",$N49=Summary!$C$11)),$F49*IF($S49&lt;&gt;"",$S49,$J49)*INDEX(Summary!$C$6:$C$8,MATCH($H49,Summary!$B$6:$B$8,0)),0)</f>
-        <v>1030.92</v>
+        <v>1030</v>
       </c>
       <c r="V49" s="22" t="n">
         <f aca="false">IF(AND($O49="Y",$Q49&lt;&gt;"Y",OR($N49="",$N49=Summary!$C$11)),$F49*IF($S49&lt;&gt;"",$S49,($I49+$J49)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H49,Summary!$B$6:$B$8,0)),0)</f>
-        <v>799.46</v>
+        <v>800</v>
       </c>
       <c r="W49" s="16" t="s">
         <v>210</v>
@@ -7603,13 +7603,13 @@
         <v>94</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I50" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50" s="20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>43</v>
@@ -7638,15 +7638,15 @@
       <c r="S50" s="21"/>
       <c r="T50" s="22" t="n">
         <f aca="false">IF(AND($O50="Y",$Q50&lt;&gt;"Y",OR($N50="",$N50=Summary!$C$11)),$F50*IF($S50&lt;&gt;"",$S50,$I50)*INDEX(Summary!$C$6:$C$8,MATCH($H50,Summary!$B$6:$B$8,0)),0)</f>
-        <v>25.56</v>
+        <v>24</v>
       </c>
       <c r="U50" s="22" t="n">
         <f aca="false">IF(AND($O50="Y",$Q50&lt;&gt;"Y",OR($N50="",$N50=Summary!$C$11)),$F50*IF($S50&lt;&gt;"",$S50,$J50)*INDEX(Summary!$C$6:$C$8,MATCH($H50,Summary!$B$6:$B$8,0)),0)</f>
-        <v>51.12</v>
+        <v>54</v>
       </c>
       <c r="V50" s="22" t="n">
         <f aca="false">IF(AND($O50="Y",$Q50&lt;&gt;"Y",OR($N50="",$N50=Summary!$C$11)),$F50*IF($S50&lt;&gt;"",$S50,($I50+$J50)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H50,Summary!$B$6:$B$8,0)),0)</f>
-        <v>38.34</v>
+        <v>39</v>
       </c>
       <c r="W50" s="16" t="s">
         <v>109</v>
@@ -7674,13 +7674,13 @@
         <v>94</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I51" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K51" s="16" t="s">
         <v>43</v>
@@ -7709,15 +7709,15 @@
       <c r="S51" s="21"/>
       <c r="T51" s="22" t="n">
         <f aca="false">IF(AND($O51="Y",$Q51&lt;&gt;"Y",OR($N51="",$N51=Summary!$C$11)),$F51*IF($S51&lt;&gt;"",$S51,$I51)*INDEX(Summary!$C$6:$C$8,MATCH($H51,Summary!$B$6:$B$8,0)),0)</f>
-        <v>8.52</v>
+        <v>6</v>
       </c>
       <c r="U51" s="22" t="n">
         <f aca="false">IF(AND($O51="Y",$Q51&lt;&gt;"Y",OR($N51="",$N51=Summary!$C$11)),$F51*IF($S51&lt;&gt;"",$S51,$J51)*INDEX(Summary!$C$6:$C$8,MATCH($H51,Summary!$B$6:$B$8,0)),0)</f>
-        <v>25.56</v>
+        <v>24</v>
       </c>
       <c r="V51" s="22" t="n">
         <f aca="false">IF(AND($O51="Y",$Q51&lt;&gt;"Y",OR($N51="",$N51=Summary!$C$11)),$F51*IF($S51&lt;&gt;"",$S51,($I51+$J51)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H51,Summary!$B$6:$B$8,0)),0)</f>
-        <v>17.04</v>
+        <v>15</v>
       </c>
       <c r="W51" s="16" t="s">
         <v>109</v>
@@ -7747,13 +7747,13 @@
         <v>94</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I52" s="20" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="J52" s="20" t="n">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="K52" s="16" t="s">
         <v>43</v>
@@ -7782,15 +7782,15 @@
       <c r="S52" s="21"/>
       <c r="T52" s="22" t="n">
         <f aca="false">IF(AND($O52="Y",$Q52&lt;&gt;"Y",OR($N52="",$N52=Summary!$C$11)),$F52*IF($S52&lt;&gt;"",$S52,$I52)*INDEX(Summary!$C$6:$C$8,MATCH($H52,Summary!$B$6:$B$8,0)),0)</f>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U52" s="22" t="n">
         <f aca="false">IF(AND($O52="Y",$Q52&lt;&gt;"Y",OR($N52="",$N52=Summary!$C$11)),$F52*IF($S52&lt;&gt;"",$S52,$J52)*INDEX(Summary!$C$6:$C$8,MATCH($H52,Summary!$B$6:$B$8,0)),0)</f>
-        <v>277.5</v>
+        <v>280</v>
       </c>
       <c r="V52" s="22" t="n">
         <f aca="false">IF(AND($O52="Y",$Q52&lt;&gt;"Y",OR($N52="",$N52=Summary!$C$11)),$F52*IF($S52&lt;&gt;"",$S52,($I52+$J52)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H52,Summary!$B$6:$B$8,0)),0)</f>
-        <v>194.25</v>
+        <v>195</v>
       </c>
       <c r="W52" s="16" t="s">
         <v>109</v>
@@ -7822,13 +7822,13 @@
         <v>94</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I53" s="20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J53" s="20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K53" s="16" t="s">
         <v>43</v>
@@ -7857,15 +7857,15 @@
       <c r="S53" s="21"/>
       <c r="T53" s="22" t="n">
         <f aca="false">IF(AND($O53="Y",$Q53&lt;&gt;"Y",OR($N53="",$N53=Summary!$C$11)),$F53*IF($S53&lt;&gt;"",$S53,$I53)*INDEX(Summary!$C$6:$C$8,MATCH($H53,Summary!$B$6:$B$8,0)),0)</f>
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="U53" s="22" t="n">
         <f aca="false">IF(AND($O53="Y",$Q53&lt;&gt;"Y",OR($N53="",$N53=Summary!$C$11)),$F53*IF($S53&lt;&gt;"",$S53,$J53)*INDEX(Summary!$C$6:$C$8,MATCH($H53,Summary!$B$6:$B$8,0)),0)</f>
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="V53" s="22" t="n">
         <f aca="false">IF(AND($O53="Y",$Q53&lt;&gt;"Y",OR($N53="",$N53=Summary!$C$11)),$F53*IF($S53&lt;&gt;"",$S53,($I53+$J53)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H53,Summary!$B$6:$B$8,0)),0)</f>
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="W53" s="16" t="s">
         <v>210</v>
@@ -8041,13 +8041,13 @@
         <v>94</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I56" s="20" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J56" s="20" t="n">
-        <v>145</v>
+        <v>270</v>
       </c>
       <c r="K56" s="16" t="s">
         <v>43</v>
@@ -8076,15 +8076,15 @@
       <c r="S56" s="21"/>
       <c r="T56" s="22" t="n">
         <f aca="false">IF(AND($O56="Y",$Q56&lt;&gt;"Y",OR($N56="",$N56=Summary!$C$11)),$F56*IF($S56&lt;&gt;"",$S56,$I56)*INDEX(Summary!$C$6:$C$8,MATCH($H56,Summary!$B$6:$B$8,0)),0)</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U56" s="22" t="n">
         <f aca="false">IF(AND($O56="Y",$Q56&lt;&gt;"Y",OR($N56="",$N56=Summary!$C$11)),$F56*IF($S56&lt;&gt;"",$S56,$J56)*INDEX(Summary!$C$6:$C$8,MATCH($H56,Summary!$B$6:$B$8,0)),0)</f>
-        <v>268.25</v>
+        <v>270</v>
       </c>
       <c r="V56" s="22" t="n">
         <f aca="false">IF(AND($O56="Y",$Q56&lt;&gt;"Y",OR($N56="",$N56=Summary!$C$11)),$F56*IF($S56&lt;&gt;"",$S56,($I56+$J56)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H56,Summary!$B$6:$B$8,0)),0)</f>
-        <v>171.125</v>
+        <v>172.5</v>
       </c>
       <c r="W56" s="16" t="s">
         <v>210</v>
@@ -8114,13 +8114,13 @@
         <v>94</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I57" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" s="20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K57" s="16" t="s">
         <v>43</v>
@@ -8149,15 +8149,15 @@
       <c r="S57" s="21"/>
       <c r="T57" s="22" t="n">
         <f aca="false">IF(AND($O57="Y",$Q57&lt;&gt;"Y",OR($N57="",$N57=Summary!$C$11)),$F57*IF($S57&lt;&gt;"",$S57,$I57)*INDEX(Summary!$C$6:$C$8,MATCH($H57,Summary!$B$6:$B$8,0)),0)</f>
-        <v>5.68</v>
+        <v>6</v>
       </c>
       <c r="U57" s="22" t="n">
         <f aca="false">IF(AND($O57="Y",$Q57&lt;&gt;"Y",OR($N57="",$N57=Summary!$C$11)),$F57*IF($S57&lt;&gt;"",$S57,$J57)*INDEX(Summary!$C$6:$C$8,MATCH($H57,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="V57" s="22" t="n">
         <f aca="false">IF(AND($O57="Y",$Q57&lt;&gt;"Y",OR($N57="",$N57=Summary!$C$11)),$F57*IF($S57&lt;&gt;"",$S57,($I57+$J57)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H57,Summary!$B$6:$B$8,0)),0)</f>
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="W57" s="16" t="s">
         <v>109</v>
@@ -8187,13 +8187,13 @@
         <v>203</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I58" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J58" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K58" s="16" t="s">
         <v>43</v>
@@ -8222,15 +8222,15 @@
       <c r="S58" s="21"/>
       <c r="T58" s="22" t="n">
         <f aca="false">IF(AND($O58="Y",$Q58&lt;&gt;"Y",OR($N58="",$N58=Summary!$C$11)),$F58*IF($S58&lt;&gt;"",$S58,$I58)*INDEX(Summary!$C$6:$C$8,MATCH($H58,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="U58" s="22" t="n">
         <f aca="false">IF(AND($O58="Y",$Q58&lt;&gt;"Y",OR($N58="",$N58=Summary!$C$11)),$F58*IF($S58&lt;&gt;"",$S58,$J58)*INDEX(Summary!$C$6:$C$8,MATCH($H58,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V58" s="22" t="n">
         <f aca="false">IF(AND($O58="Y",$Q58&lt;&gt;"Y",OR($N58="",$N58=Summary!$C$11)),$F58*IF($S58&lt;&gt;"",$S58,($I58+$J58)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H58,Summary!$B$6:$B$8,0)),0)</f>
-        <v>60.35</v>
+        <v>60</v>
       </c>
       <c r="W58" s="16" t="s">
         <v>109</v>
@@ -8260,13 +8260,13 @@
         <v>94</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I59" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="J59" s="20" t="n">
-        <v>460</v>
+        <v>655</v>
       </c>
       <c r="K59" s="16" t="s">
         <v>43</v>
@@ -8295,15 +8295,15 @@
       <c r="S59" s="21"/>
       <c r="T59" s="22" t="n">
         <f aca="false">IF(AND($O59="Y",$Q59&lt;&gt;"Y",OR($N59="",$N59=Summary!$C$11)),$F59*IF($S59&lt;&gt;"",$S59,$I59)*INDEX(Summary!$C$6:$C$8,MATCH($H59,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="U59" s="22" t="n">
         <f aca="false">IF(AND($O59="Y",$Q59&lt;&gt;"Y",OR($N59="",$N59=Summary!$C$11)),$F59*IF($S59&lt;&gt;"",$S59,$J59)*INDEX(Summary!$C$6:$C$8,MATCH($H59,Summary!$B$6:$B$8,0)),0)</f>
-        <v>653.2</v>
+        <v>655</v>
       </c>
       <c r="V59" s="22" t="n">
         <f aca="false">IF(AND($O59="Y",$Q59&lt;&gt;"Y",OR($N59="",$N59=Summary!$C$11)),$F59*IF($S59&lt;&gt;"",$S59,($I59+$J59)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H59,Summary!$B$6:$B$8,0)),0)</f>
-        <v>383.4</v>
+        <v>385</v>
       </c>
       <c r="W59" s="16" t="s">
         <v>109</v>
@@ -8335,13 +8335,13 @@
         <v>94</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I60" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J60" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K60" s="16" t="s">
         <v>44</v>
@@ -8370,15 +8370,15 @@
       <c r="S60" s="21"/>
       <c r="T60" s="22" t="n">
         <f aca="false">IF(AND($O60="Y",$Q60&lt;&gt;"Y",OR($N60="",$N60=Summary!$C$11)),$F60*IF($S60&lt;&gt;"",$S60,$I60)*INDEX(Summary!$C$6:$C$8,MATCH($H60,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U60" s="22" t="n">
         <f aca="false">IF(AND($O60="Y",$Q60&lt;&gt;"Y",OR($N60="",$N60=Summary!$C$11)),$F60*IF($S60&lt;&gt;"",$S60,$J60)*INDEX(Summary!$C$6:$C$8,MATCH($H60,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V60" s="22" t="n">
         <f aca="false">IF(AND($O60="Y",$Q60&lt;&gt;"Y",OR($N60="",$N60=Summary!$C$11)),$F60*IF($S60&lt;&gt;"",$S60,($I60+$J60)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H60,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="W60" s="16" t="s">
         <v>109</v>
@@ -8408,13 +8408,13 @@
         <v>203</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I61" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J61" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K61" s="16" t="s">
         <v>44</v>
@@ -8443,15 +8443,15 @@
       <c r="S61" s="21"/>
       <c r="T61" s="22" t="n">
         <f aca="false">IF(AND($O61="Y",$Q61&lt;&gt;"Y",OR($N61="",$N61=Summary!$C$11)),$F61*IF($S61&lt;&gt;"",$S61,$I61)*INDEX(Summary!$C$6:$C$8,MATCH($H61,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U61" s="22" t="n">
         <f aca="false">IF(AND($O61="Y",$Q61&lt;&gt;"Y",OR($N61="",$N61=Summary!$C$11)),$F61*IF($S61&lt;&gt;"",$S61,$J61)*INDEX(Summary!$C$6:$C$8,MATCH($H61,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="V61" s="22" t="n">
         <f aca="false">IF(AND($O61="Y",$Q61&lt;&gt;"Y",OR($N61="",$N61=Summary!$C$11)),$F61*IF($S61&lt;&gt;"",$S61,($I61+$J61)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H61,Summary!$B$6:$B$8,0)),0)</f>
-        <v>24.85</v>
+        <v>24.5</v>
       </c>
       <c r="W61" s="16" t="s">
         <v>109</v>
@@ -8481,13 +8481,13 @@
         <v>94</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I62" s="20" t="n">
-        <v>230</v>
+        <v>425</v>
       </c>
       <c r="J62" s="20" t="n">
-        <v>230</v>
+        <v>425</v>
       </c>
       <c r="K62" s="16" t="s">
         <v>43</v>
@@ -8556,13 +8556,13 @@
         <v>94</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I63" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J63" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K63" s="16" t="s">
         <v>43</v>
@@ -8591,15 +8591,15 @@
       <c r="S63" s="21"/>
       <c r="T63" s="22" t="n">
         <f aca="false">IF(AND($O63="Y",$Q63&lt;&gt;"Y",OR($N63="",$N63=Summary!$C$11)),$F63*IF($S63&lt;&gt;"",$S63,$I63)*INDEX(Summary!$C$6:$C$8,MATCH($H63,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="U63" s="22" t="n">
         <f aca="false">IF(AND($O63="Y",$Q63&lt;&gt;"Y",OR($N63="",$N63=Summary!$C$11)),$F63*IF($S63&lt;&gt;"",$S63,$J63)*INDEX(Summary!$C$6:$C$8,MATCH($H63,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="V63" s="22" t="n">
         <f aca="false">IF(AND($O63="Y",$Q63&lt;&gt;"Y",OR($N63="",$N63=Summary!$C$11)),$F63*IF($S63&lt;&gt;"",$S63,($I63+$J63)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H63,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="W63" s="16" t="s">
         <v>109</v>
@@ -8627,13 +8627,13 @@
         <v>131</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I64" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J64" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K64" s="16" t="s">
         <v>43</v>
@@ -8662,15 +8662,15 @@
       <c r="S64" s="21"/>
       <c r="T64" s="22" t="n">
         <f aca="false">IF(AND($O64="Y",$Q64&lt;&gt;"Y",OR($N64="",$N64=Summary!$C$11)),$F64*IF($S64&lt;&gt;"",$S64,$I64)*INDEX(Summary!$C$6:$C$8,MATCH($H64,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U64" s="22" t="n">
         <f aca="false">IF(AND($O64="Y",$Q64&lt;&gt;"Y",OR($N64="",$N64=Summary!$C$11)),$F64*IF($S64&lt;&gt;"",$S64,$J64)*INDEX(Summary!$C$6:$C$8,MATCH($H64,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="V64" s="22" t="n">
         <f aca="false">IF(AND($O64="Y",$Q64&lt;&gt;"Y",OR($N64="",$N64=Summary!$C$11)),$F64*IF($S64&lt;&gt;"",$S64,($I64+$J64)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H64,Summary!$B$6:$B$8,0)),0)</f>
-        <v>46.15</v>
+        <v>47.5</v>
       </c>
       <c r="W64" s="16" t="s">
         <v>109</v>
@@ -8700,13 +8700,13 @@
         <v>94</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I65" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J65" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K65" s="16" t="s">
         <v>43</v>
@@ -8735,15 +8735,15 @@
       <c r="S65" s="21"/>
       <c r="T65" s="22" t="n">
         <f aca="false">IF(AND($O65="Y",$Q65&lt;&gt;"Y",OR($N65="",$N65=Summary!$C$11)),$F65*IF($S65&lt;&gt;"",$S65,$I65)*INDEX(Summary!$C$6:$C$8,MATCH($H65,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U65" s="22" t="n">
         <f aca="false">IF(AND($O65="Y",$Q65&lt;&gt;"Y",OR($N65="",$N65=Summary!$C$11)),$F65*IF($S65&lt;&gt;"",$S65,$J65)*INDEX(Summary!$C$6:$C$8,MATCH($H65,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V65" s="22" t="n">
         <f aca="false">IF(AND($O65="Y",$Q65&lt;&gt;"Y",OR($N65="",$N65=Summary!$C$11)),$F65*IF($S65&lt;&gt;"",$S65,($I65+$J65)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H65,Summary!$B$6:$B$8,0)),0)</f>
-        <v>31.95</v>
+        <v>32.5</v>
       </c>
       <c r="W65" s="16" t="s">
         <v>109</v>
@@ -8844,13 +8844,13 @@
         <v>94</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I67" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J67" s="20" t="n">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="K67" s="16" t="s">
         <v>43</v>
@@ -9063,13 +9063,13 @@
         <v>94</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>300</v>
+        <v>425</v>
       </c>
       <c r="K70" s="16" t="s">
         <v>44</v>
@@ -9134,13 +9134,13 @@
         <v>203</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J71" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K71" s="16" t="s">
         <v>43</v>
@@ -9278,13 +9278,13 @@
         <v>94</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I73" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="20" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="K73" s="16" t="s">
         <v>45</v>
@@ -9349,13 +9349,13 @@
         <v>94</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J74" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K74" s="16" t="s">
         <v>43</v>
@@ -9564,13 +9564,13 @@
         <v>94</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I77" s="20" t="n">
-        <v>500</v>
+        <v>710</v>
       </c>
       <c r="J77" s="20" t="n">
-        <v>900</v>
+        <v>1280</v>
       </c>
       <c r="K77" s="16" t="s">
         <v>43</v>
@@ -9601,11 +9601,11 @@
       </c>
       <c r="U77" s="22" t="n">
         <f aca="false">IF(AND($O77="Y",$Q77&lt;&gt;"Y",OR($N77="",$N77=Summary!$C$11)),$F77*IF($S77&lt;&gt;"",$S77,$J77)*INDEX(Summary!$C$6:$C$8,MATCH($H77,Summary!$B$6:$B$8,0)),0)</f>
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="V77" s="22" t="n">
         <f aca="false">IF(AND($O77="Y",$Q77&lt;&gt;"Y",OR($N77="",$N77=Summary!$C$11)),$F77*IF($S77&lt;&gt;"",$S77,($I77+$J77)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H77,Summary!$B$6:$B$8,0)),0)</f>
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="W77" s="16" t="s">
         <v>61</v>
@@ -9633,13 +9633,13 @@
         <v>131</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J78" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K78" s="16" t="s">
         <v>43</v>
@@ -9666,15 +9666,15 @@
       <c r="S78" s="21"/>
       <c r="T78" s="22" t="n">
         <f aca="false">IF(AND($O78="Y",$Q78&lt;&gt;"Y",OR($N78="",$N78=Summary!$C$11)),$F78*IF($S78&lt;&gt;"",$S78,$I78)*INDEX(Summary!$C$6:$C$8,MATCH($H78,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U78" s="22" t="n">
         <f aca="false">IF(AND($O78="Y",$Q78&lt;&gt;"Y",OR($N78="",$N78=Summary!$C$11)),$F78*IF($S78&lt;&gt;"",$S78,$J78)*INDEX(Summary!$C$6:$C$8,MATCH($H78,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="V78" s="22" t="n">
         <f aca="false">IF(AND($O78="Y",$Q78&lt;&gt;"Y",OR($N78="",$N78=Summary!$C$11)),$F78*IF($S78&lt;&gt;"",$S78,($I78+$J78)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H78,Summary!$B$6:$B$8,0)),0)</f>
-        <v>24.85</v>
+        <v>24.5</v>
       </c>
       <c r="W78" s="16" t="s">
         <v>109</v>
@@ -9771,13 +9771,13 @@
         <v>94</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K80" s="16" t="s">
         <v>43</v>
@@ -9913,13 +9913,13 @@
         <v>94</v>
       </c>
       <c r="H82" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I82" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J82" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K82" s="16" t="s">
         <v>43</v>
@@ -9946,15 +9946,15 @@
       <c r="S82" s="21"/>
       <c r="T82" s="22" t="n">
         <f aca="false">IF(AND($O82="Y",$Q82&lt;&gt;"Y",OR($N82="",$N82=Summary!$C$11)),$F82*IF($S82&lt;&gt;"",$S82,$I82)*INDEX(Summary!$C$6:$C$8,MATCH($H82,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U82" s="22" t="n">
         <f aca="false">IF(AND($O82="Y",$Q82&lt;&gt;"Y",OR($N82="",$N82=Summary!$C$11)),$F82*IF($S82&lt;&gt;"",$S82,$J82)*INDEX(Summary!$C$6:$C$8,MATCH($H82,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V82" s="22" t="n">
         <f aca="false">IF(AND($O82="Y",$Q82&lt;&gt;"Y",OR($N82="",$N82=Summary!$C$11)),$F82*IF($S82&lt;&gt;"",$S82,($I82+$J82)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H82,Summary!$B$6:$B$8,0)),0)</f>
-        <v>120.7</v>
+        <v>120</v>
       </c>
       <c r="W82" s="16" t="s">
         <v>109</v>
@@ -9982,13 +9982,13 @@
         <v>203</v>
       </c>
       <c r="H83" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I83" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J83" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K83" s="16" t="s">
         <v>43</v>
@@ -10015,15 +10015,15 @@
       <c r="S83" s="21"/>
       <c r="T83" s="22" t="n">
         <f aca="false">IF(AND($O83="Y",$Q83&lt;&gt;"Y",OR($N83="",$N83=Summary!$C$11)),$F83*IF($S83&lt;&gt;"",$S83,$I83)*INDEX(Summary!$C$6:$C$8,MATCH($H83,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U83" s="22" t="n">
         <f aca="false">IF(AND($O83="Y",$Q83&lt;&gt;"Y",OR($N83="",$N83=Summary!$C$11)),$F83*IF($S83&lt;&gt;"",$S83,$J83)*INDEX(Summary!$C$6:$C$8,MATCH($H83,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V83" s="22" t="n">
         <f aca="false">IF(AND($O83="Y",$Q83&lt;&gt;"Y",OR($N83="",$N83=Summary!$C$11)),$F83*IF($S83&lt;&gt;"",$S83,($I83+$J83)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H83,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W83" s="16" t="s">
         <v>109</v>
@@ -10120,13 +10120,13 @@
         <v>94</v>
       </c>
       <c r="H85" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I85" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J85" s="20" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K85" s="16" t="s">
         <v>43</v>
@@ -10153,15 +10153,15 @@
       <c r="S85" s="21"/>
       <c r="T85" s="22" t="n">
         <f aca="false">IF(AND($O85="Y",$Q85&lt;&gt;"Y",OR($N85="",$N85=Summary!$C$11)),$F85*IF($S85&lt;&gt;"",$S85,$I85)*INDEX(Summary!$C$6:$C$8,MATCH($H85,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U85" s="22" t="n">
         <f aca="false">IF(AND($O85="Y",$Q85&lt;&gt;"Y",OR($N85="",$N85=Summary!$C$11)),$F85*IF($S85&lt;&gt;"",$S85,$J85)*INDEX(Summary!$C$6:$C$8,MATCH($H85,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="V85" s="22" t="n">
         <f aca="false">IF(AND($O85="Y",$Q85&lt;&gt;"Y",OR($N85="",$N85=Summary!$C$11)),$F85*IF($S85&lt;&gt;"",$S85,($I85+$J85)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H85,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>72.5</v>
       </c>
       <c r="W85" s="16" t="s">
         <v>109</v>
@@ -10615,13 +10615,13 @@
         <v>94</v>
       </c>
       <c r="H92" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>1700</v>
+        <v>2415</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>2300</v>
+        <v>3265</v>
       </c>
       <c r="K92" s="16" t="s">
         <v>43</v>
@@ -10648,11 +10648,11 @@
       <c r="S92" s="21"/>
       <c r="T92" s="22" t="n">
         <f aca="false">IF(AND($O92="Y",$Q92&lt;&gt;"Y",OR($N92="",$N92=Summary!$C$11)),$F92*IF($S92&lt;&gt;"",$S92,$I92)*INDEX(Summary!$C$6:$C$8,MATCH($H92,Summary!$B$6:$B$8,0)),0)</f>
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="U92" s="22" t="n">
         <f aca="false">IF(AND($O92="Y",$Q92&lt;&gt;"Y",OR($N92="",$N92=Summary!$C$11)),$F92*IF($S92&lt;&gt;"",$S92,$J92)*INDEX(Summary!$C$6:$C$8,MATCH($H92,Summary!$B$6:$B$8,0)),0)</f>
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="V92" s="22" t="n">
         <f aca="false">IF(AND($O92="Y",$Q92&lt;&gt;"Y",OR($N92="",$N92=Summary!$C$11)),$F92*IF($S92&lt;&gt;"",$S92,($I92+$J92)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H92,Summary!$B$6:$B$8,0)),0)</f>
@@ -10688,13 +10688,13 @@
         <v>131</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I93" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K93" s="16" t="s">
         <v>43</v>
@@ -10721,15 +10721,15 @@
       <c r="S93" s="21"/>
       <c r="T93" s="22" t="n">
         <f aca="false">IF(AND($O93="Y",$Q93&lt;&gt;"Y",OR($N93="",$N93=Summary!$C$11)),$F93*IF($S93&lt;&gt;"",$S93,$I93)*INDEX(Summary!$C$6:$C$8,MATCH($H93,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="U93" s="22" t="n">
         <f aca="false">IF(AND($O93="Y",$Q93&lt;&gt;"Y",OR($N93="",$N93=Summary!$C$11)),$F93*IF($S93&lt;&gt;"",$S93,$J93)*INDEX(Summary!$C$6:$C$8,MATCH($H93,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V93" s="22" t="n">
         <f aca="false">IF(AND($O93="Y",$Q93&lt;&gt;"Y",OR($N93="",$N93=Summary!$C$11)),$F93*IF($S93&lt;&gt;"",$S93,($I93+$J93)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H93,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>127.5</v>
       </c>
       <c r="W93" s="16" t="s">
         <v>109</v>
@@ -10757,13 +10757,13 @@
         <v>131</v>
       </c>
       <c r="H94" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K94" s="16" t="s">
         <v>43</v>
@@ -10790,15 +10790,15 @@
       <c r="S94" s="21"/>
       <c r="T94" s="22" t="n">
         <f aca="false">IF(AND($O94="Y",$Q94&lt;&gt;"Y",OR($N94="",$N94=Summary!$C$11)),$F94*IF($S94&lt;&gt;"",$S94,$I94)*INDEX(Summary!$C$6:$C$8,MATCH($H94,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U94" s="22" t="n">
         <f aca="false">IF(AND($O94="Y",$Q94&lt;&gt;"Y",OR($N94="",$N94=Summary!$C$11)),$F94*IF($S94&lt;&gt;"",$S94,$J94)*INDEX(Summary!$C$6:$C$8,MATCH($H94,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V94" s="22" t="n">
         <f aca="false">IF(AND($O94="Y",$Q94&lt;&gt;"Y",OR($N94="",$N94=Summary!$C$11)),$F94*IF($S94&lt;&gt;"",$S94,($I94+$J94)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H94,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>57.5</v>
       </c>
       <c r="W94" s="16" t="s">
         <v>109</v>
@@ -10828,13 +10828,13 @@
         <v>94</v>
       </c>
       <c r="H95" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I95" s="20" t="n">
-        <v>449.99</v>
+        <v>640</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>449.99</v>
+        <v>640</v>
       </c>
       <c r="K95" s="16" t="s">
         <v>43</v>
@@ -10899,13 +10899,13 @@
         <v>94</v>
       </c>
       <c r="H96" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>500</v>
+        <v>710</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>1000</v>
+        <v>1420</v>
       </c>
       <c r="K96" s="16" t="s">
         <v>43</v>
@@ -10970,13 +10970,13 @@
         <v>94</v>
       </c>
       <c r="H97" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I97" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J97" s="20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K97" s="16" t="s">
         <v>44</v>
@@ -11003,15 +11003,15 @@
       <c r="S97" s="21"/>
       <c r="T97" s="22" t="n">
         <f aca="false">IF(AND($O97="Y",$Q97&lt;&gt;"Y",OR($N97="",$N97=Summary!$C$11)),$F97*IF($S97&lt;&gt;"",$S97,$I97)*INDEX(Summary!$C$6:$C$8,MATCH($H97,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U97" s="22" t="n">
         <f aca="false">IF(AND($O97="Y",$Q97&lt;&gt;"Y",OR($N97="",$N97=Summary!$C$11)),$F97*IF($S97&lt;&gt;"",$S97,$J97)*INDEX(Summary!$C$6:$C$8,MATCH($H97,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>130</v>
       </c>
       <c r="V97" s="22" t="n">
         <f aca="false">IF(AND($O97="Y",$Q97&lt;&gt;"Y",OR($N97="",$N97=Summary!$C$11)),$F97*IF($S97&lt;&gt;"",$S97,($I97+$J97)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H97,Summary!$B$6:$B$8,0)),0)</f>
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="W97" s="16" t="s">
         <v>61</v>
@@ -11043,13 +11043,13 @@
         <v>94</v>
       </c>
       <c r="H98" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K98" s="16" t="s">
         <v>43</v>
@@ -11076,15 +11076,15 @@
       <c r="S98" s="21"/>
       <c r="T98" s="22" t="n">
         <f aca="false">IF(AND($O98="Y",$Q98&lt;&gt;"Y",OR($N98="",$N98=Summary!$C$11)),$F98*IF($S98&lt;&gt;"",$S98,$I98)*INDEX(Summary!$C$6:$C$8,MATCH($H98,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>110</v>
       </c>
       <c r="U98" s="22" t="n">
         <f aca="false">IF(AND($O98="Y",$Q98&lt;&gt;"Y",OR($N98="",$N98=Summary!$C$11)),$F98*IF($S98&lt;&gt;"",$S98,$J98)*INDEX(Summary!$C$6:$C$8,MATCH($H98,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="V98" s="22" t="n">
         <f aca="false">IF(AND($O98="Y",$Q98&lt;&gt;"Y",OR($N98="",$N98=Summary!$C$11)),$F98*IF($S98&lt;&gt;"",$S98,($I98+$J98)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H98,Summary!$B$6:$B$8,0)),0)</f>
-        <v>163.3</v>
+        <v>155</v>
       </c>
       <c r="W98" s="16" t="s">
         <v>109</v>
@@ -11112,13 +11112,13 @@
         <v>94</v>
       </c>
       <c r="H99" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K99" s="16" t="s">
         <v>43</v>
@@ -11145,15 +11145,15 @@
       <c r="S99" s="21"/>
       <c r="T99" s="22" t="n">
         <f aca="false">IF(AND($O99="Y",$Q99&lt;&gt;"Y",OR($N99="",$N99=Summary!$C$11)),$F99*IF($S99&lt;&gt;"",$S99,$I99)*INDEX(Summary!$C$6:$C$8,MATCH($H99,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="U99" s="22" t="n">
         <f aca="false">IF(AND($O99="Y",$Q99&lt;&gt;"Y",OR($N99="",$N99=Summary!$C$11)),$F99*IF($S99&lt;&gt;"",$S99,$J99)*INDEX(Summary!$C$6:$C$8,MATCH($H99,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="V99" s="22" t="n">
         <f aca="false">IF(AND($O99="Y",$Q99&lt;&gt;"Y",OR($N99="",$N99=Summary!$C$11)),$F99*IF($S99&lt;&gt;"",$S99,($I99+$J99)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H99,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="W99" s="16" t="s">
         <v>109</v>
@@ -11181,13 +11181,13 @@
         <v>94</v>
       </c>
       <c r="H100" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K100" s="16" t="s">
         <v>43</v>
@@ -11214,15 +11214,15 @@
       <c r="S100" s="21"/>
       <c r="T100" s="22" t="n">
         <f aca="false">IF(AND($O100="Y",$Q100&lt;&gt;"Y",OR($N100="",$N100=Summary!$C$11)),$F100*IF($S100&lt;&gt;"",$S100,$I100)*INDEX(Summary!$C$6:$C$8,MATCH($H100,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U100" s="22" t="n">
         <f aca="false">IF(AND($O100="Y",$Q100&lt;&gt;"Y",OR($N100="",$N100=Summary!$C$11)),$F100*IF($S100&lt;&gt;"",$S100,$J100)*INDEX(Summary!$C$6:$C$8,MATCH($H100,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V100" s="22" t="n">
         <f aca="false">IF(AND($O100="Y",$Q100&lt;&gt;"Y",OR($N100="",$N100=Summary!$C$11)),$F100*IF($S100&lt;&gt;"",$S100,($I100+$J100)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H100,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>112.5</v>
       </c>
       <c r="W100" s="16" t="s">
         <v>109</v>
@@ -11250,13 +11250,13 @@
         <v>94</v>
       </c>
       <c r="H101" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J101" s="20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K101" s="16" t="s">
         <v>43</v>
@@ -11283,15 +11283,15 @@
       <c r="S101" s="21"/>
       <c r="T101" s="22" t="n">
         <f aca="false">IF(AND($O101="Y",$Q101&lt;&gt;"Y",OR($N101="",$N101=Summary!$C$11)),$F101*IF($S101&lt;&gt;"",$S101,$I101)*INDEX(Summary!$C$6:$C$8,MATCH($H101,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U101" s="22" t="n">
         <f aca="false">IF(AND($O101="Y",$Q101&lt;&gt;"Y",OR($N101="",$N101=Summary!$C$11)),$F101*IF($S101&lt;&gt;"",$S101,$J101)*INDEX(Summary!$C$6:$C$8,MATCH($H101,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V101" s="22" t="n">
         <f aca="false">IF(AND($O101="Y",$Q101&lt;&gt;"Y",OR($N101="",$N101=Summary!$C$11)),$F101*IF($S101&lt;&gt;"",$S101,($I101+$J101)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H101,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="W101" s="16" t="s">
         <v>109</v>
@@ -11319,13 +11319,13 @@
         <v>131</v>
       </c>
       <c r="H102" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K102" s="16" t="s">
         <v>43</v>
@@ -11352,15 +11352,15 @@
       <c r="S102" s="21"/>
       <c r="T102" s="22" t="n">
         <f aca="false">IF(AND($O102="Y",$Q102&lt;&gt;"Y",OR($N102="",$N102=Summary!$C$11)),$F102*IF($S102&lt;&gt;"",$S102,$I102)*INDEX(Summary!$C$6:$C$8,MATCH($H102,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U102" s="22" t="n">
         <f aca="false">IF(AND($O102="Y",$Q102&lt;&gt;"Y",OR($N102="",$N102=Summary!$C$11)),$F102*IF($S102&lt;&gt;"",$S102,$J102)*INDEX(Summary!$C$6:$C$8,MATCH($H102,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V102" s="22" t="n">
         <f aca="false">IF(AND($O102="Y",$Q102&lt;&gt;"Y",OR($N102="",$N102=Summary!$C$11)),$F102*IF($S102&lt;&gt;"",$S102,($I102+$J102)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H102,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W102" s="16" t="s">
         <v>109</v>
@@ -11457,13 +11457,13 @@
         <v>94</v>
       </c>
       <c r="H104" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>250</v>
+        <v>355</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>450</v>
+        <v>640</v>
       </c>
       <c r="K104" s="16" t="s">
         <v>43</v>
@@ -11494,11 +11494,11 @@
       </c>
       <c r="U104" s="22" t="n">
         <f aca="false">IF(AND($O104="Y",$Q104&lt;&gt;"Y",OR($N104="",$N104=Summary!$C$11)),$F104*IF($S104&lt;&gt;"",$S104,$J104)*INDEX(Summary!$C$6:$C$8,MATCH($H104,Summary!$B$6:$B$8,0)),0)</f>
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="V104" s="22" t="n">
         <f aca="false">IF(AND($O104="Y",$Q104&lt;&gt;"Y",OR($N104="",$N104=Summary!$C$11)),$F104*IF($S104&lt;&gt;"",$S104,($I104+$J104)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H104,Summary!$B$6:$B$8,0)),0)</f>
-        <v>497</v>
+        <v>497.5</v>
       </c>
       <c r="W104" s="16" t="s">
         <v>109</v>
@@ -11526,13 +11526,13 @@
         <v>94</v>
       </c>
       <c r="H105" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I105" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J105" s="20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K105" s="16" t="s">
         <v>44</v>
@@ -11559,15 +11559,15 @@
       <c r="S105" s="21"/>
       <c r="T105" s="22" t="n">
         <f aca="false">IF(AND($O105="Y",$Q105&lt;&gt;"Y",OR($N105="",$N105=Summary!$C$11)),$F105*IF($S105&lt;&gt;"",$S105,$I105)*INDEX(Summary!$C$6:$C$8,MATCH($H105,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U105" s="22" t="n">
         <f aca="false">IF(AND($O105="Y",$Q105&lt;&gt;"Y",OR($N105="",$N105=Summary!$C$11)),$F105*IF($S105&lt;&gt;"",$S105,$J105)*INDEX(Summary!$C$6:$C$8,MATCH($H105,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V105" s="22" t="n">
         <f aca="false">IF(AND($O105="Y",$Q105&lt;&gt;"Y",OR($N105="",$N105=Summary!$C$11)),$F105*IF($S105&lt;&gt;"",$S105,($I105+$J105)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H105,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="W105" s="16" t="s">
         <v>109</v>
@@ -11595,13 +11595,13 @@
         <v>94</v>
       </c>
       <c r="H106" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I106" s="20" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J106" s="20" t="n">
-        <v>250</v>
+        <v>355</v>
       </c>
       <c r="K106" s="16" t="s">
         <v>43</v>
@@ -11628,7 +11628,7 @@
       <c r="S106" s="21"/>
       <c r="T106" s="22" t="n">
         <f aca="false">IF(AND($O106="Y",$Q106&lt;&gt;"Y",OR($N106="",$N106=Summary!$C$11)),$F106*IF($S106&lt;&gt;"",$S106,$I106)*INDEX(Summary!$C$6:$C$8,MATCH($H106,Summary!$B$6:$B$8,0)),0)</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="U106" s="22" t="n">
         <f aca="false">IF(AND($O106="Y",$Q106&lt;&gt;"Y",OR($N106="",$N106=Summary!$C$11)),$F106*IF($S106&lt;&gt;"",$S106,$J106)*INDEX(Summary!$C$6:$C$8,MATCH($H106,Summary!$B$6:$B$8,0)),0)</f>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="V106" s="22" t="n">
         <f aca="false">IF(AND($O106="Y",$Q106&lt;&gt;"Y",OR($N106="",$N106=Summary!$C$11)),$F106*IF($S106&lt;&gt;"",$S106,($I106+$J106)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H106,Summary!$B$6:$B$8,0)),0)</f>
-        <v>248.5</v>
+        <v>247.5</v>
       </c>
       <c r="W106" s="16" t="s">
         <v>109</v>
@@ -11664,13 +11664,13 @@
         <v>203</v>
       </c>
       <c r="H107" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I107" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="J107" s="20" t="n">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="K107" s="16" t="s">
         <v>43</v>
@@ -11697,15 +11697,15 @@
       <c r="S107" s="21"/>
       <c r="T107" s="22" t="n">
         <f aca="false">IF(AND($O107="Y",$Q107&lt;&gt;"Y",OR($N107="",$N107=Summary!$C$11)),$F107*IF($S107&lt;&gt;"",$S107,$I107)*INDEX(Summary!$C$6:$C$8,MATCH($H107,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="U107" s="22" t="n">
         <f aca="false">IF(AND($O107="Y",$Q107&lt;&gt;"Y",OR($N107="",$N107=Summary!$C$11)),$F107*IF($S107&lt;&gt;"",$S107,$J107)*INDEX(Summary!$C$6:$C$8,MATCH($H107,Summary!$B$6:$B$8,0)),0)</f>
-        <v>227.2</v>
+        <v>225</v>
       </c>
       <c r="V107" s="22" t="n">
         <f aca="false">IF(AND($O107="Y",$Q107&lt;&gt;"Y",OR($N107="",$N107=Summary!$C$11)),$F107*IF($S107&lt;&gt;"",$S107,($I107+$J107)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H107,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="W107" s="16" t="s">
         <v>109</v>
@@ -11733,13 +11733,13 @@
         <v>131</v>
       </c>
       <c r="H108" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I108" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J108" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K108" s="16" t="s">
         <v>43</v>
@@ -11766,15 +11766,15 @@
       <c r="S108" s="21"/>
       <c r="T108" s="22" t="n">
         <f aca="false">IF(AND($O108="Y",$Q108&lt;&gt;"Y",OR($N108="",$N108=Summary!$C$11)),$F108*IF($S108&lt;&gt;"",$S108,$I108)*INDEX(Summary!$C$6:$C$8,MATCH($H108,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U108" s="22" t="n">
         <f aca="false">IF(AND($O108="Y",$Q108&lt;&gt;"Y",OR($N108="",$N108=Summary!$C$11)),$F108*IF($S108&lt;&gt;"",$S108,$J108)*INDEX(Summary!$C$6:$C$8,MATCH($H108,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>130</v>
       </c>
       <c r="V108" s="22" t="n">
         <f aca="false">IF(AND($O108="Y",$Q108&lt;&gt;"Y",OR($N108="",$N108=Summary!$C$11)),$F108*IF($S108&lt;&gt;"",$S108,($I108+$J108)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H108,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="W108" s="16" t="s">
         <v>109</v>
@@ -11802,13 +11802,13 @@
         <v>94</v>
       </c>
       <c r="H109" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I109" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J109" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K109" s="16" t="s">
         <v>43</v>
@@ -11835,15 +11835,15 @@
       <c r="S109" s="21"/>
       <c r="T109" s="22" t="n">
         <f aca="false">IF(AND($O109="Y",$Q109&lt;&gt;"Y",OR($N109="",$N109=Summary!$C$11)),$F109*IF($S109&lt;&gt;"",$S109,$I109)*INDEX(Summary!$C$6:$C$8,MATCH($H109,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U109" s="22" t="n">
         <f aca="false">IF(AND($O109="Y",$Q109&lt;&gt;"Y",OR($N109="",$N109=Summary!$C$11)),$F109*IF($S109&lt;&gt;"",$S109,$J109)*INDEX(Summary!$C$6:$C$8,MATCH($H109,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V109" s="22" t="n">
         <f aca="false">IF(AND($O109="Y",$Q109&lt;&gt;"Y",OR($N109="",$N109=Summary!$C$11)),$F109*IF($S109&lt;&gt;"",$S109,($I109+$J109)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H109,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="W109" s="16" t="s">
         <v>109</v>
@@ -11873,13 +11873,13 @@
         <v>94</v>
       </c>
       <c r="H110" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I110" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K110" s="16" t="s">
         <v>43</v>
@@ -11906,15 +11906,15 @@
       <c r="S110" s="21"/>
       <c r="T110" s="22" t="n">
         <f aca="false">IF(AND($O110="Y",$Q110&lt;&gt;"Y",OR($N110="",$N110=Summary!$C$11)),$F110*IF($S110&lt;&gt;"",$S110,$I110)*INDEX(Summary!$C$6:$C$8,MATCH($H110,Summary!$B$6:$B$8,0)),0)</f>
-        <v>8.52</v>
+        <v>8</v>
       </c>
       <c r="U110" s="22" t="n">
         <f aca="false">IF(AND($O110="Y",$Q110&lt;&gt;"Y",OR($N110="",$N110=Summary!$C$11)),$F110*IF($S110&lt;&gt;"",$S110,$J110)*INDEX(Summary!$C$6:$C$8,MATCH($H110,Summary!$B$6:$B$8,0)),0)</f>
-        <v>22.72</v>
+        <v>22</v>
       </c>
       <c r="V110" s="22" t="n">
         <f aca="false">IF(AND($O110="Y",$Q110&lt;&gt;"Y",OR($N110="",$N110=Summary!$C$11)),$F110*IF($S110&lt;&gt;"",$S110,($I110+$J110)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H110,Summary!$B$6:$B$8,0)),0)</f>
-        <v>15.62</v>
+        <v>15</v>
       </c>
       <c r="W110" s="16" t="s">
         <v>109</v>
@@ -11944,13 +11944,13 @@
         <v>203</v>
       </c>
       <c r="H111" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I111" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J111" s="20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K111" s="16" t="s">
         <v>43</v>
@@ -11977,15 +11977,15 @@
       <c r="S111" s="21"/>
       <c r="T111" s="22" t="n">
         <f aca="false">IF(AND($O111="Y",$Q111&lt;&gt;"Y",OR($N111="",$N111=Summary!$C$11)),$F111*IF($S111&lt;&gt;"",$S111,$I111)*INDEX(Summary!$C$6:$C$8,MATCH($H111,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U111" s="22" t="n">
         <f aca="false">IF(AND($O111="Y",$Q111&lt;&gt;"Y",OR($N111="",$N111=Summary!$C$11)),$F111*IF($S111&lt;&gt;"",$S111,$J111)*INDEX(Summary!$C$6:$C$8,MATCH($H111,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>130</v>
       </c>
       <c r="V111" s="22" t="n">
         <f aca="false">IF(AND($O111="Y",$Q111&lt;&gt;"Y",OR($N111="",$N111=Summary!$C$11)),$F111*IF($S111&lt;&gt;"",$S111,($I111+$J111)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H111,Summary!$B$6:$B$8,0)),0)</f>
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="W111" s="16" t="s">
         <v>109</v>
@@ -12013,13 +12013,13 @@
         <v>203</v>
       </c>
       <c r="H112" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I112" s="20" t="n">
-        <v>300</v>
+        <v>425</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="K112" s="16" t="s">
         <v>43</v>
@@ -12082,13 +12082,13 @@
         <v>203</v>
       </c>
       <c r="H113" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I113" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J113" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K113" s="16" t="s">
         <v>43</v>
@@ -12115,15 +12115,15 @@
       <c r="S113" s="21"/>
       <c r="T113" s="22" t="n">
         <f aca="false">IF(AND($O113="Y",$Q113&lt;&gt;"Y",OR($N113="",$N113=Summary!$C$11)),$F113*IF($S113&lt;&gt;"",$S113,$I113)*INDEX(Summary!$C$6:$C$8,MATCH($H113,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U113" s="22" t="n">
         <f aca="false">IF(AND($O113="Y",$Q113&lt;&gt;"Y",OR($N113="",$N113=Summary!$C$11)),$F113*IF($S113&lt;&gt;"",$S113,$J113)*INDEX(Summary!$C$6:$C$8,MATCH($H113,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V113" s="22" t="n">
         <f aca="false">IF(AND($O113="Y",$Q113&lt;&gt;"Y",OR($N113="",$N113=Summary!$C$11)),$F113*IF($S113&lt;&gt;"",$S113,($I113+$J113)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H113,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="W113" s="16" t="s">
         <v>109</v>
@@ -12151,13 +12151,13 @@
         <v>94</v>
       </c>
       <c r="H114" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I114" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K114" s="16" t="s">
         <v>43</v>
@@ -12184,15 +12184,15 @@
       <c r="S114" s="21"/>
       <c r="T114" s="22" t="n">
         <f aca="false">IF(AND($O114="Y",$Q114&lt;&gt;"Y",OR($N114="",$N114=Summary!$C$11)),$F114*IF($S114&lt;&gt;"",$S114,$I114)*INDEX(Summary!$C$6:$C$8,MATCH($H114,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U114" s="22" t="n">
         <f aca="false">IF(AND($O114="Y",$Q114&lt;&gt;"Y",OR($N114="",$N114=Summary!$C$11)),$F114*IF($S114&lt;&gt;"",$S114,$J114)*INDEX(Summary!$C$6:$C$8,MATCH($H114,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>130</v>
       </c>
       <c r="V114" s="22" t="n">
         <f aca="false">IF(AND($O114="Y",$Q114&lt;&gt;"Y",OR($N114="",$N114=Summary!$C$11)),$F114*IF($S114&lt;&gt;"",$S114,($I114+$J114)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H114,Summary!$B$6:$B$8,0)),0)</f>
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="W114" s="16" t="s">
         <v>109</v>
@@ -12222,13 +12222,13 @@
         <v>203</v>
       </c>
       <c r="H115" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I115" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J115" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K115" s="16" t="s">
         <v>43</v>
@@ -12255,15 +12255,15 @@
       <c r="S115" s="21"/>
       <c r="T115" s="22" t="n">
         <f aca="false">IF(AND($O115="Y",$Q115&lt;&gt;"Y",OR($N115="",$N115=Summary!$C$11)),$F115*IF($S115&lt;&gt;"",$S115,$I115)*INDEX(Summary!$C$6:$C$8,MATCH($H115,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U115" s="22" t="n">
         <f aca="false">IF(AND($O115="Y",$Q115&lt;&gt;"Y",OR($N115="",$N115=Summary!$C$11)),$F115*IF($S115&lt;&gt;"",$S115,$J115)*INDEX(Summary!$C$6:$C$8,MATCH($H115,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V115" s="22" t="n">
         <f aca="false">IF(AND($O115="Y",$Q115&lt;&gt;"Y",OR($N115="",$N115=Summary!$C$11)),$F115*IF($S115&lt;&gt;"",$S115,($I115+$J115)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H115,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="W115" s="16" t="s">
         <v>109</v>
@@ -12291,13 +12291,13 @@
         <v>203</v>
       </c>
       <c r="H116" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I116" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J116" s="20" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K116" s="16" t="s">
         <v>43</v>
@@ -12324,15 +12324,15 @@
       <c r="S116" s="21"/>
       <c r="T116" s="22" t="n">
         <f aca="false">IF(AND($O116="Y",$Q116&lt;&gt;"Y",OR($N116="",$N116=Summary!$C$11)),$F116*IF($S116&lt;&gt;"",$S116,$I116)*INDEX(Summary!$C$6:$C$8,MATCH($H116,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U116" s="22" t="n">
         <f aca="false">IF(AND($O116="Y",$Q116&lt;&gt;"Y",OR($N116="",$N116=Summary!$C$11)),$F116*IF($S116&lt;&gt;"",$S116,$J116)*INDEX(Summary!$C$6:$C$8,MATCH($H116,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="V116" s="22" t="n">
         <f aca="false">IF(AND($O116="Y",$Q116&lt;&gt;"Y",OR($N116="",$N116=Summary!$C$11)),$F116*IF($S116&lt;&gt;"",$S116,($I116+$J116)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H116,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>72.5</v>
       </c>
       <c r="W116" s="16" t="s">
         <v>109</v>
@@ -12360,13 +12360,13 @@
         <v>94</v>
       </c>
       <c r="H117" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I117" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J117" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K117" s="16" t="s">
         <v>43</v>
@@ -12393,15 +12393,15 @@
       <c r="S117" s="21"/>
       <c r="T117" s="22" t="n">
         <f aca="false">IF(AND($O117="Y",$Q117&lt;&gt;"Y",OR($N117="",$N117=Summary!$C$11)),$F117*IF($S117&lt;&gt;"",$S117,$I117)*INDEX(Summary!$C$6:$C$8,MATCH($H117,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="U117" s="22" t="n">
         <f aca="false">IF(AND($O117="Y",$Q117&lt;&gt;"Y",OR($N117="",$N117=Summary!$C$11)),$F117*IF($S117&lt;&gt;"",$S117,$J117)*INDEX(Summary!$C$6:$C$8,MATCH($H117,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="V117" s="22" t="n">
         <f aca="false">IF(AND($O117="Y",$Q117&lt;&gt;"Y",OR($N117="",$N117=Summary!$C$11)),$F117*IF($S117&lt;&gt;"",$S117,($I117+$J117)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H117,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="W117" s="16" t="s">
         <v>109</v>
@@ -12429,13 +12429,13 @@
         <v>131</v>
       </c>
       <c r="H118" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I118" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J118" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K118" s="16" t="s">
         <v>43</v>
@@ -12462,15 +12462,15 @@
       <c r="S118" s="21"/>
       <c r="T118" s="22" t="n">
         <f aca="false">IF(AND($O118="Y",$Q118&lt;&gt;"Y",OR($N118="",$N118=Summary!$C$11)),$F118*IF($S118&lt;&gt;"",$S118,$I118)*INDEX(Summary!$C$6:$C$8,MATCH($H118,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U118" s="22" t="n">
         <f aca="false">IF(AND($O118="Y",$Q118&lt;&gt;"Y",OR($N118="",$N118=Summary!$C$11)),$F118*IF($S118&lt;&gt;"",$S118,$J118)*INDEX(Summary!$C$6:$C$8,MATCH($H118,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V118" s="22" t="n">
         <f aca="false">IF(AND($O118="Y",$Q118&lt;&gt;"Y",OR($N118="",$N118=Summary!$C$11)),$F118*IF($S118&lt;&gt;"",$S118,($I118+$J118)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H118,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="W118" s="16" t="s">
         <v>109</v>
@@ -12498,13 +12498,13 @@
         <v>131</v>
       </c>
       <c r="H119" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I119" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J119" s="20" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K119" s="16" t="s">
         <v>43</v>
@@ -12531,15 +12531,15 @@
       <c r="S119" s="21"/>
       <c r="T119" s="22" t="n">
         <f aca="false">IF(AND($O119="Y",$Q119&lt;&gt;"Y",OR($N119="",$N119=Summary!$C$11)),$F119*IF($S119&lt;&gt;"",$S119,$I119)*INDEX(Summary!$C$6:$C$8,MATCH($H119,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="U119" s="22" t="n">
         <f aca="false">IF(AND($O119="Y",$Q119&lt;&gt;"Y",OR($N119="",$N119=Summary!$C$11)),$F119*IF($S119&lt;&gt;"",$S119,$J119)*INDEX(Summary!$C$6:$C$8,MATCH($H119,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="V119" s="22" t="n">
         <f aca="false">IF(AND($O119="Y",$Q119&lt;&gt;"Y",OR($N119="",$N119=Summary!$C$11)),$F119*IF($S119&lt;&gt;"",$S119,($I119+$J119)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H119,Summary!$B$6:$B$8,0)),0)</f>
-        <v>74.55</v>
+        <v>75</v>
       </c>
       <c r="W119" s="16" t="s">
         <v>109</v>
@@ -12567,13 +12567,13 @@
         <v>94</v>
       </c>
       <c r="H120" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I120" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J120" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K120" s="16" t="s">
         <v>43</v>
@@ -12600,15 +12600,15 @@
       <c r="S120" s="21"/>
       <c r="T120" s="22" t="n">
         <f aca="false">IF(AND($O120="Y",$Q120&lt;&gt;"Y",OR($N120="",$N120=Summary!$C$11)),$F120*IF($S120&lt;&gt;"",$S120,$I120)*INDEX(Summary!$C$6:$C$8,MATCH($H120,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U120" s="22" t="n">
         <f aca="false">IF(AND($O120="Y",$Q120&lt;&gt;"Y",OR($N120="",$N120=Summary!$C$11)),$F120*IF($S120&lt;&gt;"",$S120,$J120)*INDEX(Summary!$C$6:$C$8,MATCH($H120,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V120" s="22" t="n">
         <f aca="false">IF(AND($O120="Y",$Q120&lt;&gt;"Y",OR($N120="",$N120=Summary!$C$11)),$F120*IF($S120&lt;&gt;"",$S120,($I120+$J120)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H120,Summary!$B$6:$B$8,0)),0)</f>
-        <v>31.95</v>
+        <v>32.5</v>
       </c>
       <c r="W120" s="16" t="s">
         <v>109</v>
@@ -12638,13 +12638,13 @@
         <v>94</v>
       </c>
       <c r="H121" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I121" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J121" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K121" s="16" t="s">
         <v>43</v>
@@ -12671,15 +12671,15 @@
       <c r="S121" s="21"/>
       <c r="T121" s="22" t="n">
         <f aca="false">IF(AND($O121="Y",$Q121&lt;&gt;"Y",OR($N121="",$N121=Summary!$C$11)),$F121*IF($S121&lt;&gt;"",$S121,$I121)*INDEX(Summary!$C$6:$C$8,MATCH($H121,Summary!$B$6:$B$8,0)),0)</f>
-        <v>11.36</v>
+        <v>11</v>
       </c>
       <c r="U121" s="22" t="n">
         <f aca="false">IF(AND($O121="Y",$Q121&lt;&gt;"Y",OR($N121="",$N121=Summary!$C$11)),$F121*IF($S121&lt;&gt;"",$S121,$J121)*INDEX(Summary!$C$6:$C$8,MATCH($H121,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="V121" s="22" t="n">
         <f aca="false">IF(AND($O121="Y",$Q121&lt;&gt;"Y",OR($N121="",$N121=Summary!$C$11)),$F121*IF($S121&lt;&gt;"",$S121,($I121+$J121)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H121,Summary!$B$6:$B$8,0)),0)</f>
-        <v>16.33</v>
+        <v>15.5</v>
       </c>
       <c r="W121" s="16" t="s">
         <v>109</v>
@@ -12709,13 +12709,13 @@
         <v>131</v>
       </c>
       <c r="H122" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I122" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J122" s="20" t="n">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="K122" s="16" t="s">
         <v>43</v>
@@ -12742,15 +12742,15 @@
       <c r="S122" s="21"/>
       <c r="T122" s="22" t="n">
         <f aca="false">IF(AND($O122="Y",$Q122&lt;&gt;"Y",OR($N122="",$N122=Summary!$C$11)),$F122*IF($S122&lt;&gt;"",$S122,$I122)*INDEX(Summary!$C$6:$C$8,MATCH($H122,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="U122" s="22" t="n">
         <f aca="false">IF(AND($O122="Y",$Q122&lt;&gt;"Y",OR($N122="",$N122=Summary!$C$11)),$F122*IF($S122&lt;&gt;"",$S122,$J122)*INDEX(Summary!$C$6:$C$8,MATCH($H122,Summary!$B$6:$B$8,0)),0)</f>
-        <v>184.6</v>
+        <v>185</v>
       </c>
       <c r="V122" s="22" t="n">
         <f aca="false">IF(AND($O122="Y",$Q122&lt;&gt;"Y",OR($N122="",$N122=Summary!$C$11)),$F122*IF($S122&lt;&gt;"",$S122,($I122+$J122)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H122,Summary!$B$6:$B$8,0)),0)</f>
-        <v>134.9</v>
+        <v>135</v>
       </c>
       <c r="W122" s="16" t="s">
         <v>109</v>
@@ -12778,13 +12778,13 @@
         <v>94</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I123" s="20" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="J123" s="20" t="n">
-        <v>350</v>
+        <v>495</v>
       </c>
       <c r="K123" s="16" t="s">
         <v>43</v>
@@ -12811,11 +12811,11 @@
       <c r="S123" s="21"/>
       <c r="T123" s="22" t="n">
         <f aca="false">IF(AND($O123="Y",$Q123&lt;&gt;"Y",OR($N123="",$N123=Summary!$C$11)),$F123*IF($S123&lt;&gt;"",$S123,$I123)*INDEX(Summary!$C$6:$C$8,MATCH($H123,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U123" s="22" t="n">
         <f aca="false">IF(AND($O123="Y",$Q123&lt;&gt;"Y",OR($N123="",$N123=Summary!$C$11)),$F123*IF($S123&lt;&gt;"",$S123,$J123)*INDEX(Summary!$C$6:$C$8,MATCH($H123,Summary!$B$6:$B$8,0)),0)</f>
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="V123" s="22" t="n">
         <f aca="false">IF(AND($O123="Y",$Q123&lt;&gt;"Y",OR($N123="",$N123=Summary!$C$11)),$F123*IF($S123&lt;&gt;"",$S123,($I123+$J123)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H123,Summary!$B$6:$B$8,0)),0)</f>
@@ -12916,13 +12916,13 @@
         <v>94</v>
       </c>
       <c r="H125" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I125" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J125" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K125" s="16" t="s">
         <v>43</v>
@@ -12949,15 +12949,15 @@
       <c r="S125" s="21"/>
       <c r="T125" s="22" t="n">
         <f aca="false">IF(AND($O125="Y",$Q125&lt;&gt;"Y",OR($N125="",$N125=Summary!$C$11)),$F125*IF($S125&lt;&gt;"",$S125,$I125)*INDEX(Summary!$C$6:$C$8,MATCH($H125,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>60</v>
       </c>
       <c r="U125" s="22" t="n">
         <f aca="false">IF(AND($O125="Y",$Q125&lt;&gt;"Y",OR($N125="",$N125=Summary!$C$11)),$F125*IF($S125&lt;&gt;"",$S125,$J125)*INDEX(Summary!$C$6:$C$8,MATCH($H125,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="V125" s="22" t="n">
         <f aca="false">IF(AND($O125="Y",$Q125&lt;&gt;"Y",OR($N125="",$N125=Summary!$C$11)),$F125*IF($S125&lt;&gt;"",$S125,($I125+$J125)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H125,Summary!$B$6:$B$8,0)),0)</f>
-        <v>78.1</v>
+        <v>80</v>
       </c>
       <c r="W125" s="16" t="s">
         <v>109</v>
@@ -12985,13 +12985,13 @@
         <v>94</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I126" s="20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J126" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K126" s="16" t="s">
         <v>43</v>
@@ -13018,15 +13018,15 @@
       <c r="S126" s="21"/>
       <c r="T126" s="22" t="n">
         <f aca="false">IF(AND($O126="Y",$Q126&lt;&gt;"Y",OR($N126="",$N126=Summary!$C$11)),$F126*IF($S126&lt;&gt;"",$S126,$I126)*INDEX(Summary!$C$6:$C$8,MATCH($H126,Summary!$B$6:$B$8,0)),0)</f>
-        <v>102.24</v>
+        <v>102</v>
       </c>
       <c r="U126" s="22" t="n">
         <f aca="false">IF(AND($O126="Y",$Q126&lt;&gt;"Y",OR($N126="",$N126=Summary!$C$11)),$F126*IF($S126&lt;&gt;"",$S126,$J126)*INDEX(Summary!$C$6:$C$8,MATCH($H126,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="V126" s="22" t="n">
         <f aca="false">IF(AND($O126="Y",$Q126&lt;&gt;"Y",OR($N126="",$N126=Summary!$C$11)),$F126*IF($S126&lt;&gt;"",$S126,($I126+$J126)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H126,Summary!$B$6:$B$8,0)),0)</f>
-        <v>157.62</v>
+        <v>156</v>
       </c>
       <c r="W126" s="16" t="s">
         <v>109</v>
@@ -13054,13 +13054,13 @@
         <v>94</v>
       </c>
       <c r="H127" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I127" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J127" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K127" s="16" t="s">
         <v>43</v>
@@ -13087,15 +13087,15 @@
       <c r="S127" s="21"/>
       <c r="T127" s="22" t="n">
         <f aca="false">IF(AND($O127="Y",$Q127&lt;&gt;"Y",OR($N127="",$N127=Summary!$C$11)),$F127*IF($S127&lt;&gt;"",$S127,$I127)*INDEX(Summary!$C$6:$C$8,MATCH($H127,Summary!$B$6:$B$8,0)),0)</f>
-        <v>90.88</v>
+        <v>88</v>
       </c>
       <c r="U127" s="22" t="n">
         <f aca="false">IF(AND($O127="Y",$Q127&lt;&gt;"Y",OR($N127="",$N127=Summary!$C$11)),$F127*IF($S127&lt;&gt;"",$S127,$J127)*INDEX(Summary!$C$6:$C$8,MATCH($H127,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>160</v>
       </c>
       <c r="V127" s="22" t="n">
         <f aca="false">IF(AND($O127="Y",$Q127&lt;&gt;"Y",OR($N127="",$N127=Summary!$C$11)),$F127*IF($S127&lt;&gt;"",$S127,($I127+$J127)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H127,Summary!$B$6:$B$8,0)),0)</f>
-        <v>130.64</v>
+        <v>124</v>
       </c>
       <c r="W127" s="16" t="s">
         <v>109</v>
@@ -13123,13 +13123,13 @@
         <v>94</v>
       </c>
       <c r="H128" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I128" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J128" s="20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K128" s="16" t="s">
         <v>43</v>
@@ -13156,15 +13156,15 @@
       <c r="S128" s="21"/>
       <c r="T128" s="22" t="n">
         <f aca="false">IF(AND($O128="Y",$Q128&lt;&gt;"Y",OR($N128="",$N128=Summary!$C$11)),$F128*IF($S128&lt;&gt;"",$S128,$I128)*INDEX(Summary!$C$6:$C$8,MATCH($H128,Summary!$B$6:$B$8,0)),0)</f>
-        <v>68.16</v>
+        <v>64</v>
       </c>
       <c r="U128" s="22" t="n">
         <f aca="false">IF(AND($O128="Y",$Q128&lt;&gt;"Y",OR($N128="",$N128=Summary!$C$11)),$F128*IF($S128&lt;&gt;"",$S128,$J128)*INDEX(Summary!$C$6:$C$8,MATCH($H128,Summary!$B$6:$B$8,0)),0)</f>
-        <v>136.32</v>
+        <v>144</v>
       </c>
       <c r="V128" s="22" t="n">
         <f aca="false">IF(AND($O128="Y",$Q128&lt;&gt;"Y",OR($N128="",$N128=Summary!$C$11)),$F128*IF($S128&lt;&gt;"",$S128,($I128+$J128)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H128,Summary!$B$6:$B$8,0)),0)</f>
-        <v>102.24</v>
+        <v>104</v>
       </c>
       <c r="W128" s="16" t="s">
         <v>109</v>
@@ -13192,13 +13192,13 @@
         <v>203</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I129" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J129" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K129" s="16" t="s">
         <v>43</v>
@@ -13225,15 +13225,15 @@
       <c r="S129" s="21"/>
       <c r="T129" s="22" t="n">
         <f aca="false">IF(AND($O129="Y",$Q129&lt;&gt;"Y",OR($N129="",$N129=Summary!$C$11)),$F129*IF($S129&lt;&gt;"",$S129,$I129)*INDEX(Summary!$C$6:$C$8,MATCH($H129,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U129" s="22" t="n">
         <f aca="false">IF(AND($O129="Y",$Q129&lt;&gt;"Y",OR($N129="",$N129=Summary!$C$11)),$F129*IF($S129&lt;&gt;"",$S129,$J129)*INDEX(Summary!$C$6:$C$8,MATCH($H129,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V129" s="22" t="n">
         <f aca="false">IF(AND($O129="Y",$Q129&lt;&gt;"Y",OR($N129="",$N129=Summary!$C$11)),$F129*IF($S129&lt;&gt;"",$S129,($I129+$J129)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H129,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W129" s="16" t="s">
         <v>109</v>
@@ -13401,13 +13401,13 @@
         <v>94</v>
       </c>
       <c r="H132" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I132" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J132" s="20" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K132" s="16" t="s">
         <v>43</v>
@@ -13434,15 +13434,15 @@
       <c r="S132" s="21"/>
       <c r="T132" s="22" t="n">
         <f aca="false">IF(AND($O132="Y",$Q132&lt;&gt;"Y",OR($N132="",$N132=Summary!$C$11)),$F132*IF($S132&lt;&gt;"",$S132,$I132)*INDEX(Summary!$C$6:$C$8,MATCH($H132,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U132" s="22" t="n">
         <f aca="false">IF(AND($O132="Y",$Q132&lt;&gt;"Y",OR($N132="",$N132=Summary!$C$11)),$F132*IF($S132&lt;&gt;"",$S132,$J132)*INDEX(Summary!$C$6:$C$8,MATCH($H132,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="V132" s="22" t="n">
         <f aca="false">IF(AND($O132="Y",$Q132&lt;&gt;"Y",OR($N132="",$N132=Summary!$C$11)),$F132*IF($S132&lt;&gt;"",$S132,($I132+$J132)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H132,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>72.5</v>
       </c>
       <c r="W132" s="16" t="s">
         <v>109</v>
@@ -13470,13 +13470,13 @@
         <v>203</v>
       </c>
       <c r="H133" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I133" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J133" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K133" s="16" t="s">
         <v>43</v>
@@ -13503,15 +13503,15 @@
       <c r="S133" s="21"/>
       <c r="T133" s="22" t="n">
         <f aca="false">IF(AND($O133="Y",$Q133&lt;&gt;"Y",OR($N133="",$N133=Summary!$C$11)),$F133*IF($S133&lt;&gt;"",$S133,$I133)*INDEX(Summary!$C$6:$C$8,MATCH($H133,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U133" s="22" t="n">
         <f aca="false">IF(AND($O133="Y",$Q133&lt;&gt;"Y",OR($N133="",$N133=Summary!$C$11)),$F133*IF($S133&lt;&gt;"",$S133,$J133)*INDEX(Summary!$C$6:$C$8,MATCH($H133,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V133" s="22" t="n">
         <f aca="false">IF(AND($O133="Y",$Q133&lt;&gt;"Y",OR($N133="",$N133=Summary!$C$11)),$F133*IF($S133&lt;&gt;"",$S133,($I133+$J133)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H133,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="W133" s="16" t="s">
         <v>109</v>
@@ -13610,13 +13610,13 @@
         <v>94</v>
       </c>
       <c r="H135" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I135" s="20" t="n">
-        <v>500</v>
+        <v>710</v>
       </c>
       <c r="J135" s="20" t="n">
-        <v>800</v>
+        <v>1135</v>
       </c>
       <c r="K135" s="16" t="s">
         <v>43</v>
@@ -13681,13 +13681,13 @@
         <v>94</v>
       </c>
       <c r="H136" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I136" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J136" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="K136" s="16" t="s">
         <v>43</v>
@@ -13714,15 +13714,15 @@
       <c r="S136" s="21"/>
       <c r="T136" s="22" t="n">
         <f aca="false">IF(AND($O136="Y",$Q136&lt;&gt;"Y",OR($N136="",$N136=Summary!$C$11)),$F136*IF($S136&lt;&gt;"",$S136,$I136)*INDEX(Summary!$C$6:$C$8,MATCH($H136,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U136" s="22" t="n">
         <f aca="false">IF(AND($O136="Y",$Q136&lt;&gt;"Y",OR($N136="",$N136=Summary!$C$11)),$F136*IF($S136&lt;&gt;"",$S136,$J136)*INDEX(Summary!$C$6:$C$8,MATCH($H136,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="V136" s="22" t="n">
         <f aca="false">IF(AND($O136="Y",$Q136&lt;&gt;"Y",OR($N136="",$N136=Summary!$C$11)),$F136*IF($S136&lt;&gt;"",$S136,($I136+$J136)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H136,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="W136" s="16" t="s">
         <v>109</v>
@@ -13752,13 +13752,13 @@
         <v>94</v>
       </c>
       <c r="H137" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I137" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J137" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="K137" s="16" t="s">
         <v>43</v>
@@ -13785,15 +13785,15 @@
       <c r="S137" s="21"/>
       <c r="T137" s="22" t="n">
         <f aca="false">IF(AND($O137="Y",$Q137&lt;&gt;"Y",OR($N137="",$N137=Summary!$C$11)),$F137*IF($S137&lt;&gt;"",$S137,$I137)*INDEX(Summary!$C$6:$C$8,MATCH($H137,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U137" s="22" t="n">
         <f aca="false">IF(AND($O137="Y",$Q137&lt;&gt;"Y",OR($N137="",$N137=Summary!$C$11)),$F137*IF($S137&lt;&gt;"",$S137,$J137)*INDEX(Summary!$C$6:$C$8,MATCH($H137,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="V137" s="22" t="n">
         <f aca="false">IF(AND($O137="Y",$Q137&lt;&gt;"Y",OR($N137="",$N137=Summary!$C$11)),$F137*IF($S137&lt;&gt;"",$S137,($I137+$J137)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H137,Summary!$B$6:$B$8,0)),0)</f>
-        <v>78.1</v>
+        <v>80</v>
       </c>
       <c r="W137" s="16" t="s">
         <v>109</v>
@@ -13821,13 +13821,13 @@
         <v>203</v>
       </c>
       <c r="H138" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I138" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J138" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K138" s="16" t="s">
         <v>43</v>
@@ -13854,15 +13854,15 @@
       <c r="S138" s="21"/>
       <c r="T138" s="22" t="n">
         <f aca="false">IF(AND($O138="Y",$Q138&lt;&gt;"Y",OR($N138="",$N138=Summary!$C$11)),$F138*IF($S138&lt;&gt;"",$S138,$I138)*INDEX(Summary!$C$6:$C$8,MATCH($H138,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U138" s="22" t="n">
         <f aca="false">IF(AND($O138="Y",$Q138&lt;&gt;"Y",OR($N138="",$N138=Summary!$C$11)),$F138*IF($S138&lt;&gt;"",$S138,$J138)*INDEX(Summary!$C$6:$C$8,MATCH($H138,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V138" s="22" t="n">
         <f aca="false">IF(AND($O138="Y",$Q138&lt;&gt;"Y",OR($N138="",$N138=Summary!$C$11)),$F138*IF($S138&lt;&gt;"",$S138,($I138+$J138)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H138,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W138" s="16" t="s">
         <v>109</v>
@@ -13890,13 +13890,13 @@
         <v>94</v>
       </c>
       <c r="H139" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I139" s="20" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J139" s="20" t="n">
-        <v>200</v>
+        <v>285</v>
       </c>
       <c r="K139" s="16" t="s">
         <v>43</v>
@@ -13923,15 +13923,15 @@
       <c r="S139" s="21"/>
       <c r="T139" s="22" t="n">
         <f aca="false">IF(AND($O139="Y",$Q139&lt;&gt;"Y",OR($N139="",$N139=Summary!$C$11)),$F139*IF($S139&lt;&gt;"",$S139,$I139)*INDEX(Summary!$C$6:$C$8,MATCH($H139,Summary!$B$6:$B$8,0)),0)</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="U139" s="22" t="n">
         <f aca="false">IF(AND($O139="Y",$Q139&lt;&gt;"Y",OR($N139="",$N139=Summary!$C$11)),$F139*IF($S139&lt;&gt;"",$S139,$J139)*INDEX(Summary!$C$6:$C$8,MATCH($H139,Summary!$B$6:$B$8,0)),0)</f>
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="V139" s="22" t="n">
         <f aca="false">IF(AND($O139="Y",$Q139&lt;&gt;"Y",OR($N139="",$N139=Summary!$C$11)),$F139*IF($S139&lt;&gt;"",$S139,($I139+$J139)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H139,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>212.5</v>
       </c>
       <c r="W139" s="16" t="s">
         <v>109</v>
@@ -13961,13 +13961,13 @@
         <v>94</v>
       </c>
       <c r="H140" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I140" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J140" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K140" s="16" t="s">
         <v>43</v>
@@ -13998,11 +13998,11 @@
       </c>
       <c r="U140" s="22" t="n">
         <f aca="false">IF(AND($O140="Y",$Q140&lt;&gt;"Y",OR($N140="",$N140=Summary!$C$11)),$F140*IF($S140&lt;&gt;"",$S140,$J140)*INDEX(Summary!$C$6:$C$8,MATCH($H140,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V140" s="22" t="n">
         <f aca="false">IF(AND($O140="Y",$Q140&lt;&gt;"Y",OR($N140="",$N140=Summary!$C$11)),$F140*IF($S140&lt;&gt;"",$S140,($I140+$J140)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H140,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>22.5</v>
       </c>
       <c r="W140" s="16" t="s">
         <v>109</v>
@@ -14032,13 +14032,13 @@
         <v>94</v>
       </c>
       <c r="H141" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I141" s="20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J141" s="20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K141" s="16" t="s">
         <v>43</v>
@@ -14065,15 +14065,15 @@
       <c r="S141" s="21"/>
       <c r="T141" s="22" t="n">
         <f aca="false">IF(AND($O141="Y",$Q141&lt;&gt;"Y",OR($N141="",$N141=Summary!$C$11)),$F141*IF($S141&lt;&gt;"",$S141,$I141)*INDEX(Summary!$C$6:$C$8,MATCH($H141,Summary!$B$6:$B$8,0)),0)</f>
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="U141" s="22" t="n">
         <f aca="false">IF(AND($O141="Y",$Q141&lt;&gt;"Y",OR($N141="",$N141=Summary!$C$11)),$F141*IF($S141&lt;&gt;"",$S141,$J141)*INDEX(Summary!$C$6:$C$8,MATCH($H141,Summary!$B$6:$B$8,0)),0)</f>
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="V141" s="22" t="n">
         <f aca="false">IF(AND($O141="Y",$Q141&lt;&gt;"Y",OR($N141="",$N141=Summary!$C$11)),$F141*IF($S141&lt;&gt;"",$S141,($I141+$J141)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H141,Summary!$B$6:$B$8,0)),0)</f>
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="W141" s="16" t="s">
         <v>109</v>
@@ -14103,13 +14103,13 @@
         <v>131</v>
       </c>
       <c r="H142" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I142" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J142" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K142" s="16" t="s">
         <v>43</v>
@@ -14140,11 +14140,11 @@
       </c>
       <c r="U142" s="22" t="n">
         <f aca="false">IF(AND($O142="Y",$Q142&lt;&gt;"Y",OR($N142="",$N142=Summary!$C$11)),$F142*IF($S142&lt;&gt;"",$S142,$J142)*INDEX(Summary!$C$6:$C$8,MATCH($H142,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V142" s="22" t="n">
         <f aca="false">IF(AND($O142="Y",$Q142&lt;&gt;"Y",OR($N142="",$N142=Summary!$C$11)),$F142*IF($S142&lt;&gt;"",$S142,($I142+$J142)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H142,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>27.5</v>
       </c>
       <c r="W142" s="16" t="s">
         <v>109</v>
@@ -14172,13 +14172,13 @@
         <v>94</v>
       </c>
       <c r="H143" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I143" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J143" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K143" s="16" t="s">
         <v>43</v>
@@ -14209,11 +14209,11 @@
       </c>
       <c r="U143" s="22" t="n">
         <f aca="false">IF(AND($O143="Y",$Q143&lt;&gt;"Y",OR($N143="",$N143=Summary!$C$11)),$F143*IF($S143&lt;&gt;"",$S143,$J143)*INDEX(Summary!$C$6:$C$8,MATCH($H143,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V143" s="22" t="n">
         <f aca="false">IF(AND($O143="Y",$Q143&lt;&gt;"Y",OR($N143="",$N143=Summary!$C$11)),$F143*IF($S143&lt;&gt;"",$S143,($I143+$J143)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H143,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>27.5</v>
       </c>
       <c r="W143" s="16" t="s">
         <v>109</v>
@@ -14243,13 +14243,13 @@
         <v>94</v>
       </c>
       <c r="H144" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I144" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="J144" s="20" t="n">
-        <v>250</v>
+        <v>355</v>
       </c>
       <c r="K144" s="16" t="s">
         <v>43</v>
@@ -14276,7 +14276,7 @@
       <c r="S144" s="21"/>
       <c r="T144" s="22" t="n">
         <f aca="false">IF(AND($O144="Y",$Q144&lt;&gt;"Y",OR($N144="",$N144=Summary!$C$11)),$F144*IF($S144&lt;&gt;"",$S144,$I144)*INDEX(Summary!$C$6:$C$8,MATCH($H144,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="U144" s="22" t="n">
         <f aca="false">IF(AND($O144="Y",$Q144&lt;&gt;"Y",OR($N144="",$N144=Summary!$C$11)),$F144*IF($S144&lt;&gt;"",$S144,$J144)*INDEX(Summary!$C$6:$C$8,MATCH($H144,Summary!$B$6:$B$8,0)),0)</f>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="V144" s="22" t="n">
         <f aca="false">IF(AND($O144="Y",$Q144&lt;&gt;"Y",OR($N144="",$N144=Summary!$C$11)),$F144*IF($S144&lt;&gt;"",$S144,($I144+$J144)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H144,Summary!$B$6:$B$8,0)),0)</f>
-        <v>262.7</v>
+        <v>262.5</v>
       </c>
       <c r="W144" s="16" t="s">
         <v>109</v>
@@ -14312,13 +14312,13 @@
         <v>94</v>
       </c>
       <c r="H145" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I145" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J145" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="K145" s="16" t="s">
         <v>43</v>
@@ -14345,15 +14345,15 @@
       <c r="S145" s="21"/>
       <c r="T145" s="22" t="n">
         <f aca="false">IF(AND($O145="Y",$Q145&lt;&gt;"Y",OR($N145="",$N145=Summary!$C$11)),$F145*IF($S145&lt;&gt;"",$S145,$I145)*INDEX(Summary!$C$6:$C$8,MATCH($H145,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>130</v>
       </c>
       <c r="U145" s="22" t="n">
         <f aca="false">IF(AND($O145="Y",$Q145&lt;&gt;"Y",OR($N145="",$N145=Summary!$C$11)),$F145*IF($S145&lt;&gt;"",$S145,$J145)*INDEX(Summary!$C$6:$C$8,MATCH($H145,Summary!$B$6:$B$8,0)),0)</f>
-        <v>227.2</v>
+        <v>230</v>
       </c>
       <c r="V145" s="22" t="n">
         <f aca="false">IF(AND($O145="Y",$Q145&lt;&gt;"Y",OR($N145="",$N145=Summary!$C$11)),$F145*IF($S145&lt;&gt;"",$S145,($I145+$J145)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H145,Summary!$B$6:$B$8,0)),0)</f>
-        <v>177.5</v>
+        <v>180</v>
       </c>
       <c r="W145" s="16" t="s">
         <v>109</v>
@@ -14381,13 +14381,13 @@
         <v>94</v>
       </c>
       <c r="H146" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I146" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J146" s="20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K146" s="16" t="s">
         <v>43</v>
@@ -14414,15 +14414,15 @@
       <c r="S146" s="21"/>
       <c r="T146" s="22" t="n">
         <f aca="false">IF(AND($O146="Y",$Q146&lt;&gt;"Y",OR($N146="",$N146=Summary!$C$11)),$F146*IF($S146&lt;&gt;"",$S146,$I146)*INDEX(Summary!$C$6:$C$8,MATCH($H146,Summary!$B$6:$B$8,0)),0)</f>
-        <v>90.88</v>
+        <v>88</v>
       </c>
       <c r="U146" s="22" t="n">
         <f aca="false">IF(AND($O146="Y",$Q146&lt;&gt;"Y",OR($N146="",$N146=Summary!$C$11)),$F146*IF($S146&lt;&gt;"",$S146,$J146)*INDEX(Summary!$C$6:$C$8,MATCH($H146,Summary!$B$6:$B$8,0)),0)</f>
-        <v>159.04</v>
+        <v>160</v>
       </c>
       <c r="V146" s="22" t="n">
         <f aca="false">IF(AND($O146="Y",$Q146&lt;&gt;"Y",OR($N146="",$N146=Summary!$C$11)),$F146*IF($S146&lt;&gt;"",$S146,($I146+$J146)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H146,Summary!$B$6:$B$8,0)),0)</f>
-        <v>124.96</v>
+        <v>124</v>
       </c>
       <c r="W146" s="16" t="s">
         <v>109</v>
@@ -14450,13 +14450,13 @@
         <v>131</v>
       </c>
       <c r="H147" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I147" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J147" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K147" s="16" t="s">
         <v>43</v>
@@ -14483,15 +14483,15 @@
       <c r="S147" s="21"/>
       <c r="T147" s="22" t="n">
         <f aca="false">IF(AND($O147="Y",$Q147&lt;&gt;"Y",OR($N147="",$N147=Summary!$C$11)),$F147*IF($S147&lt;&gt;"",$S147,$I147)*INDEX(Summary!$C$6:$C$8,MATCH($H147,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U147" s="22" t="n">
         <f aca="false">IF(AND($O147="Y",$Q147&lt;&gt;"Y",OR($N147="",$N147=Summary!$C$11)),$F147*IF($S147&lt;&gt;"",$S147,$J147)*INDEX(Summary!$C$6:$C$8,MATCH($H147,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="V147" s="22" t="n">
         <f aca="false">IF(AND($O147="Y",$Q147&lt;&gt;"Y",OR($N147="",$N147=Summary!$C$11)),$F147*IF($S147&lt;&gt;"",$S147,($I147+$J147)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H147,Summary!$B$6:$B$8,0)),0)</f>
-        <v>46.15</v>
+        <v>47.5</v>
       </c>
       <c r="W147" s="16" t="s">
         <v>109</v>
@@ -14521,13 +14521,13 @@
         <v>94</v>
       </c>
       <c r="H148" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I148" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J148" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K148" s="16" t="s">
         <v>43</v>
@@ -14554,15 +14554,15 @@
       <c r="S148" s="21"/>
       <c r="T148" s="22" t="n">
         <f aca="false">IF(AND($O148="Y",$Q148&lt;&gt;"Y",OR($N148="",$N148=Summary!$C$11)),$F148*IF($S148&lt;&gt;"",$S148,$I148)*INDEX(Summary!$C$6:$C$8,MATCH($H148,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U148" s="22" t="n">
         <f aca="false">IF(AND($O148="Y",$Q148&lt;&gt;"Y",OR($N148="",$N148=Summary!$C$11)),$F148*IF($S148&lt;&gt;"",$S148,$J148)*INDEX(Summary!$C$6:$C$8,MATCH($H148,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V148" s="22" t="n">
         <f aca="false">IF(AND($O148="Y",$Q148&lt;&gt;"Y",OR($N148="",$N148=Summary!$C$11)),$F148*IF($S148&lt;&gt;"",$S148,($I148+$J148)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H148,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>57.5</v>
       </c>
       <c r="W148" s="16" t="s">
         <v>109</v>
@@ -14590,13 +14590,13 @@
         <v>94</v>
       </c>
       <c r="H149" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I149" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J149" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K149" s="16" t="s">
         <v>43</v>
@@ -14623,15 +14623,15 @@
       <c r="S149" s="21"/>
       <c r="T149" s="22" t="n">
         <f aca="false">IF(AND($O149="Y",$Q149&lt;&gt;"Y",OR($N149="",$N149=Summary!$C$11)),$F149*IF($S149&lt;&gt;"",$S149,$I149)*INDEX(Summary!$C$6:$C$8,MATCH($H149,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U149" s="22" t="n">
         <f aca="false">IF(AND($O149="Y",$Q149&lt;&gt;"Y",OR($N149="",$N149=Summary!$C$11)),$F149*IF($S149&lt;&gt;"",$S149,$J149)*INDEX(Summary!$C$6:$C$8,MATCH($H149,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V149" s="22" t="n">
         <f aca="false">IF(AND($O149="Y",$Q149&lt;&gt;"Y",OR($N149="",$N149=Summary!$C$11)),$F149*IF($S149&lt;&gt;"",$S149,($I149+$J149)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H149,Summary!$B$6:$B$8,0)),0)</f>
-        <v>31.95</v>
+        <v>32.5</v>
       </c>
       <c r="W149" s="16" t="s">
         <v>109</v>
@@ -14659,13 +14659,13 @@
         <v>94</v>
       </c>
       <c r="H150" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I150" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J150" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="K150" s="16" t="s">
         <v>43</v>
@@ -14692,15 +14692,15 @@
       <c r="S150" s="21"/>
       <c r="T150" s="22" t="n">
         <f aca="false">IF(AND($O150="Y",$Q150&lt;&gt;"Y",OR($N150="",$N150=Summary!$C$11)),$F150*IF($S150&lt;&gt;"",$S150,$I150)*INDEX(Summary!$C$6:$C$8,MATCH($H150,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U150" s="22" t="n">
         <f aca="false">IF(AND($O150="Y",$Q150&lt;&gt;"Y",OR($N150="",$N150=Summary!$C$11)),$F150*IF($S150&lt;&gt;"",$S150,$J150)*INDEX(Summary!$C$6:$C$8,MATCH($H150,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="V150" s="22" t="n">
         <f aca="false">IF(AND($O150="Y",$Q150&lt;&gt;"Y",OR($N150="",$N150=Summary!$C$11)),$F150*IF($S150&lt;&gt;"",$S150,($I150+$J150)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H150,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="W150" s="16" t="s">
         <v>109</v>
@@ -14728,13 +14728,13 @@
         <v>203</v>
       </c>
       <c r="H151" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I151" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J151" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K151" s="16" t="s">
         <v>43</v>
@@ -14761,15 +14761,15 @@
       <c r="S151" s="21"/>
       <c r="T151" s="22" t="n">
         <f aca="false">IF(AND($O151="Y",$Q151&lt;&gt;"Y",OR($N151="",$N151=Summary!$C$11)),$F151*IF($S151&lt;&gt;"",$S151,$I151)*INDEX(Summary!$C$6:$C$8,MATCH($H151,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U151" s="22" t="n">
         <f aca="false">IF(AND($O151="Y",$Q151&lt;&gt;"Y",OR($N151="",$N151=Summary!$C$11)),$F151*IF($S151&lt;&gt;"",$S151,$J151)*INDEX(Summary!$C$6:$C$8,MATCH($H151,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V151" s="22" t="n">
         <f aca="false">IF(AND($O151="Y",$Q151&lt;&gt;"Y",OR($N151="",$N151=Summary!$C$11)),$F151*IF($S151&lt;&gt;"",$S151,($I151+$J151)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H151,Summary!$B$6:$B$8,0)),0)</f>
-        <v>31.95</v>
+        <v>32.5</v>
       </c>
       <c r="W151" s="16" t="s">
         <v>109</v>
@@ -14797,13 +14797,13 @@
         <v>94</v>
       </c>
       <c r="H152" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I152" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J152" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="K152" s="16" t="s">
         <v>43</v>
@@ -14830,15 +14830,15 @@
       <c r="S152" s="21"/>
       <c r="T152" s="22" t="n">
         <f aca="false">IF(AND($O152="Y",$Q152&lt;&gt;"Y",OR($N152="",$N152=Summary!$C$11)),$F152*IF($S152&lt;&gt;"",$S152,$I152)*INDEX(Summary!$C$6:$C$8,MATCH($H152,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U152" s="22" t="n">
         <f aca="false">IF(AND($O152="Y",$Q152&lt;&gt;"Y",OR($N152="",$N152=Summary!$C$11)),$F152*IF($S152&lt;&gt;"",$S152,$J152)*INDEX(Summary!$C$6:$C$8,MATCH($H152,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="V152" s="22" t="n">
         <f aca="false">IF(AND($O152="Y",$Q152&lt;&gt;"Y",OR($N152="",$N152=Summary!$C$11)),$F152*IF($S152&lt;&gt;"",$S152,($I152+$J152)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H152,Summary!$B$6:$B$8,0)),0)</f>
-        <v>78.1</v>
+        <v>80</v>
       </c>
       <c r="W152" s="16" t="s">
         <v>109</v>
@@ -14937,13 +14937,13 @@
         <v>94</v>
       </c>
       <c r="H154" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I154" s="20" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="J154" s="20" t="n">
-        <v>195</v>
+        <v>275</v>
       </c>
       <c r="K154" s="16" t="s">
         <v>43</v>
@@ -14970,15 +14970,15 @@
       <c r="S154" s="21"/>
       <c r="T154" s="22" t="n">
         <f aca="false">IF(AND($O154="Y",$Q154&lt;&gt;"Y",OR($N154="",$N154=Summary!$C$11)),$F154*IF($S154&lt;&gt;"",$S154,$I154)*INDEX(Summary!$C$6:$C$8,MATCH($H154,Summary!$B$6:$B$8,0)),0)</f>
-        <v>198.8</v>
+        <v>200</v>
       </c>
       <c r="U154" s="22" t="n">
         <f aca="false">IF(AND($O154="Y",$Q154&lt;&gt;"Y",OR($N154="",$N154=Summary!$C$11)),$F154*IF($S154&lt;&gt;"",$S154,$J154)*INDEX(Summary!$C$6:$C$8,MATCH($H154,Summary!$B$6:$B$8,0)),0)</f>
-        <v>276.9</v>
+        <v>275</v>
       </c>
       <c r="V154" s="22" t="n">
         <f aca="false">IF(AND($O154="Y",$Q154&lt;&gt;"Y",OR($N154="",$N154=Summary!$C$11)),$F154*IF($S154&lt;&gt;"",$S154,($I154+$J154)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H154,Summary!$B$6:$B$8,0)),0)</f>
-        <v>237.85</v>
+        <v>237.5</v>
       </c>
       <c r="W154" s="16" t="s">
         <v>61</v>
@@ -15008,13 +15008,13 @@
         <v>94</v>
       </c>
       <c r="H155" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I155" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J155" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K155" s="16" t="s">
         <v>43</v>
@@ -15041,15 +15041,15 @@
       <c r="S155" s="21"/>
       <c r="T155" s="22" t="n">
         <f aca="false">IF(AND($O155="Y",$Q155&lt;&gt;"Y",OR($N155="",$N155=Summary!$C$11)),$F155*IF($S155&lt;&gt;"",$S155,$I155)*INDEX(Summary!$C$6:$C$8,MATCH($H155,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="U155" s="22" t="n">
         <f aca="false">IF(AND($O155="Y",$Q155&lt;&gt;"Y",OR($N155="",$N155=Summary!$C$11)),$F155*IF($S155&lt;&gt;"",$S155,$J155)*INDEX(Summary!$C$6:$C$8,MATCH($H155,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="V155" s="22" t="n">
         <f aca="false">IF(AND($O155="Y",$Q155&lt;&gt;"Y",OR($N155="",$N155=Summary!$C$11)),$F155*IF($S155&lt;&gt;"",$S155,($I155+$J155)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H155,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="W155" s="16" t="s">
         <v>61</v>
@@ -15077,13 +15077,13 @@
         <v>94</v>
       </c>
       <c r="H156" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I156" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J156" s="20" t="n">
-        <v>700</v>
+        <v>995</v>
       </c>
       <c r="K156" s="16" t="s">
         <v>43</v>
@@ -15114,11 +15114,11 @@
       </c>
       <c r="U156" s="22" t="n">
         <f aca="false">IF(AND($O156="Y",$Q156&lt;&gt;"Y",OR($N156="",$N156=Summary!$C$11)),$F156*IF($S156&lt;&gt;"",$S156,$J156)*INDEX(Summary!$C$6:$C$8,MATCH($H156,Summary!$B$6:$B$8,0)),0)</f>
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="V156" s="22" t="n">
         <f aca="false">IF(AND($O156="Y",$Q156&lt;&gt;"Y",OR($N156="",$N156=Summary!$C$11)),$F156*IF($S156&lt;&gt;"",$S156,($I156+$J156)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H156,Summary!$B$6:$B$8,0)),0)</f>
-        <v>497</v>
+        <v>497.5</v>
       </c>
       <c r="W156" s="16" t="s">
         <v>61</v>
@@ -15146,13 +15146,13 @@
         <v>94</v>
       </c>
       <c r="H157" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I157" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J157" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="K157" s="16" t="s">
         <v>43</v>
@@ -15179,15 +15179,15 @@
       <c r="S157" s="21"/>
       <c r="T157" s="22" t="n">
         <f aca="false">IF(AND($O157="Y",$Q157&lt;&gt;"Y",OR($N157="",$N157=Summary!$C$11)),$F157*IF($S157&lt;&gt;"",$S157,$I157)*INDEX(Summary!$C$6:$C$8,MATCH($H157,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="U157" s="22" t="n">
         <f aca="false">IF(AND($O157="Y",$Q157&lt;&gt;"Y",OR($N157="",$N157=Summary!$C$11)),$F157*IF($S157&lt;&gt;"",$S157,$J157)*INDEX(Summary!$C$6:$C$8,MATCH($H157,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="V157" s="22" t="n">
         <f aca="false">IF(AND($O157="Y",$Q157&lt;&gt;"Y",OR($N157="",$N157=Summary!$C$11)),$F157*IF($S157&lt;&gt;"",$S157,($I157+$J157)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H157,Summary!$B$6:$B$8,0)),0)</f>
-        <v>74.55</v>
+        <v>75</v>
       </c>
       <c r="W157" s="16" t="s">
         <v>109</v>
@@ -15284,13 +15284,13 @@
         <v>94</v>
       </c>
       <c r="H159" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I159" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J159" s="20" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K159" s="16" t="s">
         <v>43</v>
@@ -15317,15 +15317,15 @@
       <c r="S159" s="21"/>
       <c r="T159" s="22" t="n">
         <f aca="false">IF(AND($O159="Y",$Q159&lt;&gt;"Y",OR($N159="",$N159=Summary!$C$11)),$F159*IF($S159&lt;&gt;"",$S159,$I159)*INDEX(Summary!$C$6:$C$8,MATCH($H159,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U159" s="22" t="n">
         <f aca="false">IF(AND($O159="Y",$Q159&lt;&gt;"Y",OR($N159="",$N159=Summary!$C$11)),$F159*IF($S159&lt;&gt;"",$S159,$J159)*INDEX(Summary!$C$6:$C$8,MATCH($H159,Summary!$B$6:$B$8,0)),0)</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="V159" s="22" t="n">
         <f aca="false">IF(AND($O159="Y",$Q159&lt;&gt;"Y",OR($N159="",$N159=Summary!$C$11)),$F159*IF($S159&lt;&gt;"",$S159,($I159+$J159)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H159,Summary!$B$6:$B$8,0)),0)</f>
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="W159" s="16" t="s">
         <v>109</v>
@@ -15493,13 +15493,13 @@
         <v>203</v>
       </c>
       <c r="H162" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I162" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J162" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K162" s="16" t="s">
         <v>43</v>
@@ -15526,15 +15526,15 @@
       <c r="S162" s="21"/>
       <c r="T162" s="22" t="n">
         <f aca="false">IF(AND($O162="Y",$Q162&lt;&gt;"Y",OR($N162="",$N162=Summary!$C$11)),$F162*IF($S162&lt;&gt;"",$S162,$I162)*INDEX(Summary!$C$6:$C$8,MATCH($H162,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U162" s="22" t="n">
         <f aca="false">IF(AND($O162="Y",$Q162&lt;&gt;"Y",OR($N162="",$N162=Summary!$C$11)),$F162*IF($S162&lt;&gt;"",$S162,$J162)*INDEX(Summary!$C$6:$C$8,MATCH($H162,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V162" s="22" t="n">
         <f aca="false">IF(AND($O162="Y",$Q162&lt;&gt;"Y",OR($N162="",$N162=Summary!$C$11)),$F162*IF($S162&lt;&gt;"",$S162,($I162+$J162)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H162,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W162" s="16" t="s">
         <v>109</v>
@@ -15562,13 +15562,13 @@
         <v>94</v>
       </c>
       <c r="H163" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I163" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J163" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K163" s="16" t="s">
         <v>43</v>
@@ -15599,11 +15599,11 @@
       </c>
       <c r="U163" s="22" t="n">
         <f aca="false">IF(AND($O163="Y",$Q163&lt;&gt;"Y",OR($N163="",$N163=Summary!$C$11)),$F163*IF($S163&lt;&gt;"",$S163,$J163)*INDEX(Summary!$C$6:$C$8,MATCH($H163,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V163" s="22" t="n">
         <f aca="false">IF(AND($O163="Y",$Q163&lt;&gt;"Y",OR($N163="",$N163=Summary!$C$11)),$F163*IF($S163&lt;&gt;"",$S163,($I163+$J163)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H163,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W163" s="16" t="s">
         <v>109</v>
@@ -15631,13 +15631,13 @@
         <v>638</v>
       </c>
       <c r="H164" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I164" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J164" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K164" s="16" t="s">
         <v>43</v>
@@ -15664,15 +15664,15 @@
       <c r="S164" s="21"/>
       <c r="T164" s="22" t="n">
         <f aca="false">IF(AND($O164="Y",$Q164&lt;&gt;"Y",OR($N164="",$N164=Summary!$C$11)),$F164*IF($S164&lt;&gt;"",$S164,$I164)*INDEX(Summary!$C$6:$C$8,MATCH($H164,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U164" s="22" t="n">
         <f aca="false">IF(AND($O164="Y",$Q164&lt;&gt;"Y",OR($N164="",$N164=Summary!$C$11)),$F164*IF($S164&lt;&gt;"",$S164,$J164)*INDEX(Summary!$C$6:$C$8,MATCH($H164,Summary!$B$6:$B$8,0)),0)</f>
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="V164" s="22" t="n">
         <f aca="false">IF(AND($O164="Y",$Q164&lt;&gt;"Y",OR($N164="",$N164=Summary!$C$11)),$F164*IF($S164&lt;&gt;"",$S164,($I164+$J164)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H164,Summary!$B$6:$B$8,0)),0)</f>
-        <v>106.5</v>
+        <v>110</v>
       </c>
       <c r="W164" s="16" t="s">
         <v>109</v>
@@ -15700,13 +15700,13 @@
         <v>203</v>
       </c>
       <c r="H165" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I165" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J165" s="20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K165" s="16" t="s">
         <v>43</v>
@@ -15733,15 +15733,15 @@
       <c r="S165" s="21"/>
       <c r="T165" s="22" t="n">
         <f aca="false">IF(AND($O165="Y",$Q165&lt;&gt;"Y",OR($N165="",$N165=Summary!$C$11)),$F165*IF($S165&lt;&gt;"",$S165,$I165)*INDEX(Summary!$C$6:$C$8,MATCH($H165,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U165" s="22" t="n">
         <f aca="false">IF(AND($O165="Y",$Q165&lt;&gt;"Y",OR($N165="",$N165=Summary!$C$11)),$F165*IF($S165&lt;&gt;"",$S165,$J165)*INDEX(Summary!$C$6:$C$8,MATCH($H165,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>130</v>
       </c>
       <c r="V165" s="22" t="n">
         <f aca="false">IF(AND($O165="Y",$Q165&lt;&gt;"Y",OR($N165="",$N165=Summary!$C$11)),$F165*IF($S165&lt;&gt;"",$S165,($I165+$J165)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H165,Summary!$B$6:$B$8,0)),0)</f>
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="W165" s="16" t="s">
         <v>109</v>
@@ -15769,13 +15769,13 @@
         <v>150</v>
       </c>
       <c r="H166" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I166" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J166" s="20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K166" s="16" t="s">
         <v>43</v>
@@ -15802,15 +15802,15 @@
       <c r="S166" s="21"/>
       <c r="T166" s="22" t="n">
         <f aca="false">IF(AND($O166="Y",$Q166&lt;&gt;"Y",OR($N166="",$N166=Summary!$C$11)),$F166*IF($S166&lt;&gt;"",$S166,$I166)*INDEX(Summary!$C$6:$C$8,MATCH($H166,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U166" s="22" t="n">
         <f aca="false">IF(AND($O166="Y",$Q166&lt;&gt;"Y",OR($N166="",$N166=Summary!$C$11)),$F166*IF($S166&lt;&gt;"",$S166,$J166)*INDEX(Summary!$C$6:$C$8,MATCH($H166,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>130</v>
       </c>
       <c r="V166" s="22" t="n">
         <f aca="false">IF(AND($O166="Y",$Q166&lt;&gt;"Y",OR($N166="",$N166=Summary!$C$11)),$F166*IF($S166&lt;&gt;"",$S166,($I166+$J166)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H166,Summary!$B$6:$B$8,0)),0)</f>
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="W166" s="16" t="s">
         <v>109</v>
@@ -15838,13 +15838,13 @@
         <v>150</v>
       </c>
       <c r="H167" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I167" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J167" s="20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K167" s="16" t="s">
         <v>43</v>
@@ -15871,15 +15871,15 @@
       <c r="S167" s="21"/>
       <c r="T167" s="22" t="n">
         <f aca="false">IF(AND($O167="Y",$Q167&lt;&gt;"Y",OR($N167="",$N167=Summary!$C$11)),$F167*IF($S167&lt;&gt;"",$S167,$I167)*INDEX(Summary!$C$6:$C$8,MATCH($H167,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="U167" s="22" t="n">
         <f aca="false">IF(AND($O167="Y",$Q167&lt;&gt;"Y",OR($N167="",$N167=Summary!$C$11)),$F167*IF($S167&lt;&gt;"",$S167,$J167)*INDEX(Summary!$C$6:$C$8,MATCH($H167,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>130</v>
       </c>
       <c r="V167" s="22" t="n">
         <f aca="false">IF(AND($O167="Y",$Q167&lt;&gt;"Y",OR($N167="",$N167=Summary!$C$11)),$F167*IF($S167&lt;&gt;"",$S167,($I167+$J167)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H167,Summary!$B$6:$B$8,0)),0)</f>
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="W167" s="16" t="s">
         <v>109</v>
@@ -15907,13 +15907,13 @@
         <v>203</v>
       </c>
       <c r="H168" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I168" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J168" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K168" s="16" t="s">
         <v>43</v>
@@ -15940,15 +15940,15 @@
       <c r="S168" s="21"/>
       <c r="T168" s="22" t="n">
         <f aca="false">IF(AND($O168="Y",$Q168&lt;&gt;"Y",OR($N168="",$N168=Summary!$C$11)),$F168*IF($S168&lt;&gt;"",$S168,$I168)*INDEX(Summary!$C$6:$C$8,MATCH($H168,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U168" s="22" t="n">
         <f aca="false">IF(AND($O168="Y",$Q168&lt;&gt;"Y",OR($N168="",$N168=Summary!$C$11)),$F168*IF($S168&lt;&gt;"",$S168,$J168)*INDEX(Summary!$C$6:$C$8,MATCH($H168,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V168" s="22" t="n">
         <f aca="false">IF(AND($O168="Y",$Q168&lt;&gt;"Y",OR($N168="",$N168=Summary!$C$11)),$F168*IF($S168&lt;&gt;"",$S168,($I168+$J168)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H168,Summary!$B$6:$B$8,0)),0)</f>
-        <v>31.95</v>
+        <v>32.5</v>
       </c>
       <c r="W168" s="16" t="s">
         <v>109</v>
@@ -15976,13 +15976,13 @@
         <v>203</v>
       </c>
       <c r="H169" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I169" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J169" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K169" s="16" t="s">
         <v>43</v>
@@ -16009,15 +16009,15 @@
       <c r="S169" s="21"/>
       <c r="T169" s="22" t="n">
         <f aca="false">IF(AND($O169="Y",$Q169&lt;&gt;"Y",OR($N169="",$N169=Summary!$C$11)),$F169*IF($S169&lt;&gt;"",$S169,$I169)*INDEX(Summary!$C$6:$C$8,MATCH($H169,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U169" s="22" t="n">
         <f aca="false">IF(AND($O169="Y",$Q169&lt;&gt;"Y",OR($N169="",$N169=Summary!$C$11)),$F169*IF($S169&lt;&gt;"",$S169,$J169)*INDEX(Summary!$C$6:$C$8,MATCH($H169,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V169" s="22" t="n">
         <f aca="false">IF(AND($O169="Y",$Q169&lt;&gt;"Y",OR($N169="",$N169=Summary!$C$11)),$F169*IF($S169&lt;&gt;"",$S169,($I169+$J169)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H169,Summary!$B$6:$B$8,0)),0)</f>
-        <v>31.95</v>
+        <v>32.5</v>
       </c>
       <c r="W169" s="16" t="s">
         <v>109</v>
@@ -16045,13 +16045,13 @@
         <v>203</v>
       </c>
       <c r="H170" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I170" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J170" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K170" s="16" t="s">
         <v>43</v>
@@ -16078,15 +16078,15 @@
       <c r="S170" s="21"/>
       <c r="T170" s="22" t="n">
         <f aca="false">IF(AND($O170="Y",$Q170&lt;&gt;"Y",OR($N170="",$N170=Summary!$C$11)),$F170*IF($S170&lt;&gt;"",$S170,$I170)*INDEX(Summary!$C$6:$C$8,MATCH($H170,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U170" s="22" t="n">
         <f aca="false">IF(AND($O170="Y",$Q170&lt;&gt;"Y",OR($N170="",$N170=Summary!$C$11)),$F170*IF($S170&lt;&gt;"",$S170,$J170)*INDEX(Summary!$C$6:$C$8,MATCH($H170,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V170" s="22" t="n">
         <f aca="false">IF(AND($O170="Y",$Q170&lt;&gt;"Y",OR($N170="",$N170=Summary!$C$11)),$F170*IF($S170&lt;&gt;"",$S170,($I170+$J170)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H170,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W170" s="16" t="s">
         <v>109</v>
@@ -16114,13 +16114,13 @@
         <v>94</v>
       </c>
       <c r="H171" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I171" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J171" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K171" s="16" t="s">
         <v>43</v>
@@ -16147,15 +16147,15 @@
       <c r="S171" s="21"/>
       <c r="T171" s="22" t="n">
         <f aca="false">IF(AND($O171="Y",$Q171&lt;&gt;"Y",OR($N171="",$N171=Summary!$C$11)),$F171*IF($S171&lt;&gt;"",$S171,$I171)*INDEX(Summary!$C$6:$C$8,MATCH($H171,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U171" s="22" t="n">
         <f aca="false">IF(AND($O171="Y",$Q171&lt;&gt;"Y",OR($N171="",$N171=Summary!$C$11)),$F171*IF($S171&lt;&gt;"",$S171,$J171)*INDEX(Summary!$C$6:$C$8,MATCH($H171,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="V171" s="22" t="n">
         <f aca="false">IF(AND($O171="Y",$Q171&lt;&gt;"Y",OR($N171="",$N171=Summary!$C$11)),$F171*IF($S171&lt;&gt;"",$S171,($I171+$J171)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H171,Summary!$B$6:$B$8,0)),0)</f>
-        <v>46.15</v>
+        <v>47.5</v>
       </c>
       <c r="W171" s="16" t="s">
         <v>109</v>
@@ -16185,13 +16185,13 @@
         <v>94</v>
       </c>
       <c r="H172" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I172" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J172" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K172" s="16" t="s">
         <v>43</v>
@@ -16218,15 +16218,15 @@
       <c r="S172" s="21"/>
       <c r="T172" s="22" t="n">
         <f aca="false">IF(AND($O172="Y",$Q172&lt;&gt;"Y",OR($N172="",$N172=Summary!$C$11)),$F172*IF($S172&lt;&gt;"",$S172,$I172)*INDEX(Summary!$C$6:$C$8,MATCH($H172,Summary!$B$6:$B$8,0)),0)</f>
-        <v>8.52</v>
+        <v>9</v>
       </c>
       <c r="U172" s="22" t="n">
         <f aca="false">IF(AND($O172="Y",$Q172&lt;&gt;"Y",OR($N172="",$N172=Summary!$C$11)),$F172*IF($S172&lt;&gt;"",$S172,$J172)*INDEX(Summary!$C$6:$C$8,MATCH($H172,Summary!$B$6:$B$8,0)),0)</f>
-        <v>17.04</v>
+        <v>18</v>
       </c>
       <c r="V172" s="22" t="n">
         <f aca="false">IF(AND($O172="Y",$Q172&lt;&gt;"Y",OR($N172="",$N172=Summary!$C$11)),$F172*IF($S172&lt;&gt;"",$S172,($I172+$J172)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H172,Summary!$B$6:$B$8,0)),0)</f>
-        <v>12.78</v>
+        <v>13.5</v>
       </c>
       <c r="W172" s="16" t="s">
         <v>109</v>
@@ -16254,13 +16254,13 @@
         <v>203</v>
       </c>
       <c r="H173" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I173" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J173" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K173" s="16" t="s">
         <v>43</v>
@@ -16287,15 +16287,15 @@
       <c r="S173" s="21"/>
       <c r="T173" s="22" t="n">
         <f aca="false">IF(AND($O173="Y",$Q173&lt;&gt;"Y",OR($N173="",$N173=Summary!$C$11)),$F173*IF($S173&lt;&gt;"",$S173,$I173)*INDEX(Summary!$C$6:$C$8,MATCH($H173,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U173" s="22" t="n">
         <f aca="false">IF(AND($O173="Y",$Q173&lt;&gt;"Y",OR($N173="",$N173=Summary!$C$11)),$F173*IF($S173&lt;&gt;"",$S173,$J173)*INDEX(Summary!$C$6:$C$8,MATCH($H173,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V173" s="22" t="n">
         <f aca="false">IF(AND($O173="Y",$Q173&lt;&gt;"Y",OR($N173="",$N173=Summary!$C$11)),$F173*IF($S173&lt;&gt;"",$S173,($I173+$J173)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H173,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W173" s="16" t="s">
         <v>109</v>
@@ -16323,13 +16323,13 @@
         <v>94</v>
       </c>
       <c r="H174" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I174" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J174" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K174" s="16" t="s">
         <v>44</v>
@@ -16356,15 +16356,15 @@
       <c r="S174" s="21"/>
       <c r="T174" s="22" t="n">
         <f aca="false">IF(AND($O174="Y",$Q174&lt;&gt;"Y",OR($N174="",$N174=Summary!$C$11)),$F174*IF($S174&lt;&gt;"",$S174,$I174)*INDEX(Summary!$C$6:$C$8,MATCH($H174,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U174" s="22" t="n">
         <f aca="false">IF(AND($O174="Y",$Q174&lt;&gt;"Y",OR($N174="",$N174=Summary!$C$11)),$F174*IF($S174&lt;&gt;"",$S174,$J174)*INDEX(Summary!$C$6:$C$8,MATCH($H174,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="V174" s="22" t="n">
         <f aca="false">IF(AND($O174="Y",$Q174&lt;&gt;"Y",OR($N174="",$N174=Summary!$C$11)),$F174*IF($S174&lt;&gt;"",$S174,($I174+$J174)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H174,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="W174" s="16" t="s">
         <v>109</v>
@@ -16394,13 +16394,13 @@
         <v>94</v>
       </c>
       <c r="H175" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I175" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J175" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K175" s="16" t="s">
         <v>43</v>
@@ -16427,15 +16427,15 @@
       <c r="S175" s="21"/>
       <c r="T175" s="22" t="n">
         <f aca="false">IF(AND($O175="Y",$Q175&lt;&gt;"Y",OR($N175="",$N175=Summary!$C$11)),$F175*IF($S175&lt;&gt;"",$S175,$I175)*INDEX(Summary!$C$6:$C$8,MATCH($H175,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U175" s="22" t="n">
         <f aca="false">IF(AND($O175="Y",$Q175&lt;&gt;"Y",OR($N175="",$N175=Summary!$C$11)),$F175*IF($S175&lt;&gt;"",$S175,$J175)*INDEX(Summary!$C$6:$C$8,MATCH($H175,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V175" s="22" t="n">
         <f aca="false">IF(AND($O175="Y",$Q175&lt;&gt;"Y",OR($N175="",$N175=Summary!$C$11)),$F175*IF($S175&lt;&gt;"",$S175,($I175+$J175)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H175,Summary!$B$6:$B$8,0)),0)</f>
-        <v>53.25</v>
+        <v>52.5</v>
       </c>
       <c r="W175" s="16" t="s">
         <v>109</v>
@@ -16463,13 +16463,13 @@
         <v>94</v>
       </c>
       <c r="H176" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I176" s="20" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="J176" s="20" t="n">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="K176" s="16" t="s">
         <v>43</v>
@@ -16496,15 +16496,15 @@
       <c r="S176" s="21"/>
       <c r="T176" s="22" t="n">
         <f aca="false">IF(AND($O176="Y",$Q176&lt;&gt;"Y",OR($N176="",$N176=Summary!$C$11)),$F176*IF($S176&lt;&gt;"",$S176,$I176)*INDEX(Summary!$C$6:$C$8,MATCH($H176,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>130</v>
       </c>
       <c r="U176" s="22" t="n">
         <f aca="false">IF(AND($O176="Y",$Q176&lt;&gt;"Y",OR($N176="",$N176=Summary!$C$11)),$F176*IF($S176&lt;&gt;"",$S176,$J176)*INDEX(Summary!$C$6:$C$8,MATCH($H176,Summary!$B$6:$B$8,0)),0)</f>
-        <v>312.4</v>
+        <v>310</v>
       </c>
       <c r="V176" s="22" t="n">
         <f aca="false">IF(AND($O176="Y",$Q176&lt;&gt;"Y",OR($N176="",$N176=Summary!$C$11)),$F176*IF($S176&lt;&gt;"",$S176,($I176+$J176)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H176,Summary!$B$6:$B$8,0)),0)</f>
-        <v>220.1</v>
+        <v>220</v>
       </c>
       <c r="W176" s="16" t="s">
         <v>109</v>
@@ -16532,13 +16532,13 @@
         <v>94</v>
       </c>
       <c r="H177" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I177" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J177" s="20" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K177" s="16" t="s">
         <v>43</v>
@@ -16565,15 +16565,15 @@
       <c r="S177" s="21"/>
       <c r="T177" s="22" t="n">
         <f aca="false">IF(AND($O177="Y",$Q177&lt;&gt;"Y",OR($N177="",$N177=Summary!$C$11)),$F177*IF($S177&lt;&gt;"",$S177,$I177)*INDEX(Summary!$C$6:$C$8,MATCH($H177,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U177" s="22" t="n">
         <f aca="false">IF(AND($O177="Y",$Q177&lt;&gt;"Y",OR($N177="",$N177=Summary!$C$11)),$F177*IF($S177&lt;&gt;"",$S177,$J177)*INDEX(Summary!$C$6:$C$8,MATCH($H177,Summary!$B$6:$B$8,0)),0)</f>
-        <v>99.4</v>
+        <v>100</v>
       </c>
       <c r="V177" s="22" t="n">
         <f aca="false">IF(AND($O177="Y",$Q177&lt;&gt;"Y",OR($N177="",$N177=Summary!$C$11)),$F177*IF($S177&lt;&gt;"",$S177,($I177+$J177)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H177,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>72.5</v>
       </c>
       <c r="W177" s="16" t="s">
         <v>109</v>
@@ -16601,13 +16601,13 @@
         <v>94</v>
       </c>
       <c r="H178" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I178" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J178" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K178" s="16" t="s">
         <v>43</v>
@@ -16634,15 +16634,15 @@
       <c r="S178" s="21"/>
       <c r="T178" s="22" t="n">
         <f aca="false">IF(AND($O178="Y",$Q178&lt;&gt;"Y",OR($N178="",$N178=Summary!$C$11)),$F178*IF($S178&lt;&gt;"",$S178,$I178)*INDEX(Summary!$C$6:$C$8,MATCH($H178,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U178" s="22" t="n">
         <f aca="false">IF(AND($O178="Y",$Q178&lt;&gt;"Y",OR($N178="",$N178=Summary!$C$11)),$F178*IF($S178&lt;&gt;"",$S178,$J178)*INDEX(Summary!$C$6:$C$8,MATCH($H178,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V178" s="22" t="n">
         <f aca="false">IF(AND($O178="Y",$Q178&lt;&gt;"Y",OR($N178="",$N178=Summary!$C$11)),$F178*IF($S178&lt;&gt;"",$S178,($I178+$J178)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H178,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W178" s="16" t="s">
         <v>109</v>
@@ -16670,13 +16670,13 @@
         <v>94</v>
       </c>
       <c r="H179" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I179" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J179" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="K179" s="16" t="s">
         <v>43</v>
@@ -16703,15 +16703,15 @@
       <c r="S179" s="21"/>
       <c r="T179" s="22" t="n">
         <f aca="false">IF(AND($O179="Y",$Q179&lt;&gt;"Y",OR($N179="",$N179=Summary!$C$11)),$F179*IF($S179&lt;&gt;"",$S179,$I179)*INDEX(Summary!$C$6:$C$8,MATCH($H179,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U179" s="22" t="n">
         <f aca="false">IF(AND($O179="Y",$Q179&lt;&gt;"Y",OR($N179="",$N179=Summary!$C$11)),$F179*IF($S179&lt;&gt;"",$S179,$J179)*INDEX(Summary!$C$6:$C$8,MATCH($H179,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="V179" s="22" t="n">
         <f aca="false">IF(AND($O179="Y",$Q179&lt;&gt;"Y",OR($N179="",$N179=Summary!$C$11)),$F179*IF($S179&lt;&gt;"",$S179,($I179+$J179)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H179,Summary!$B$6:$B$8,0)),0)</f>
-        <v>78.1</v>
+        <v>80</v>
       </c>
       <c r="W179" s="16" t="s">
         <v>109</v>
@@ -16741,13 +16741,13 @@
         <v>94</v>
       </c>
       <c r="H180" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I180" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J180" s="20" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="K180" s="16" t="s">
         <v>43</v>
@@ -16778,11 +16778,11 @@
       </c>
       <c r="U180" s="22" t="n">
         <f aca="false">IF(AND($O180="Y",$Q180&lt;&gt;"Y",OR($N180="",$N180=Summary!$C$11)),$F180*IF($S180&lt;&gt;"",$S180,$J180)*INDEX(Summary!$C$6:$C$8,MATCH($H180,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V180" s="22" t="n">
         <f aca="false">IF(AND($O180="Y",$Q180&lt;&gt;"Y",OR($N180="",$N180=Summary!$C$11)),$F180*IF($S180&lt;&gt;"",$S180,($I180+$J180)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H180,Summary!$B$6:$B$8,0)),0)</f>
-        <v>106.5</v>
+        <v>107.5</v>
       </c>
       <c r="W180" s="16" t="s">
         <v>109</v>
@@ -16810,13 +16810,13 @@
         <v>94</v>
       </c>
       <c r="H181" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I181" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J181" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K181" s="16" t="s">
         <v>44</v>
@@ -16843,15 +16843,15 @@
       <c r="S181" s="21"/>
       <c r="T181" s="22" t="n">
         <f aca="false">IF(AND($O181="Y",$Q181&lt;&gt;"Y",OR($N181="",$N181=Summary!$C$11)),$F181*IF($S181&lt;&gt;"",$S181,$I181)*INDEX(Summary!$C$6:$C$8,MATCH($H181,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U181" s="22" t="n">
         <f aca="false">IF(AND($O181="Y",$Q181&lt;&gt;"Y",OR($N181="",$N181=Summary!$C$11)),$F181*IF($S181&lt;&gt;"",$S181,$J181)*INDEX(Summary!$C$6:$C$8,MATCH($H181,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V181" s="22" t="n">
         <f aca="false">IF(AND($O181="Y",$Q181&lt;&gt;"Y",OR($N181="",$N181=Summary!$C$11)),$F181*IF($S181&lt;&gt;"",$S181,($I181+$J181)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H181,Summary!$B$6:$B$8,0)),0)</f>
-        <v>31.95</v>
+        <v>32.5</v>
       </c>
       <c r="W181" s="16" t="s">
         <v>109</v>
@@ -17017,13 +17017,13 @@
         <v>203</v>
       </c>
       <c r="H184" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I184" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J184" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K184" s="16" t="s">
         <v>43</v>
@@ -17050,15 +17050,15 @@
       <c r="S184" s="21"/>
       <c r="T184" s="22" t="n">
         <f aca="false">IF(AND($O184="Y",$Q184&lt;&gt;"Y",OR($N184="",$N184=Summary!$C$11)),$F184*IF($S184&lt;&gt;"",$S184,$I184)*INDEX(Summary!$C$6:$C$8,MATCH($H184,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U184" s="22" t="n">
         <f aca="false">IF(AND($O184="Y",$Q184&lt;&gt;"Y",OR($N184="",$N184=Summary!$C$11)),$F184*IF($S184&lt;&gt;"",$S184,$J184)*INDEX(Summary!$C$6:$C$8,MATCH($H184,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V184" s="22" t="n">
         <f aca="false">IF(AND($O184="Y",$Q184&lt;&gt;"Y",OR($N184="",$N184=Summary!$C$11)),$F184*IF($S184&lt;&gt;"",$S184,($I184+$J184)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H184,Summary!$B$6:$B$8,0)),0)</f>
-        <v>39.05</v>
+        <v>37.5</v>
       </c>
       <c r="W184" s="16" t="s">
         <v>109</v>
@@ -17088,13 +17088,13 @@
         <v>203</v>
       </c>
       <c r="H185" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I185" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J185" s="20" t="n">
-        <v>800</v>
+        <v>1135</v>
       </c>
       <c r="K185" s="16" t="s">
         <v>43</v>
@@ -17226,13 +17226,13 @@
         <v>94</v>
       </c>
       <c r="H187" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I187" s="20" t="n">
-        <v>200</v>
+        <v>285</v>
       </c>
       <c r="J187" s="20" t="n">
-        <v>350</v>
+        <v>495</v>
       </c>
       <c r="K187" s="16" t="s">
         <v>43</v>
@@ -17366,13 +17366,13 @@
         <v>203</v>
       </c>
       <c r="H189" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I189" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J189" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K189" s="16" t="s">
         <v>43</v>
@@ -17399,15 +17399,15 @@
       <c r="S189" s="21"/>
       <c r="T189" s="22" t="n">
         <f aca="false">IF(AND($O189="Y",$Q189&lt;&gt;"Y",OR($N189="",$N189=Summary!$C$11)),$F189*IF($S189&lt;&gt;"",$S189,$I189)*INDEX(Summary!$C$6:$C$8,MATCH($H189,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="U189" s="22" t="n">
         <f aca="false">IF(AND($O189="Y",$Q189&lt;&gt;"Y",OR($N189="",$N189=Summary!$C$11)),$F189*IF($S189&lt;&gt;"",$S189,$J189)*INDEX(Summary!$C$6:$C$8,MATCH($H189,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V189" s="22" t="n">
         <f aca="false">IF(AND($O189="Y",$Q189&lt;&gt;"Y",OR($N189="",$N189=Summary!$C$11)),$F189*IF($S189&lt;&gt;"",$S189,($I189+$J189)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H189,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>127.5</v>
       </c>
       <c r="W189" s="16" t="s">
         <v>109</v>
@@ -17435,13 +17435,13 @@
         <v>94</v>
       </c>
       <c r="H190" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I190" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J190" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K190" s="16" t="s">
         <v>43</v>
@@ -17468,15 +17468,15 @@
       <c r="S190" s="21"/>
       <c r="T190" s="22" t="n">
         <f aca="false">IF(AND($O190="Y",$Q190&lt;&gt;"Y",OR($N190="",$N190=Summary!$C$11)),$F190*IF($S190&lt;&gt;"",$S190,$I190)*INDEX(Summary!$C$6:$C$8,MATCH($H190,Summary!$B$6:$B$8,0)),0)</f>
-        <v>34.08</v>
+        <v>33</v>
       </c>
       <c r="U190" s="22" t="n">
         <f aca="false">IF(AND($O190="Y",$Q190&lt;&gt;"Y",OR($N190="",$N190=Summary!$C$11)),$F190*IF($S190&lt;&gt;"",$S190,$J190)*INDEX(Summary!$C$6:$C$8,MATCH($H190,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>60</v>
       </c>
       <c r="V190" s="22" t="n">
         <f aca="false">IF(AND($O190="Y",$Q190&lt;&gt;"Y",OR($N190="",$N190=Summary!$C$11)),$F190*IF($S190&lt;&gt;"",$S190,($I190+$J190)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H190,Summary!$B$6:$B$8,0)),0)</f>
-        <v>48.99</v>
+        <v>46.5</v>
       </c>
       <c r="W190" s="16" t="s">
         <v>109</v>
@@ -17504,13 +17504,13 @@
         <v>94</v>
       </c>
       <c r="H191" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I191" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J191" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K191" s="16" t="s">
         <v>43</v>
@@ -17537,15 +17537,15 @@
       <c r="S191" s="21"/>
       <c r="T191" s="22" t="n">
         <f aca="false">IF(AND($O191="Y",$Q191&lt;&gt;"Y",OR($N191="",$N191=Summary!$C$11)),$F191*IF($S191&lt;&gt;"",$S191,$I191)*INDEX(Summary!$C$6:$C$8,MATCH($H191,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>20</v>
       </c>
       <c r="U191" s="22" t="n">
         <f aca="false">IF(AND($O191="Y",$Q191&lt;&gt;"Y",OR($N191="",$N191=Summary!$C$11)),$F191*IF($S191&lt;&gt;"",$S191,$J191)*INDEX(Summary!$C$6:$C$8,MATCH($H191,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>60</v>
       </c>
       <c r="V191" s="22" t="n">
         <f aca="false">IF(AND($O191="Y",$Q191&lt;&gt;"Y",OR($N191="",$N191=Summary!$C$11)),$F191*IF($S191&lt;&gt;"",$S191,($I191+$J191)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H191,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>40</v>
       </c>
       <c r="W191" s="16" t="s">
         <v>109</v>
@@ -17573,13 +17573,13 @@
         <v>203</v>
       </c>
       <c r="H192" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I192" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J192" s="20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K192" s="16" t="s">
         <v>44</v>
@@ -17606,15 +17606,15 @@
       <c r="S192" s="21"/>
       <c r="T192" s="22" t="n">
         <f aca="false">IF(AND($O192="Y",$Q192&lt;&gt;"Y",OR($N192="",$N192=Summary!$C$11)),$F192*IF($S192&lt;&gt;"",$S192,$I192)*INDEX(Summary!$C$6:$C$8,MATCH($H192,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U192" s="22" t="n">
         <f aca="false">IF(AND($O192="Y",$Q192&lt;&gt;"Y",OR($N192="",$N192=Summary!$C$11)),$F192*IF($S192&lt;&gt;"",$S192,$J192)*INDEX(Summary!$C$6:$C$8,MATCH($H192,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V192" s="22" t="n">
         <f aca="false">IF(AND($O192="Y",$Q192&lt;&gt;"Y",OR($N192="",$N192=Summary!$C$11)),$F192*IF($S192&lt;&gt;"",$S192,($I192+$J192)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H192,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="W192" s="16" t="s">
         <v>109</v>
@@ -17642,13 +17642,13 @@
         <v>94</v>
       </c>
       <c r="H193" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I193" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J193" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K193" s="16" t="s">
         <v>43</v>
@@ -17675,15 +17675,15 @@
       <c r="S193" s="21"/>
       <c r="T193" s="22" t="n">
         <f aca="false">IF(AND($O193="Y",$Q193&lt;&gt;"Y",OR($N193="",$N193=Summary!$C$11)),$F193*IF($S193&lt;&gt;"",$S193,$I193)*INDEX(Summary!$C$6:$C$8,MATCH($H193,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U193" s="22" t="n">
         <f aca="false">IF(AND($O193="Y",$Q193&lt;&gt;"Y",OR($N193="",$N193=Summary!$C$11)),$F193*IF($S193&lt;&gt;"",$S193,$J193)*INDEX(Summary!$C$6:$C$8,MATCH($H193,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V193" s="22" t="n">
         <f aca="false">IF(AND($O193="Y",$Q193&lt;&gt;"Y",OR($N193="",$N193=Summary!$C$11)),$F193*IF($S193&lt;&gt;"",$S193,($I193+$J193)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H193,Summary!$B$6:$B$8,0)),0)</f>
-        <v>39.05</v>
+        <v>37.5</v>
       </c>
       <c r="W193" s="16" t="s">
         <v>61</v>
@@ -17711,13 +17711,13 @@
         <v>94</v>
       </c>
       <c r="H194" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I194" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J194" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K194" s="16" t="s">
         <v>44</v>
@@ -17748,11 +17748,11 @@
       </c>
       <c r="U194" s="22" t="n">
         <f aca="false">IF(AND($O194="Y",$Q194&lt;&gt;"Y",OR($N194="",$N194=Summary!$C$11)),$F194*IF($S194&lt;&gt;"",$S194,$J194)*INDEX(Summary!$C$6:$C$8,MATCH($H194,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V194" s="22" t="n">
         <f aca="false">IF(AND($O194="Y",$Q194&lt;&gt;"Y",OR($N194="",$N194=Summary!$C$11)),$F194*IF($S194&lt;&gt;"",$S194,($I194+$J194)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H194,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>22.5</v>
       </c>
       <c r="W194" s="16" t="s">
         <v>109</v>
@@ -17782,13 +17782,13 @@
         <v>203</v>
       </c>
       <c r="H195" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I195" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J195" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K195" s="16" t="s">
         <v>43</v>
@@ -17815,15 +17815,15 @@
       <c r="S195" s="21"/>
       <c r="T195" s="22" t="n">
         <f aca="false">IF(AND($O195="Y",$Q195&lt;&gt;"Y",OR($N195="",$N195=Summary!$C$11)),$F195*IF($S195&lt;&gt;"",$S195,$I195)*INDEX(Summary!$C$6:$C$8,MATCH($H195,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U195" s="22" t="n">
         <f aca="false">IF(AND($O195="Y",$Q195&lt;&gt;"Y",OR($N195="",$N195=Summary!$C$11)),$F195*IF($S195&lt;&gt;"",$S195,$J195)*INDEX(Summary!$C$6:$C$8,MATCH($H195,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V195" s="22" t="n">
         <f aca="false">IF(AND($O195="Y",$Q195&lt;&gt;"Y",OR($N195="",$N195=Summary!$C$11)),$F195*IF($S195&lt;&gt;"",$S195,($I195+$J195)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H195,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W195" s="16" t="s">
         <v>109</v>
@@ -17851,13 +17851,13 @@
         <v>94</v>
       </c>
       <c r="H196" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I196" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J196" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K196" s="16" t="s">
         <v>43</v>
@@ -17884,15 +17884,15 @@
       <c r="S196" s="21"/>
       <c r="T196" s="22" t="n">
         <f aca="false">IF(AND($O196="Y",$Q196&lt;&gt;"Y",OR($N196="",$N196=Summary!$C$11)),$F196*IF($S196&lt;&gt;"",$S196,$I196)*INDEX(Summary!$C$6:$C$8,MATCH($H196,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U196" s="22" t="n">
         <f aca="false">IF(AND($O196="Y",$Q196&lt;&gt;"Y",OR($N196="",$N196=Summary!$C$11)),$F196*IF($S196&lt;&gt;"",$S196,$J196)*INDEX(Summary!$C$6:$C$8,MATCH($H196,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V196" s="22" t="n">
         <f aca="false">IF(AND($O196="Y",$Q196&lt;&gt;"Y",OR($N196="",$N196=Summary!$C$11)),$F196*IF($S196&lt;&gt;"",$S196,($I196+$J196)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H196,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>57.5</v>
       </c>
       <c r="W196" s="16" t="s">
         <v>109</v>
@@ -17991,13 +17991,13 @@
         <v>94</v>
       </c>
       <c r="H198" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I198" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J198" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K198" s="16" t="s">
         <v>43</v>
@@ -18024,15 +18024,15 @@
       <c r="S198" s="21"/>
       <c r="T198" s="22" t="n">
         <f aca="false">IF(AND($O198="Y",$Q198&lt;&gt;"Y",OR($N198="",$N198=Summary!$C$11)),$F198*IF($S198&lt;&gt;"",$S198,$I198)*INDEX(Summary!$C$6:$C$8,MATCH($H198,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="U198" s="22" t="n">
         <f aca="false">IF(AND($O198="Y",$Q198&lt;&gt;"Y",OR($N198="",$N198=Summary!$C$11)),$F198*IF($S198&lt;&gt;"",$S198,$J198)*INDEX(Summary!$C$6:$C$8,MATCH($H198,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V198" s="22" t="n">
         <f aca="false">IF(AND($O198="Y",$Q198&lt;&gt;"Y",OR($N198="",$N198=Summary!$C$11)),$F198*IF($S198&lt;&gt;"",$S198,($I198+$J198)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H198,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>127.5</v>
       </c>
       <c r="W198" s="16" t="s">
         <v>109</v>
@@ -18060,13 +18060,13 @@
         <v>94</v>
       </c>
       <c r="H199" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I199" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="J199" s="20" t="n">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="K199" s="16" t="s">
         <v>43</v>
@@ -18093,15 +18093,15 @@
       <c r="S199" s="21"/>
       <c r="T199" s="22" t="n">
         <f aca="false">IF(AND($O199="Y",$Q199&lt;&gt;"Y",OR($N199="",$N199=Summary!$C$11)),$F199*IF($S199&lt;&gt;"",$S199,$I199)*INDEX(Summary!$C$6:$C$8,MATCH($H199,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="U199" s="22" t="n">
         <f aca="false">IF(AND($O199="Y",$Q199&lt;&gt;"Y",OR($N199="",$N199=Summary!$C$11)),$F199*IF($S199&lt;&gt;"",$S199,$J199)*INDEX(Summary!$C$6:$C$8,MATCH($H199,Summary!$B$6:$B$8,0)),0)</f>
-        <v>255.6</v>
+        <v>255</v>
       </c>
       <c r="V199" s="22" t="n">
         <f aca="false">IF(AND($O199="Y",$Q199&lt;&gt;"Y",OR($N199="",$N199=Summary!$C$11)),$F199*IF($S199&lt;&gt;"",$S199,($I199+$J199)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H199,Summary!$B$6:$B$8,0)),0)</f>
-        <v>184.6</v>
+        <v>185</v>
       </c>
       <c r="W199" s="16" t="s">
         <v>109</v>
@@ -18129,13 +18129,13 @@
         <v>131</v>
       </c>
       <c r="H200" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I200" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="J200" s="20" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="K200" s="16" t="s">
         <v>43</v>
@@ -18162,15 +18162,15 @@
       <c r="S200" s="21"/>
       <c r="T200" s="22" t="n">
         <f aca="false">IF(AND($O200="Y",$Q200&lt;&gt;"Y",OR($N200="",$N200=Summary!$C$11)),$F200*IF($S200&lt;&gt;"",$S200,$I200)*INDEX(Summary!$C$6:$C$8,MATCH($H200,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="U200" s="22" t="n">
         <f aca="false">IF(AND($O200="Y",$Q200&lt;&gt;"Y",OR($N200="",$N200=Summary!$C$11)),$F200*IF($S200&lt;&gt;"",$S200,$J200)*INDEX(Summary!$C$6:$C$8,MATCH($H200,Summary!$B$6:$B$8,0)),0)</f>
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V200" s="22" t="n">
         <f aca="false">IF(AND($O200="Y",$Q200&lt;&gt;"Y",OR($N200="",$N200=Summary!$C$11)),$F200*IF($S200&lt;&gt;"",$S200,($I200+$J200)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H200,Summary!$B$6:$B$8,0)),0)</f>
-        <v>163.3</v>
+        <v>165</v>
       </c>
       <c r="W200" s="16" t="s">
         <v>109</v>
@@ -18338,13 +18338,13 @@
         <v>94</v>
       </c>
       <c r="H203" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I203" s="20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J203" s="20" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K203" s="16" t="s">
         <v>44</v>
@@ -18371,15 +18371,15 @@
       <c r="S203" s="21"/>
       <c r="T203" s="22" t="n">
         <f aca="false">IF(AND($O203="Y",$Q203&lt;&gt;"Y",OR($N203="",$N203=Summary!$C$11)),$F203*IF($S203&lt;&gt;"",$S203,$I203)*INDEX(Summary!$C$6:$C$8,MATCH($H203,Summary!$B$6:$B$8,0)),0)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U203" s="22" t="n">
         <f aca="false">IF(AND($O203="Y",$Q203&lt;&gt;"Y",OR($N203="",$N203=Summary!$C$11)),$F203*IF($S203&lt;&gt;"",$S203,$J203)*INDEX(Summary!$C$6:$C$8,MATCH($H203,Summary!$B$6:$B$8,0)),0)</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="V203" s="22" t="n">
         <f aca="false">IF(AND($O203="Y",$Q203&lt;&gt;"Y",OR($N203="",$N203=Summary!$C$11)),$F203*IF($S203&lt;&gt;"",$S203,($I203+$J203)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H203,Summary!$B$6:$B$8,0)),0)</f>
-        <v>106.5</v>
+        <v>105</v>
       </c>
       <c r="W203" s="16" t="s">
         <v>109</v>
@@ -18409,13 +18409,13 @@
         <v>131</v>
       </c>
       <c r="H204" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I204" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J204" s="20" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="K204" s="16" t="s">
         <v>44</v>
@@ -18446,11 +18446,11 @@
       </c>
       <c r="U204" s="22" t="n">
         <f aca="false">IF(AND($O204="Y",$Q204&lt;&gt;"Y",OR($N204="",$N204=Summary!$C$11)),$F204*IF($S204&lt;&gt;"",$S204,$J204)*INDEX(Summary!$C$6:$C$8,MATCH($H204,Summary!$B$6:$B$8,0)),0)</f>
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="V204" s="22" t="n">
         <f aca="false">IF(AND($O204="Y",$Q204&lt;&gt;"Y",OR($N204="",$N204=Summary!$C$11)),$F204*IF($S204&lt;&gt;"",$S204,($I204+$J204)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H204,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>57.5</v>
       </c>
       <c r="W204" s="16" t="s">
         <v>109</v>
@@ -18478,13 +18478,13 @@
         <v>94</v>
       </c>
       <c r="H205" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I205" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J205" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K205" s="16" t="s">
         <v>44</v>
@@ -18511,15 +18511,15 @@
       <c r="S205" s="21"/>
       <c r="T205" s="22" t="n">
         <f aca="false">IF(AND($O205="Y",$Q205&lt;&gt;"Y",OR($N205="",$N205=Summary!$C$11)),$F205*IF($S205&lt;&gt;"",$S205,$I205)*INDEX(Summary!$C$6:$C$8,MATCH($H205,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U205" s="22" t="n">
         <f aca="false">IF(AND($O205="Y",$Q205&lt;&gt;"Y",OR($N205="",$N205=Summary!$C$11)),$F205*IF($S205&lt;&gt;"",$S205,$J205)*INDEX(Summary!$C$6:$C$8,MATCH($H205,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V205" s="22" t="n">
         <f aca="false">IF(AND($O205="Y",$Q205&lt;&gt;"Y",OR($N205="",$N205=Summary!$C$11)),$F205*IF($S205&lt;&gt;"",$S205,($I205+$J205)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H205,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>29.5</v>
       </c>
       <c r="W205" s="16" t="s">
         <v>109</v>
@@ -18547,13 +18547,13 @@
         <v>131</v>
       </c>
       <c r="H206" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I206" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J206" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K206" s="16" t="s">
         <v>43</v>
@@ -18580,15 +18580,15 @@
       <c r="S206" s="21"/>
       <c r="T206" s="22" t="n">
         <f aca="false">IF(AND($O206="Y",$Q206&lt;&gt;"Y",OR($N206="",$N206=Summary!$C$11)),$F206*IF($S206&lt;&gt;"",$S206,$I206)*INDEX(Summary!$C$6:$C$8,MATCH($H206,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U206" s="22" t="n">
         <f aca="false">IF(AND($O206="Y",$Q206&lt;&gt;"Y",OR($N206="",$N206=Summary!$C$11)),$F206*IF($S206&lt;&gt;"",$S206,$J206)*INDEX(Summary!$C$6:$C$8,MATCH($H206,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="V206" s="22" t="n">
         <f aca="false">IF(AND($O206="Y",$Q206&lt;&gt;"Y",OR($N206="",$N206=Summary!$C$11)),$F206*IF($S206&lt;&gt;"",$S206,($I206+$J206)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H206,Summary!$B$6:$B$8,0)),0)</f>
-        <v>24.85</v>
+        <v>24.5</v>
       </c>
       <c r="W206" s="16" t="s">
         <v>109</v>
@@ -18616,13 +18616,13 @@
         <v>203</v>
       </c>
       <c r="H207" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I207" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J207" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K207" s="16" t="s">
         <v>43</v>
@@ -18649,15 +18649,15 @@
       <c r="S207" s="21"/>
       <c r="T207" s="22" t="n">
         <f aca="false">IF(AND($O207="Y",$Q207&lt;&gt;"Y",OR($N207="",$N207=Summary!$C$11)),$F207*IF($S207&lt;&gt;"",$S207,$I207)*INDEX(Summary!$C$6:$C$8,MATCH($H207,Summary!$B$6:$B$8,0)),0)</f>
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="U207" s="22" t="n">
         <f aca="false">IF(AND($O207="Y",$Q207&lt;&gt;"Y",OR($N207="",$N207=Summary!$C$11)),$F207*IF($S207&lt;&gt;"",$S207,$J207)*INDEX(Summary!$C$6:$C$8,MATCH($H207,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="V207" s="22" t="n">
         <f aca="false">IF(AND($O207="Y",$Q207&lt;&gt;"Y",OR($N207="",$N207=Summary!$C$11)),$F207*IF($S207&lt;&gt;"",$S207,($I207+$J207)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H207,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="W207" s="16" t="s">
         <v>109</v>
@@ -18754,13 +18754,13 @@
         <v>94</v>
       </c>
       <c r="H209" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I209" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J209" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K209" s="16" t="s">
         <v>44</v>
@@ -18791,11 +18791,11 @@
       </c>
       <c r="U209" s="22" t="n">
         <f aca="false">IF(AND($O209="Y",$Q209&lt;&gt;"Y",OR($N209="",$N209=Summary!$C$11)),$F209*IF($S209&lt;&gt;"",$S209,$J209)*INDEX(Summary!$C$6:$C$8,MATCH($H209,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="V209" s="22" t="n">
         <f aca="false">IF(AND($O209="Y",$Q209&lt;&gt;"Y",OR($N209="",$N209=Summary!$C$11)),$F209*IF($S209&lt;&gt;"",$S209,($I209+$J209)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H209,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>22.5</v>
       </c>
       <c r="W209" s="16" t="s">
         <v>109</v>
@@ -18825,13 +18825,13 @@
         <v>94</v>
       </c>
       <c r="H210" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I210" s="20" t="n">
-        <v>1210</v>
+        <v>1720</v>
       </c>
       <c r="J210" s="20" t="n">
-        <v>1210</v>
+        <v>1720</v>
       </c>
       <c r="K210" s="16" t="s">
         <v>43</v>
@@ -18898,13 +18898,13 @@
         <v>150</v>
       </c>
       <c r="H211" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I211" s="20" t="n">
-        <v>250</v>
+        <v>355</v>
       </c>
       <c r="J211" s="20" t="n">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="K211" s="16" t="s">
         <v>43</v>
@@ -18935,11 +18935,11 @@
       </c>
       <c r="U211" s="22" t="n">
         <f aca="false">IF(AND($O211="Y",$Q211&lt;&gt;"Y",OR($N211="",$N211=Summary!$C$11)),$F211*IF($S211&lt;&gt;"",$S211,$J211)*INDEX(Summary!$C$6:$C$8,MATCH($H211,Summary!$B$6:$B$8,0)),0)</f>
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="V211" s="22" t="n">
         <f aca="false">IF(AND($O211="Y",$Q211&lt;&gt;"Y",OR($N211="",$N211=Summary!$C$11)),$F211*IF($S211&lt;&gt;"",$S211,($I211+$J211)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H211,Summary!$B$6:$B$8,0)),0)</f>
-        <v>461.5</v>
+        <v>462.5</v>
       </c>
       <c r="W211" s="16" t="s">
         <v>61</v>
@@ -18969,13 +18969,13 @@
         <v>203</v>
       </c>
       <c r="H212" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I212" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J212" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K212" s="16" t="s">
         <v>43</v>
@@ -19002,15 +19002,15 @@
       <c r="S212" s="21"/>
       <c r="T212" s="22" t="n">
         <f aca="false">IF(AND($O212="Y",$Q212&lt;&gt;"Y",OR($N212="",$N212=Summary!$C$11)),$F212*IF($S212&lt;&gt;"",$S212,$I212)*INDEX(Summary!$C$6:$C$8,MATCH($H212,Summary!$B$6:$B$8,0)),0)</f>
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U212" s="22" t="n">
         <f aca="false">IF(AND($O212="Y",$Q212&lt;&gt;"Y",OR($N212="",$N212=Summary!$C$11)),$F212*IF($S212&lt;&gt;"",$S212,$J212)*INDEX(Summary!$C$6:$C$8,MATCH($H212,Summary!$B$6:$B$8,0)),0)</f>
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="V212" s="22" t="n">
         <f aca="false">IF(AND($O212="Y",$Q212&lt;&gt;"Y",OR($N212="",$N212=Summary!$C$11)),$F212*IF($S212&lt;&gt;"",$S212,($I212+$J212)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H212,Summary!$B$6:$B$8,0)),0)</f>
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="W212" s="16" t="s">
         <v>109</v>
@@ -19245,13 +19245,13 @@
         <v>203</v>
       </c>
       <c r="H216" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I216" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J216" s="20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K216" s="16" t="s">
         <v>43</v>
@@ -19278,15 +19278,15 @@
       <c r="S216" s="21"/>
       <c r="T216" s="22" t="n">
         <f aca="false">IF(AND($O216="Y",$Q216&lt;&gt;"Y",OR($N216="",$N216=Summary!$C$11)),$F216*IF($S216&lt;&gt;"",$S216,$I216)*INDEX(Summary!$C$6:$C$8,MATCH($H216,Summary!$B$6:$B$8,0)),0)</f>
-        <v>28.4</v>
+        <v>30</v>
       </c>
       <c r="U216" s="22" t="n">
         <f aca="false">IF(AND($O216="Y",$Q216&lt;&gt;"Y",OR($N216="",$N216=Summary!$C$11)),$F216*IF($S216&lt;&gt;"",$S216,$J216)*INDEX(Summary!$C$6:$C$8,MATCH($H216,Summary!$B$6:$B$8,0)),0)</f>
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="V216" s="22" t="n">
         <f aca="false">IF(AND($O216="Y",$Q216&lt;&gt;"Y",OR($N216="",$N216=Summary!$C$11)),$F216*IF($S216&lt;&gt;"",$S216,($I216+$J216)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H216,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="W216" s="16" t="s">
         <v>109</v>
@@ -19939,13 +19939,13 @@
         <v>94</v>
       </c>
       <c r="H226" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I226" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J226" s="20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K226" s="16" t="s">
         <v>43</v>
@@ -19972,15 +19972,15 @@
       <c r="S226" s="21"/>
       <c r="T226" s="22" t="n">
         <f aca="false">IF(AND($O226="Y",$Q226&lt;&gt;"Y",OR($N226="",$N226=Summary!$C$11)),$F226*IF($S226&lt;&gt;"",$S226,$I226)*INDEX(Summary!$C$6:$C$8,MATCH($H226,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="U226" s="22" t="n">
         <f aca="false">IF(AND($O226="Y",$Q226&lt;&gt;"Y",OR($N226="",$N226=Summary!$C$11)),$F226*IF($S226&lt;&gt;"",$S226,$J226)*INDEX(Summary!$C$6:$C$8,MATCH($H226,Summary!$B$6:$B$8,0)),0)</f>
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="V226" s="22" t="n">
         <f aca="false">IF(AND($O226="Y",$Q226&lt;&gt;"Y",OR($N226="",$N226=Summary!$C$11)),$F226*IF($S226&lt;&gt;"",$S226,($I226+$J226)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H226,Summary!$B$6:$B$8,0)),0)</f>
-        <v>127.8</v>
+        <v>127.5</v>
       </c>
       <c r="W226" s="16" t="s">
         <v>109</v>
@@ -20079,13 +20079,13 @@
         <v>131</v>
       </c>
       <c r="H228" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I228" s="20" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J228" s="20" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K228" s="16" t="s">
         <v>43</v>
@@ -20112,15 +20112,15 @@
       <c r="S228" s="21"/>
       <c r="T228" s="22" t="n">
         <f aca="false">IF(AND($O228="Y",$Q228&lt;&gt;"Y",OR($N228="",$N228=Summary!$C$11)),$F228*IF($S228&lt;&gt;"",$S228,$I228)*INDEX(Summary!$C$6:$C$8,MATCH($H228,Summary!$B$6:$B$8,0)),0)</f>
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U228" s="22" t="n">
         <f aca="false">IF(AND($O228="Y",$Q228&lt;&gt;"Y",OR($N228="",$N228=Summary!$C$11)),$F228*IF($S228&lt;&gt;"",$S228,$J228)*INDEX(Summary!$C$6:$C$8,MATCH($H228,Summary!$B$6:$B$8,0)),0)</f>
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="V228" s="22" t="n">
         <f aca="false">IF(AND($O228="Y",$Q228&lt;&gt;"Y",OR($N228="",$N228=Summary!$C$11)),$F228*IF($S228&lt;&gt;"",$S228,($I228+$J228)/2)*INDEX(Summary!$C$6:$C$8,MATCH($H228,Summary!$B$6:$B$8,0)),0)</f>
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="W228" s="16" t="s">
         <v>109</v>
@@ -20482,15 +20482,15 @@
       </c>
       <c r="T234" s="13" t="n">
         <f aca="false">SUM(T5:T233)</f>
-        <v>25368.06</v>
+        <v>25392</v>
       </c>
       <c r="U234" s="13" t="n">
         <f aca="false">SUM(U5:U233)</f>
-        <v>52455.67</v>
+        <v>52476</v>
       </c>
       <c r="V234" s="13" t="n">
         <f aca="false">SUM(V5:V233)</f>
-        <v>38911.865</v>
+        <v>38934</v>
       </c>
     </row>
   </sheetData>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4437" uniqueCount="1109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4463" uniqueCount="1149">
   <si>
     <t xml:space="preserve">07K ZN6 Turbo Swap — Cost Summary</t>
   </si>
@@ -2832,7 +2832,7 @@
     <t xml:space="preserve">07K ZN6 — CNC mill BOM (HTMCNC-style, 450 x 750 x 110 mm work area)</t>
   </si>
   <si>
-    <t xml:space="preserve">Same rules as the BOM tab. Blue column H = your real price (CAD). Lines with NO price are undecided: fill D/E with an estimate or H with the real price once you pick a listing. Decided so far (Oct 4, 2026): motor/driver/supply kit (Amazon), extrusion (Amazon). Have: Arduino UNO, filament. Candidate AliExpress listings are in the Link column; prices for those are NOT entered on purpose.</t>
+    <t xml:space="preserve">Same rules as the BOM tab. Blue column H = your real price (CAD). Lines with NO price are undecided: fill D/E with an estimate or H with the real price once you pick a listing. Decided so far (Oct 4, 2026): motor/driver/supply kit (Amazon), extrusion (Amazon). Have: Arduino UNO, filament. Every line has a candidate listing in the Link column at the far right (click to open); columns L–W with the notes are grouped — click the + above them to expand.</t>
   </si>
   <si>
     <t xml:space="preserve">2040 T-slot extrusion, 1000 mm, black — VEVOR 5-pack</t>
@@ -2928,10 +2928,13 @@
     <t xml:space="preserve">Socket-head bolt kit (author's list)</t>
   </si>
   <si>
-    <t xml:space="preserve">M3x12 ×10, M3x16 ×5, M3x30 ×5, M4x10 ×5, M4x12 ×5, M4x14 ×60, M4x25 ×10, M5x12 ×50, M5x16 ×40, M5x20 ×40, M5x30 ×40, M5x50 ×25, M5x60 ×35, M5x70 ×5. Cheapest as an assorted M4/M5 kit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon / AliExpress</t>
+    <t xml:space="preserve">Pick the sizes from the list; 304 DIN912. Or an assorted M4/M5 kit on Amazon.ca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 32968483467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/32968483467.html</t>
   </si>
   <si>
     <t xml:space="preserve">HGR15 linear rail 1000 mm + 2 HGH15CA blocks (Y)</t>
@@ -3033,10 +3036,13 @@
     <t xml:space="preserve">M12x1 locknut (ballscrew end)</t>
   </si>
   <si>
-    <t xml:space="preserve">Also included in BK12 support kits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AliExpress</t>
+    <t xml:space="preserve">BK12 lock nut listing; M12x1 for the 1605 screw end.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 4000909595284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/4000909595284.html</t>
   </si>
   <si>
     <t xml:space="preserve">C19</t>
@@ -3126,6 +3132,15 @@
     <t xml:space="preserve">E-stop button, NC</t>
   </si>
   <si>
+    <t xml:space="preserve">22 mm metal, 2NO 2NC, latching.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005001806206333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005001806206333.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">C25</t>
   </si>
   <si>
@@ -3135,25 +3150,40 @@
     <t xml:space="preserve">Wiring</t>
   </si>
   <si>
-    <t xml:space="preserve">Author used double-shielded; ground the shield at the box only.</t>
+    <t xml:space="preserve">Pick the 4-core 22AWG shielded option. Author used double-shielded; ground the shield at the box only.</t>
   </si>
   <si>
     <t xml:space="preserve">m</t>
   </si>
   <si>
+    <t xml:space="preserve">AliExpress 4000564582198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/4000564582198.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">C26</t>
   </si>
   <si>
     <t xml:space="preserve">Shielded 2-wire cable, limit switches</t>
   </si>
   <si>
+    <t xml:space="preserve">Same listing, 2-core 24AWG shielded.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C27</t>
   </si>
   <si>
     <t xml:space="preserve">Drag chain 10x20 + end mounts</t>
   </si>
   <si>
-    <t xml:space="preserve">X and Y runs.</t>
+    <t xml:space="preserve">Open bridge type, 10x20, 1 m lengths. X and Y runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005001795469984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005001795469984.html</t>
   </si>
   <si>
     <t xml:space="preserve">C28</t>
@@ -3162,6 +3192,15 @@
     <t xml:space="preserve">Terminal blocks, ferrules, USB cable, hookup wire</t>
   </si>
   <si>
+    <t xml:space="preserve">Ratchet ferrule crimper + ferrule kit. Terminal strips and USB cable from Amazon.ca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005007097035466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005007097035466.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">C29</t>
   </si>
   <si>
@@ -3171,7 +3210,13 @@
     <t xml:space="preserve">Control box</t>
   </si>
   <si>
-    <t xml:space="preserve">Author's metal enclosure + GX16 connectors cost ~US$500; an open panel does the job.</t>
+    <t xml:space="preserve">Author's metal enclosure + GX16 connectors cost ~US$500; a plywood panel does the job.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Depot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.homedepot.ca/search?q=plywood%201%2F2</t>
   </si>
   <si>
     <t xml:space="preserve">C30</t>
@@ -3180,7 +3225,13 @@
     <t xml:space="preserve">12 V fan + DC-DC converter for the box</t>
   </si>
   <si>
-    <t xml:space="preserve">Only if the drivers go in a closed box.</t>
+    <t xml:space="preserve">36 V → 12 V 3 A buck module. Add any 80 mm 12 V fan. Only if the drivers go in a closed box.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005007181838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005007181838501.html</t>
   </si>
   <si>
     <t xml:space="preserve">C31</t>
@@ -3189,7 +3240,13 @@
     <t xml:space="preserve">Ethernet CNC controller (grblHAL Teensy 4.1 + breakout) — EMI fix</t>
   </si>
   <si>
-    <t xml:space="preserve">Author could not fully stop USB/EMI false alarms on Arduino+GRBL. Upgrade path, not needed to start.</t>
+    <t xml:space="preserve">Author could not fully stop USB/EMI false alarms on Arduino+GRBL. Ethernet upgrade path, not needed to start.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grblHAL Teensy 4.1 breakout (PCBWay) + Teensy 4.1 (pjrc.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/phil-barrett/grblHAL-teensy-4.x</t>
   </si>
   <si>
     <t xml:space="preserve">C32</t>
@@ -3204,10 +3261,13 @@
     <t xml:space="preserve">Router</t>
   </si>
   <si>
-    <t xml:space="preserve">New vs used vs 65 mm clone. The printed mount is sized for the 65 mm Makita body; the Craftsman does not fit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Depot / Amazon.ca / Marketplace</t>
+    <t xml:space="preserve">New vs used vs 65 mm clone. Bare RT0701C is the one to buy; the CX7 kit (B00HAQMHEO) adds bases you don't need. The printed mount is sized for the 65 mm Makita body; the Craftsman does not fit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon B00E7D3V4S (bare tool) / Home Depot.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ca/dp/B00E7D3V4S</t>
   </si>
   <si>
     <t xml:space="preserve">C33</t>
@@ -3216,7 +3276,13 @@
     <t xml:space="preserve">6 mm collet for RT0701C</t>
   </si>
   <si>
-    <t xml:space="preserve">Router ships with 1/4 in only.</t>
+    <t xml:space="preserve">Router ships with the 1/4 in cone (763637-1) only. Buy the genuine 6 mm cone, not a sleeve adapter (adds runout).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon.ca search; Makita part 763636-3 (verify)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ca/makita-rt0701c-collet/s?k=makita+rt0701c+collet</t>
   </si>
   <si>
     <t xml:space="preserve">C34</t>
@@ -3228,7 +3294,13 @@
     <t xml:space="preserve">Upgrade</t>
   </si>
   <si>
-    <t xml:space="preserve">Author moved to a 2.2 kW VFD spindle for runout; do this before the gearbox adapter plate.</t>
+    <t xml:space="preserve">2.2 kW ER20 air-cooled 80 mm round + VFD. Water-cooled kit with clamp: 1005003968400625. Author moved to a 2.2 kW VFD spindle for runout; do this before the gearbox adapter plate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005008081995923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005008081995923.html</t>
   </si>
   <si>
     <t xml:space="preserve">C35</t>
@@ -3237,7 +3309,13 @@
     <t xml:space="preserve">80 mm spindle mount (if VFD spindle)</t>
   </si>
   <si>
-    <t xml:space="preserve">Machine it on the CNC itself.</t>
+    <t xml:space="preserve">80 mm clamp if you'd rather buy it than machine it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005009168636967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005009168636967.html</t>
   </si>
   <si>
     <t xml:space="preserve">C36</t>
@@ -3285,7 +3363,7 @@
     <t xml:space="preserve">Surface it with the machine once running.</t>
   </si>
   <si>
-    <t xml:space="preserve">Home Depot</t>
+    <t xml:space="preserve">https://www.homedepot.ca/search?q=mdf%203%2F4</t>
   </si>
   <si>
     <t xml:space="preserve">C39</t>
@@ -3294,13 +3372,28 @@
     <t xml:space="preserve">Threaded inserts M6 (or T-track) for hold-downs</t>
   </si>
   <si>
+    <t xml:space="preserve">M6 hex-drive wood inserts, 100-pack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005011942750737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005011942750737.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">C40</t>
   </si>
   <si>
     <t xml:space="preserve">Clamps / hold-down set</t>
   </si>
   <si>
-    <t xml:space="preserve">Print the first set; machine aluminum ones later.</t>
+    <t xml:space="preserve">Arc press-plate clamps. Print the first set; machine aluminum ones later.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005005244930679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005005244930679.html</t>
   </si>
   <si>
     <t xml:space="preserve">C41</t>
@@ -3342,7 +3435,13 @@
     <t xml:space="preserve">Setup</t>
   </si>
   <si>
-    <t xml:space="preserve">Tramming, squareness, collet runout. Mark Have if you own one.</t>
+    <t xml:space="preserve">0.01 mm indicator with flexible magnetic base. Tramming, squareness, collet runout. Mark Have if you own one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005007169855682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005007169855682.html</t>
   </si>
   <si>
     <t xml:space="preserve">C44</t>
@@ -3351,13 +3450,25 @@
     <t xml:space="preserve">Z touch plate / probe</t>
   </si>
   <si>
+    <t xml:space="preserve">AliExpress 1005008660120770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005008660120770.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">C45</t>
   </si>
   <si>
     <t xml:space="preserve">Air blast or mist setup (isopropyl / WD-40) for aluminum</t>
   </si>
   <si>
-    <t xml:space="preserve">Stops chip welding on the single-flute cutters.</t>
+    <t xml:space="preserve">Pneumatic mist sprayer, magnetic base. Stops chip welding on the single-flute cutters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress 1005008490356061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005008490356061.html</t>
   </si>
   <si>
     <t xml:space="preserve">C46</t>
@@ -3370,6 +3481,15 @@
   </si>
   <si>
     <t xml:space="preserve">Consumables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLGI 2 lithium grease for rails and screws; zip ties and heat shrink from the same order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon.ca / Canadian Tire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ca/s?k=white+lithium+grease</t>
   </si>
   <si>
     <t xml:space="preserve">How to use this sheet</t>
@@ -3733,7 +3853,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3878,20 +3998,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5083,12 +5189,12 @@
       <c r="D66" s="15"/>
       <c r="E66" s="15"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="5" t="s">
         <v>18</v>
       </c>
@@ -5102,7 +5208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="3" t="s">
         <v>67</v>
       </c>
@@ -5119,7 +5225,7 @@
         <v>349.98</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="3" t="s">
         <v>51</v>
       </c>
@@ -5136,7 +5242,7 @@
         <v>349.98</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="3" t="s">
         <v>52</v>
       </c>
@@ -5153,7 +5259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="3" t="s">
         <v>53</v>
       </c>
@@ -5170,7 +5276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="3" t="s">
         <v>68</v>
       </c>
@@ -5187,12 +5293,12 @@
         <v>349.98</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="3" t="s">
         <v>70</v>
       </c>
@@ -5201,7 +5307,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="3" t="s">
         <v>71</v>
       </c>
@@ -5210,7 +5316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="3" t="s">
         <v>59</v>
       </c>
@@ -5219,7 +5325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="3" t="s">
         <v>72</v>
       </c>
@@ -5228,7 +5334,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="3" t="s">
         <v>61</v>
       </c>
@@ -5237,7 +5343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="9" t="s">
         <v>73</v>
       </c>
@@ -22605,10 +22711,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="12" min="12" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="24" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="23" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>914</v>
       </c>
@@ -23319,14 +23426,16 @@
       <c r="W13" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X13" s="26"/>
+      <c r="X13" s="26" t="s">
+        <v>949</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
         <v>798</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>2</v>
@@ -23351,13 +23460,13 @@
         <v>103</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M14" s="24" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="O14" s="18" t="s">
         <v>106</v>
@@ -23369,7 +23478,7 @@
         <v>44</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="S14" s="18" t="s">
         <v>922</v>
@@ -23387,7 +23496,7 @@
         <v>62</v>
       </c>
       <c r="X14" s="26" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23395,7 +23504,7 @@
         <v>802</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C15" s="20" t="n">
         <v>2</v>
@@ -23420,13 +23529,13 @@
         <v>103</v>
       </c>
       <c r="L15" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M15" s="24" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="N15" s="19" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="O15" s="18" t="s">
         <v>106</v>
@@ -23438,7 +23547,7 @@
         <v>44</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="S15" s="18" t="s">
         <v>922</v>
@@ -23456,7 +23565,7 @@
         <v>62</v>
       </c>
       <c r="X15" s="26" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23464,7 +23573,7 @@
         <v>806</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C16" s="20" t="n">
         <v>2</v>
@@ -23489,13 +23598,13 @@
         <v>103</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M16" s="24" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="O16" s="18" t="s">
         <v>106</v>
@@ -23507,7 +23616,7 @@
         <v>44</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="S16" s="18" t="s">
         <v>922</v>
@@ -23525,7 +23634,7 @@
         <v>62</v>
       </c>
       <c r="X16" s="26" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23533,7 +23642,7 @@
         <v>808</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C17" s="20" t="n">
         <v>2</v>
@@ -23558,13 +23667,13 @@
         <v>103</v>
       </c>
       <c r="L17" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M17" s="24" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="N17" s="19" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="O17" s="18" t="s">
         <v>106</v>
@@ -23576,7 +23685,7 @@
         <v>44</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="S17" s="18" t="s">
         <v>922</v>
@@ -23594,7 +23703,7 @@
         <v>62</v>
       </c>
       <c r="X17" s="26" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23602,7 +23711,7 @@
         <v>813</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C18" s="20" t="n">
         <v>1</v>
@@ -23627,10 +23736,10 @@
         <v>103</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="N18" s="19"/>
       <c r="O18" s="18" t="s">
@@ -23643,7 +23752,7 @@
         <v>44</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="S18" s="18" t="s">
         <v>922</v>
@@ -23661,7 +23770,7 @@
         <v>62</v>
       </c>
       <c r="X18" s="26" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23669,7 +23778,7 @@
         <v>816</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C19" s="20" t="n">
         <v>1</v>
@@ -23694,13 +23803,13 @@
         <v>103</v>
       </c>
       <c r="L19" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M19" s="24" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="N19" s="19" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="O19" s="18" t="s">
         <v>106</v>
@@ -23712,7 +23821,7 @@
         <v>44</v>
       </c>
       <c r="R19" s="24" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="S19" s="18" t="s">
         <v>922</v>
@@ -23730,7 +23839,7 @@
         <v>62</v>
       </c>
       <c r="X19" s="26" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23738,7 +23847,7 @@
         <v>818</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C20" s="20" t="n">
         <v>4</v>
@@ -23763,16 +23872,16 @@
         <v>103</v>
       </c>
       <c r="L20" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M20" s="24" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="N20" s="19" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="P20" s="20" t="s">
         <v>6</v>
@@ -23781,7 +23890,7 @@
         <v>44</v>
       </c>
       <c r="R20" s="24" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="S20" s="18" t="s">
         <v>922</v>
@@ -23799,15 +23908,15 @@
         <v>62</v>
       </c>
       <c r="X20" s="26" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C21" s="20" t="n">
         <v>4</v>
@@ -23832,13 +23941,13 @@
         <v>103</v>
       </c>
       <c r="L21" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M21" s="24" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="N21" s="19" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="O21" s="18" t="s">
         <v>106</v>
@@ -23850,7 +23959,7 @@
         <v>44</v>
       </c>
       <c r="R21" s="24" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="S21" s="18" t="s">
         <v>922</v>
@@ -23868,15 +23977,15 @@
         <v>62</v>
       </c>
       <c r="X21" s="26" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C22" s="20" t="n">
         <v>4</v>
@@ -23901,13 +24010,13 @@
         <v>103</v>
       </c>
       <c r="L22" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="N22" s="19" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="O22" s="18" t="s">
         <v>106</v>
@@ -23919,7 +24028,7 @@
         <v>44</v>
       </c>
       <c r="R22" s="24" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="S22" s="18" t="s">
         <v>922</v>
@@ -23936,14 +24045,16 @@
       <c r="W22" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X22" s="26"/>
+      <c r="X22" s="26" t="s">
+        <v>985</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C23" s="20" t="n">
         <v>4</v>
@@ -23968,13 +24079,13 @@
         <v>103</v>
       </c>
       <c r="L23" s="24" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M23" s="24" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="N23" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="O23" s="18" t="s">
         <v>106</v>
@@ -23986,7 +24097,7 @@
         <v>44</v>
       </c>
       <c r="R23" s="24" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="S23" s="18" t="s">
         <v>922</v>
@@ -24004,15 +24115,15 @@
         <v>62</v>
       </c>
       <c r="X23" s="26" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C24" s="20" t="n">
         <v>1</v>
@@ -24039,13 +24150,13 @@
         <v>103</v>
       </c>
       <c r="L24" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M24" s="24" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="N24" s="19" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="O24" s="18" t="s">
         <v>160</v>
@@ -24057,7 +24168,7 @@
         <v>44</v>
       </c>
       <c r="R24" s="24" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="S24" s="18" t="s">
         <v>922</v>
@@ -24075,15 +24186,15 @@
         <v>219</v>
       </c>
       <c r="X24" s="26" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C25" s="20" t="n">
         <v>1</v>
@@ -24108,13 +24219,13 @@
         <v>103</v>
       </c>
       <c r="L25" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M25" s="24" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="O25" s="18" t="s">
         <v>106</v>
@@ -24147,10 +24258,10 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C26" s="20" t="n">
         <v>1</v>
@@ -24175,13 +24286,13 @@
         <v>103</v>
       </c>
       <c r="L26" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M26" s="24" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="N26" s="19" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="O26" s="18" t="s">
         <v>106</v>
@@ -24193,7 +24304,7 @@
         <v>44</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="S26" s="18" t="s">
         <v>922</v>
@@ -24211,15 +24322,15 @@
         <v>62</v>
       </c>
       <c r="X26" s="26" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C27" s="20" t="n">
         <v>6</v>
@@ -24244,13 +24355,13 @@
         <v>103</v>
       </c>
       <c r="L27" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M27" s="24" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="N27" s="19" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="O27" s="18" t="s">
         <v>106</v>
@@ -24262,7 +24373,7 @@
         <v>44</v>
       </c>
       <c r="R27" s="24" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="S27" s="18" t="s">
         <v>922</v>
@@ -24280,15 +24391,15 @@
         <v>62</v>
       </c>
       <c r="X27" s="26" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C28" s="20" t="n">
         <v>1</v>
@@ -24313,12 +24424,14 @@
         <v>103</v>
       </c>
       <c r="L28" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M28" s="24" t="s">
-        <v>1007</v>
-      </c>
-      <c r="N28" s="19"/>
+        <v>1009</v>
+      </c>
+      <c r="N28" s="19" t="s">
+        <v>1015</v>
+      </c>
       <c r="O28" s="18" t="s">
         <v>106</v>
       </c>
@@ -24329,7 +24442,7 @@
         <v>44</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>983</v>
+        <v>1016</v>
       </c>
       <c r="S28" s="18" t="s">
         <v>922</v>
@@ -24346,14 +24459,16 @@
       <c r="W28" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X28" s="26"/>
+      <c r="X28" s="26" t="s">
+        <v>1017</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="C29" s="20" t="n">
         <v>15</v>
@@ -24378,16 +24493,16 @@
         <v>103</v>
       </c>
       <c r="L29" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M29" s="24" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="N29" s="19" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="P29" s="20" t="s">
         <v>6</v>
@@ -24396,7 +24511,7 @@
         <v>44</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>983</v>
+        <v>1023</v>
       </c>
       <c r="S29" s="18" t="s">
         <v>922</v>
@@ -24413,14 +24528,16 @@
       <c r="W29" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X29" s="26"/>
+      <c r="X29" s="26" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="C30" s="20" t="n">
         <v>10</v>
@@ -24445,14 +24562,16 @@
         <v>103</v>
       </c>
       <c r="L30" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M30" s="24" t="s">
-        <v>1015</v>
-      </c>
-      <c r="N30" s="19"/>
+        <v>1020</v>
+      </c>
+      <c r="N30" s="19" t="s">
+        <v>1027</v>
+      </c>
       <c r="O30" s="18" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="P30" s="20" t="s">
         <v>6</v>
@@ -24461,7 +24580,7 @@
         <v>44</v>
       </c>
       <c r="R30" s="24" t="s">
-        <v>983</v>
+        <v>1023</v>
       </c>
       <c r="S30" s="18" t="s">
         <v>922</v>
@@ -24478,14 +24597,16 @@
       <c r="W30" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X30" s="26"/>
+      <c r="X30" s="26" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="C31" s="20" t="n">
         <v>2</v>
@@ -24510,16 +24631,16 @@
         <v>103</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M31" s="24" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="N31" s="19" t="s">
+        <v>1030</v>
+      </c>
+      <c r="O31" s="18" t="s">
         <v>1022</v>
-      </c>
-      <c r="O31" s="18" t="s">
-        <v>1017</v>
       </c>
       <c r="P31" s="20" t="s">
         <v>6</v>
@@ -24528,7 +24649,7 @@
         <v>44</v>
       </c>
       <c r="R31" s="24" t="s">
-        <v>983</v>
+        <v>1031</v>
       </c>
       <c r="S31" s="18" t="s">
         <v>922</v>
@@ -24545,14 +24666,16 @@
       <c r="W31" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X31" s="26"/>
+      <c r="X31" s="26" t="s">
+        <v>1032</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
       <c r="C32" s="20" t="n">
         <v>1</v>
@@ -24577,12 +24700,14 @@
         <v>103</v>
       </c>
       <c r="L32" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M32" s="24" t="s">
-        <v>1015</v>
-      </c>
-      <c r="N32" s="19"/>
+        <v>1020</v>
+      </c>
+      <c r="N32" s="19" t="s">
+        <v>1035</v>
+      </c>
       <c r="O32" s="18" t="s">
         <v>212</v>
       </c>
@@ -24593,7 +24718,7 @@
         <v>44</v>
       </c>
       <c r="R32" s="24" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="S32" s="18" t="s">
         <v>922</v>
@@ -24610,14 +24735,16 @@
       <c r="W32" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X32" s="26"/>
+      <c r="X32" s="26" t="s">
+        <v>1037</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
-        <v>1025</v>
+        <v>1038</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="C33" s="20" t="n">
         <v>1</v>
@@ -24642,13 +24769,13 @@
         <v>103</v>
       </c>
       <c r="L33" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M33" s="24" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="N33" s="19" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="O33" s="18" t="s">
         <v>106</v>
@@ -24660,7 +24787,7 @@
         <v>45</v>
       </c>
       <c r="R33" s="24" t="s">
-        <v>7</v>
+        <v>1042</v>
       </c>
       <c r="S33" s="18" t="s">
         <v>922</v>
@@ -24677,14 +24804,16 @@
       <c r="W33" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X33" s="26"/>
+      <c r="X33" s="26" t="s">
+        <v>1043</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>1029</v>
+        <v>1044</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>1030</v>
+        <v>1045</v>
       </c>
       <c r="C34" s="20" t="n">
         <v>1</v>
@@ -24709,13 +24838,13 @@
         <v>101</v>
       </c>
       <c r="L34" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M34" s="24" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="N34" s="19" t="s">
-        <v>1031</v>
+        <v>1046</v>
       </c>
       <c r="O34" s="18" t="s">
         <v>106</v>
@@ -24727,7 +24856,7 @@
         <v>44</v>
       </c>
       <c r="R34" s="24" t="s">
-        <v>983</v>
+        <v>1047</v>
       </c>
       <c r="S34" s="18" t="s">
         <v>922</v>
@@ -24744,14 +24873,16 @@
       <c r="W34" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X34" s="26"/>
+      <c r="X34" s="26" t="s">
+        <v>1048</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="s">
-        <v>1032</v>
+        <v>1049</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>1033</v>
+        <v>1050</v>
       </c>
       <c r="C35" s="20" t="n">
         <v>1</v>
@@ -24776,13 +24907,13 @@
         <v>101</v>
       </c>
       <c r="L35" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="M35" s="24" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="N35" s="19" t="s">
-        <v>1034</v>
+        <v>1051</v>
       </c>
       <c r="O35" s="18" t="s">
         <v>106</v>
@@ -24794,7 +24925,7 @@
         <v>44</v>
       </c>
       <c r="R35" s="24" t="s">
-        <v>7</v>
+        <v>1052</v>
       </c>
       <c r="S35" s="18" t="s">
         <v>922</v>
@@ -24811,14 +24942,16 @@
       <c r="W35" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X35" s="26"/>
+      <c r="X35" s="26" t="s">
+        <v>1053</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>1035</v>
+        <v>1054</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>1036</v>
+        <v>1055</v>
       </c>
       <c r="C36" s="20" t="n">
         <v>1</v>
@@ -24843,13 +24976,13 @@
         <v>103</v>
       </c>
       <c r="L36" s="24" t="s">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="M36" s="24" t="s">
-        <v>1038</v>
+        <v>1057</v>
       </c>
       <c r="N36" s="19" t="s">
-        <v>1039</v>
+        <v>1058</v>
       </c>
       <c r="O36" s="18" t="s">
         <v>106</v>
@@ -24861,7 +24994,7 @@
         <v>44</v>
       </c>
       <c r="R36" s="24" t="s">
-        <v>1040</v>
+        <v>1059</v>
       </c>
       <c r="S36" s="18" t="s">
         <v>922</v>
@@ -24878,14 +25011,16 @@
       <c r="W36" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X36" s="26"/>
+      <c r="X36" s="26" t="s">
+        <v>1060</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>1041</v>
+        <v>1061</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>1042</v>
+        <v>1062</v>
       </c>
       <c r="C37" s="20" t="n">
         <v>1</v>
@@ -24910,13 +25045,13 @@
         <v>103</v>
       </c>
       <c r="L37" s="24" t="s">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="M37" s="24" t="s">
-        <v>1038</v>
+        <v>1057</v>
       </c>
       <c r="N37" s="19" t="s">
-        <v>1043</v>
+        <v>1063</v>
       </c>
       <c r="O37" s="18" t="s">
         <v>106</v>
@@ -24928,7 +25063,7 @@
         <v>44</v>
       </c>
       <c r="R37" s="24" t="s">
-        <v>948</v>
+        <v>1064</v>
       </c>
       <c r="S37" s="18" t="s">
         <v>922</v>
@@ -24945,14 +25080,16 @@
       <c r="W37" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X37" s="26"/>
+      <c r="X37" s="26" t="s">
+        <v>1065</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>1044</v>
+        <v>1066</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>1045</v>
+        <v>1067</v>
       </c>
       <c r="C38" s="20" t="n">
         <v>1</v>
@@ -24977,13 +25114,13 @@
         <v>101</v>
       </c>
       <c r="L38" s="24" t="s">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="M38" s="24" t="s">
-        <v>1046</v>
+        <v>1068</v>
       </c>
       <c r="N38" s="19" t="s">
-        <v>1047</v>
+        <v>1069</v>
       </c>
       <c r="O38" s="18" t="s">
         <v>106</v>
@@ -24995,7 +25132,7 @@
         <v>44</v>
       </c>
       <c r="R38" s="24" t="s">
-        <v>983</v>
+        <v>1070</v>
       </c>
       <c r="S38" s="18" t="s">
         <v>922</v>
@@ -25012,14 +25149,16 @@
       <c r="W38" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X38" s="26"/>
+      <c r="X38" s="26" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>1048</v>
+        <v>1072</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="C39" s="20" t="n">
         <v>1</v>
@@ -25044,13 +25183,13 @@
         <v>101</v>
       </c>
       <c r="L39" s="24" t="s">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="M39" s="24" t="s">
-        <v>1046</v>
+        <v>1068</v>
       </c>
       <c r="N39" s="19" t="s">
-        <v>1050</v>
+        <v>1074</v>
       </c>
       <c r="O39" s="18" t="s">
         <v>106</v>
@@ -25062,7 +25201,7 @@
         <v>45</v>
       </c>
       <c r="R39" s="24" t="s">
-        <v>7</v>
+        <v>1075</v>
       </c>
       <c r="S39" s="18" t="s">
         <v>922</v>
@@ -25079,14 +25218,16 @@
       <c r="W39" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X39" s="26"/>
+      <c r="X39" s="26" t="s">
+        <v>1076</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>1051</v>
+        <v>1077</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>1052</v>
+        <v>1078</v>
       </c>
       <c r="C40" s="20" t="n">
         <v>3</v>
@@ -25111,13 +25252,13 @@
         <v>103</v>
       </c>
       <c r="L40" s="24" t="s">
-        <v>1053</v>
+        <v>1079</v>
       </c>
       <c r="M40" s="24" t="s">
         <v>867</v>
       </c>
       <c r="N40" s="19" t="s">
-        <v>1054</v>
+        <v>1080</v>
       </c>
       <c r="O40" s="18" t="s">
         <v>868</v>
@@ -25150,10 +25291,10 @@
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>1055</v>
+        <v>1081</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>1056</v>
+        <v>1082</v>
       </c>
       <c r="C41" s="20" t="n">
         <v>1</v>
@@ -25178,13 +25319,13 @@
         <v>103</v>
       </c>
       <c r="L41" s="24" t="s">
-        <v>1053</v>
+        <v>1079</v>
       </c>
       <c r="M41" s="24" t="s">
-        <v>1057</v>
+        <v>1083</v>
       </c>
       <c r="N41" s="19" t="s">
-        <v>1058</v>
+        <v>1084</v>
       </c>
       <c r="O41" s="18" t="s">
         <v>106</v>
@@ -25196,7 +25337,7 @@
         <v>44</v>
       </c>
       <c r="R41" s="24" t="s">
-        <v>1059</v>
+        <v>1085</v>
       </c>
       <c r="S41" s="18" t="s">
         <v>922</v>
@@ -25214,15 +25355,15 @@
         <v>62</v>
       </c>
       <c r="X41" s="26" t="s">
-        <v>1060</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>1061</v>
+        <v>1087</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>1062</v>
+        <v>1088</v>
       </c>
       <c r="C42" s="20" t="n">
         <v>1</v>
@@ -25247,13 +25388,13 @@
         <v>103</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>1063</v>
+        <v>1089</v>
       </c>
       <c r="M42" s="24" t="s">
-        <v>1064</v>
+        <v>1090</v>
       </c>
       <c r="N42" s="19" t="s">
-        <v>1065</v>
+        <v>1091</v>
       </c>
       <c r="O42" s="18" t="s">
         <v>106</v>
@@ -25265,7 +25406,7 @@
         <v>44</v>
       </c>
       <c r="R42" s="24" t="s">
-        <v>1066</v>
+        <v>1042</v>
       </c>
       <c r="S42" s="18" t="s">
         <v>922</v>
@@ -25282,14 +25423,16 @@
       <c r="W42" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X42" s="26"/>
+      <c r="X42" s="26" t="s">
+        <v>1092</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>1067</v>
+        <v>1093</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>1068</v>
+        <v>1094</v>
       </c>
       <c r="C43" s="20" t="n">
         <v>1</v>
@@ -25314,12 +25457,14 @@
         <v>103</v>
       </c>
       <c r="L43" s="24" t="s">
-        <v>1063</v>
+        <v>1089</v>
       </c>
       <c r="M43" s="24" t="s">
-        <v>1064</v>
-      </c>
-      <c r="N43" s="19"/>
+        <v>1090</v>
+      </c>
+      <c r="N43" s="19" t="s">
+        <v>1095</v>
+      </c>
       <c r="O43" s="18" t="s">
         <v>212</v>
       </c>
@@ -25330,7 +25475,7 @@
         <v>44</v>
       </c>
       <c r="R43" s="24" t="s">
-        <v>948</v>
+        <v>1096</v>
       </c>
       <c r="S43" s="18" t="s">
         <v>922</v>
@@ -25347,14 +25492,16 @@
       <c r="W43" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X43" s="26"/>
+      <c r="X43" s="26" t="s">
+        <v>1097</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>1069</v>
+        <v>1098</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>1070</v>
+        <v>1099</v>
       </c>
       <c r="C44" s="20" t="n">
         <v>1</v>
@@ -25379,13 +25526,13 @@
         <v>103</v>
       </c>
       <c r="L44" s="24" t="s">
-        <v>1063</v>
+        <v>1089</v>
       </c>
       <c r="M44" s="24" t="s">
-        <v>1064</v>
+        <v>1090</v>
       </c>
       <c r="N44" s="19" t="s">
-        <v>1071</v>
+        <v>1100</v>
       </c>
       <c r="O44" s="18" t="s">
         <v>140</v>
@@ -25397,7 +25544,7 @@
         <v>45</v>
       </c>
       <c r="R44" s="24" t="s">
-        <v>7</v>
+        <v>1101</v>
       </c>
       <c r="S44" s="18" t="s">
         <v>922</v>
@@ -25414,14 +25561,16 @@
       <c r="W44" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X44" s="26"/>
+      <c r="X44" s="26" t="s">
+        <v>1102</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="s">
-        <v>1072</v>
+        <v>1103</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>1073</v>
+        <v>1104</v>
       </c>
       <c r="C45" s="20" t="n">
         <v>2</v>
@@ -25446,13 +25595,13 @@
         <v>103</v>
       </c>
       <c r="L45" s="24" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="M45" s="24" t="s">
-        <v>1075</v>
+        <v>1106</v>
       </c>
       <c r="N45" s="19" t="s">
-        <v>1076</v>
+        <v>1107</v>
       </c>
       <c r="O45" s="18" t="s">
         <v>106</v>
@@ -25464,7 +25613,7 @@
         <v>44</v>
       </c>
       <c r="R45" s="24" t="s">
-        <v>1077</v>
+        <v>1108</v>
       </c>
       <c r="S45" s="18" t="s">
         <v>922</v>
@@ -25482,15 +25631,15 @@
         <v>62</v>
       </c>
       <c r="X45" s="26" t="s">
-        <v>1078</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="18" t="s">
-        <v>1079</v>
+        <v>1110</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>1080</v>
+        <v>1111</v>
       </c>
       <c r="C46" s="20" t="n">
         <v>2</v>
@@ -25515,13 +25664,13 @@
         <v>103</v>
       </c>
       <c r="L46" s="24" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>1075</v>
+        <v>1106</v>
       </c>
       <c r="N46" s="19" t="s">
-        <v>1081</v>
+        <v>1112</v>
       </c>
       <c r="O46" s="18" t="s">
         <v>106</v>
@@ -25533,7 +25682,7 @@
         <v>44</v>
       </c>
       <c r="R46" s="24" t="s">
-        <v>1077</v>
+        <v>1108</v>
       </c>
       <c r="S46" s="18" t="s">
         <v>922</v>
@@ -25551,15 +25700,15 @@
         <v>62</v>
       </c>
       <c r="X46" s="26" t="s">
-        <v>1078</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="s">
-        <v>1082</v>
+        <v>1113</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>1083</v>
+        <v>1114</v>
       </c>
       <c r="C47" s="20" t="n">
         <v>1</v>
@@ -25584,13 +25733,13 @@
         <v>103</v>
       </c>
       <c r="L47" s="24" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="M47" s="24" t="s">
-        <v>1084</v>
+        <v>1115</v>
       </c>
       <c r="N47" s="19" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="O47" s="18" t="s">
         <v>106</v>
@@ -25602,7 +25751,7 @@
         <v>44</v>
       </c>
       <c r="R47" s="24" t="s">
-        <v>609</v>
+        <v>1117</v>
       </c>
       <c r="S47" s="18" t="s">
         <v>922</v>
@@ -25619,14 +25768,16 @@
       <c r="W47" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X47" s="26"/>
+      <c r="X47" s="26" t="s">
+        <v>1118</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="s">
-        <v>1086</v>
+        <v>1119</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>1087</v>
+        <v>1120</v>
       </c>
       <c r="C48" s="20" t="n">
         <v>1</v>
@@ -25651,10 +25802,10 @@
         <v>103</v>
       </c>
       <c r="L48" s="24" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="M48" s="24" t="s">
-        <v>1084</v>
+        <v>1115</v>
       </c>
       <c r="N48" s="19"/>
       <c r="O48" s="18" t="s">
@@ -25667,7 +25818,7 @@
         <v>44</v>
       </c>
       <c r="R48" s="24" t="s">
-        <v>983</v>
+        <v>1121</v>
       </c>
       <c r="S48" s="18" t="s">
         <v>922</v>
@@ -25684,14 +25835,16 @@
       <c r="W48" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X48" s="26"/>
+      <c r="X48" s="26" t="s">
+        <v>1122</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="18" t="s">
-        <v>1088</v>
+        <v>1123</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>1089</v>
+        <v>1124</v>
       </c>
       <c r="C49" s="20" t="n">
         <v>1</v>
@@ -25716,13 +25869,13 @@
         <v>103</v>
       </c>
       <c r="L49" s="24" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>1084</v>
+        <v>1115</v>
       </c>
       <c r="N49" s="19" t="s">
-        <v>1090</v>
+        <v>1125</v>
       </c>
       <c r="O49" s="18" t="s">
         <v>106</v>
@@ -25734,7 +25887,7 @@
         <v>44</v>
       </c>
       <c r="R49" s="24" t="s">
-        <v>948</v>
+        <v>1126</v>
       </c>
       <c r="S49" s="18" t="s">
         <v>922</v>
@@ -25751,14 +25904,16 @@
       <c r="W49" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X49" s="26"/>
+      <c r="X49" s="26" t="s">
+        <v>1127</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>1091</v>
+        <v>1128</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>1092</v>
+        <v>1129</v>
       </c>
       <c r="C50" s="20" t="n">
         <v>1</v>
@@ -25783,12 +25938,14 @@
         <v>103</v>
       </c>
       <c r="L50" s="24" t="s">
-        <v>1093</v>
+        <v>1130</v>
       </c>
       <c r="M50" s="24" t="s">
-        <v>1094</v>
-      </c>
-      <c r="N50" s="19"/>
+        <v>1131</v>
+      </c>
+      <c r="N50" s="19" t="s">
+        <v>1132</v>
+      </c>
       <c r="O50" s="18" t="s">
         <v>212</v>
       </c>
@@ -25799,7 +25956,7 @@
         <v>44</v>
       </c>
       <c r="R50" s="24" t="s">
-        <v>860</v>
+        <v>1133</v>
       </c>
       <c r="S50" s="18" t="s">
         <v>922</v>
@@ -25816,9 +25973,11 @@
       <c r="W50" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X50" s="26"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="X50" s="26" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H51" s="14" t="s">
         <v>913</v>
       </c>
@@ -25847,17 +26006,17 @@
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>AND($T5&lt;&gt;"",$T5&lt;&gt;Summary!$C$11)</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$F5="Y"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:J50">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$J5="To decide"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:E50">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>AND($K5="Y",$F5&lt;&gt;"Y",$H5="",$D5="",$E5="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25892,21 +26051,42 @@
     <hyperlink ref="X10" r:id="rId6" display="https://www.aliexpress.com/item/32814359094.html"/>
     <hyperlink ref="X11" r:id="rId7" display="https://www.aliexpress.com/item/1005007883028035.html"/>
     <hyperlink ref="X12" r:id="rId8" display="https://www.aliexpress.com/item/32814359094.html"/>
-    <hyperlink ref="X14" r:id="rId9" display="https://www.aliexpress.com/item/1005004825209262.html"/>
-    <hyperlink ref="X15" r:id="rId10" display="https://www.aliexpress.com/item/1005004825209262.html"/>
-    <hyperlink ref="X16" r:id="rId11" display="https://www.aliexpress.com/item/1005004825209262.html"/>
-    <hyperlink ref="X17" r:id="rId12" display="https://www.aliexpress.com/item/1005007791178337.html"/>
-    <hyperlink ref="X18" r:id="rId13" display="https://www.aliexpress.com/item/1005007791178337.html"/>
-    <hyperlink ref="X19" r:id="rId14" display="https://www.aliexpress.com/item/32995243964.html"/>
-    <hyperlink ref="X20" r:id="rId15" display="https://www.aliexpress.com/item/32794645480.html"/>
-    <hyperlink ref="X21" r:id="rId16" display="https://www.aliexpress.com/item/1005006093979302.html"/>
-    <hyperlink ref="X23" r:id="rId17" display="https://www.aliexpress.com/item/1005007121900242.html"/>
-    <hyperlink ref="X24" r:id="rId18" display="https://www.amazon.ca/dp/B0BTJTXHNN"/>
-    <hyperlink ref="X26" r:id="rId19" display="https://www.aliexpress.com/item/1005006478108991.html"/>
-    <hyperlink ref="X27" r:id="rId20" display="https://www.aliexpress.com/item/1005001599112235.html"/>
-    <hyperlink ref="X41" r:id="rId21" display="https://cults3d.com/en/3d-model/tool/diy-3d-printed-cnc-machine-htmcnc"/>
-    <hyperlink ref="X45" r:id="rId22" display="https://www.aliexpress.com/item/1005001948417279.html"/>
-    <hyperlink ref="X46" r:id="rId23" display="https://www.aliexpress.com/item/1005001948417279.html"/>
+    <hyperlink ref="X13" r:id="rId9" display="https://www.aliexpress.com/item/32968483467.html"/>
+    <hyperlink ref="X14" r:id="rId10" display="https://www.aliexpress.com/item/1005004825209262.html"/>
+    <hyperlink ref="X15" r:id="rId11" display="https://www.aliexpress.com/item/1005004825209262.html"/>
+    <hyperlink ref="X16" r:id="rId12" display="https://www.aliexpress.com/item/1005004825209262.html"/>
+    <hyperlink ref="X17" r:id="rId13" display="https://www.aliexpress.com/item/1005007791178337.html"/>
+    <hyperlink ref="X18" r:id="rId14" display="https://www.aliexpress.com/item/1005007791178337.html"/>
+    <hyperlink ref="X19" r:id="rId15" display="https://www.aliexpress.com/item/32995243964.html"/>
+    <hyperlink ref="X20" r:id="rId16" display="https://www.aliexpress.com/item/32794645480.html"/>
+    <hyperlink ref="X21" r:id="rId17" display="https://www.aliexpress.com/item/1005006093979302.html"/>
+    <hyperlink ref="X22" r:id="rId18" display="https://www.aliexpress.com/item/4000909595284.html"/>
+    <hyperlink ref="X23" r:id="rId19" display="https://www.aliexpress.com/item/1005007121900242.html"/>
+    <hyperlink ref="X24" r:id="rId20" display="https://www.amazon.ca/dp/B0BTJTXHNN"/>
+    <hyperlink ref="X26" r:id="rId21" display="https://www.aliexpress.com/item/1005006478108991.html"/>
+    <hyperlink ref="X27" r:id="rId22" display="https://www.aliexpress.com/item/1005001599112235.html"/>
+    <hyperlink ref="X28" r:id="rId23" display="https://www.aliexpress.com/item/1005001806206333.html"/>
+    <hyperlink ref="X29" r:id="rId24" display="https://www.aliexpress.com/item/4000564582198.html"/>
+    <hyperlink ref="X30" r:id="rId25" display="https://www.aliexpress.com/item/4000564582198.html"/>
+    <hyperlink ref="X31" r:id="rId26" display="https://www.aliexpress.com/item/1005001795469984.html"/>
+    <hyperlink ref="X32" r:id="rId27" display="https://www.aliexpress.com/item/1005007097035466.html"/>
+    <hyperlink ref="X33" r:id="rId28" display="https://www.homedepot.ca/search?q=plywood%201%2F2"/>
+    <hyperlink ref="X34" r:id="rId29" display="https://www.aliexpress.com/item/1005007181838501.html"/>
+    <hyperlink ref="X35" r:id="rId30" display="https://github.com/phil-barrett/grblHAL-teensy-4.x"/>
+    <hyperlink ref="X36" r:id="rId31" display="https://www.amazon.ca/dp/B00E7D3V4S"/>
+    <hyperlink ref="X37" r:id="rId32" display="https://www.amazon.ca/makita-rt0701c-collet/s?k=makita+rt0701c+collet"/>
+    <hyperlink ref="X38" r:id="rId33" display="https://www.aliexpress.com/item/1005008081995923.html"/>
+    <hyperlink ref="X39" r:id="rId34" display="https://www.aliexpress.com/item/1005009168636967.html"/>
+    <hyperlink ref="X41" r:id="rId35" display="https://cults3d.com/en/3d-model/tool/diy-3d-printed-cnc-machine-htmcnc"/>
+    <hyperlink ref="X42" r:id="rId36" display="https://www.homedepot.ca/search?q=mdf%203%2F4"/>
+    <hyperlink ref="X43" r:id="rId37" display="https://www.aliexpress.com/item/1005011942750737.html"/>
+    <hyperlink ref="X44" r:id="rId38" display="https://www.aliexpress.com/item/1005005244930679.html"/>
+    <hyperlink ref="X45" r:id="rId39" display="https://www.aliexpress.com/item/1005001948417279.html"/>
+    <hyperlink ref="X46" r:id="rId40" display="https://www.aliexpress.com/item/1005001948417279.html"/>
+    <hyperlink ref="X47" r:id="rId41" display="https://www.aliexpress.com/item/1005007169855682.html"/>
+    <hyperlink ref="X48" r:id="rId42" display="https://www.aliexpress.com/item/1005008660120770.html"/>
+    <hyperlink ref="X49" r:id="rId43" display="https://www.aliexpress.com/item/1005008490356061.html"/>
+    <hyperlink ref="X50" r:id="rId44" display="https://www.amazon.ca/s?k=white+lithium+grease"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -25915,7 +26095,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId24"/>
+  <drawing r:id="rId45"/>
 </worksheet>
 </file>
 
@@ -25932,72 +26112,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>1095</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>1096</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>1097</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>1098</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>1099</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>1100</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>1101</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>1102</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>1103</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>1104</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>1105</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>1106</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>1108</v>
+        <v>1148</v>
       </c>
     </row>
   </sheetData>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4463" uniqueCount="1149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4467" uniqueCount="1154">
   <si>
     <t xml:space="preserve">07K ZN6 Turbo Swap — Cost Summary</t>
   </si>
@@ -2832,7 +2832,7 @@
     <t xml:space="preserve">07K ZN6 — CNC mill BOM (HTMCNC-style, 450 x 750 x 110 mm work area)</t>
   </si>
   <si>
-    <t xml:space="preserve">Same rules as the BOM tab. Blue column H = your real price (CAD). Lines with NO price are undecided: fill D/E with an estimate or H with the real price once you pick a listing. Decided so far (Oct 4, 2026): motor/driver/supply kit (Amazon), extrusion (Amazon). Have: Arduino UNO, filament. Every line has a candidate listing in the Link column at the far right (click to open); columns L–W with the notes are grouped — click the + above them to expand.</t>
+    <t xml:space="preserve">Same rules as the BOM tab. Est. low/high (D/E) = the prices I found on Oct 4–5, 2026, per unit in CAD, mostly AliExpress listing prices (Basis = Listing) or inferred from them (Basis = Estimate). That is the number to beat: when you find cheaper, type your real price in the blue column H and it overrides the estimate. Decided and bought-price lines: C01, C02, C20. Have: C21, C36. Every line has a candidate listing in the Link column at the far right; columns L–W with the notes are grouped (click the + above them).</t>
   </si>
   <si>
     <t xml:space="preserve">2040 T-slot extrusion, 1000 mm, black — VEVOR 5-pack</t>
@@ -2844,7 +2844,7 @@
     <t xml:space="preserve">Extrusion</t>
   </si>
   <si>
-    <t xml:space="preserve">Cut plan: two bars → 700 + 200 + 100; three bars stay 600. Cut 2–3 mm long, file square. Decided Oct 4: Amazon.</t>
+    <t xml:space="preserve">Cut plan: two bars → 700 + 200 + 100; three bars stay 600. Cut 2–3 mm long, file square. Decided Oct 4: Amazon. Found: To beat: Spool3D 2040 T-slot 1500 mm 31.50 / 1000 mm 21.00; AliExpress ~8–12 per 600 mm.</t>
   </si>
   <si>
     <t xml:space="preserve">pack</t>
@@ -2862,7 +2862,7 @@
     <t xml:space="preserve">2080 T-slot extrusion, 1000 mm, silver — 2-pack (Y rails)</t>
   </si>
   <si>
-    <t xml:space="preserve">Check the variant selector is on 1000 mm silver before buying. Decided Oct 4: Amazon. Alt: Spool3D 2080 V-slot 1000 mm.</t>
+    <t xml:space="preserve">Check the variant selector is on 1000 mm silver before buying. Decided Oct 4: Amazon. Alt: Spool3D 2080 V-slot 1000 mm. Found: To beat: Spool3D 2080 V-slot 1000 mm CAD 39.00 each (free ship over $140); AliExpress ~25–35 each plus shipping.</t>
   </si>
   <si>
     <t xml:space="preserve">Amazon B09MWBZRGH</t>
@@ -2874,19 +2874,22 @@
     <t xml:space="preserve">Corner bracket 28x20x28 (2028), with T-nuts + M5 bolts</t>
   </si>
   <si>
-    <t xml:space="preserve">Author's BOM: 18. Sold in 10-packs → buy 2 packs.</t>
+    <t xml:space="preserve">Author's BOM: 18. Sold in 10-packs → buy 2 packs. Found: 10-pack from CAD 5.11 (169 sold).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005007660268625</t>
   </si>
   <si>
+    <t xml:space="preserve">Listing</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.aliexpress.com/item/1005007660268625.html</t>
   </si>
   <si>
     <t xml:space="preserve">Corner bracket 20x20x20, with T-nuts + M5 bolts</t>
   </si>
   <si>
-    <t xml:space="preserve">Author's BOM: 8.</t>
+    <t xml:space="preserve">Author's BOM: 8. Found: Listing shows a teaser 'from' price; 0.30–0.80 each is typical.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005002491882309</t>
@@ -2898,7 +2901,7 @@
     <t xml:space="preserve">M5 sliding T-nut</t>
   </si>
   <si>
-    <t xml:space="preserve">20-series, 6 mm slot.</t>
+    <t xml:space="preserve">20-series, 6 mm slot. Found: 100-packs run CAD 6–12.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005007883028035</t>
@@ -2910,7 +2913,7 @@
     <t xml:space="preserve">M5 hammer-head T-nut</t>
   </si>
   <si>
-    <t xml:space="preserve">Drop-in type for adding parts after assembly.</t>
+    <t xml:space="preserve">Drop-in type for adding parts after assembly. Found: 100-packs run CAD 8–15.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 32814359094</t>
@@ -2922,13 +2925,19 @@
     <t xml:space="preserve">M4 sliding T-nut</t>
   </si>
   <si>
+    <t xml:space="preserve">Found: 50-packs run CAD 3–6.</t>
+  </si>
+  <si>
     <t xml:space="preserve">M4 hammer-head T-nut</t>
   </si>
   <si>
+    <t xml:space="preserve">Found: 50-packs run CAD 4–8.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Socket-head bolt kit (author's list)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick the sizes from the list; 304 DIN912. Or an assorted M4/M5 kit on Amazon.ca.</t>
+    <t xml:space="preserve">Pick the sizes from the list; 304 DIN912. Or an assorted M4/M5 kit on Amazon.ca. Found: Full set per the author's list from HZYUEGOU 304 DIN912 bags (10,000+ sold).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 32968483467</t>
@@ -2946,7 +2955,7 @@
     <t xml:space="preserve">Linear rails</t>
   </si>
   <si>
-    <t xml:space="preserve">Y scaled to 750 mm travel: 600 + 400. Buy as a 2-rail + 4-block set.</t>
+    <t xml:space="preserve">Y scaled to 750 mm travel: 600 + 400. Buy as a 2-rail + 4-block set. Found: 2-rail + 4-block 1000 mm sets run CAD 140–190; single rail + 1 block listing from 13.84 (100 mm).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005004825209262</t>
@@ -2958,13 +2967,13 @@
     <t xml:space="preserve">HGR15 linear rail 600 mm + 2 HGH15CA blocks (X)</t>
   </si>
   <si>
-    <t xml:space="preserve">Same listing, 600 mm option.</t>
+    <t xml:space="preserve">Same listing, 600 mm option. Found: Same set listing, 600 mm option.</t>
   </si>
   <si>
     <t xml:space="preserve">HGR15 linear rail 300 mm + 2 HGH15CA blocks (Z)</t>
   </si>
   <si>
-    <t xml:space="preserve">Same listing, 300 mm option; fixed-length alt 1005012673253692.</t>
+    <t xml:space="preserve">Same listing, 300 mm option; fixed-length alt 1005012673253692. Found: Fixed-length: 2 rails + 4 blocks 200–300 mm at 119.93; 300 mm rail + block at 76.99.</t>
   </si>
   <si>
     <t xml:space="preserve">SFU1605 ballscrew 900 mm, flange nut, ends machined (Y)</t>
@@ -2973,7 +2982,7 @@
     <t xml:space="preserve">Ballscrews</t>
   </si>
   <si>
-    <t xml:space="preserve">C7 rolled. Y = 500 + 400. Check critical speed for 900 mm (author's note).</t>
+    <t xml:space="preserve">C7 rolled. Y = 500 + 400. Check critical speed for 900 mm (author's note). Found: 200–1000 mm listing from 16.08 (short length); 600 mm screw alone seen at 56.68.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005007791178337</t>
@@ -2985,10 +2994,13 @@
     <t xml:space="preserve">SFU1605 ballscrew 600 mm, flange nut, ends machined (X)</t>
   </si>
   <si>
+    <t xml:space="preserve">Found: 600 mm C7 screw-only fixed listing 56.68 (4 sold); with nut 45–65.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SFU1605 ballscrew 300 mm, flange nut, ends machined (Z)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixed-length listing with 105 orders.</t>
+    <t xml:space="preserve">Fixed-length listing with 105 orders. Found: Fixed 300 mm with nut: 38.99 (105 sold, 5 stars) and 37.58.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 32995243964</t>
@@ -3003,7 +3015,7 @@
     <t xml:space="preserve">Bearing blocks</t>
   </si>
   <si>
-    <t xml:space="preserve">One pair per printed ballscrew bearing block.</t>
+    <t xml:space="preserve">One pair per printed ballscrew bearing block. Found: MOCHU 7001AC P5 DFA pair 24.99; cheaper pair listing from 10.58.</t>
   </si>
   <si>
     <t xml:space="preserve">pair</t>
@@ -3021,7 +3033,7 @@
     <t xml:space="preserve">6000-2RS bearing (10x26x8)</t>
   </si>
   <si>
-    <t xml:space="preserve">Floating-end bearings.</t>
+    <t xml:space="preserve">Floating-end bearings. Found: 10-pack 20.79 = 2.08 each; NSK 2-pack from 1.44.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005006093979302</t>
@@ -3036,7 +3048,7 @@
     <t xml:space="preserve">M12x1 locknut (ballscrew end)</t>
   </si>
   <si>
-    <t xml:space="preserve">BK12 lock nut listing; M12x1 for the 1605 screw end.</t>
+    <t xml:space="preserve">BK12 lock nut listing; M12x1 for the 1605 screw end. Found: BK/BF locknut listing from 1.73 (500+ sold).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 4000909595284</t>
@@ -3054,7 +3066,7 @@
     <t xml:space="preserve">Drive</t>
   </si>
   <si>
-    <t xml:space="preserve">Motor shaft 8 mm → screw end 10 mm.</t>
+    <t xml:space="preserve">Motor shaft 8 mm → screw end 10 mm. Found: D19 x L25 jaw coupling listing shows a teaser price; 2.50–4.00 each is typical.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005007121900242</t>
@@ -3099,7 +3111,7 @@
     <t xml:space="preserve">CNC Shield V3 (shield only, no stepsticks)</t>
   </si>
   <si>
-    <t xml:space="preserve">TB6600 step/dir wired to the shield's driver sockets.</t>
+    <t xml:space="preserve">TB6600 step/dir wired to the shield's driver sockets. Found: Shield-only 4–6; shield + driver kit 8.69 (71 sold).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005006478108991</t>
@@ -3117,7 +3129,7 @@
     <t xml:space="preserve">Switches</t>
   </si>
   <si>
-    <t xml:space="preserve">2 per axis. 5-packs.</t>
+    <t xml:space="preserve">2 per axis. 5-packs. Found: 5-pack endstops 5.35 = 1.07 each; ME-8108 roller 5-pack 21.02 = 4.20 each.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005001599112235</t>
@@ -3132,7 +3144,7 @@
     <t xml:space="preserve">E-stop button, NC</t>
   </si>
   <si>
-    <t xml:space="preserve">22 mm metal, 2NO 2NC, latching.</t>
+    <t xml:space="preserve">22 mm metal, 2NO 2NC, latching. Found: 22 mm metal 2NO/2NC 5.89 (4,000+ sold); 2.48 (3,000+).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005001806206333</t>
@@ -3150,7 +3162,7 @@
     <t xml:space="preserve">Wiring</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick the 4-core 22AWG shielded option. Author used double-shielded; ground the shield at the box only.</t>
+    <t xml:space="preserve">Pick the 4-core 22AWG shielded option. Author used double-shielded; ground the shield at the box only. Found: 24AWG shielded multi-core listing from 1.44/m teaser; 1–2 per m typical.</t>
   </si>
   <si>
     <t xml:space="preserve">m</t>
@@ -3168,7 +3180,7 @@
     <t xml:space="preserve">Shielded 2-wire cable, limit switches</t>
   </si>
   <si>
-    <t xml:space="preserve">Same listing, 2-core 24AWG shielded.</t>
+    <t xml:space="preserve">Same listing, 2-core 24AWG shielded. Found: Same listing, 2-core option.</t>
   </si>
   <si>
     <t xml:space="preserve">C27</t>
@@ -3177,7 +3189,7 @@
     <t xml:space="preserve">Drag chain 10x20 + end mounts</t>
   </si>
   <si>
-    <t xml:space="preserve">Open bridge type, 10x20, 1 m lengths. X and Y runs.</t>
+    <t xml:space="preserve">Open bridge type, 10x20, 1 m lengths. X and Y runs. Found: 10x20 open bridge 1 m 4.45 (1,000+); 3.50 (4,000+).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005001795469984</t>
@@ -3192,7 +3204,7 @@
     <t xml:space="preserve">Terminal blocks, ferrules, USB cable, hookup wire</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratchet ferrule crimper + ferrule kit. Terminal strips and USB cable from Amazon.ca.</t>
+    <t xml:space="preserve">Ratchet ferrule crimper + ferrule kit. Terminal strips and USB cable from Amazon.ca. Found: Ratchet ferrule crimper + ferrule kit 17.39 (10,000+ sold); terminal strips ~10 extra.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005007097035466</t>
@@ -3210,7 +3222,7 @@
     <t xml:space="preserve">Control box</t>
   </si>
   <si>
-    <t xml:space="preserve">Author's metal enclosure + GX16 connectors cost ~US$500; a plywood panel does the job.</t>
+    <t xml:space="preserve">Author's metal enclosure + GX16 connectors cost ~US$500; a plywood panel does the job. Found: Plywood offcut.</t>
   </si>
   <si>
     <t xml:space="preserve">Home Depot</t>
@@ -3225,7 +3237,7 @@
     <t xml:space="preserve">12 V fan + DC-DC converter for the box</t>
   </si>
   <si>
-    <t xml:space="preserve">36 V → 12 V 3 A buck module. Add any 80 mm 12 V fan. Only if the drivers go in a closed box.</t>
+    <t xml:space="preserve">36 V → 12 V 3 A buck module. Add any 80 mm 12 V fan. Only if the drivers go in a closed box. Found: 36→12 V buck 3–6 (5,000+ sold) + 80 mm fan 5–8.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005007181838501</t>
@@ -3240,7 +3252,7 @@
     <t xml:space="preserve">Ethernet CNC controller (grblHAL Teensy 4.1 + breakout) — EMI fix</t>
   </si>
   <si>
-    <t xml:space="preserve">Author could not fully stop USB/EMI false alarms on Arduino+GRBL. Ethernet upgrade path, not needed to start.</t>
+    <t xml:space="preserve">Author could not fully stop USB/EMI false alarms on Arduino+GRBL. Ethernet upgrade path, not needed to start. Found: Teensy 4.1 ~US$32 + grblHAL breakout ~US$40–60.</t>
   </si>
   <si>
     <t xml:space="preserve">grblHAL Teensy 4.1 breakout (PCBWay) + Teensy 4.1 (pjrc.com)</t>
@@ -3261,7 +3273,7 @@
     <t xml:space="preserve">Router</t>
   </si>
   <si>
-    <t xml:space="preserve">New vs used vs 65 mm clone. Bare RT0701C is the one to buy; the CX7 kit (B00HAQMHEO) adds bases you don't need. The printed mount is sized for the 65 mm Makita body; the Craftsman does not fit.</t>
+    <t xml:space="preserve">New vs used vs 65 mm clone. Bare RT0701C is the one to buy; the CX7 kit (B00HAQMHEO) adds bases you don't need. The printed mount is sized for the 65 mm Makita body; the Craftsman does not fit. Found: Used 80–120; new bare RT0701C ~150–170 at Home Depot.ca; Amazon CX7 kit 292.92 is more than you need.</t>
   </si>
   <si>
     <t xml:space="preserve">Amazon B00E7D3V4S (bare tool) / Home Depot.ca</t>
@@ -3276,7 +3288,7 @@
     <t xml:space="preserve">6 mm collet for RT0701C</t>
   </si>
   <si>
-    <t xml:space="preserve">Router ships with the 1/4 in cone (763637-1) only. Buy the genuine 6 mm cone, not a sleeve adapter (adds runout).</t>
+    <t xml:space="preserve">Router ships with the 1/4 in cone (763637-1) only. Buy the genuine 6 mm cone, not a sleeve adapter (adds runout). Found: Genuine Makita 6 mm cone.</t>
   </si>
   <si>
     <t xml:space="preserve">Amazon.ca search; Makita part 763636-3 (verify)</t>
@@ -3294,7 +3306,7 @@
     <t xml:space="preserve">Upgrade</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2 kW ER20 air-cooled 80 mm round + VFD. Water-cooled kit with clamp: 1005003968400625. Author moved to a 2.2 kW VFD spindle for runout; do this before the gearbox adapter plate.</t>
+    <t xml:space="preserve">2.2 kW ER20 air-cooled 80 mm round + VFD. Water-cooled kit with clamp: 1005003968400625. Author moved to a 2.2 kW VFD spindle for runout; do this before the gearbox adapter plate. Found: 2.2 kW ER20 air-cooled + VFD 238.68 (33 sold); water-cooled kit with clamp 266.99 (43 sold).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005008081995923</t>
@@ -3309,7 +3321,7 @@
     <t xml:space="preserve">80 mm spindle mount (if VFD spindle)</t>
   </si>
   <si>
-    <t xml:space="preserve">80 mm clamp if you'd rather buy it than machine it.</t>
+    <t xml:space="preserve">80 mm clamp if you'd rather buy it than machine it. Found: 80 mm clamp 16.38 (137 sold) to 23.38 (283 sold).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005009168636967</t>
@@ -3339,7 +3351,7 @@
     <t xml:space="preserve">Files</t>
   </si>
   <si>
-    <t xml:space="preserve">Onshape model is free to view; files are paid.</t>
+    <t xml:space="preserve">Onshape model is free to view; files are paid. Found: Cults3D price not fetched (blocked); the author's other projects sell for US$10–25.</t>
   </si>
   <si>
     <t xml:space="preserve">Cults3D</t>
@@ -3360,7 +3372,7 @@
     <t xml:space="preserve">Workholding</t>
   </si>
   <si>
-    <t xml:space="preserve">Surface it with the machine once running.</t>
+    <t xml:space="preserve">Surface it with the machine once running. Found: Half sheet / offcut 25–35; full 4x8 3/4 in MDF 45–60 at Home Depot.</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.homedepot.ca/search?q=mdf%203%2F4</t>
@@ -3372,7 +3384,7 @@
     <t xml:space="preserve">Threaded inserts M6 (or T-track) for hold-downs</t>
   </si>
   <si>
-    <t xml:space="preserve">M6 hex-drive wood inserts, 100-pack.</t>
+    <t xml:space="preserve">M6 hex-drive wood inserts, 100-pack. Found: M6 hex-drive wood inserts 100-pack 10.85 (766 sold).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005011942750737</t>
@@ -3387,7 +3399,7 @@
     <t xml:space="preserve">Clamps / hold-down set</t>
   </si>
   <si>
-    <t xml:space="preserve">Arc press-plate clamps. Print the first set; machine aluminum ones later.</t>
+    <t xml:space="preserve">Arc press-plate clamps. Print the first set; machine aluminum ones later. Found: Arc press-plate clamps 0.70 each (314 sold); set of 4–6 with bolts 10–25.</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005005244930679</t>
@@ -3408,7 +3420,7 @@
     <t xml:space="preserve">Cutters</t>
   </si>
   <si>
-    <t xml:space="preserve">Roughing + profiling the flanges and adapter.</t>
+    <t xml:space="preserve">Roughing + profiling the flanges and adapter. Found: Single-flute 6 mm 5.55 (10,000+ sold); Dreanique 6 mm shank 17.09 (1,000+).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005001948417279</t>
@@ -3423,7 +3435,7 @@
     <t xml:space="preserve">Single-flute carbide endmill, 3 mm or 1/8 in</t>
   </si>
   <si>
-    <t xml:space="preserve">Small features, bung holes.</t>
+    <t xml:space="preserve">Small features, bung holes. Found: Same listing, 3–4 mm sizes; DLC-coated 8.19 (308 sold).</t>
   </si>
   <si>
     <t xml:space="preserve">C43</t>
@@ -3435,7 +3447,7 @@
     <t xml:space="preserve">Setup</t>
   </si>
   <si>
-    <t xml:space="preserve">0.01 mm indicator with flexible magnetic base. Tramming, squareness, collet runout. Mark Have if you own one.</t>
+    <t xml:space="preserve">0.01 mm indicator with flexible magnetic base. Tramming, squareness, collet runout. Mark Have if you own one. Found: 0.01 mm indicator set with flexible base 19.46 (1,000+, 4.9); magnetic stand set 22.79 (2,000+).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005007169855682</t>
@@ -3450,6 +3462,9 @@
     <t xml:space="preserve">Z touch plate / probe</t>
   </si>
   <si>
+    <t xml:space="preserve">Found: Z touch plate 5.39 (1,000+) to 7.79.</t>
+  </si>
+  <si>
     <t xml:space="preserve">AliExpress 1005008660120770</t>
   </si>
   <si>
@@ -3462,7 +3477,7 @@
     <t xml:space="preserve">Air blast or mist setup (isopropyl / WD-40) for aluminum</t>
   </si>
   <si>
-    <t xml:space="preserve">Pneumatic mist sprayer, magnetic base. Stops chip welding on the single-flute cutters.</t>
+    <t xml:space="preserve">Pneumatic mist sprayer, magnetic base. Stops chip welding on the single-flute cutters. Found: Pneumatic mist sprayer with magnetic base 11.78 (1,000+ sold).</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress 1005008490356061</t>
@@ -3483,7 +3498,7 @@
     <t xml:space="preserve">Consumables</t>
   </si>
   <si>
-    <t xml:space="preserve">NLGI 2 lithium grease for rails and screws; zip ties and heat shrink from the same order.</t>
+    <t xml:space="preserve">NLGI 2 lithium grease for rails and screws; zip ties and heat shrink from the same order. Found: Lithium grease 8–12 + zip ties / heat shrink.</t>
   </si>
   <si>
     <t xml:space="preserve">Amazon.ca / Canadian Tire</t>
@@ -3853,7 +3868,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3970,14 +3985,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBE5E5"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5214,15 +5221,15 @@
       </c>
       <c r="C70" s="12" t="n">
         <f aca="false">SUM(CNC!$U$5:$U$50)</f>
-        <v>349.98</v>
+        <v>1252.25</v>
       </c>
       <c r="D70" s="12" t="n">
         <f aca="false">SUM(CNC!$V$5:$V$50)</f>
-        <v>349.98</v>
+        <v>1900.05</v>
       </c>
       <c r="E70" s="12" t="n">
         <f aca="false">SUM(CNC!$I$5:$I$50)</f>
-        <v>349.98</v>
+        <v>1576.15</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5248,15 +5255,15 @@
       </c>
       <c r="C72" s="12" t="n">
         <f aca="false">C70-C71</f>
-        <v>0</v>
+        <v>902.27</v>
       </c>
       <c r="D72" s="12" t="n">
         <f aca="false">D70-D71</f>
-        <v>0</v>
+        <v>1550.07</v>
       </c>
       <c r="E72" s="12" t="n">
         <f aca="false">E70-E71</f>
-        <v>0</v>
+        <v>1226.17</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5265,15 +5272,15 @@
       </c>
       <c r="C73" s="12" t="n">
         <f aca="false">C72*$C$10</f>
-        <v>0</v>
+        <v>225.5675</v>
       </c>
       <c r="D73" s="12" t="n">
         <f aca="false">D72*$C$10</f>
-        <v>0</v>
+        <v>387.5175</v>
       </c>
       <c r="E73" s="12" t="n">
         <f aca="false">E72*$C$10</f>
-        <v>0</v>
+        <v>306.5425</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5282,15 +5289,15 @@
       </c>
       <c r="C74" s="12" t="n">
         <f aca="false">C70+C73</f>
-        <v>349.98</v>
+        <v>1477.8175</v>
       </c>
       <c r="D74" s="12" t="n">
         <f aca="false">D70+D73</f>
-        <v>349.98</v>
+        <v>2287.5675</v>
       </c>
       <c r="E74" s="12" t="n">
         <f aca="false">E70+E73</f>
-        <v>349.98</v>
+        <v>1882.6925</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5331,7 +5338,7 @@
       </c>
       <c r="C80" s="3" t="n">
         <f aca="false">COUNTIFS(CNC!$K$5:$K$50,"Y",CNC!$F$5:$F$50,"&lt;&gt;Y",CNC!$H$5:$H$50,"",CNC!$D$5:$D$50,"",CNC!$E$5:$E$50,"")</f>
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22699,20 +22706,20 @@
   <dimension ref="A1:X51"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="12" min="12" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="23" min="13" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="12" min="12" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="23" min="13" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22961,8 +22968,12 @@
       <c r="C7" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
+      <c r="D7" s="21" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>1</v>
+      </c>
       <c r="F7" s="20" t="s">
         <v>101</v>
       </c>
@@ -22972,7 +22983,7 @@
       <c r="H7" s="22"/>
       <c r="I7" s="23" t="n">
         <f aca="false">IF(AND($K7="Y",$F7&lt;&gt;"Y",OR($T7="",$T7=Summary!$C$11)),$C7*IF($H7&lt;&gt;"",$H7,($D7+$E7)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P7,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>13.59</v>
       </c>
       <c r="J7" s="20" t="s">
         <v>102</v>
@@ -23007,17 +23018,17 @@
       <c r="T7" s="18"/>
       <c r="U7" s="25" t="n">
         <f aca="false">IF(AND($K7="Y",$F7&lt;&gt;"Y",OR($T7="",$T7=Summary!$C$11)),$C7*IF($H7&lt;&gt;"",$H7,$D7)*INDEX(Summary!$C$6:$C$8,MATCH($P7,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>9.18</v>
       </c>
       <c r="V7" s="25" t="n">
         <f aca="false">IF(AND($K7="Y",$F7&lt;&gt;"Y",OR($T7="",$T7=Summary!$C$11)),$C7*IF($H7&lt;&gt;"",$H7,$E7)*INDEX(Summary!$C$6:$C$8,MATCH($P7,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W7" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X7" s="26" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23025,13 +23036,17 @@
         <v>783</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
+      <c r="D8" s="21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0.8</v>
+      </c>
       <c r="F8" s="20" t="s">
         <v>101</v>
       </c>
@@ -23041,7 +23056,7 @@
       <c r="H8" s="22"/>
       <c r="I8" s="23" t="n">
         <f aca="false">IF(AND($K8="Y",$F8&lt;&gt;"Y",OR($T8="",$T8=Summary!$C$11)),$C8*IF($H8&lt;&gt;"",$H8,($D8+$E8)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P8,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J8" s="20" t="s">
         <v>102</v>
@@ -23056,7 +23071,7 @@
         <v>856</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="O8" s="18" t="s">
         <v>106</v>
@@ -23068,7 +23083,7 @@
         <v>44</v>
       </c>
       <c r="R8" s="24" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="S8" s="18" t="s">
         <v>922</v>
@@ -23076,17 +23091,17 @@
       <c r="T8" s="18"/>
       <c r="U8" s="25" t="n">
         <f aca="false">IF(AND($K8="Y",$F8&lt;&gt;"Y",OR($T8="",$T8=Summary!$C$11)),$C8*IF($H8&lt;&gt;"",$H8,$D8)*INDEX(Summary!$C$6:$C$8,MATCH($P8,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V8" s="25" t="n">
         <f aca="false">IF(AND($K8="Y",$F8&lt;&gt;"Y",OR($T8="",$T8=Summary!$C$11)),$C8*IF($H8&lt;&gt;"",$H8,$E8)*INDEX(Summary!$C$6:$C$8,MATCH($P8,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W8" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X8" s="26" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23094,13 +23109,17 @@
         <v>787</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
+      <c r="D9" s="21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>0.12</v>
+      </c>
       <c r="F9" s="20" t="s">
         <v>101</v>
       </c>
@@ -23110,7 +23129,7 @@
       <c r="H9" s="22"/>
       <c r="I9" s="23" t="n">
         <f aca="false">IF(AND($K9="Y",$F9&lt;&gt;"Y",OR($T9="",$T9=Summary!$C$11)),$C9*IF($H9&lt;&gt;"",$H9,($D9+$E9)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P9,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J9" s="20" t="s">
         <v>102</v>
@@ -23125,7 +23144,7 @@
         <v>856</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="O9" s="18" t="s">
         <v>106</v>
@@ -23137,7 +23156,7 @@
         <v>44</v>
       </c>
       <c r="R9" s="24" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="S9" s="18" t="s">
         <v>922</v>
@@ -23145,17 +23164,17 @@
       <c r="T9" s="18"/>
       <c r="U9" s="25" t="n">
         <f aca="false">IF(AND($K9="Y",$F9&lt;&gt;"Y",OR($T9="",$T9=Summary!$C$11)),$C9*IF($H9&lt;&gt;"",$H9,$D9)*INDEX(Summary!$C$6:$C$8,MATCH($P9,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V9" s="25" t="n">
         <f aca="false">IF(AND($K9="Y",$F9&lt;&gt;"Y",OR($T9="",$T9=Summary!$C$11)),$C9*IF($H9&lt;&gt;"",$H9,$E9)*INDEX(Summary!$C$6:$C$8,MATCH($P9,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W9" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X9" s="26" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23163,13 +23182,17 @@
         <v>789</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
+      <c r="D10" s="21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>0.15</v>
+      </c>
       <c r="F10" s="20" t="s">
         <v>101</v>
       </c>
@@ -23179,7 +23202,7 @@
       <c r="H10" s="22"/>
       <c r="I10" s="23" t="n">
         <f aca="false">IF(AND($K10="Y",$F10&lt;&gt;"Y",OR($T10="",$T10=Summary!$C$11)),$C10*IF($H10&lt;&gt;"",$H10,($D10+$E10)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P10,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="J10" s="20" t="s">
         <v>102</v>
@@ -23194,7 +23217,7 @@
         <v>856</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="O10" s="18" t="s">
         <v>106</v>
@@ -23206,7 +23229,7 @@
         <v>44</v>
       </c>
       <c r="R10" s="24" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="S10" s="18" t="s">
         <v>922</v>
@@ -23214,17 +23237,17 @@
       <c r="T10" s="18"/>
       <c r="U10" s="25" t="n">
         <f aca="false">IF(AND($K10="Y",$F10&lt;&gt;"Y",OR($T10="",$T10=Summary!$C$11)),$C10*IF($H10&lt;&gt;"",$H10,$D10)*INDEX(Summary!$C$6:$C$8,MATCH($P10,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V10" s="25" t="n">
         <f aca="false">IF(AND($K10="Y",$F10&lt;&gt;"Y",OR($T10="",$T10=Summary!$C$11)),$C10*IF($H10&lt;&gt;"",$H10,$E10)*INDEX(Summary!$C$6:$C$8,MATCH($P10,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W10" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X10" s="26" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23232,13 +23255,17 @@
         <v>791</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
+      <c r="D11" s="21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0.12</v>
+      </c>
       <c r="F11" s="20" t="s">
         <v>101</v>
       </c>
@@ -23248,7 +23275,7 @@
       <c r="H11" s="22"/>
       <c r="I11" s="23" t="n">
         <f aca="false">IF(AND($K11="Y",$F11&lt;&gt;"Y",OR($T11="",$T11=Summary!$C$11)),$C11*IF($H11&lt;&gt;"",$H11,($D11+$E11)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P11,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J11" s="20" t="s">
         <v>102</v>
@@ -23262,7 +23289,9 @@
       <c r="M11" s="24" t="s">
         <v>856</v>
       </c>
-      <c r="N11" s="19"/>
+      <c r="N11" s="19" t="s">
+        <v>946</v>
+      </c>
       <c r="O11" s="18" t="s">
         <v>106</v>
       </c>
@@ -23273,7 +23302,7 @@
         <v>44</v>
       </c>
       <c r="R11" s="24" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="S11" s="18" t="s">
         <v>922</v>
@@ -23281,17 +23310,17 @@
       <c r="T11" s="18"/>
       <c r="U11" s="25" t="n">
         <f aca="false">IF(AND($K11="Y",$F11&lt;&gt;"Y",OR($T11="",$T11=Summary!$C$11)),$C11*IF($H11&lt;&gt;"",$H11,$D11)*INDEX(Summary!$C$6:$C$8,MATCH($P11,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" s="25" t="n">
         <f aca="false">IF(AND($K11="Y",$F11&lt;&gt;"Y",OR($T11="",$T11=Summary!$C$11)),$C11*IF($H11&lt;&gt;"",$H11,$E11)*INDEX(Summary!$C$6:$C$8,MATCH($P11,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X11" s="26" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23299,13 +23328,17 @@
         <v>793</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="D12" s="21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0.15</v>
+      </c>
       <c r="F12" s="20" t="s">
         <v>101</v>
       </c>
@@ -23315,7 +23348,7 @@
       <c r="H12" s="22"/>
       <c r="I12" s="23" t="n">
         <f aca="false">IF(AND($K12="Y",$F12&lt;&gt;"Y",OR($T12="",$T12=Summary!$C$11)),$C12*IF($H12&lt;&gt;"",$H12,($D12+$E12)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P12,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="J12" s="20" t="s">
         <v>102</v>
@@ -23329,7 +23362,9 @@
       <c r="M12" s="24" t="s">
         <v>856</v>
       </c>
-      <c r="N12" s="19"/>
+      <c r="N12" s="19" t="s">
+        <v>948</v>
+      </c>
       <c r="O12" s="18" t="s">
         <v>106</v>
       </c>
@@ -23340,7 +23375,7 @@
         <v>44</v>
       </c>
       <c r="R12" s="24" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="S12" s="18" t="s">
         <v>922</v>
@@ -23348,17 +23383,17 @@
       <c r="T12" s="18"/>
       <c r="U12" s="25" t="n">
         <f aca="false">IF(AND($K12="Y",$F12&lt;&gt;"Y",OR($T12="",$T12=Summary!$C$11)),$C12*IF($H12&lt;&gt;"",$H12,$D12)*INDEX(Summary!$C$6:$C$8,MATCH($P12,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" s="25" t="n">
         <f aca="false">IF(AND($K12="Y",$F12&lt;&gt;"Y",OR($T12="",$T12=Summary!$C$11)),$C12*IF($H12&lt;&gt;"",$H12,$E12)*INDEX(Summary!$C$6:$C$8,MATCH($P12,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W12" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X12" s="26" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23366,13 +23401,17 @@
         <v>796</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
+      <c r="D13" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>45</v>
+      </c>
       <c r="F13" s="20" t="s">
         <v>101</v>
       </c>
@@ -23382,7 +23421,7 @@
       <c r="H13" s="22"/>
       <c r="I13" s="23" t="n">
         <f aca="false">IF(AND($K13="Y",$F13&lt;&gt;"Y",OR($T13="",$T13=Summary!$C$11)),$C13*IF($H13&lt;&gt;"",$H13,($D13+$E13)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P13,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>102</v>
@@ -23397,7 +23436,7 @@
         <v>856</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="O13" s="18" t="s">
         <v>160</v>
@@ -23409,7 +23448,7 @@
         <v>44</v>
       </c>
       <c r="R13" s="24" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="S13" s="18" t="s">
         <v>922</v>
@@ -23417,17 +23456,17 @@
       <c r="T13" s="18"/>
       <c r="U13" s="25" t="n">
         <f aca="false">IF(AND($K13="Y",$F13&lt;&gt;"Y",OR($T13="",$T13=Summary!$C$11)),$C13*IF($H13&lt;&gt;"",$H13,$D13)*INDEX(Summary!$C$6:$C$8,MATCH($P13,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V13" s="25" t="n">
         <f aca="false">IF(AND($K13="Y",$F13&lt;&gt;"Y",OR($T13="",$T13=Summary!$C$11)),$C13*IF($H13&lt;&gt;"",$H13,$E13)*INDEX(Summary!$C$6:$C$8,MATCH($P13,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W13" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X13" s="26" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23435,13 +23474,17 @@
         <v>798</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
+      <c r="D14" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>95</v>
+      </c>
       <c r="F14" s="20" t="s">
         <v>101</v>
       </c>
@@ -23451,7 +23494,7 @@
       <c r="H14" s="22"/>
       <c r="I14" s="23" t="n">
         <f aca="false">IF(AND($K14="Y",$F14&lt;&gt;"Y",OR($T14="",$T14=Summary!$C$11)),$C14*IF($H14&lt;&gt;"",$H14,($D14+$E14)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P14,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="J14" s="20" t="s">
         <v>102</v>
@@ -23460,13 +23503,13 @@
         <v>103</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M14" s="24" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="O14" s="18" t="s">
         <v>106</v>
@@ -23478,7 +23521,7 @@
         <v>44</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="S14" s="18" t="s">
         <v>922</v>
@@ -23486,17 +23529,17 @@
       <c r="T14" s="18"/>
       <c r="U14" s="25" t="n">
         <f aca="false">IF(AND($K14="Y",$F14&lt;&gt;"Y",OR($T14="",$T14=Summary!$C$11)),$C14*IF($H14&lt;&gt;"",$H14,$D14)*INDEX(Summary!$C$6:$C$8,MATCH($P14,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="V14" s="25" t="n">
         <f aca="false">IF(AND($K14="Y",$F14&lt;&gt;"Y",OR($T14="",$T14=Summary!$C$11)),$C14*IF($H14&lt;&gt;"",$H14,$E14)*INDEX(Summary!$C$6:$C$8,MATCH($P14,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="W14" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X14" s="26" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23504,13 +23547,17 @@
         <v>802</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C15" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
+      <c r="D15" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>65</v>
+      </c>
       <c r="F15" s="20" t="s">
         <v>101</v>
       </c>
@@ -23520,7 +23567,7 @@
       <c r="H15" s="22"/>
       <c r="I15" s="23" t="n">
         <f aca="false">IF(AND($K15="Y",$F15&lt;&gt;"Y",OR($T15="",$T15=Summary!$C$11)),$C15*IF($H15&lt;&gt;"",$H15,($D15+$E15)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P15,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J15" s="20" t="s">
         <v>102</v>
@@ -23529,13 +23576,13 @@
         <v>103</v>
       </c>
       <c r="L15" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M15" s="24" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="N15" s="19" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="O15" s="18" t="s">
         <v>106</v>
@@ -23547,7 +23594,7 @@
         <v>44</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="S15" s="18" t="s">
         <v>922</v>
@@ -23555,17 +23602,17 @@
       <c r="T15" s="18"/>
       <c r="U15" s="25" t="n">
         <f aca="false">IF(AND($K15="Y",$F15&lt;&gt;"Y",OR($T15="",$T15=Summary!$C$11)),$C15*IF($H15&lt;&gt;"",$H15,$D15)*INDEX(Summary!$C$6:$C$8,MATCH($P15,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V15" s="25" t="n">
         <f aca="false">IF(AND($K15="Y",$F15&lt;&gt;"Y",OR($T15="",$T15=Summary!$C$11)),$C15*IF($H15&lt;&gt;"",$H15,$E15)*INDEX(Summary!$C$6:$C$8,MATCH($P15,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="W15" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X15" s="26" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23573,13 +23620,17 @@
         <v>806</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C16" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
+      <c r="D16" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>60</v>
+      </c>
       <c r="F16" s="20" t="s">
         <v>101</v>
       </c>
@@ -23589,7 +23640,7 @@
       <c r="H16" s="22"/>
       <c r="I16" s="23" t="n">
         <f aca="false">IF(AND($K16="Y",$F16&lt;&gt;"Y",OR($T16="",$T16=Summary!$C$11)),$C16*IF($H16&lt;&gt;"",$H16,($D16+$E16)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P16,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J16" s="20" t="s">
         <v>102</v>
@@ -23598,13 +23649,13 @@
         <v>103</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M16" s="24" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="O16" s="18" t="s">
         <v>106</v>
@@ -23616,7 +23667,7 @@
         <v>44</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="S16" s="18" t="s">
         <v>922</v>
@@ -23624,17 +23675,17 @@
       <c r="T16" s="18"/>
       <c r="U16" s="25" t="n">
         <f aca="false">IF(AND($K16="Y",$F16&lt;&gt;"Y",OR($T16="",$T16=Summary!$C$11)),$C16*IF($H16&lt;&gt;"",$H16,$D16)*INDEX(Summary!$C$6:$C$8,MATCH($P16,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V16" s="25" t="n">
         <f aca="false">IF(AND($K16="Y",$F16&lt;&gt;"Y",OR($T16="",$T16=Summary!$C$11)),$C16*IF($H16&lt;&gt;"",$H16,$E16)*INDEX(Summary!$C$6:$C$8,MATCH($P16,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="W16" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X16" s="26" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23642,13 +23693,17 @@
         <v>808</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C17" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="D17" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>80</v>
+      </c>
       <c r="F17" s="20" t="s">
         <v>101</v>
       </c>
@@ -23658,7 +23713,7 @@
       <c r="H17" s="22"/>
       <c r="I17" s="23" t="n">
         <f aca="false">IF(AND($K17="Y",$F17&lt;&gt;"Y",OR($T17="",$T17=Summary!$C$11)),$C17*IF($H17&lt;&gt;"",$H17,($D17+$E17)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P17,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="J17" s="20" t="s">
         <v>102</v>
@@ -23667,13 +23722,13 @@
         <v>103</v>
       </c>
       <c r="L17" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M17" s="24" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="N17" s="19" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="O17" s="18" t="s">
         <v>106</v>
@@ -23685,7 +23740,7 @@
         <v>44</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="S17" s="18" t="s">
         <v>922</v>
@@ -23693,17 +23748,17 @@
       <c r="T17" s="18"/>
       <c r="U17" s="25" t="n">
         <f aca="false">IF(AND($K17="Y",$F17&lt;&gt;"Y",OR($T17="",$T17=Summary!$C$11)),$C17*IF($H17&lt;&gt;"",$H17,$D17)*INDEX(Summary!$C$6:$C$8,MATCH($P17,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="V17" s="25" t="n">
         <f aca="false">IF(AND($K17="Y",$F17&lt;&gt;"Y",OR($T17="",$T17=Summary!$C$11)),$C17*IF($H17&lt;&gt;"",$H17,$E17)*INDEX(Summary!$C$6:$C$8,MATCH($P17,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="W17" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X17" s="26" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23711,13 +23766,17 @@
         <v>813</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C18" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="D18" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>65</v>
+      </c>
       <c r="F18" s="20" t="s">
         <v>101</v>
       </c>
@@ -23727,7 +23786,7 @@
       <c r="H18" s="22"/>
       <c r="I18" s="23" t="n">
         <f aca="false">IF(AND($K18="Y",$F18&lt;&gt;"Y",OR($T18="",$T18=Summary!$C$11)),$C18*IF($H18&lt;&gt;"",$H18,($D18+$E18)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P18,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J18" s="20" t="s">
         <v>102</v>
@@ -23736,12 +23795,14 @@
         <v>103</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>961</v>
-      </c>
-      <c r="N18" s="19"/>
+        <v>964</v>
+      </c>
+      <c r="N18" s="19" t="s">
+        <v>969</v>
+      </c>
       <c r="O18" s="18" t="s">
         <v>106</v>
       </c>
@@ -23752,7 +23813,7 @@
         <v>44</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="S18" s="18" t="s">
         <v>922</v>
@@ -23760,17 +23821,17 @@
       <c r="T18" s="18"/>
       <c r="U18" s="25" t="n">
         <f aca="false">IF(AND($K18="Y",$F18&lt;&gt;"Y",OR($T18="",$T18=Summary!$C$11)),$C18*IF($H18&lt;&gt;"",$H18,$D18)*INDEX(Summary!$C$6:$C$8,MATCH($P18,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="V18" s="25" t="n">
         <f aca="false">IF(AND($K18="Y",$F18&lt;&gt;"Y",OR($T18="",$T18=Summary!$C$11)),$C18*IF($H18&lt;&gt;"",$H18,$E18)*INDEX(Summary!$C$6:$C$8,MATCH($P18,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="W18" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X18" s="26" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23778,13 +23839,17 @@
         <v>816</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="C19" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
+      <c r="D19" s="21" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>38.99</v>
+      </c>
       <c r="F19" s="20" t="s">
         <v>101</v>
       </c>
@@ -23794,7 +23859,7 @@
       <c r="H19" s="22"/>
       <c r="I19" s="23" t="n">
         <f aca="false">IF(AND($K19="Y",$F19&lt;&gt;"Y",OR($T19="",$T19=Summary!$C$11)),$C19*IF($H19&lt;&gt;"",$H19,($D19+$E19)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P19,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>38.285</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>102</v>
@@ -23803,13 +23868,13 @@
         <v>103</v>
       </c>
       <c r="L19" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M19" s="24" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="N19" s="19" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="O19" s="18" t="s">
         <v>106</v>
@@ -23821,7 +23886,7 @@
         <v>44</v>
       </c>
       <c r="R19" s="24" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="S19" s="18" t="s">
         <v>922</v>
@@ -23829,17 +23894,17 @@
       <c r="T19" s="18"/>
       <c r="U19" s="25" t="n">
         <f aca="false">IF(AND($K19="Y",$F19&lt;&gt;"Y",OR($T19="",$T19=Summary!$C$11)),$C19*IF($H19&lt;&gt;"",$H19,$D19)*INDEX(Summary!$C$6:$C$8,MATCH($P19,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>37.58</v>
       </c>
       <c r="V19" s="25" t="n">
         <f aca="false">IF(AND($K19="Y",$F19&lt;&gt;"Y",OR($T19="",$T19=Summary!$C$11)),$C19*IF($H19&lt;&gt;"",$H19,$E19)*INDEX(Summary!$C$6:$C$8,MATCH($P19,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>38.99</v>
       </c>
       <c r="W19" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X19" s="26" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23847,13 +23912,17 @@
         <v>818</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="C20" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
+      <c r="D20" s="21" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>24.99</v>
+      </c>
       <c r="F20" s="20" t="s">
         <v>101</v>
       </c>
@@ -23863,7 +23932,7 @@
       <c r="H20" s="22"/>
       <c r="I20" s="23" t="n">
         <f aca="false">IF(AND($K20="Y",$F20&lt;&gt;"Y",OR($T20="",$T20=Summary!$C$11)),$C20*IF($H20&lt;&gt;"",$H20,($D20+$E20)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P20,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>71.14</v>
       </c>
       <c r="J20" s="20" t="s">
         <v>102</v>
@@ -23872,16 +23941,16 @@
         <v>103</v>
       </c>
       <c r="L20" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M20" s="24" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="N20" s="19" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="P20" s="20" t="s">
         <v>6</v>
@@ -23890,7 +23959,7 @@
         <v>44</v>
       </c>
       <c r="R20" s="24" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="S20" s="18" t="s">
         <v>922</v>
@@ -23898,31 +23967,35 @@
       <c r="T20" s="18"/>
       <c r="U20" s="25" t="n">
         <f aca="false">IF(AND($K20="Y",$F20&lt;&gt;"Y",OR($T20="",$T20=Summary!$C$11)),$C20*IF($H20&lt;&gt;"",$H20,$D20)*INDEX(Summary!$C$6:$C$8,MATCH($P20,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>42.32</v>
       </c>
       <c r="V20" s="25" t="n">
         <f aca="false">IF(AND($K20="Y",$F20&lt;&gt;"Y",OR($T20="",$T20=Summary!$C$11)),$C20*IF($H20&lt;&gt;"",$H20,$E20)*INDEX(Summary!$C$6:$C$8,MATCH($P20,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>99.96</v>
       </c>
       <c r="W20" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X20" s="26" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C21" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
+      <c r="D21" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>2.1</v>
+      </c>
       <c r="F21" s="20" t="s">
         <v>101</v>
       </c>
@@ -23932,7 +24005,7 @@
       <c r="H21" s="22"/>
       <c r="I21" s="23" t="n">
         <f aca="false">IF(AND($K21="Y",$F21&lt;&gt;"Y",OR($T21="",$T21=Summary!$C$11)),$C21*IF($H21&lt;&gt;"",$H21,($D21+$E21)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P21,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>102</v>
@@ -23941,13 +24014,13 @@
         <v>103</v>
       </c>
       <c r="L21" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M21" s="24" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="N21" s="19" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="O21" s="18" t="s">
         <v>106</v>
@@ -23959,7 +24032,7 @@
         <v>44</v>
       </c>
       <c r="R21" s="24" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="S21" s="18" t="s">
         <v>922</v>
@@ -23967,31 +24040,35 @@
       <c r="T21" s="18"/>
       <c r="U21" s="25" t="n">
         <f aca="false">IF(AND($K21="Y",$F21&lt;&gt;"Y",OR($T21="",$T21=Summary!$C$11)),$C21*IF($H21&lt;&gt;"",$H21,$D21)*INDEX(Summary!$C$6:$C$8,MATCH($P21,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V21" s="25" t="n">
         <f aca="false">IF(AND($K21="Y",$F21&lt;&gt;"Y",OR($T21="",$T21=Summary!$C$11)),$C21*IF($H21&lt;&gt;"",$H21,$E21)*INDEX(Summary!$C$6:$C$8,MATCH($P21,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W21" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X21" s="26" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="C22" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
+      <c r="D22" s="21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="F22" s="20" t="s">
         <v>101</v>
       </c>
@@ -24001,7 +24078,7 @@
       <c r="H22" s="22"/>
       <c r="I22" s="23" t="n">
         <f aca="false">IF(AND($K22="Y",$F22&lt;&gt;"Y",OR($T22="",$T22=Summary!$C$11)),$C22*IF($H22&lt;&gt;"",$H22,($D22+$E22)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P22,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>9.46</v>
       </c>
       <c r="J22" s="20" t="s">
         <v>102</v>
@@ -24010,13 +24087,13 @@
         <v>103</v>
       </c>
       <c r="L22" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="N22" s="19" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="O22" s="18" t="s">
         <v>106</v>
@@ -24028,7 +24105,7 @@
         <v>44</v>
       </c>
       <c r="R22" s="24" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="S22" s="18" t="s">
         <v>922</v>
@@ -24036,31 +24113,35 @@
       <c r="T22" s="18"/>
       <c r="U22" s="25" t="n">
         <f aca="false">IF(AND($K22="Y",$F22&lt;&gt;"Y",OR($T22="",$T22=Summary!$C$11)),$C22*IF($H22&lt;&gt;"",$H22,$D22)*INDEX(Summary!$C$6:$C$8,MATCH($P22,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="V22" s="25" t="n">
         <f aca="false">IF(AND($K22="Y",$F22&lt;&gt;"Y",OR($T22="",$T22=Summary!$C$11)),$C22*IF($H22&lt;&gt;"",$H22,$E22)*INDEX(Summary!$C$6:$C$8,MATCH($P22,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W22" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X22" s="26" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="C23" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
+      <c r="D23" s="21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>4</v>
+      </c>
       <c r="F23" s="20" t="s">
         <v>101</v>
       </c>
@@ -24070,7 +24151,7 @@
       <c r="H23" s="22"/>
       <c r="I23" s="23" t="n">
         <f aca="false">IF(AND($K23="Y",$F23&lt;&gt;"Y",OR($T23="",$T23=Summary!$C$11)),$C23*IF($H23&lt;&gt;"",$H23,($D23+$E23)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P23,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J23" s="20" t="s">
         <v>102</v>
@@ -24079,13 +24160,13 @@
         <v>103</v>
       </c>
       <c r="L23" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M23" s="24" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="N23" s="19" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="O23" s="18" t="s">
         <v>106</v>
@@ -24097,7 +24178,7 @@
         <v>44</v>
       </c>
       <c r="R23" s="24" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="S23" s="18" t="s">
         <v>922</v>
@@ -24105,25 +24186,25 @@
       <c r="T23" s="18"/>
       <c r="U23" s="25" t="n">
         <f aca="false">IF(AND($K23="Y",$F23&lt;&gt;"Y",OR($T23="",$T23=Summary!$C$11)),$C23*IF($H23&lt;&gt;"",$H23,$D23)*INDEX(Summary!$C$6:$C$8,MATCH($P23,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V23" s="25" t="n">
         <f aca="false">IF(AND($K23="Y",$F23&lt;&gt;"Y",OR($T23="",$T23=Summary!$C$11)),$C23*IF($H23&lt;&gt;"",$H23,$E23)*INDEX(Summary!$C$6:$C$8,MATCH($P23,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W23" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X23" s="26" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C24" s="20" t="n">
         <v>1</v>
@@ -24150,13 +24231,13 @@
         <v>103</v>
       </c>
       <c r="L24" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M24" s="24" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="N24" s="19" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="O24" s="18" t="s">
         <v>160</v>
@@ -24168,7 +24249,7 @@
         <v>44</v>
       </c>
       <c r="R24" s="24" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="S24" s="18" t="s">
         <v>922</v>
@@ -24186,15 +24267,15 @@
         <v>219</v>
       </c>
       <c r="X24" s="26" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C25" s="20" t="n">
         <v>1</v>
@@ -24219,13 +24300,13 @@
         <v>103</v>
       </c>
       <c r="L25" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M25" s="24" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="O25" s="18" t="s">
         <v>106</v>
@@ -24258,16 +24339,20 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="C26" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
+      <c r="D26" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>8.69</v>
+      </c>
       <c r="F26" s="20" t="s">
         <v>101</v>
       </c>
@@ -24277,7 +24362,7 @@
       <c r="H26" s="22"/>
       <c r="I26" s="23" t="n">
         <f aca="false">IF(AND($K26="Y",$F26&lt;&gt;"Y",OR($T26="",$T26=Summary!$C$11)),$C26*IF($H26&lt;&gt;"",$H26,($D26+$E26)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P26,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>6.345</v>
       </c>
       <c r="J26" s="20" t="s">
         <v>102</v>
@@ -24286,13 +24371,13 @@
         <v>103</v>
       </c>
       <c r="L26" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M26" s="24" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="N26" s="19" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="O26" s="18" t="s">
         <v>106</v>
@@ -24304,7 +24389,7 @@
         <v>44</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="S26" s="18" t="s">
         <v>922</v>
@@ -24312,31 +24397,35 @@
       <c r="T26" s="18"/>
       <c r="U26" s="25" t="n">
         <f aca="false">IF(AND($K26="Y",$F26&lt;&gt;"Y",OR($T26="",$T26=Summary!$C$11)),$C26*IF($H26&lt;&gt;"",$H26,$D26)*INDEX(Summary!$C$6:$C$8,MATCH($P26,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" s="25" t="n">
         <f aca="false">IF(AND($K26="Y",$F26&lt;&gt;"Y",OR($T26="",$T26=Summary!$C$11)),$C26*IF($H26&lt;&gt;"",$H26,$E26)*INDEX(Summary!$C$6:$C$8,MATCH($P26,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>8.69</v>
       </c>
       <c r="W26" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X26" s="26" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="C27" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
+      <c r="D27" s="21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>4.2</v>
+      </c>
       <c r="F27" s="20" t="s">
         <v>101</v>
       </c>
@@ -24346,7 +24435,7 @@
       <c r="H27" s="22"/>
       <c r="I27" s="23" t="n">
         <f aca="false">IF(AND($K27="Y",$F27&lt;&gt;"Y",OR($T27="",$T27=Summary!$C$11)),$C27*IF($H27&lt;&gt;"",$H27,($D27+$E27)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P27,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>15.81</v>
       </c>
       <c r="J27" s="20" t="s">
         <v>102</v>
@@ -24355,13 +24444,13 @@
         <v>103</v>
       </c>
       <c r="L27" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M27" s="24" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="N27" s="19" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="O27" s="18" t="s">
         <v>106</v>
@@ -24373,7 +24462,7 @@
         <v>44</v>
       </c>
       <c r="R27" s="24" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="S27" s="18" t="s">
         <v>922</v>
@@ -24381,31 +24470,35 @@
       <c r="T27" s="18"/>
       <c r="U27" s="25" t="n">
         <f aca="false">IF(AND($K27="Y",$F27&lt;&gt;"Y",OR($T27="",$T27=Summary!$C$11)),$C27*IF($H27&lt;&gt;"",$H27,$D27)*INDEX(Summary!$C$6:$C$8,MATCH($P27,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="V27" s="25" t="n">
         <f aca="false">IF(AND($K27="Y",$F27&lt;&gt;"Y",OR($T27="",$T27=Summary!$C$11)),$C27*IF($H27&lt;&gt;"",$H27,$E27)*INDEX(Summary!$C$6:$C$8,MATCH($P27,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="W27" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X27" s="26" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="C28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
+      <c r="D28" s="21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E28" s="21" t="n">
+        <v>5.89</v>
+      </c>
       <c r="F28" s="20" t="s">
         <v>101</v>
       </c>
@@ -24415,7 +24508,7 @@
       <c r="H28" s="22"/>
       <c r="I28" s="23" t="n">
         <f aca="false">IF(AND($K28="Y",$F28&lt;&gt;"Y",OR($T28="",$T28=Summary!$C$11)),$C28*IF($H28&lt;&gt;"",$H28,($D28+$E28)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P28,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>4.185</v>
       </c>
       <c r="J28" s="20" t="s">
         <v>102</v>
@@ -24424,13 +24517,13 @@
         <v>103</v>
       </c>
       <c r="L28" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M28" s="24" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="N28" s="19" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="O28" s="18" t="s">
         <v>106</v>
@@ -24442,7 +24535,7 @@
         <v>44</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="S28" s="18" t="s">
         <v>922</v>
@@ -24450,31 +24543,35 @@
       <c r="T28" s="18"/>
       <c r="U28" s="25" t="n">
         <f aca="false">IF(AND($K28="Y",$F28&lt;&gt;"Y",OR($T28="",$T28=Summary!$C$11)),$C28*IF($H28&lt;&gt;"",$H28,$D28)*INDEX(Summary!$C$6:$C$8,MATCH($P28,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V28" s="25" t="n">
         <f aca="false">IF(AND($K28="Y",$F28&lt;&gt;"Y",OR($T28="",$T28=Summary!$C$11)),$C28*IF($H28&lt;&gt;"",$H28,$E28)*INDEX(Summary!$C$6:$C$8,MATCH($P28,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="W28" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X28" s="26" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="C29" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
+      <c r="D29" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="F29" s="20" t="s">
         <v>101</v>
       </c>
@@ -24484,7 +24581,7 @@
       <c r="H29" s="22"/>
       <c r="I29" s="23" t="n">
         <f aca="false">IF(AND($K29="Y",$F29&lt;&gt;"Y",OR($T29="",$T29=Summary!$C$11)),$C29*IF($H29&lt;&gt;"",$H29,($D29+$E29)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P29,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="J29" s="20" t="s">
         <v>102</v>
@@ -24493,16 +24590,16 @@
         <v>103</v>
       </c>
       <c r="L29" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M29" s="24" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="N29" s="19" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="P29" s="20" t="s">
         <v>6</v>
@@ -24511,7 +24608,7 @@
         <v>44</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="S29" s="18" t="s">
         <v>922</v>
@@ -24519,31 +24616,35 @@
       <c r="T29" s="18"/>
       <c r="U29" s="25" t="n">
         <f aca="false">IF(AND($K29="Y",$F29&lt;&gt;"Y",OR($T29="",$T29=Summary!$C$11)),$C29*IF($H29&lt;&gt;"",$H29,$D29)*INDEX(Summary!$C$6:$C$8,MATCH($P29,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V29" s="25" t="n">
         <f aca="false">IF(AND($K29="Y",$F29&lt;&gt;"Y",OR($T29="",$T29=Summary!$C$11)),$C29*IF($H29&lt;&gt;"",$H29,$E29)*INDEX(Summary!$C$6:$C$8,MATCH($P29,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W29" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X29" s="26" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="C30" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
+      <c r="D30" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F30" s="20" t="s">
         <v>101</v>
       </c>
@@ -24553,7 +24654,7 @@
       <c r="H30" s="22"/>
       <c r="I30" s="23" t="n">
         <f aca="false">IF(AND($K30="Y",$F30&lt;&gt;"Y",OR($T30="",$T30=Summary!$C$11)),$C30*IF($H30&lt;&gt;"",$H30,($D30+$E30)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P30,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="J30" s="20" t="s">
         <v>102</v>
@@ -24562,16 +24663,16 @@
         <v>103</v>
       </c>
       <c r="L30" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M30" s="24" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="N30" s="19" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="P30" s="20" t="s">
         <v>6</v>
@@ -24580,7 +24681,7 @@
         <v>44</v>
       </c>
       <c r="R30" s="24" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="S30" s="18" t="s">
         <v>922</v>
@@ -24588,31 +24689,35 @@
       <c r="T30" s="18"/>
       <c r="U30" s="25" t="n">
         <f aca="false">IF(AND($K30="Y",$F30&lt;&gt;"Y",OR($T30="",$T30=Summary!$C$11)),$C30*IF($H30&lt;&gt;"",$H30,$D30)*INDEX(Summary!$C$6:$C$8,MATCH($P30,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V30" s="25" t="n">
         <f aca="false">IF(AND($K30="Y",$F30&lt;&gt;"Y",OR($T30="",$T30=Summary!$C$11)),$C30*IF($H30&lt;&gt;"",$H30,$E30)*INDEX(Summary!$C$6:$C$8,MATCH($P30,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W30" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X30" s="26" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="C31" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
+      <c r="D31" s="21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>4.45</v>
+      </c>
       <c r="F31" s="20" t="s">
         <v>101</v>
       </c>
@@ -24622,7 +24727,7 @@
       <c r="H31" s="22"/>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(AND($K31="Y",$F31&lt;&gt;"Y",OR($T31="",$T31=Summary!$C$11)),$C31*IF($H31&lt;&gt;"",$H31,($D31+$E31)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P31,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="J31" s="20" t="s">
         <v>102</v>
@@ -24631,16 +24736,16 @@
         <v>103</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M31" s="24" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="N31" s="19" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="O31" s="18" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="P31" s="20" t="s">
         <v>6</v>
@@ -24649,7 +24754,7 @@
         <v>44</v>
       </c>
       <c r="R31" s="24" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="S31" s="18" t="s">
         <v>922</v>
@@ -24657,31 +24762,35 @@
       <c r="T31" s="18"/>
       <c r="U31" s="25" t="n">
         <f aca="false">IF(AND($K31="Y",$F31&lt;&gt;"Y",OR($T31="",$T31=Summary!$C$11)),$C31*IF($H31&lt;&gt;"",$H31,$D31)*INDEX(Summary!$C$6:$C$8,MATCH($P31,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V31" s="25" t="n">
         <f aca="false">IF(AND($K31="Y",$F31&lt;&gt;"Y",OR($T31="",$T31=Summary!$C$11)),$C31*IF($H31&lt;&gt;"",$H31,$E31)*INDEX(Summary!$C$6:$C$8,MATCH($P31,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W31" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X31" s="26" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C32" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
+      <c r="D32" s="21" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>30</v>
+      </c>
       <c r="F32" s="20" t="s">
         <v>101</v>
       </c>
@@ -24691,7 +24800,7 @@
       <c r="H32" s="22"/>
       <c r="I32" s="23" t="n">
         <f aca="false">IF(AND($K32="Y",$F32&lt;&gt;"Y",OR($T32="",$T32=Summary!$C$11)),$C32*IF($H32&lt;&gt;"",$H32,($D32+$E32)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P32,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>23.695</v>
       </c>
       <c r="J32" s="20" t="s">
         <v>102</v>
@@ -24700,13 +24809,13 @@
         <v>103</v>
       </c>
       <c r="L32" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M32" s="24" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="N32" s="19" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="O32" s="18" t="s">
         <v>212</v>
@@ -24718,7 +24827,7 @@
         <v>44</v>
       </c>
       <c r="R32" s="24" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="S32" s="18" t="s">
         <v>922</v>
@@ -24726,31 +24835,35 @@
       <c r="T32" s="18"/>
       <c r="U32" s="25" t="n">
         <f aca="false">IF(AND($K32="Y",$F32&lt;&gt;"Y",OR($T32="",$T32=Summary!$C$11)),$C32*IF($H32&lt;&gt;"",$H32,$D32)*INDEX(Summary!$C$6:$C$8,MATCH($P32,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>17.39</v>
       </c>
       <c r="V32" s="25" t="n">
         <f aca="false">IF(AND($K32="Y",$F32&lt;&gt;"Y",OR($T32="",$T32=Summary!$C$11)),$C32*IF($H32&lt;&gt;"",$H32,$E32)*INDEX(Summary!$C$6:$C$8,MATCH($P32,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W32" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X32" s="26" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="C33" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
+      <c r="D33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>15</v>
+      </c>
       <c r="F33" s="20" t="s">
         <v>101</v>
       </c>
@@ -24760,7 +24873,7 @@
       <c r="H33" s="22"/>
       <c r="I33" s="23" t="n">
         <f aca="false">IF(AND($K33="Y",$F33&lt;&gt;"Y",OR($T33="",$T33=Summary!$C$11)),$C33*IF($H33&lt;&gt;"",$H33,($D33+$E33)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P33,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J33" s="20" t="s">
         <v>126</v>
@@ -24769,13 +24882,13 @@
         <v>103</v>
       </c>
       <c r="L33" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M33" s="24" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="N33" s="19" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="O33" s="18" t="s">
         <v>106</v>
@@ -24787,7 +24900,7 @@
         <v>45</v>
       </c>
       <c r="R33" s="24" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="S33" s="18" t="s">
         <v>922</v>
@@ -24799,27 +24912,31 @@
       </c>
       <c r="V33" s="25" t="n">
         <f aca="false">IF(AND($K33="Y",$F33&lt;&gt;"Y",OR($T33="",$T33=Summary!$C$11)),$C33*IF($H33&lt;&gt;"",$H33,$E33)*INDEX(Summary!$C$6:$C$8,MATCH($P33,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W33" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X33" s="26" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="C34" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
+      <c r="D34" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>14</v>
+      </c>
       <c r="F34" s="20" t="s">
         <v>101</v>
       </c>
@@ -24838,13 +24955,13 @@
         <v>101</v>
       </c>
       <c r="L34" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M34" s="24" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="N34" s="19" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="O34" s="18" t="s">
         <v>106</v>
@@ -24856,7 +24973,7 @@
         <v>44</v>
       </c>
       <c r="R34" s="24" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="S34" s="18" t="s">
         <v>922</v>
@@ -24871,24 +24988,28 @@
         <v>0</v>
       </c>
       <c r="W34" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X34" s="26" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="C35" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
+      <c r="D35" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>140</v>
+      </c>
       <c r="F35" s="20" t="s">
         <v>101</v>
       </c>
@@ -24907,13 +25028,13 @@
         <v>101</v>
       </c>
       <c r="L35" s="24" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="M35" s="24" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="N35" s="19" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="O35" s="18" t="s">
         <v>106</v>
@@ -24925,7 +25046,7 @@
         <v>44</v>
       </c>
       <c r="R35" s="24" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="S35" s="18" t="s">
         <v>922</v>
@@ -24940,24 +25061,28 @@
         <v>0</v>
       </c>
       <c r="W35" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X35" s="26" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C36" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
+      <c r="D36" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>170</v>
+      </c>
       <c r="F36" s="20" t="s">
         <v>101</v>
       </c>
@@ -24967,7 +25092,7 @@
       <c r="H36" s="22"/>
       <c r="I36" s="23" t="n">
         <f aca="false">IF(AND($K36="Y",$F36&lt;&gt;"Y",OR($T36="",$T36=Summary!$C$11)),$C36*IF($H36&lt;&gt;"",$H36,($D36+$E36)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P36,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J36" s="20" t="s">
         <v>157</v>
@@ -24976,13 +25101,13 @@
         <v>103</v>
       </c>
       <c r="L36" s="24" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="M36" s="24" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="N36" s="19" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="O36" s="18" t="s">
         <v>106</v>
@@ -24994,7 +25119,7 @@
         <v>44</v>
       </c>
       <c r="R36" s="24" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="S36" s="18" t="s">
         <v>922</v>
@@ -25002,31 +25127,35 @@
       <c r="T36" s="18"/>
       <c r="U36" s="25" t="n">
         <f aca="false">IF(AND($K36="Y",$F36&lt;&gt;"Y",OR($T36="",$T36=Summary!$C$11)),$C36*IF($H36&lt;&gt;"",$H36,$D36)*INDEX(Summary!$C$6:$C$8,MATCH($P36,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V36" s="25" t="n">
         <f aca="false">IF(AND($K36="Y",$F36&lt;&gt;"Y",OR($T36="",$T36=Summary!$C$11)),$C36*IF($H36&lt;&gt;"",$H36,$E36)*INDEX(Summary!$C$6:$C$8,MATCH($P36,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="W36" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X36" s="26" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="C37" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
+      <c r="D37" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>35</v>
+      </c>
       <c r="F37" s="20" t="s">
         <v>101</v>
       </c>
@@ -25036,7 +25165,7 @@
       <c r="H37" s="22"/>
       <c r="I37" s="23" t="n">
         <f aca="false">IF(AND($K37="Y",$F37&lt;&gt;"Y",OR($T37="",$T37=Summary!$C$11)),$C37*IF($H37&lt;&gt;"",$H37,($D37+$E37)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P37,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="J37" s="20" t="s">
         <v>102</v>
@@ -25045,13 +25174,13 @@
         <v>103</v>
       </c>
       <c r="L37" s="24" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="M37" s="24" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="N37" s="19" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="O37" s="18" t="s">
         <v>106</v>
@@ -25063,7 +25192,7 @@
         <v>44</v>
       </c>
       <c r="R37" s="24" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="S37" s="18" t="s">
         <v>922</v>
@@ -25071,31 +25200,35 @@
       <c r="T37" s="18"/>
       <c r="U37" s="25" t="n">
         <f aca="false">IF(AND($K37="Y",$F37&lt;&gt;"Y",OR($T37="",$T37=Summary!$C$11)),$C37*IF($H37&lt;&gt;"",$H37,$D37)*INDEX(Summary!$C$6:$C$8,MATCH($P37,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V37" s="25" t="n">
         <f aca="false">IF(AND($K37="Y",$F37&lt;&gt;"Y",OR($T37="",$T37=Summary!$C$11)),$C37*IF($H37&lt;&gt;"",$H37,$E37)*INDEX(Summary!$C$6:$C$8,MATCH($P37,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="W37" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X37" s="26" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="C38" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
+      <c r="D38" s="21" t="n">
+        <v>238.68</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>266.99</v>
+      </c>
       <c r="F38" s="20" t="s">
         <v>101</v>
       </c>
@@ -25114,13 +25247,13 @@
         <v>101</v>
       </c>
       <c r="L38" s="24" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="M38" s="24" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="N38" s="19" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="O38" s="18" t="s">
         <v>106</v>
@@ -25132,7 +25265,7 @@
         <v>44</v>
       </c>
       <c r="R38" s="24" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="S38" s="18" t="s">
         <v>922</v>
@@ -25147,24 +25280,28 @@
         <v>0</v>
       </c>
       <c r="W38" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X38" s="26" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="C39" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
+      <c r="D39" s="21" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>23.38</v>
+      </c>
       <c r="F39" s="20" t="s">
         <v>101</v>
       </c>
@@ -25183,13 +25320,13 @@
         <v>101</v>
       </c>
       <c r="L39" s="24" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="M39" s="24" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="N39" s="19" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="O39" s="18" t="s">
         <v>106</v>
@@ -25201,7 +25338,7 @@
         <v>45</v>
       </c>
       <c r="R39" s="24" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="S39" s="18" t="s">
         <v>922</v>
@@ -25216,18 +25353,18 @@
         <v>0</v>
       </c>
       <c r="W39" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X39" s="26" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C40" s="20" t="n">
         <v>3</v>
@@ -25252,13 +25389,13 @@
         <v>103</v>
       </c>
       <c r="L40" s="24" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="M40" s="24" t="s">
         <v>867</v>
       </c>
       <c r="N40" s="19" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="O40" s="18" t="s">
         <v>868</v>
@@ -25291,16 +25428,20 @@
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="C41" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
+      <c r="D41" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="21" t="n">
+        <v>35</v>
+      </c>
       <c r="F41" s="20" t="s">
         <v>101</v>
       </c>
@@ -25310,7 +25451,7 @@
       <c r="H41" s="22"/>
       <c r="I41" s="23" t="n">
         <f aca="false">IF(AND($K41="Y",$F41&lt;&gt;"Y",OR($T41="",$T41=Summary!$C$11)),$C41*IF($H41&lt;&gt;"",$H41,($D41+$E41)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P41,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>102</v>
@@ -25319,13 +25460,13 @@
         <v>103</v>
       </c>
       <c r="L41" s="24" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="M41" s="24" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="N41" s="19" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="O41" s="18" t="s">
         <v>106</v>
@@ -25337,7 +25478,7 @@
         <v>44</v>
       </c>
       <c r="R41" s="24" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="S41" s="18" t="s">
         <v>922</v>
@@ -25345,31 +25486,35 @@
       <c r="T41" s="18"/>
       <c r="U41" s="25" t="n">
         <f aca="false">IF(AND($K41="Y",$F41&lt;&gt;"Y",OR($T41="",$T41=Summary!$C$11)),$C41*IF($H41&lt;&gt;"",$H41,$D41)*INDEX(Summary!$C$6:$C$8,MATCH($P41,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V41" s="25" t="n">
         <f aca="false">IF(AND($K41="Y",$F41&lt;&gt;"Y",OR($T41="",$T41=Summary!$C$11)),$C41*IF($H41&lt;&gt;"",$H41,$E41)*INDEX(Summary!$C$6:$C$8,MATCH($P41,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="W41" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X41" s="26" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="C42" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
+      <c r="D42" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>60</v>
+      </c>
       <c r="F42" s="20" t="s">
         <v>101</v>
       </c>
@@ -25379,7 +25524,7 @@
       <c r="H42" s="22"/>
       <c r="I42" s="23" t="n">
         <f aca="false">IF(AND($K42="Y",$F42&lt;&gt;"Y",OR($T42="",$T42=Summary!$C$11)),$C42*IF($H42&lt;&gt;"",$H42,($D42+$E42)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P42,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="J42" s="20" t="s">
         <v>102</v>
@@ -25388,13 +25533,13 @@
         <v>103</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="M42" s="24" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="N42" s="19" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="O42" s="18" t="s">
         <v>106</v>
@@ -25406,7 +25551,7 @@
         <v>44</v>
       </c>
       <c r="R42" s="24" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="S42" s="18" t="s">
         <v>922</v>
@@ -25414,31 +25559,35 @@
       <c r="T42" s="18"/>
       <c r="U42" s="25" t="n">
         <f aca="false">IF(AND($K42="Y",$F42&lt;&gt;"Y",OR($T42="",$T42=Summary!$C$11)),$C42*IF($H42&lt;&gt;"",$H42,$D42)*INDEX(Summary!$C$6:$C$8,MATCH($P42,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V42" s="25" t="n">
         <f aca="false">IF(AND($K42="Y",$F42&lt;&gt;"Y",OR($T42="",$T42=Summary!$C$11)),$C42*IF($H42&lt;&gt;"",$H42,$E42)*INDEX(Summary!$C$6:$C$8,MATCH($P42,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W42" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X42" s="26" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="C43" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
+      <c r="D43" s="21" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>15</v>
+      </c>
       <c r="F43" s="20" t="s">
         <v>101</v>
       </c>
@@ -25448,7 +25597,7 @@
       <c r="H43" s="22"/>
       <c r="I43" s="23" t="n">
         <f aca="false">IF(AND($K43="Y",$F43&lt;&gt;"Y",OR($T43="",$T43=Summary!$C$11)),$C43*IF($H43&lt;&gt;"",$H43,($D43+$E43)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P43,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>12.925</v>
       </c>
       <c r="J43" s="20" t="s">
         <v>102</v>
@@ -25457,13 +25606,13 @@
         <v>103</v>
       </c>
       <c r="L43" s="24" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="M43" s="24" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="N43" s="19" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="O43" s="18" t="s">
         <v>212</v>
@@ -25475,7 +25624,7 @@
         <v>44</v>
       </c>
       <c r="R43" s="24" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="S43" s="18" t="s">
         <v>922</v>
@@ -25483,31 +25632,35 @@
       <c r="T43" s="18"/>
       <c r="U43" s="25" t="n">
         <f aca="false">IF(AND($K43="Y",$F43&lt;&gt;"Y",OR($T43="",$T43=Summary!$C$11)),$C43*IF($H43&lt;&gt;"",$H43,$D43)*INDEX(Summary!$C$6:$C$8,MATCH($P43,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="V43" s="25" t="n">
         <f aca="false">IF(AND($K43="Y",$F43&lt;&gt;"Y",OR($T43="",$T43=Summary!$C$11)),$C43*IF($H43&lt;&gt;"",$H43,$E43)*INDEX(Summary!$C$6:$C$8,MATCH($P43,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W43" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X43" s="26" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="C44" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
+      <c r="D44" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>25</v>
+      </c>
       <c r="F44" s="20" t="s">
         <v>101</v>
       </c>
@@ -25517,7 +25670,7 @@
       <c r="H44" s="22"/>
       <c r="I44" s="23" t="n">
         <f aca="false">IF(AND($K44="Y",$F44&lt;&gt;"Y",OR($T44="",$T44=Summary!$C$11)),$C44*IF($H44&lt;&gt;"",$H44,($D44+$E44)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P44,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="J44" s="20" t="s">
         <v>102</v>
@@ -25526,13 +25679,13 @@
         <v>103</v>
       </c>
       <c r="L44" s="24" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="M44" s="24" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="N44" s="19" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="O44" s="18" t="s">
         <v>140</v>
@@ -25544,7 +25697,7 @@
         <v>45</v>
       </c>
       <c r="R44" s="24" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="S44" s="18" t="s">
         <v>922</v>
@@ -25552,31 +25705,35 @@
       <c r="T44" s="18"/>
       <c r="U44" s="25" t="n">
         <f aca="false">IF(AND($K44="Y",$F44&lt;&gt;"Y",OR($T44="",$T44=Summary!$C$11)),$C44*IF($H44&lt;&gt;"",$H44,$D44)*INDEX(Summary!$C$6:$C$8,MATCH($P44,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V44" s="25" t="n">
         <f aca="false">IF(AND($K44="Y",$F44&lt;&gt;"Y",OR($T44="",$T44=Summary!$C$11)),$C44*IF($H44&lt;&gt;"",$H44,$E44)*INDEX(Summary!$C$6:$C$8,MATCH($P44,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="W44" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X44" s="26" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="C45" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
+      <c r="D45" s="21" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="E45" s="21" t="n">
+        <v>17.09</v>
+      </c>
       <c r="F45" s="20" t="s">
         <v>101</v>
       </c>
@@ -25586,7 +25743,7 @@
       <c r="H45" s="22"/>
       <c r="I45" s="23" t="n">
         <f aca="false">IF(AND($K45="Y",$F45&lt;&gt;"Y",OR($T45="",$T45=Summary!$C$11)),$C45*IF($H45&lt;&gt;"",$H45,($D45+$E45)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P45,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>22.64</v>
       </c>
       <c r="J45" s="20" t="s">
         <v>102</v>
@@ -25595,13 +25752,13 @@
         <v>103</v>
       </c>
       <c r="L45" s="24" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="M45" s="24" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="N45" s="19" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="O45" s="18" t="s">
         <v>106</v>
@@ -25613,7 +25770,7 @@
         <v>44</v>
       </c>
       <c r="R45" s="24" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="S45" s="18" t="s">
         <v>922</v>
@@ -25621,31 +25778,35 @@
       <c r="T45" s="18"/>
       <c r="U45" s="25" t="n">
         <f aca="false">IF(AND($K45="Y",$F45&lt;&gt;"Y",OR($T45="",$T45=Summary!$C$11)),$C45*IF($H45&lt;&gt;"",$H45,$D45)*INDEX(Summary!$C$6:$C$8,MATCH($P45,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="V45" s="25" t="n">
         <f aca="false">IF(AND($K45="Y",$F45&lt;&gt;"Y",OR($T45="",$T45=Summary!$C$11)),$C45*IF($H45&lt;&gt;"",$H45,$E45)*INDEX(Summary!$C$6:$C$8,MATCH($P45,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>34.18</v>
       </c>
       <c r="W45" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X45" s="26" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="18" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="C46" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
+      <c r="D46" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>8.19</v>
+      </c>
       <c r="F46" s="20" t="s">
         <v>101</v>
       </c>
@@ -25655,7 +25816,7 @@
       <c r="H46" s="22"/>
       <c r="I46" s="23" t="n">
         <f aca="false">IF(AND($K46="Y",$F46&lt;&gt;"Y",OR($T46="",$T46=Summary!$C$11)),$C46*IF($H46&lt;&gt;"",$H46,($D46+$E46)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P46,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="J46" s="20" t="s">
         <v>102</v>
@@ -25664,13 +25825,13 @@
         <v>103</v>
       </c>
       <c r="L46" s="24" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="N46" s="19" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="O46" s="18" t="s">
         <v>106</v>
@@ -25682,7 +25843,7 @@
         <v>44</v>
       </c>
       <c r="R46" s="24" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="S46" s="18" t="s">
         <v>922</v>
@@ -25690,31 +25851,35 @@
       <c r="T46" s="18"/>
       <c r="U46" s="25" t="n">
         <f aca="false">IF(AND($K46="Y",$F46&lt;&gt;"Y",OR($T46="",$T46=Summary!$C$11)),$C46*IF($H46&lt;&gt;"",$H46,$D46)*INDEX(Summary!$C$6:$C$8,MATCH($P46,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V46" s="25" t="n">
         <f aca="false">IF(AND($K46="Y",$F46&lt;&gt;"Y",OR($T46="",$T46=Summary!$C$11)),$C46*IF($H46&lt;&gt;"",$H46,$E46)*INDEX(Summary!$C$6:$C$8,MATCH($P46,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>16.38</v>
       </c>
       <c r="W46" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X46" s="26" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C47" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
+      <c r="D47" s="21" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="E47" s="21" t="n">
+        <v>22.79</v>
+      </c>
       <c r="F47" s="20" t="s">
         <v>101</v>
       </c>
@@ -25724,7 +25889,7 @@
       <c r="H47" s="22"/>
       <c r="I47" s="23" t="n">
         <f aca="false">IF(AND($K47="Y",$F47&lt;&gt;"Y",OR($T47="",$T47=Summary!$C$11)),$C47*IF($H47&lt;&gt;"",$H47,($D47+$E47)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P47,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>21.125</v>
       </c>
       <c r="J47" s="20" t="s">
         <v>157</v>
@@ -25733,13 +25898,13 @@
         <v>103</v>
       </c>
       <c r="L47" s="24" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="M47" s="24" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="N47" s="19" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="O47" s="18" t="s">
         <v>106</v>
@@ -25751,7 +25916,7 @@
         <v>44</v>
       </c>
       <c r="R47" s="24" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="S47" s="18" t="s">
         <v>922</v>
@@ -25759,31 +25924,35 @@
       <c r="T47" s="18"/>
       <c r="U47" s="25" t="n">
         <f aca="false">IF(AND($K47="Y",$F47&lt;&gt;"Y",OR($T47="",$T47=Summary!$C$11)),$C47*IF($H47&lt;&gt;"",$H47,$D47)*INDEX(Summary!$C$6:$C$8,MATCH($P47,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>19.46</v>
       </c>
       <c r="V47" s="25" t="n">
         <f aca="false">IF(AND($K47="Y",$F47&lt;&gt;"Y",OR($T47="",$T47=Summary!$C$11)),$C47*IF($H47&lt;&gt;"",$H47,$E47)*INDEX(Summary!$C$6:$C$8,MATCH($P47,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>22.79</v>
       </c>
       <c r="W47" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X47" s="26" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="C48" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
+      <c r="D48" s="21" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>7.79</v>
+      </c>
       <c r="F48" s="20" t="s">
         <v>101</v>
       </c>
@@ -25793,7 +25962,7 @@
       <c r="H48" s="22"/>
       <c r="I48" s="23" t="n">
         <f aca="false">IF(AND($K48="Y",$F48&lt;&gt;"Y",OR($T48="",$T48=Summary!$C$11)),$C48*IF($H48&lt;&gt;"",$H48,($D48+$E48)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P48,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="J48" s="20" t="s">
         <v>126</v>
@@ -25802,12 +25971,14 @@
         <v>103</v>
       </c>
       <c r="L48" s="24" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="M48" s="24" t="s">
-        <v>1115</v>
-      </c>
-      <c r="N48" s="19"/>
+        <v>1119</v>
+      </c>
+      <c r="N48" s="19" t="s">
+        <v>1125</v>
+      </c>
       <c r="O48" s="18" t="s">
         <v>106</v>
       </c>
@@ -25818,7 +25989,7 @@
         <v>44</v>
       </c>
       <c r="R48" s="24" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="S48" s="18" t="s">
         <v>922</v>
@@ -25826,31 +25997,35 @@
       <c r="T48" s="18"/>
       <c r="U48" s="25" t="n">
         <f aca="false">IF(AND($K48="Y",$F48&lt;&gt;"Y",OR($T48="",$T48=Summary!$C$11)),$C48*IF($H48&lt;&gt;"",$H48,$D48)*INDEX(Summary!$C$6:$C$8,MATCH($P48,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="V48" s="25" t="n">
         <f aca="false">IF(AND($K48="Y",$F48&lt;&gt;"Y",OR($T48="",$T48=Summary!$C$11)),$C48*IF($H48&lt;&gt;"",$H48,$E48)*INDEX(Summary!$C$6:$C$8,MATCH($P48,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>7.79</v>
       </c>
       <c r="W48" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X48" s="26" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="18" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="C49" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
+      <c r="D49" s="21" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="E49" s="21" t="n">
+        <v>20</v>
+      </c>
       <c r="F49" s="20" t="s">
         <v>101</v>
       </c>
@@ -25860,7 +26035,7 @@
       <c r="H49" s="22"/>
       <c r="I49" s="23" t="n">
         <f aca="false">IF(AND($K49="Y",$F49&lt;&gt;"Y",OR($T49="",$T49=Summary!$C$11)),$C49*IF($H49&lt;&gt;"",$H49,($D49+$E49)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P49,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>15.89</v>
       </c>
       <c r="J49" s="20" t="s">
         <v>126</v>
@@ -25869,13 +26044,13 @@
         <v>103</v>
       </c>
       <c r="L49" s="24" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="N49" s="19" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="O49" s="18" t="s">
         <v>106</v>
@@ -25887,7 +26062,7 @@
         <v>44</v>
       </c>
       <c r="R49" s="24" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="S49" s="18" t="s">
         <v>922</v>
@@ -25895,31 +26070,35 @@
       <c r="T49" s="18"/>
       <c r="U49" s="25" t="n">
         <f aca="false">IF(AND($K49="Y",$F49&lt;&gt;"Y",OR($T49="",$T49=Summary!$C$11)),$C49*IF($H49&lt;&gt;"",$H49,$D49)*INDEX(Summary!$C$6:$C$8,MATCH($P49,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>11.78</v>
       </c>
       <c r="V49" s="25" t="n">
         <f aca="false">IF(AND($K49="Y",$F49&lt;&gt;"Y",OR($T49="",$T49=Summary!$C$11)),$C49*IF($H49&lt;&gt;"",$H49,$E49)*INDEX(Summary!$C$6:$C$8,MATCH($P49,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W49" s="18" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="X49" s="26" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="C50" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
+      <c r="D50" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>20</v>
+      </c>
       <c r="F50" s="20" t="s">
         <v>101</v>
       </c>
@@ -25929,7 +26108,7 @@
       <c r="H50" s="22"/>
       <c r="I50" s="23" t="n">
         <f aca="false">IF(AND($K50="Y",$F50&lt;&gt;"Y",OR($T50="",$T50=Summary!$C$11)),$C50*IF($H50&lt;&gt;"",$H50,($D50+$E50)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P50,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J50" s="20" t="s">
         <v>102</v>
@@ -25938,13 +26117,13 @@
         <v>103</v>
       </c>
       <c r="L50" s="24" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="M50" s="24" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="N50" s="19" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="O50" s="18" t="s">
         <v>212</v>
@@ -25956,7 +26135,7 @@
         <v>44</v>
       </c>
       <c r="R50" s="24" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="S50" s="18" t="s">
         <v>922</v>
@@ -25964,17 +26143,17 @@
       <c r="T50" s="18"/>
       <c r="U50" s="25" t="n">
         <f aca="false">IF(AND($K50="Y",$F50&lt;&gt;"Y",OR($T50="",$T50=Summary!$C$11)),$C50*IF($H50&lt;&gt;"",$H50,$D50)*INDEX(Summary!$C$6:$C$8,MATCH($P50,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V50" s="25" t="n">
         <f aca="false">IF(AND($K50="Y",$F50&lt;&gt;"Y",OR($T50="",$T50=Summary!$C$11)),$C50*IF($H50&lt;&gt;"",$H50,$E50)*INDEX(Summary!$C$6:$C$8,MATCH($P50,Summary!$B$6:$B$8,0)),0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W50" s="18" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="X50" s="26" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25983,15 +26162,15 @@
       </c>
       <c r="I51" s="14" t="n">
         <f aca="false">SUM(I5:I50)</f>
-        <v>349.98</v>
+        <v>1576.15</v>
       </c>
       <c r="U51" s="14" t="n">
         <f aca="false">SUM(U5:U50)</f>
-        <v>349.98</v>
+        <v>1252.25</v>
       </c>
       <c r="V51" s="14" t="n">
         <f aca="false">SUM(V5:V50)</f>
-        <v>349.98</v>
+        <v>1900.05</v>
       </c>
     </row>
   </sheetData>
@@ -26000,10 +26179,10 @@
     <mergeCell ref="A2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:X50">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$K5="N"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>AND($T5&lt;&gt;"",$T5&lt;&gt;Summary!$C$11)</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
@@ -26016,7 +26195,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:E50">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>AND($K5="Y",$F5&lt;&gt;"Y",$H5="",$D5="",$E5="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26112,72 +26291,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
     </row>
   </sheetData>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -85,12 +85,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4472" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4473" uniqueCount="1159">
   <si>
     <t xml:space="preserve">07K ZN6 Turbo Swap — Cost Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">All prices in CAD (USD × 1.42, GBP × 1.85 at Oct 4, 2026), before HST. Low/High = estimate range. WORKING = your actual price where you've entered one, otherwise the midpoint of the estimate. Have = Y lines count $0.</t>
+    <t xml:space="preserve">All prices in CAD (USD × 1.42, GBP × 1.85 at Oct 4, 2026), before HST. Low/High = estimate range. Best estimate = your actual price where you've entered one, otherwise the midpoint of the estimate range. Have = Y lines count $0.</t>
   </si>
   <si>
     <t xml:space="preserve">Assumptions</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">High (CAD)</t>
   </si>
   <si>
-    <t xml:space="preserve">WORKING (CAD)</t>
+    <t xml:space="preserve">Best estimate (CAD)</t>
   </si>
   <si>
     <t xml:space="preserve">Donors</t>
@@ -330,10 +330,10 @@
     <t xml:space="preserve">Qty</t>
   </si>
   <si>
-    <t xml:space="preserve">Est. low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. high</t>
+    <t xml:space="preserve">Est. unit low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. unit high</t>
   </si>
   <si>
     <t xml:space="preserve">Have?</t>
@@ -342,10 +342,10 @@
     <t xml:space="preserve">Make?</t>
   </si>
   <si>
-    <t xml:space="preserve">MY cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working (CAD)</t>
+    <t xml:space="preserve">MY unit cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line total (CAD)</t>
   </si>
   <si>
     <t xml:space="preserve">Status</t>
@@ -378,10 +378,10 @@
     <t xml:space="preserve">Route</t>
   </si>
   <si>
-    <t xml:space="preserve">Ext low (CAD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ext high (CAD)</t>
+    <t xml:space="preserve">Line total low (CAD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line total high (CAD)</t>
   </si>
   <si>
     <t xml:space="preserve">Basis</t>
@@ -2838,7 +2838,7 @@
     <t xml:space="preserve">07K ZN6 — CNC mill BOM (HTMCNC-style, 450 x 750 x 110 mm work area)</t>
   </si>
   <si>
-    <t xml:space="preserve">Same rules as the BOM tab. Est. low/high (D/E) = the prices I found on Oct 4–5, 2026, per unit in CAD, mostly AliExpress listing prices (Basis = Listing) or inferred from them (Basis = Estimate). That is the number to beat: when you find cheaper, type your real price in the blue column H and it overrides the estimate. Decided and bought-price lines: C01, C02, C20. Have: C21, C36. Every line has a candidate listing in the Link column at the far right; columns L–W with the notes are grouped (click the + above them).</t>
+    <t xml:space="preserve">Prices are PER UNIT (each, pack, metre or lot as the Unit column says). Est. unit low / high = the cheapest and dearest price I found for one unit. Line total = Qty × price, using your MY unit cost if you typed one, otherwise the midpoint of low and high. Have = Y makes a line $0; Incl. = N drops it. Example: C03 is 18 brackets at $0.51–$1.00 each, so its line total is 18 × $0.76 = $13.59.</t>
   </si>
   <si>
     <t xml:space="preserve">2040 T-slot extrusion, 1000 mm, black — VEVOR 5-pack</t>
@@ -3559,17 +3559,21 @@
   </si>
   <si>
     <t xml:space="preserve">10. CNC tab — the parts list for the DIY CNC mill (HTMCNC-style, Y scaled to 750 mm). Same columns and colour rules as the BOM tab, plus pink Est. cells = no price decided yet. The Summary has its own CNC block; it is not added to the car's ALL-IN.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Every price column is PER UNIT. Line total (CAD) = Qty × unit price. The Summary's 'Best estimate' column is the sum of line totals, using your real price where you've entered one and the midpoint of the estimate range where you haven't.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -3754,7 +3758,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3861,6 +3865,30 @@
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -5316,7 +5344,7 @@
         <v>1226.17</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="3" t="s">
         <v>53</v>
       </c>
@@ -5383,7 +5411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="3" t="s">
         <v>74</v>
       </c>
@@ -5401,7 +5429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="9" t="s">
         <v>75</v>
       </c>
@@ -22760,12 +22788,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="12" min="12" style="1" width="15"/>
@@ -22877,18 +22904,18 @@
       <c r="C5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
       <c r="F5" s="20" t="s">
         <v>103</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="28" t="n">
         <v>57.99</v>
       </c>
-      <c r="I5" s="23" t="n">
+      <c r="I5" s="29" t="n">
         <f aca="false">IF(AND($K5="Y",$F5&lt;&gt;"Y",OR($T5="",$T5=Summary!$C$11)),$C5*IF($H5&lt;&gt;"",$H5,($D5+$E5)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P5,Summary!$B$6:$B$8,0)),0)</f>
         <v>57.99</v>
       </c>
@@ -22923,11 +22950,11 @@
         <v>924</v>
       </c>
       <c r="T5" s="18"/>
-      <c r="U5" s="25" t="n">
+      <c r="U5" s="30" t="n">
         <f aca="false">IF(AND($K5="Y",$F5&lt;&gt;"Y",OR($T5="",$T5=Summary!$C$11)),$C5*IF($H5&lt;&gt;"",$H5,$D5)*INDEX(Summary!$C$6:$C$8,MATCH($P5,Summary!$B$6:$B$8,0)),0)</f>
         <v>57.99</v>
       </c>
-      <c r="V5" s="25" t="n">
+      <c r="V5" s="30" t="n">
         <f aca="false">IF(AND($K5="Y",$F5&lt;&gt;"Y",OR($T5="",$T5=Summary!$C$11)),$C5*IF($H5&lt;&gt;"",$H5,$E5)*INDEX(Summary!$C$6:$C$8,MATCH($P5,Summary!$B$6:$B$8,0)),0)</f>
         <v>57.99</v>
       </c>
@@ -22948,18 +22975,18 @@
       <c r="C6" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
       <c r="F6" s="20" t="s">
         <v>103</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="28" t="n">
         <v>106.99</v>
       </c>
-      <c r="I6" s="23" t="n">
+      <c r="I6" s="29" t="n">
         <f aca="false">IF(AND($K6="Y",$F6&lt;&gt;"Y",OR($T6="",$T6=Summary!$C$11)),$C6*IF($H6&lt;&gt;"",$H6,($D6+$E6)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P6,Summary!$B$6:$B$8,0)),0)</f>
         <v>106.99</v>
       </c>
@@ -22994,11 +23021,11 @@
         <v>924</v>
       </c>
       <c r="T6" s="18"/>
-      <c r="U6" s="25" t="n">
+      <c r="U6" s="30" t="n">
         <f aca="false">IF(AND($K6="Y",$F6&lt;&gt;"Y",OR($T6="",$T6=Summary!$C$11)),$C6*IF($H6&lt;&gt;"",$H6,$D6)*INDEX(Summary!$C$6:$C$8,MATCH($P6,Summary!$B$6:$B$8,0)),0)</f>
         <v>106.99</v>
       </c>
-      <c r="V6" s="25" t="n">
+      <c r="V6" s="30" t="n">
         <f aca="false">IF(AND($K6="Y",$F6&lt;&gt;"Y",OR($T6="",$T6=Summary!$C$11)),$C6*IF($H6&lt;&gt;"",$H6,$E6)*INDEX(Summary!$C$6:$C$8,MATCH($P6,Summary!$B$6:$B$8,0)),0)</f>
         <v>106.99</v>
       </c>
@@ -23019,10 +23046,10 @@
       <c r="C7" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="27" t="n">
         <v>0.51</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="27" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="20" t="s">
@@ -23031,8 +23058,8 @@
       <c r="G7" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="23" t="n">
+      <c r="H7" s="28"/>
+      <c r="I7" s="29" t="n">
         <f aca="false">IF(AND($K7="Y",$F7&lt;&gt;"Y",OR($T7="",$T7=Summary!$C$11)),$C7*IF($H7&lt;&gt;"",$H7,($D7+$E7)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P7,Summary!$B$6:$B$8,0)),0)</f>
         <v>13.59</v>
       </c>
@@ -23067,11 +23094,11 @@
         <v>924</v>
       </c>
       <c r="T7" s="18"/>
-      <c r="U7" s="25" t="n">
+      <c r="U7" s="30" t="n">
         <f aca="false">IF(AND($K7="Y",$F7&lt;&gt;"Y",OR($T7="",$T7=Summary!$C$11)),$C7*IF($H7&lt;&gt;"",$H7,$D7)*INDEX(Summary!$C$6:$C$8,MATCH($P7,Summary!$B$6:$B$8,0)),0)</f>
         <v>9.18</v>
       </c>
-      <c r="V7" s="25" t="n">
+      <c r="V7" s="30" t="n">
         <f aca="false">IF(AND($K7="Y",$F7&lt;&gt;"Y",OR($T7="",$T7=Summary!$C$11)),$C7*IF($H7&lt;&gt;"",$H7,$E7)*INDEX(Summary!$C$6:$C$8,MATCH($P7,Summary!$B$6:$B$8,0)),0)</f>
         <v>18</v>
       </c>
@@ -23092,10 +23119,10 @@
       <c r="C8" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="27" t="n">
         <v>0.3</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="F8" s="20" t="s">
@@ -23104,8 +23131,8 @@
       <c r="G8" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="23" t="n">
+      <c r="H8" s="28"/>
+      <c r="I8" s="29" t="n">
         <f aca="false">IF(AND($K8="Y",$F8&lt;&gt;"Y",OR($T8="",$T8=Summary!$C$11)),$C8*IF($H8&lt;&gt;"",$H8,($D8+$E8)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P8,Summary!$B$6:$B$8,0)),0)</f>
         <v>4.4</v>
       </c>
@@ -23140,11 +23167,11 @@
         <v>924</v>
       </c>
       <c r="T8" s="18"/>
-      <c r="U8" s="25" t="n">
+      <c r="U8" s="30" t="n">
         <f aca="false">IF(AND($K8="Y",$F8&lt;&gt;"Y",OR($T8="",$T8=Summary!$C$11)),$C8*IF($H8&lt;&gt;"",$H8,$D8)*INDEX(Summary!$C$6:$C$8,MATCH($P8,Summary!$B$6:$B$8,0)),0)</f>
         <v>2.4</v>
       </c>
-      <c r="V8" s="25" t="n">
+      <c r="V8" s="30" t="n">
         <f aca="false">IF(AND($K8="Y",$F8&lt;&gt;"Y",OR($T8="",$T8=Summary!$C$11)),$C8*IF($H8&lt;&gt;"",$H8,$E8)*INDEX(Summary!$C$6:$C$8,MATCH($P8,Summary!$B$6:$B$8,0)),0)</f>
         <v>6.4</v>
       </c>
@@ -23165,10 +23192,10 @@
       <c r="C9" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="27" t="n">
         <v>0.06</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="27" t="n">
         <v>0.12</v>
       </c>
       <c r="F9" s="20" t="s">
@@ -23177,8 +23204,8 @@
       <c r="G9" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="23" t="n">
+      <c r="H9" s="28"/>
+      <c r="I9" s="29" t="n">
         <f aca="false">IF(AND($K9="Y",$F9&lt;&gt;"Y",OR($T9="",$T9=Summary!$C$11)),$C9*IF($H9&lt;&gt;"",$H9,($D9+$E9)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P9,Summary!$B$6:$B$8,0)),0)</f>
         <v>9</v>
       </c>
@@ -23213,11 +23240,11 @@
         <v>924</v>
       </c>
       <c r="T9" s="18"/>
-      <c r="U9" s="25" t="n">
+      <c r="U9" s="30" t="n">
         <f aca="false">IF(AND($K9="Y",$F9&lt;&gt;"Y",OR($T9="",$T9=Summary!$C$11)),$C9*IF($H9&lt;&gt;"",$H9,$D9)*INDEX(Summary!$C$6:$C$8,MATCH($P9,Summary!$B$6:$B$8,0)),0)</f>
         <v>6</v>
       </c>
-      <c r="V9" s="25" t="n">
+      <c r="V9" s="30" t="n">
         <f aca="false">IF(AND($K9="Y",$F9&lt;&gt;"Y",OR($T9="",$T9=Summary!$C$11)),$C9*IF($H9&lt;&gt;"",$H9,$E9)*INDEX(Summary!$C$6:$C$8,MATCH($P9,Summary!$B$6:$B$8,0)),0)</f>
         <v>12</v>
       </c>
@@ -23238,10 +23265,10 @@
       <c r="C10" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="27" t="n">
         <v>0.08</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="27" t="n">
         <v>0.15</v>
       </c>
       <c r="F10" s="20" t="s">
@@ -23250,8 +23277,8 @@
       <c r="G10" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="22"/>
-      <c r="I10" s="23" t="n">
+      <c r="H10" s="28"/>
+      <c r="I10" s="29" t="n">
         <f aca="false">IF(AND($K10="Y",$F10&lt;&gt;"Y",OR($T10="",$T10=Summary!$C$11)),$C10*IF($H10&lt;&gt;"",$H10,($D10+$E10)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P10,Summary!$B$6:$B$8,0)),0)</f>
         <v>11.5</v>
       </c>
@@ -23286,11 +23313,11 @@
         <v>924</v>
       </c>
       <c r="T10" s="18"/>
-      <c r="U10" s="25" t="n">
+      <c r="U10" s="30" t="n">
         <f aca="false">IF(AND($K10="Y",$F10&lt;&gt;"Y",OR($T10="",$T10=Summary!$C$11)),$C10*IF($H10&lt;&gt;"",$H10,$D10)*INDEX(Summary!$C$6:$C$8,MATCH($P10,Summary!$B$6:$B$8,0)),0)</f>
         <v>8</v>
       </c>
-      <c r="V10" s="25" t="n">
+      <c r="V10" s="30" t="n">
         <f aca="false">IF(AND($K10="Y",$F10&lt;&gt;"Y",OR($T10="",$T10=Summary!$C$11)),$C10*IF($H10&lt;&gt;"",$H10,$E10)*INDEX(Summary!$C$6:$C$8,MATCH($P10,Summary!$B$6:$B$8,0)),0)</f>
         <v>15</v>
       </c>
@@ -23311,10 +23338,10 @@
       <c r="C11" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="27" t="n">
         <v>0.06</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="27" t="n">
         <v>0.12</v>
       </c>
       <c r="F11" s="20" t="s">
@@ -23323,8 +23350,8 @@
       <c r="G11" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="23" t="n">
+      <c r="H11" s="28"/>
+      <c r="I11" s="29" t="n">
         <f aca="false">IF(AND($K11="Y",$F11&lt;&gt;"Y",OR($T11="",$T11=Summary!$C$11)),$C11*IF($H11&lt;&gt;"",$H11,($D11+$E11)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P11,Summary!$B$6:$B$8,0)),0)</f>
         <v>4.5</v>
       </c>
@@ -23359,11 +23386,11 @@
         <v>924</v>
       </c>
       <c r="T11" s="18"/>
-      <c r="U11" s="25" t="n">
+      <c r="U11" s="30" t="n">
         <f aca="false">IF(AND($K11="Y",$F11&lt;&gt;"Y",OR($T11="",$T11=Summary!$C$11)),$C11*IF($H11&lt;&gt;"",$H11,$D11)*INDEX(Summary!$C$6:$C$8,MATCH($P11,Summary!$B$6:$B$8,0)),0)</f>
         <v>3</v>
       </c>
-      <c r="V11" s="25" t="n">
+      <c r="V11" s="30" t="n">
         <f aca="false">IF(AND($K11="Y",$F11&lt;&gt;"Y",OR($T11="",$T11=Summary!$C$11)),$C11*IF($H11&lt;&gt;"",$H11,$E11)*INDEX(Summary!$C$6:$C$8,MATCH($P11,Summary!$B$6:$B$8,0)),0)</f>
         <v>6</v>
       </c>
@@ -23384,10 +23411,10 @@
       <c r="C12" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="27" t="n">
         <v>0.08</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="27" t="n">
         <v>0.15</v>
       </c>
       <c r="F12" s="20" t="s">
@@ -23396,8 +23423,8 @@
       <c r="G12" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="23" t="n">
+      <c r="H12" s="28"/>
+      <c r="I12" s="29" t="n">
         <f aca="false">IF(AND($K12="Y",$F12&lt;&gt;"Y",OR($T12="",$T12=Summary!$C$11)),$C12*IF($H12&lt;&gt;"",$H12,($D12+$E12)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P12,Summary!$B$6:$B$8,0)),0)</f>
         <v>5.75</v>
       </c>
@@ -23432,11 +23459,11 @@
         <v>924</v>
       </c>
       <c r="T12" s="18"/>
-      <c r="U12" s="25" t="n">
+      <c r="U12" s="30" t="n">
         <f aca="false">IF(AND($K12="Y",$F12&lt;&gt;"Y",OR($T12="",$T12=Summary!$C$11)),$C12*IF($H12&lt;&gt;"",$H12,$D12)*INDEX(Summary!$C$6:$C$8,MATCH($P12,Summary!$B$6:$B$8,0)),0)</f>
         <v>4</v>
       </c>
-      <c r="V12" s="25" t="n">
+      <c r="V12" s="30" t="n">
         <f aca="false">IF(AND($K12="Y",$F12&lt;&gt;"Y",OR($T12="",$T12=Summary!$C$11)),$C12*IF($H12&lt;&gt;"",$H12,$E12)*INDEX(Summary!$C$6:$C$8,MATCH($P12,Summary!$B$6:$B$8,0)),0)</f>
         <v>7.5</v>
       </c>
@@ -23457,10 +23484,10 @@
       <c r="C13" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="27" t="n">
         <v>45</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -23469,8 +23496,8 @@
       <c r="G13" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="22"/>
-      <c r="I13" s="23" t="n">
+      <c r="H13" s="28"/>
+      <c r="I13" s="29" t="n">
         <f aca="false">IF(AND($K13="Y",$F13&lt;&gt;"Y",OR($T13="",$T13=Summary!$C$11)),$C13*IF($H13&lt;&gt;"",$H13,($D13+$E13)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P13,Summary!$B$6:$B$8,0)),0)</f>
         <v>35</v>
       </c>
@@ -23505,11 +23532,11 @@
         <v>924</v>
       </c>
       <c r="T13" s="18"/>
-      <c r="U13" s="25" t="n">
+      <c r="U13" s="30" t="n">
         <f aca="false">IF(AND($K13="Y",$F13&lt;&gt;"Y",OR($T13="",$T13=Summary!$C$11)),$C13*IF($H13&lt;&gt;"",$H13,$D13)*INDEX(Summary!$C$6:$C$8,MATCH($P13,Summary!$B$6:$B$8,0)),0)</f>
         <v>25</v>
       </c>
-      <c r="V13" s="25" t="n">
+      <c r="V13" s="30" t="n">
         <f aca="false">IF(AND($K13="Y",$F13&lt;&gt;"Y",OR($T13="",$T13=Summary!$C$11)),$C13*IF($H13&lt;&gt;"",$H13,$E13)*INDEX(Summary!$C$6:$C$8,MATCH($P13,Summary!$B$6:$B$8,0)),0)</f>
         <v>45</v>
       </c>
@@ -23530,10 +23557,10 @@
       <c r="C14" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="27" t="n">
         <v>70</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="27" t="n">
         <v>95</v>
       </c>
       <c r="F14" s="20" t="s">
@@ -23542,8 +23569,8 @@
       <c r="G14" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="23" t="n">
+      <c r="H14" s="28"/>
+      <c r="I14" s="29" t="n">
         <f aca="false">IF(AND($K14="Y",$F14&lt;&gt;"Y",OR($T14="",$T14=Summary!$C$11)),$C14*IF($H14&lt;&gt;"",$H14,($D14+$E14)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P14,Summary!$B$6:$B$8,0)),0)</f>
         <v>165</v>
       </c>
@@ -23578,11 +23605,11 @@
         <v>924</v>
       </c>
       <c r="T14" s="18"/>
-      <c r="U14" s="25" t="n">
+      <c r="U14" s="30" t="n">
         <f aca="false">IF(AND($K14="Y",$F14&lt;&gt;"Y",OR($T14="",$T14=Summary!$C$11)),$C14*IF($H14&lt;&gt;"",$H14,$D14)*INDEX(Summary!$C$6:$C$8,MATCH($P14,Summary!$B$6:$B$8,0)),0)</f>
         <v>140</v>
       </c>
-      <c r="V14" s="25" t="n">
+      <c r="V14" s="30" t="n">
         <f aca="false">IF(AND($K14="Y",$F14&lt;&gt;"Y",OR($T14="",$T14=Summary!$C$11)),$C14*IF($H14&lt;&gt;"",$H14,$E14)*INDEX(Summary!$C$6:$C$8,MATCH($P14,Summary!$B$6:$B$8,0)),0)</f>
         <v>190</v>
       </c>
@@ -23603,10 +23630,10 @@
       <c r="C15" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="27" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="27" t="n">
         <v>65</v>
       </c>
       <c r="F15" s="20" t="s">
@@ -23615,8 +23642,8 @@
       <c r="G15" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="22"/>
-      <c r="I15" s="23" t="n">
+      <c r="H15" s="28"/>
+      <c r="I15" s="29" t="n">
         <f aca="false">IF(AND($K15="Y",$F15&lt;&gt;"Y",OR($T15="",$T15=Summary!$C$11)),$C15*IF($H15&lt;&gt;"",$H15,($D15+$E15)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P15,Summary!$B$6:$B$8,0)),0)</f>
         <v>110</v>
       </c>
@@ -23651,11 +23678,11 @@
         <v>924</v>
       </c>
       <c r="T15" s="18"/>
-      <c r="U15" s="25" t="n">
+      <c r="U15" s="30" t="n">
         <f aca="false">IF(AND($K15="Y",$F15&lt;&gt;"Y",OR($T15="",$T15=Summary!$C$11)),$C15*IF($H15&lt;&gt;"",$H15,$D15)*INDEX(Summary!$C$6:$C$8,MATCH($P15,Summary!$B$6:$B$8,0)),0)</f>
         <v>90</v>
       </c>
-      <c r="V15" s="25" t="n">
+      <c r="V15" s="30" t="n">
         <f aca="false">IF(AND($K15="Y",$F15&lt;&gt;"Y",OR($T15="",$T15=Summary!$C$11)),$C15*IF($H15&lt;&gt;"",$H15,$E15)*INDEX(Summary!$C$6:$C$8,MATCH($P15,Summary!$B$6:$B$8,0)),0)</f>
         <v>130</v>
       </c>
@@ -23676,10 +23703,10 @@
       <c r="C16" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="27" t="n">
         <v>60</v>
       </c>
       <c r="F16" s="20" t="s">
@@ -23688,8 +23715,8 @@
       <c r="G16" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="23" t="n">
+      <c r="H16" s="28"/>
+      <c r="I16" s="29" t="n">
         <f aca="false">IF(AND($K16="Y",$F16&lt;&gt;"Y",OR($T16="",$T16=Summary!$C$11)),$C16*IF($H16&lt;&gt;"",$H16,($D16+$E16)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P16,Summary!$B$6:$B$8,0)),0)</f>
         <v>95</v>
       </c>
@@ -23724,11 +23751,11 @@
         <v>924</v>
       </c>
       <c r="T16" s="18"/>
-      <c r="U16" s="25" t="n">
+      <c r="U16" s="30" t="n">
         <f aca="false">IF(AND($K16="Y",$F16&lt;&gt;"Y",OR($T16="",$T16=Summary!$C$11)),$C16*IF($H16&lt;&gt;"",$H16,$D16)*INDEX(Summary!$C$6:$C$8,MATCH($P16,Summary!$B$6:$B$8,0)),0)</f>
         <v>70</v>
       </c>
-      <c r="V16" s="25" t="n">
+      <c r="V16" s="30" t="n">
         <f aca="false">IF(AND($K16="Y",$F16&lt;&gt;"Y",OR($T16="",$T16=Summary!$C$11)),$C16*IF($H16&lt;&gt;"",$H16,$E16)*INDEX(Summary!$C$6:$C$8,MATCH($P16,Summary!$B$6:$B$8,0)),0)</f>
         <v>120</v>
       </c>
@@ -23749,10 +23776,10 @@
       <c r="C17" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="27" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="27" t="n">
         <v>80</v>
       </c>
       <c r="F17" s="20" t="s">
@@ -23761,8 +23788,8 @@
       <c r="G17" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H17" s="22"/>
-      <c r="I17" s="23" t="n">
+      <c r="H17" s="28"/>
+      <c r="I17" s="29" t="n">
         <f aca="false">IF(AND($K17="Y",$F17&lt;&gt;"Y",OR($T17="",$T17=Summary!$C$11)),$C17*IF($H17&lt;&gt;"",$H17,($D17+$E17)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P17,Summary!$B$6:$B$8,0)),0)</f>
         <v>135</v>
       </c>
@@ -23797,11 +23824,11 @@
         <v>924</v>
       </c>
       <c r="T17" s="18"/>
-      <c r="U17" s="25" t="n">
+      <c r="U17" s="30" t="n">
         <f aca="false">IF(AND($K17="Y",$F17&lt;&gt;"Y",OR($T17="",$T17=Summary!$C$11)),$C17*IF($H17&lt;&gt;"",$H17,$D17)*INDEX(Summary!$C$6:$C$8,MATCH($P17,Summary!$B$6:$B$8,0)),0)</f>
         <v>110</v>
       </c>
-      <c r="V17" s="25" t="n">
+      <c r="V17" s="30" t="n">
         <f aca="false">IF(AND($K17="Y",$F17&lt;&gt;"Y",OR($T17="",$T17=Summary!$C$11)),$C17*IF($H17&lt;&gt;"",$H17,$E17)*INDEX(Summary!$C$6:$C$8,MATCH($P17,Summary!$B$6:$B$8,0)),0)</f>
         <v>160</v>
       </c>
@@ -23822,10 +23849,10 @@
       <c r="C18" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="27" t="n">
         <v>45</v>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="27" t="n">
         <v>65</v>
       </c>
       <c r="F18" s="20" t="s">
@@ -23834,8 +23861,8 @@
       <c r="G18" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="23" t="n">
+      <c r="H18" s="28"/>
+      <c r="I18" s="29" t="n">
         <f aca="false">IF(AND($K18="Y",$F18&lt;&gt;"Y",OR($T18="",$T18=Summary!$C$11)),$C18*IF($H18&lt;&gt;"",$H18,($D18+$E18)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P18,Summary!$B$6:$B$8,0)),0)</f>
         <v>55</v>
       </c>
@@ -23870,11 +23897,11 @@
         <v>924</v>
       </c>
       <c r="T18" s="18"/>
-      <c r="U18" s="25" t="n">
+      <c r="U18" s="30" t="n">
         <f aca="false">IF(AND($K18="Y",$F18&lt;&gt;"Y",OR($T18="",$T18=Summary!$C$11)),$C18*IF($H18&lt;&gt;"",$H18,$D18)*INDEX(Summary!$C$6:$C$8,MATCH($P18,Summary!$B$6:$B$8,0)),0)</f>
         <v>45</v>
       </c>
-      <c r="V18" s="25" t="n">
+      <c r="V18" s="30" t="n">
         <f aca="false">IF(AND($K18="Y",$F18&lt;&gt;"Y",OR($T18="",$T18=Summary!$C$11)),$C18*IF($H18&lt;&gt;"",$H18,$E18)*INDEX(Summary!$C$6:$C$8,MATCH($P18,Summary!$B$6:$B$8,0)),0)</f>
         <v>65</v>
       </c>
@@ -23895,10 +23922,10 @@
       <c r="C19" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="27" t="n">
         <v>37.58</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="27" t="n">
         <v>38.99</v>
       </c>
       <c r="F19" s="20" t="s">
@@ -23907,8 +23934,8 @@
       <c r="G19" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H19" s="22"/>
-      <c r="I19" s="23" t="n">
+      <c r="H19" s="28"/>
+      <c r="I19" s="29" t="n">
         <f aca="false">IF(AND($K19="Y",$F19&lt;&gt;"Y",OR($T19="",$T19=Summary!$C$11)),$C19*IF($H19&lt;&gt;"",$H19,($D19+$E19)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P19,Summary!$B$6:$B$8,0)),0)</f>
         <v>38.285</v>
       </c>
@@ -23943,11 +23970,11 @@
         <v>924</v>
       </c>
       <c r="T19" s="18"/>
-      <c r="U19" s="25" t="n">
+      <c r="U19" s="30" t="n">
         <f aca="false">IF(AND($K19="Y",$F19&lt;&gt;"Y",OR($T19="",$T19=Summary!$C$11)),$C19*IF($H19&lt;&gt;"",$H19,$D19)*INDEX(Summary!$C$6:$C$8,MATCH($P19,Summary!$B$6:$B$8,0)),0)</f>
         <v>37.58</v>
       </c>
-      <c r="V19" s="25" t="n">
+      <c r="V19" s="30" t="n">
         <f aca="false">IF(AND($K19="Y",$F19&lt;&gt;"Y",OR($T19="",$T19=Summary!$C$11)),$C19*IF($H19&lt;&gt;"",$H19,$E19)*INDEX(Summary!$C$6:$C$8,MATCH($P19,Summary!$B$6:$B$8,0)),0)</f>
         <v>38.99</v>
       </c>
@@ -23968,10 +23995,10 @@
       <c r="C20" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="27" t="n">
         <v>10.58</v>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="E20" s="27" t="n">
         <v>24.99</v>
       </c>
       <c r="F20" s="20" t="s">
@@ -23980,8 +24007,8 @@
       <c r="G20" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="22"/>
-      <c r="I20" s="23" t="n">
+      <c r="H20" s="28"/>
+      <c r="I20" s="29" t="n">
         <f aca="false">IF(AND($K20="Y",$F20&lt;&gt;"Y",OR($T20="",$T20=Summary!$C$11)),$C20*IF($H20&lt;&gt;"",$H20,($D20+$E20)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P20,Summary!$B$6:$B$8,0)),0)</f>
         <v>71.14</v>
       </c>
@@ -24016,11 +24043,11 @@
         <v>924</v>
       </c>
       <c r="T20" s="18"/>
-      <c r="U20" s="25" t="n">
+      <c r="U20" s="30" t="n">
         <f aca="false">IF(AND($K20="Y",$F20&lt;&gt;"Y",OR($T20="",$T20=Summary!$C$11)),$C20*IF($H20&lt;&gt;"",$H20,$D20)*INDEX(Summary!$C$6:$C$8,MATCH($P20,Summary!$B$6:$B$8,0)),0)</f>
         <v>42.32</v>
       </c>
-      <c r="V20" s="25" t="n">
+      <c r="V20" s="30" t="n">
         <f aca="false">IF(AND($K20="Y",$F20&lt;&gt;"Y",OR($T20="",$T20=Summary!$C$11)),$C20*IF($H20&lt;&gt;"",$H20,$E20)*INDEX(Summary!$C$6:$C$8,MATCH($P20,Summary!$B$6:$B$8,0)),0)</f>
         <v>99.96</v>
       </c>
@@ -24041,10 +24068,10 @@
       <c r="C21" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="27" t="n">
         <v>1.5</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="27" t="n">
         <v>2.1</v>
       </c>
       <c r="F21" s="20" t="s">
@@ -24053,8 +24080,8 @@
       <c r="G21" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H21" s="22"/>
-      <c r="I21" s="23" t="n">
+      <c r="H21" s="28"/>
+      <c r="I21" s="29" t="n">
         <f aca="false">IF(AND($K21="Y",$F21&lt;&gt;"Y",OR($T21="",$T21=Summary!$C$11)),$C21*IF($H21&lt;&gt;"",$H21,($D21+$E21)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P21,Summary!$B$6:$B$8,0)),0)</f>
         <v>7.2</v>
       </c>
@@ -24089,11 +24116,11 @@
         <v>924</v>
       </c>
       <c r="T21" s="18"/>
-      <c r="U21" s="25" t="n">
+      <c r="U21" s="30" t="n">
         <f aca="false">IF(AND($K21="Y",$F21&lt;&gt;"Y",OR($T21="",$T21=Summary!$C$11)),$C21*IF($H21&lt;&gt;"",$H21,$D21)*INDEX(Summary!$C$6:$C$8,MATCH($P21,Summary!$B$6:$B$8,0)),0)</f>
         <v>6</v>
       </c>
-      <c r="V21" s="25" t="n">
+      <c r="V21" s="30" t="n">
         <f aca="false">IF(AND($K21="Y",$F21&lt;&gt;"Y",OR($T21="",$T21=Summary!$C$11)),$C21*IF($H21&lt;&gt;"",$H21,$E21)*INDEX(Summary!$C$6:$C$8,MATCH($P21,Summary!$B$6:$B$8,0)),0)</f>
         <v>8.4</v>
       </c>
@@ -24114,10 +24141,10 @@
       <c r="C22" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="21" t="n">
+      <c r="D22" s="27" t="n">
         <v>1.73</v>
       </c>
-      <c r="E22" s="21" t="n">
+      <c r="E22" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F22" s="20" t="s">
@@ -24126,8 +24153,8 @@
       <c r="G22" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H22" s="22"/>
-      <c r="I22" s="23" t="n">
+      <c r="H22" s="28"/>
+      <c r="I22" s="29" t="n">
         <f aca="false">IF(AND($K22="Y",$F22&lt;&gt;"Y",OR($T22="",$T22=Summary!$C$11)),$C22*IF($H22&lt;&gt;"",$H22,($D22+$E22)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P22,Summary!$B$6:$B$8,0)),0)</f>
         <v>9.46</v>
       </c>
@@ -24162,11 +24189,11 @@
         <v>924</v>
       </c>
       <c r="T22" s="18"/>
-      <c r="U22" s="25" t="n">
+      <c r="U22" s="30" t="n">
         <f aca="false">IF(AND($K22="Y",$F22&lt;&gt;"Y",OR($T22="",$T22=Summary!$C$11)),$C22*IF($H22&lt;&gt;"",$H22,$D22)*INDEX(Summary!$C$6:$C$8,MATCH($P22,Summary!$B$6:$B$8,0)),0)</f>
         <v>6.92</v>
       </c>
-      <c r="V22" s="25" t="n">
+      <c r="V22" s="30" t="n">
         <f aca="false">IF(AND($K22="Y",$F22&lt;&gt;"Y",OR($T22="",$T22=Summary!$C$11)),$C22*IF($H22&lt;&gt;"",$H22,$E22)*INDEX(Summary!$C$6:$C$8,MATCH($P22,Summary!$B$6:$B$8,0)),0)</f>
         <v>12</v>
       </c>
@@ -24187,10 +24214,10 @@
       <c r="C23" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="21" t="n">
+      <c r="D23" s="27" t="n">
         <v>2.5</v>
       </c>
-      <c r="E23" s="21" t="n">
+      <c r="E23" s="27" t="n">
         <v>4</v>
       </c>
       <c r="F23" s="20" t="s">
@@ -24199,8 +24226,8 @@
       <c r="G23" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H23" s="22"/>
-      <c r="I23" s="23" t="n">
+      <c r="H23" s="28"/>
+      <c r="I23" s="29" t="n">
         <f aca="false">IF(AND($K23="Y",$F23&lt;&gt;"Y",OR($T23="",$T23=Summary!$C$11)),$C23*IF($H23&lt;&gt;"",$H23,($D23+$E23)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P23,Summary!$B$6:$B$8,0)),0)</f>
         <v>13</v>
       </c>
@@ -24235,11 +24262,11 @@
         <v>924</v>
       </c>
       <c r="T23" s="18"/>
-      <c r="U23" s="25" t="n">
+      <c r="U23" s="30" t="n">
         <f aca="false">IF(AND($K23="Y",$F23&lt;&gt;"Y",OR($T23="",$T23=Summary!$C$11)),$C23*IF($H23&lt;&gt;"",$H23,$D23)*INDEX(Summary!$C$6:$C$8,MATCH($P23,Summary!$B$6:$B$8,0)),0)</f>
         <v>10</v>
       </c>
-      <c r="V23" s="25" t="n">
+      <c r="V23" s="30" t="n">
         <f aca="false">IF(AND($K23="Y",$F23&lt;&gt;"Y",OR($T23="",$T23=Summary!$C$11)),$C23*IF($H23&lt;&gt;"",$H23,$E23)*INDEX(Summary!$C$6:$C$8,MATCH($P23,Summary!$B$6:$B$8,0)),0)</f>
         <v>16</v>
       </c>
@@ -24260,18 +24287,18 @@
       <c r="C24" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
       <c r="F24" s="20" t="s">
         <v>103</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="22" t="n">
+      <c r="H24" s="28" t="n">
         <v>185</v>
       </c>
-      <c r="I24" s="23" t="n">
+      <c r="I24" s="29" t="n">
         <f aca="false">IF(AND($K24="Y",$F24&lt;&gt;"Y",OR($T24="",$T24=Summary!$C$11)),$C24*IF($H24&lt;&gt;"",$H24,($D24+$E24)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P24,Summary!$B$6:$B$8,0)),0)</f>
         <v>185</v>
       </c>
@@ -24306,11 +24333,11 @@
         <v>924</v>
       </c>
       <c r="T24" s="18"/>
-      <c r="U24" s="25" t="n">
+      <c r="U24" s="30" t="n">
         <f aca="false">IF(AND($K24="Y",$F24&lt;&gt;"Y",OR($T24="",$T24=Summary!$C$11)),$C24*IF($H24&lt;&gt;"",$H24,$D24)*INDEX(Summary!$C$6:$C$8,MATCH($P24,Summary!$B$6:$B$8,0)),0)</f>
         <v>185</v>
       </c>
-      <c r="V24" s="25" t="n">
+      <c r="V24" s="30" t="n">
         <f aca="false">IF(AND($K24="Y",$F24&lt;&gt;"Y",OR($T24="",$T24=Summary!$C$11)),$C24*IF($H24&lt;&gt;"",$H24,$E24)*INDEX(Summary!$C$6:$C$8,MATCH($P24,Summary!$B$6:$B$8,0)),0)</f>
         <v>185</v>
       </c>
@@ -24331,16 +24358,16 @@
       <c r="C25" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
       <c r="F25" s="20" t="s">
         <v>105</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H25" s="22"/>
-      <c r="I25" s="23" t="n">
+      <c r="H25" s="28"/>
+      <c r="I25" s="29" t="n">
         <f aca="false">IF(AND($K25="Y",$F25&lt;&gt;"Y",OR($T25="",$T25=Summary!$C$11)),$C25*IF($H25&lt;&gt;"",$H25,($D25+$E25)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P25,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -24375,11 +24402,11 @@
         <v>924</v>
       </c>
       <c r="T25" s="18"/>
-      <c r="U25" s="25" t="n">
+      <c r="U25" s="30" t="n">
         <f aca="false">IF(AND($K25="Y",$F25&lt;&gt;"Y",OR($T25="",$T25=Summary!$C$11)),$C25*IF($H25&lt;&gt;"",$H25,$D25)*INDEX(Summary!$C$6:$C$8,MATCH($P25,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="V25" s="25" t="n">
+      <c r="V25" s="30" t="n">
         <f aca="false">IF(AND($K25="Y",$F25&lt;&gt;"Y",OR($T25="",$T25=Summary!$C$11)),$C25*IF($H25&lt;&gt;"",$H25,$E25)*INDEX(Summary!$C$6:$C$8,MATCH($P25,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -24398,10 +24425,10 @@
       <c r="C26" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="21" t="n">
+      <c r="E26" s="27" t="n">
         <v>8.69</v>
       </c>
       <c r="F26" s="20" t="s">
@@ -24410,8 +24437,8 @@
       <c r="G26" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H26" s="22"/>
-      <c r="I26" s="23" t="n">
+      <c r="H26" s="28"/>
+      <c r="I26" s="29" t="n">
         <f aca="false">IF(AND($K26="Y",$F26&lt;&gt;"Y",OR($T26="",$T26=Summary!$C$11)),$C26*IF($H26&lt;&gt;"",$H26,($D26+$E26)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P26,Summary!$B$6:$B$8,0)),0)</f>
         <v>6.345</v>
       </c>
@@ -24446,11 +24473,11 @@
         <v>924</v>
       </c>
       <c r="T26" s="18"/>
-      <c r="U26" s="25" t="n">
+      <c r="U26" s="30" t="n">
         <f aca="false">IF(AND($K26="Y",$F26&lt;&gt;"Y",OR($T26="",$T26=Summary!$C$11)),$C26*IF($H26&lt;&gt;"",$H26,$D26)*INDEX(Summary!$C$6:$C$8,MATCH($P26,Summary!$B$6:$B$8,0)),0)</f>
         <v>4</v>
       </c>
-      <c r="V26" s="25" t="n">
+      <c r="V26" s="30" t="n">
         <f aca="false">IF(AND($K26="Y",$F26&lt;&gt;"Y",OR($T26="",$T26=Summary!$C$11)),$C26*IF($H26&lt;&gt;"",$H26,$E26)*INDEX(Summary!$C$6:$C$8,MATCH($P26,Summary!$B$6:$B$8,0)),0)</f>
         <v>8.69</v>
       </c>
@@ -24471,10 +24498,10 @@
       <c r="C27" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="27" t="n">
         <v>1.07</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="27" t="n">
         <v>4.2</v>
       </c>
       <c r="F27" s="20" t="s">
@@ -24483,8 +24510,8 @@
       <c r="G27" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H27" s="22"/>
-      <c r="I27" s="23" t="n">
+      <c r="H27" s="28"/>
+      <c r="I27" s="29" t="n">
         <f aca="false">IF(AND($K27="Y",$F27&lt;&gt;"Y",OR($T27="",$T27=Summary!$C$11)),$C27*IF($H27&lt;&gt;"",$H27,($D27+$E27)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P27,Summary!$B$6:$B$8,0)),0)</f>
         <v>15.81</v>
       </c>
@@ -24519,11 +24546,11 @@
         <v>924</v>
       </c>
       <c r="T27" s="18"/>
-      <c r="U27" s="25" t="n">
+      <c r="U27" s="30" t="n">
         <f aca="false">IF(AND($K27="Y",$F27&lt;&gt;"Y",OR($T27="",$T27=Summary!$C$11)),$C27*IF($H27&lt;&gt;"",$H27,$D27)*INDEX(Summary!$C$6:$C$8,MATCH($P27,Summary!$B$6:$B$8,0)),0)</f>
         <v>6.42</v>
       </c>
-      <c r="V27" s="25" t="n">
+      <c r="V27" s="30" t="n">
         <f aca="false">IF(AND($K27="Y",$F27&lt;&gt;"Y",OR($T27="",$T27=Summary!$C$11)),$C27*IF($H27&lt;&gt;"",$H27,$E27)*INDEX(Summary!$C$6:$C$8,MATCH($P27,Summary!$B$6:$B$8,0)),0)</f>
         <v>25.2</v>
       </c>
@@ -24544,10 +24571,10 @@
       <c r="C28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="27" t="n">
         <v>2.48</v>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E28" s="27" t="n">
         <v>5.89</v>
       </c>
       <c r="F28" s="20" t="s">
@@ -24556,8 +24583,8 @@
       <c r="G28" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="22"/>
-      <c r="I28" s="23" t="n">
+      <c r="H28" s="28"/>
+      <c r="I28" s="29" t="n">
         <f aca="false">IF(AND($K28="Y",$F28&lt;&gt;"Y",OR($T28="",$T28=Summary!$C$11)),$C28*IF($H28&lt;&gt;"",$H28,($D28+$E28)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P28,Summary!$B$6:$B$8,0)),0)</f>
         <v>4.185</v>
       </c>
@@ -24592,11 +24619,11 @@
         <v>924</v>
       </c>
       <c r="T28" s="18"/>
-      <c r="U28" s="25" t="n">
+      <c r="U28" s="30" t="n">
         <f aca="false">IF(AND($K28="Y",$F28&lt;&gt;"Y",OR($T28="",$T28=Summary!$C$11)),$C28*IF($H28&lt;&gt;"",$H28,$D28)*INDEX(Summary!$C$6:$C$8,MATCH($P28,Summary!$B$6:$B$8,0)),0)</f>
         <v>2.48</v>
       </c>
-      <c r="V28" s="25" t="n">
+      <c r="V28" s="30" t="n">
         <f aca="false">IF(AND($K28="Y",$F28&lt;&gt;"Y",OR($T28="",$T28=Summary!$C$11)),$C28*IF($H28&lt;&gt;"",$H28,$E28)*INDEX(Summary!$C$6:$C$8,MATCH($P28,Summary!$B$6:$B$8,0)),0)</f>
         <v>5.89</v>
       </c>
@@ -24617,10 +24644,10 @@
       <c r="C29" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="21" t="n">
+      <c r="E29" s="27" t="n">
         <v>2</v>
       </c>
       <c r="F29" s="20" t="s">
@@ -24629,8 +24656,8 @@
       <c r="G29" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H29" s="22"/>
-      <c r="I29" s="23" t="n">
+      <c r="H29" s="28"/>
+      <c r="I29" s="29" t="n">
         <f aca="false">IF(AND($K29="Y",$F29&lt;&gt;"Y",OR($T29="",$T29=Summary!$C$11)),$C29*IF($H29&lt;&gt;"",$H29,($D29+$E29)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P29,Summary!$B$6:$B$8,0)),0)</f>
         <v>22.5</v>
       </c>
@@ -24665,11 +24692,11 @@
         <v>924</v>
       </c>
       <c r="T29" s="18"/>
-      <c r="U29" s="25" t="n">
+      <c r="U29" s="30" t="n">
         <f aca="false">IF(AND($K29="Y",$F29&lt;&gt;"Y",OR($T29="",$T29=Summary!$C$11)),$C29*IF($H29&lt;&gt;"",$H29,$D29)*INDEX(Summary!$C$6:$C$8,MATCH($P29,Summary!$B$6:$B$8,0)),0)</f>
         <v>15</v>
       </c>
-      <c r="V29" s="25" t="n">
+      <c r="V29" s="30" t="n">
         <f aca="false">IF(AND($K29="Y",$F29&lt;&gt;"Y",OR($T29="",$T29=Summary!$C$11)),$C29*IF($H29&lt;&gt;"",$H29,$E29)*INDEX(Summary!$C$6:$C$8,MATCH($P29,Summary!$B$6:$B$8,0)),0)</f>
         <v>30</v>
       </c>
@@ -24690,10 +24717,10 @@
       <c r="C30" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="27" t="n">
         <v>0.8</v>
       </c>
-      <c r="E30" s="21" t="n">
+      <c r="E30" s="27" t="n">
         <v>1.5</v>
       </c>
       <c r="F30" s="20" t="s">
@@ -24702,8 +24729,8 @@
       <c r="G30" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H30" s="22"/>
-      <c r="I30" s="23" t="n">
+      <c r="H30" s="28"/>
+      <c r="I30" s="29" t="n">
         <f aca="false">IF(AND($K30="Y",$F30&lt;&gt;"Y",OR($T30="",$T30=Summary!$C$11)),$C30*IF($H30&lt;&gt;"",$H30,($D30+$E30)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P30,Summary!$B$6:$B$8,0)),0)</f>
         <v>11.5</v>
       </c>
@@ -24738,11 +24765,11 @@
         <v>924</v>
       </c>
       <c r="T30" s="18"/>
-      <c r="U30" s="25" t="n">
+      <c r="U30" s="30" t="n">
         <f aca="false">IF(AND($K30="Y",$F30&lt;&gt;"Y",OR($T30="",$T30=Summary!$C$11)),$C30*IF($H30&lt;&gt;"",$H30,$D30)*INDEX(Summary!$C$6:$C$8,MATCH($P30,Summary!$B$6:$B$8,0)),0)</f>
         <v>8</v>
       </c>
-      <c r="V30" s="25" t="n">
+      <c r="V30" s="30" t="n">
         <f aca="false">IF(AND($K30="Y",$F30&lt;&gt;"Y",OR($T30="",$T30=Summary!$C$11)),$C30*IF($H30&lt;&gt;"",$H30,$E30)*INDEX(Summary!$C$6:$C$8,MATCH($P30,Summary!$B$6:$B$8,0)),0)</f>
         <v>15</v>
       </c>
@@ -24763,10 +24790,10 @@
       <c r="C31" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="27" t="n">
         <v>4.45</v>
       </c>
       <c r="F31" s="20" t="s">
@@ -24775,8 +24802,8 @@
       <c r="G31" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H31" s="22"/>
-      <c r="I31" s="23" t="n">
+      <c r="H31" s="28"/>
+      <c r="I31" s="29" t="n">
         <f aca="false">IF(AND($K31="Y",$F31&lt;&gt;"Y",OR($T31="",$T31=Summary!$C$11)),$C31*IF($H31&lt;&gt;"",$H31,($D31+$E31)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P31,Summary!$B$6:$B$8,0)),0)</f>
         <v>7.95</v>
       </c>
@@ -24811,11 +24838,11 @@
         <v>924</v>
       </c>
       <c r="T31" s="18"/>
-      <c r="U31" s="25" t="n">
+      <c r="U31" s="30" t="n">
         <f aca="false">IF(AND($K31="Y",$F31&lt;&gt;"Y",OR($T31="",$T31=Summary!$C$11)),$C31*IF($H31&lt;&gt;"",$H31,$D31)*INDEX(Summary!$C$6:$C$8,MATCH($P31,Summary!$B$6:$B$8,0)),0)</f>
         <v>7</v>
       </c>
-      <c r="V31" s="25" t="n">
+      <c r="V31" s="30" t="n">
         <f aca="false">IF(AND($K31="Y",$F31&lt;&gt;"Y",OR($T31="",$T31=Summary!$C$11)),$C31*IF($H31&lt;&gt;"",$H31,$E31)*INDEX(Summary!$C$6:$C$8,MATCH($P31,Summary!$B$6:$B$8,0)),0)</f>
         <v>8.9</v>
       </c>
@@ -24836,10 +24863,10 @@
       <c r="C32" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="21" t="n">
+      <c r="D32" s="27" t="n">
         <v>17.39</v>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="E32" s="27" t="n">
         <v>30</v>
       </c>
       <c r="F32" s="20" t="s">
@@ -24848,8 +24875,8 @@
       <c r="G32" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H32" s="22"/>
-      <c r="I32" s="23" t="n">
+      <c r="H32" s="28"/>
+      <c r="I32" s="29" t="n">
         <f aca="false">IF(AND($K32="Y",$F32&lt;&gt;"Y",OR($T32="",$T32=Summary!$C$11)),$C32*IF($H32&lt;&gt;"",$H32,($D32+$E32)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P32,Summary!$B$6:$B$8,0)),0)</f>
         <v>23.695</v>
       </c>
@@ -24884,11 +24911,11 @@
         <v>924</v>
       </c>
       <c r="T32" s="18"/>
-      <c r="U32" s="25" t="n">
+      <c r="U32" s="30" t="n">
         <f aca="false">IF(AND($K32="Y",$F32&lt;&gt;"Y",OR($T32="",$T32=Summary!$C$11)),$C32*IF($H32&lt;&gt;"",$H32,$D32)*INDEX(Summary!$C$6:$C$8,MATCH($P32,Summary!$B$6:$B$8,0)),0)</f>
         <v>17.39</v>
       </c>
-      <c r="V32" s="25" t="n">
+      <c r="V32" s="30" t="n">
         <f aca="false">IF(AND($K32="Y",$F32&lt;&gt;"Y",OR($T32="",$T32=Summary!$C$11)),$C32*IF($H32&lt;&gt;"",$H32,$E32)*INDEX(Summary!$C$6:$C$8,MATCH($P32,Summary!$B$6:$B$8,0)),0)</f>
         <v>30</v>
       </c>
@@ -24909,10 +24936,10 @@
       <c r="C33" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="21" t="n">
+      <c r="D33" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="21" t="n">
+      <c r="E33" s="27" t="n">
         <v>15</v>
       </c>
       <c r="F33" s="20" t="s">
@@ -24921,8 +24948,8 @@
       <c r="G33" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H33" s="22"/>
-      <c r="I33" s="23" t="n">
+      <c r="H33" s="28"/>
+      <c r="I33" s="29" t="n">
         <f aca="false">IF(AND($K33="Y",$F33&lt;&gt;"Y",OR($T33="",$T33=Summary!$C$11)),$C33*IF($H33&lt;&gt;"",$H33,($D33+$E33)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P33,Summary!$B$6:$B$8,0)),0)</f>
         <v>7.5</v>
       </c>
@@ -24957,11 +24984,11 @@
         <v>924</v>
       </c>
       <c r="T33" s="18"/>
-      <c r="U33" s="25" t="n">
+      <c r="U33" s="30" t="n">
         <f aca="false">IF(AND($K33="Y",$F33&lt;&gt;"Y",OR($T33="",$T33=Summary!$C$11)),$C33*IF($H33&lt;&gt;"",$H33,$D33)*INDEX(Summary!$C$6:$C$8,MATCH($P33,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="V33" s="25" t="n">
+      <c r="V33" s="30" t="n">
         <f aca="false">IF(AND($K33="Y",$F33&lt;&gt;"Y",OR($T33="",$T33=Summary!$C$11)),$C33*IF($H33&lt;&gt;"",$H33,$E33)*INDEX(Summary!$C$6:$C$8,MATCH($P33,Summary!$B$6:$B$8,0)),0)</f>
         <v>15</v>
       </c>
@@ -24982,10 +25009,10 @@
       <c r="C34" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="21" t="n">
+      <c r="D34" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="E34" s="21" t="n">
+      <c r="E34" s="27" t="n">
         <v>14</v>
       </c>
       <c r="F34" s="20" t="s">
@@ -24994,8 +25021,8 @@
       <c r="G34" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H34" s="22"/>
-      <c r="I34" s="23" t="n">
+      <c r="H34" s="28"/>
+      <c r="I34" s="29" t="n">
         <f aca="false">IF(AND($K34="Y",$F34&lt;&gt;"Y",OR($T34="",$T34=Summary!$C$11)),$C34*IF($H34&lt;&gt;"",$H34,($D34+$E34)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P34,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25030,11 +25057,11 @@
         <v>924</v>
       </c>
       <c r="T34" s="18"/>
-      <c r="U34" s="25" t="n">
+      <c r="U34" s="30" t="n">
         <f aca="false">IF(AND($K34="Y",$F34&lt;&gt;"Y",OR($T34="",$T34=Summary!$C$11)),$C34*IF($H34&lt;&gt;"",$H34,$D34)*INDEX(Summary!$C$6:$C$8,MATCH($P34,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="V34" s="25" t="n">
+      <c r="V34" s="30" t="n">
         <f aca="false">IF(AND($K34="Y",$F34&lt;&gt;"Y",OR($T34="",$T34=Summary!$C$11)),$C34*IF($H34&lt;&gt;"",$H34,$E34)*INDEX(Summary!$C$6:$C$8,MATCH($P34,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25055,10 +25082,10 @@
       <c r="C35" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="21" t="n">
+      <c r="D35" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="E35" s="21" t="n">
+      <c r="E35" s="27" t="n">
         <v>140</v>
       </c>
       <c r="F35" s="20" t="s">
@@ -25067,8 +25094,8 @@
       <c r="G35" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H35" s="22"/>
-      <c r="I35" s="23" t="n">
+      <c r="H35" s="28"/>
+      <c r="I35" s="29" t="n">
         <f aca="false">IF(AND($K35="Y",$F35&lt;&gt;"Y",OR($T35="",$T35=Summary!$C$11)),$C35*IF($H35&lt;&gt;"",$H35,($D35+$E35)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P35,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25103,11 +25130,11 @@
         <v>924</v>
       </c>
       <c r="T35" s="18"/>
-      <c r="U35" s="25" t="n">
+      <c r="U35" s="30" t="n">
         <f aca="false">IF(AND($K35="Y",$F35&lt;&gt;"Y",OR($T35="",$T35=Summary!$C$11)),$C35*IF($H35&lt;&gt;"",$H35,$D35)*INDEX(Summary!$C$6:$C$8,MATCH($P35,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="V35" s="25" t="n">
+      <c r="V35" s="30" t="n">
         <f aca="false">IF(AND($K35="Y",$F35&lt;&gt;"Y",OR($T35="",$T35=Summary!$C$11)),$C35*IF($H35&lt;&gt;"",$H35,$E35)*INDEX(Summary!$C$6:$C$8,MATCH($P35,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25128,10 +25155,10 @@
       <c r="C36" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="21" t="n">
+      <c r="D36" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="E36" s="21" t="n">
+      <c r="E36" s="27" t="n">
         <v>170</v>
       </c>
       <c r="F36" s="20" t="s">
@@ -25140,8 +25167,8 @@
       <c r="G36" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H36" s="22"/>
-      <c r="I36" s="23" t="n">
+      <c r="H36" s="28"/>
+      <c r="I36" s="29" t="n">
         <f aca="false">IF(AND($K36="Y",$F36&lt;&gt;"Y",OR($T36="",$T36=Summary!$C$11)),$C36*IF($H36&lt;&gt;"",$H36,($D36+$E36)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P36,Summary!$B$6:$B$8,0)),0)</f>
         <v>125</v>
       </c>
@@ -25176,11 +25203,11 @@
         <v>924</v>
       </c>
       <c r="T36" s="18"/>
-      <c r="U36" s="25" t="n">
+      <c r="U36" s="30" t="n">
         <f aca="false">IF(AND($K36="Y",$F36&lt;&gt;"Y",OR($T36="",$T36=Summary!$C$11)),$C36*IF($H36&lt;&gt;"",$H36,$D36)*INDEX(Summary!$C$6:$C$8,MATCH($P36,Summary!$B$6:$B$8,0)),0)</f>
         <v>80</v>
       </c>
-      <c r="V36" s="25" t="n">
+      <c r="V36" s="30" t="n">
         <f aca="false">IF(AND($K36="Y",$F36&lt;&gt;"Y",OR($T36="",$T36=Summary!$C$11)),$C36*IF($H36&lt;&gt;"",$H36,$E36)*INDEX(Summary!$C$6:$C$8,MATCH($P36,Summary!$B$6:$B$8,0)),0)</f>
         <v>170</v>
       </c>
@@ -25201,10 +25228,10 @@
       <c r="C37" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="21" t="n">
+      <c r="D37" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="E37" s="27" t="n">
         <v>35</v>
       </c>
       <c r="F37" s="20" t="s">
@@ -25213,8 +25240,8 @@
       <c r="G37" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H37" s="22"/>
-      <c r="I37" s="23" t="n">
+      <c r="H37" s="28"/>
+      <c r="I37" s="29" t="n">
         <f aca="false">IF(AND($K37="Y",$F37&lt;&gt;"Y",OR($T37="",$T37=Summary!$C$11)),$C37*IF($H37&lt;&gt;"",$H37,($D37+$E37)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P37,Summary!$B$6:$B$8,0)),0)</f>
         <v>27.5</v>
       </c>
@@ -25249,11 +25276,11 @@
         <v>924</v>
       </c>
       <c r="T37" s="18"/>
-      <c r="U37" s="25" t="n">
+      <c r="U37" s="30" t="n">
         <f aca="false">IF(AND($K37="Y",$F37&lt;&gt;"Y",OR($T37="",$T37=Summary!$C$11)),$C37*IF($H37&lt;&gt;"",$H37,$D37)*INDEX(Summary!$C$6:$C$8,MATCH($P37,Summary!$B$6:$B$8,0)),0)</f>
         <v>20</v>
       </c>
-      <c r="V37" s="25" t="n">
+      <c r="V37" s="30" t="n">
         <f aca="false">IF(AND($K37="Y",$F37&lt;&gt;"Y",OR($T37="",$T37=Summary!$C$11)),$C37*IF($H37&lt;&gt;"",$H37,$E37)*INDEX(Summary!$C$6:$C$8,MATCH($P37,Summary!$B$6:$B$8,0)),0)</f>
         <v>35</v>
       </c>
@@ -25274,10 +25301,10 @@
       <c r="C38" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="27" t="n">
         <v>238.68</v>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="E38" s="27" t="n">
         <v>266.99</v>
       </c>
       <c r="F38" s="20" t="s">
@@ -25286,8 +25313,8 @@
       <c r="G38" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H38" s="22"/>
-      <c r="I38" s="23" t="n">
+      <c r="H38" s="28"/>
+      <c r="I38" s="29" t="n">
         <f aca="false">IF(AND($K38="Y",$F38&lt;&gt;"Y",OR($T38="",$T38=Summary!$C$11)),$C38*IF($H38&lt;&gt;"",$H38,($D38+$E38)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P38,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25322,11 +25349,11 @@
         <v>924</v>
       </c>
       <c r="T38" s="18"/>
-      <c r="U38" s="25" t="n">
+      <c r="U38" s="30" t="n">
         <f aca="false">IF(AND($K38="Y",$F38&lt;&gt;"Y",OR($T38="",$T38=Summary!$C$11)),$C38*IF($H38&lt;&gt;"",$H38,$D38)*INDEX(Summary!$C$6:$C$8,MATCH($P38,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="V38" s="25" t="n">
+      <c r="V38" s="30" t="n">
         <f aca="false">IF(AND($K38="Y",$F38&lt;&gt;"Y",OR($T38="",$T38=Summary!$C$11)),$C38*IF($H38&lt;&gt;"",$H38,$E38)*INDEX(Summary!$C$6:$C$8,MATCH($P38,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25347,10 +25374,10 @@
       <c r="C39" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="21" t="n">
+      <c r="D39" s="27" t="n">
         <v>16.38</v>
       </c>
-      <c r="E39" s="21" t="n">
+      <c r="E39" s="27" t="n">
         <v>23.38</v>
       </c>
       <c r="F39" s="20" t="s">
@@ -25359,8 +25386,8 @@
       <c r="G39" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H39" s="22"/>
-      <c r="I39" s="23" t="n">
+      <c r="H39" s="28"/>
+      <c r="I39" s="29" t="n">
         <f aca="false">IF(AND($K39="Y",$F39&lt;&gt;"Y",OR($T39="",$T39=Summary!$C$11)),$C39*IF($H39&lt;&gt;"",$H39,($D39+$E39)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P39,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25395,11 +25422,11 @@
         <v>924</v>
       </c>
       <c r="T39" s="18"/>
-      <c r="U39" s="25" t="n">
+      <c r="U39" s="30" t="n">
         <f aca="false">IF(AND($K39="Y",$F39&lt;&gt;"Y",OR($T39="",$T39=Summary!$C$11)),$C39*IF($H39&lt;&gt;"",$H39,$D39)*INDEX(Summary!$C$6:$C$8,MATCH($P39,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="V39" s="25" t="n">
+      <c r="V39" s="30" t="n">
         <f aca="false">IF(AND($K39="Y",$F39&lt;&gt;"Y",OR($T39="",$T39=Summary!$C$11)),$C39*IF($H39&lt;&gt;"",$H39,$E39)*INDEX(Summary!$C$6:$C$8,MATCH($P39,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25420,16 +25447,16 @@
       <c r="C40" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
       <c r="F40" s="20" t="s">
         <v>105</v>
       </c>
       <c r="G40" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H40" s="22"/>
-      <c r="I40" s="23" t="n">
+      <c r="H40" s="28"/>
+      <c r="I40" s="29" t="n">
         <f aca="false">IF(AND($K40="Y",$F40&lt;&gt;"Y",OR($T40="",$T40=Summary!$C$11)),$C40*IF($H40&lt;&gt;"",$H40,($D40+$E40)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P40,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25464,11 +25491,11 @@
         <v>924</v>
       </c>
       <c r="T40" s="18"/>
-      <c r="U40" s="25" t="n">
+      <c r="U40" s="30" t="n">
         <f aca="false">IF(AND($K40="Y",$F40&lt;&gt;"Y",OR($T40="",$T40=Summary!$C$11)),$C40*IF($H40&lt;&gt;"",$H40,$D40)*INDEX(Summary!$C$6:$C$8,MATCH($P40,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="V40" s="25" t="n">
+      <c r="V40" s="30" t="n">
         <f aca="false">IF(AND($K40="Y",$F40&lt;&gt;"Y",OR($T40="",$T40=Summary!$C$11)),$C40*IF($H40&lt;&gt;"",$H40,$E40)*INDEX(Summary!$C$6:$C$8,MATCH($P40,Summary!$B$6:$B$8,0)),0)</f>
         <v>0</v>
       </c>
@@ -25487,10 +25514,10 @@
       <c r="C41" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="21" t="n">
+      <c r="D41" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="E41" s="21" t="n">
+      <c r="E41" s="27" t="n">
         <v>35</v>
       </c>
       <c r="F41" s="20" t="s">
@@ -25499,8 +25526,8 @@
       <c r="G41" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H41" s="22"/>
-      <c r="I41" s="23" t="n">
+      <c r="H41" s="28"/>
+      <c r="I41" s="29" t="n">
         <f aca="false">IF(AND($K41="Y",$F41&lt;&gt;"Y",OR($T41="",$T41=Summary!$C$11)),$C41*IF($H41&lt;&gt;"",$H41,($D41+$E41)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P41,Summary!$B$6:$B$8,0)),0)</f>
         <v>25</v>
       </c>
@@ -25535,11 +25562,11 @@
         <v>924</v>
       </c>
       <c r="T41" s="18"/>
-      <c r="U41" s="25" t="n">
+      <c r="U41" s="30" t="n">
         <f aca="false">IF(AND($K41="Y",$F41&lt;&gt;"Y",OR($T41="",$T41=Summary!$C$11)),$C41*IF($H41&lt;&gt;"",$H41,$D41)*INDEX(Summary!$C$6:$C$8,MATCH($P41,Summary!$B$6:$B$8,0)),0)</f>
         <v>15</v>
       </c>
-      <c r="V41" s="25" t="n">
+      <c r="V41" s="30" t="n">
         <f aca="false">IF(AND($K41="Y",$F41&lt;&gt;"Y",OR($T41="",$T41=Summary!$C$11)),$C41*IF($H41&lt;&gt;"",$H41,$E41)*INDEX(Summary!$C$6:$C$8,MATCH($P41,Summary!$B$6:$B$8,0)),0)</f>
         <v>35</v>
       </c>
@@ -25560,10 +25587,10 @@
       <c r="C42" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="21" t="n">
+      <c r="D42" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="E42" s="21" t="n">
+      <c r="E42" s="27" t="n">
         <v>60</v>
       </c>
       <c r="F42" s="20" t="s">
@@ -25572,8 +25599,8 @@
       <c r="G42" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H42" s="22"/>
-      <c r="I42" s="23" t="n">
+      <c r="H42" s="28"/>
+      <c r="I42" s="29" t="n">
         <f aca="false">IF(AND($K42="Y",$F42&lt;&gt;"Y",OR($T42="",$T42=Summary!$C$11)),$C42*IF($H42&lt;&gt;"",$H42,($D42+$E42)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P42,Summary!$B$6:$B$8,0)),0)</f>
         <v>42.5</v>
       </c>
@@ -25608,11 +25635,11 @@
         <v>924</v>
       </c>
       <c r="T42" s="18"/>
-      <c r="U42" s="25" t="n">
+      <c r="U42" s="30" t="n">
         <f aca="false">IF(AND($K42="Y",$F42&lt;&gt;"Y",OR($T42="",$T42=Summary!$C$11)),$C42*IF($H42&lt;&gt;"",$H42,$D42)*INDEX(Summary!$C$6:$C$8,MATCH($P42,Summary!$B$6:$B$8,0)),0)</f>
         <v>25</v>
       </c>
-      <c r="V42" s="25" t="n">
+      <c r="V42" s="30" t="n">
         <f aca="false">IF(AND($K42="Y",$F42&lt;&gt;"Y",OR($T42="",$T42=Summary!$C$11)),$C42*IF($H42&lt;&gt;"",$H42,$E42)*INDEX(Summary!$C$6:$C$8,MATCH($P42,Summary!$B$6:$B$8,0)),0)</f>
         <v>60</v>
       </c>
@@ -25633,10 +25660,10 @@
       <c r="C43" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="21" t="n">
+      <c r="D43" s="27" t="n">
         <v>10.85</v>
       </c>
-      <c r="E43" s="21" t="n">
+      <c r="E43" s="27" t="n">
         <v>15</v>
       </c>
       <c r="F43" s="20" t="s">
@@ -25645,8 +25672,8 @@
       <c r="G43" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H43" s="22"/>
-      <c r="I43" s="23" t="n">
+      <c r="H43" s="28"/>
+      <c r="I43" s="29" t="n">
         <f aca="false">IF(AND($K43="Y",$F43&lt;&gt;"Y",OR($T43="",$T43=Summary!$C$11)),$C43*IF($H43&lt;&gt;"",$H43,($D43+$E43)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P43,Summary!$B$6:$B$8,0)),0)</f>
         <v>12.925</v>
       </c>
@@ -25681,11 +25708,11 @@
         <v>924</v>
       </c>
       <c r="T43" s="18"/>
-      <c r="U43" s="25" t="n">
+      <c r="U43" s="30" t="n">
         <f aca="false">IF(AND($K43="Y",$F43&lt;&gt;"Y",OR($T43="",$T43=Summary!$C$11)),$C43*IF($H43&lt;&gt;"",$H43,$D43)*INDEX(Summary!$C$6:$C$8,MATCH($P43,Summary!$B$6:$B$8,0)),0)</f>
         <v>10.85</v>
       </c>
-      <c r="V43" s="25" t="n">
+      <c r="V43" s="30" t="n">
         <f aca="false">IF(AND($K43="Y",$F43&lt;&gt;"Y",OR($T43="",$T43=Summary!$C$11)),$C43*IF($H43&lt;&gt;"",$H43,$E43)*INDEX(Summary!$C$6:$C$8,MATCH($P43,Summary!$B$6:$B$8,0)),0)</f>
         <v>15</v>
       </c>
@@ -25706,10 +25733,10 @@
       <c r="C44" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="21" t="n">
+      <c r="D44" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E44" s="21" t="n">
+      <c r="E44" s="27" t="n">
         <v>25</v>
       </c>
       <c r="F44" s="20" t="s">
@@ -25718,8 +25745,8 @@
       <c r="G44" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H44" s="22"/>
-      <c r="I44" s="23" t="n">
+      <c r="H44" s="28"/>
+      <c r="I44" s="29" t="n">
         <f aca="false">IF(AND($K44="Y",$F44&lt;&gt;"Y",OR($T44="",$T44=Summary!$C$11)),$C44*IF($H44&lt;&gt;"",$H44,($D44+$E44)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P44,Summary!$B$6:$B$8,0)),0)</f>
         <v>17.5</v>
       </c>
@@ -25754,11 +25781,11 @@
         <v>924</v>
       </c>
       <c r="T44" s="18"/>
-      <c r="U44" s="25" t="n">
+      <c r="U44" s="30" t="n">
         <f aca="false">IF(AND($K44="Y",$F44&lt;&gt;"Y",OR($T44="",$T44=Summary!$C$11)),$C44*IF($H44&lt;&gt;"",$H44,$D44)*INDEX(Summary!$C$6:$C$8,MATCH($P44,Summary!$B$6:$B$8,0)),0)</f>
         <v>10</v>
       </c>
-      <c r="V44" s="25" t="n">
+      <c r="V44" s="30" t="n">
         <f aca="false">IF(AND($K44="Y",$F44&lt;&gt;"Y",OR($T44="",$T44=Summary!$C$11)),$C44*IF($H44&lt;&gt;"",$H44,$E44)*INDEX(Summary!$C$6:$C$8,MATCH($P44,Summary!$B$6:$B$8,0)),0)</f>
         <v>25</v>
       </c>
@@ -25779,10 +25806,10 @@
       <c r="C45" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="21" t="n">
+      <c r="D45" s="27" t="n">
         <v>5.55</v>
       </c>
-      <c r="E45" s="21" t="n">
+      <c r="E45" s="27" t="n">
         <v>17.09</v>
       </c>
       <c r="F45" s="20" t="s">
@@ -25791,8 +25818,8 @@
       <c r="G45" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H45" s="22"/>
-      <c r="I45" s="23" t="n">
+      <c r="H45" s="28"/>
+      <c r="I45" s="29" t="n">
         <f aca="false">IF(AND($K45="Y",$F45&lt;&gt;"Y",OR($T45="",$T45=Summary!$C$11)),$C45*IF($H45&lt;&gt;"",$H45,($D45+$E45)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P45,Summary!$B$6:$B$8,0)),0)</f>
         <v>22.64</v>
       </c>
@@ -25827,11 +25854,11 @@
         <v>924</v>
       </c>
       <c r="T45" s="18"/>
-      <c r="U45" s="25" t="n">
+      <c r="U45" s="30" t="n">
         <f aca="false">IF(AND($K45="Y",$F45&lt;&gt;"Y",OR($T45="",$T45=Summary!$C$11)),$C45*IF($H45&lt;&gt;"",$H45,$D45)*INDEX(Summary!$C$6:$C$8,MATCH($P45,Summary!$B$6:$B$8,0)),0)</f>
         <v>11.1</v>
       </c>
-      <c r="V45" s="25" t="n">
+      <c r="V45" s="30" t="n">
         <f aca="false">IF(AND($K45="Y",$F45&lt;&gt;"Y",OR($T45="",$T45=Summary!$C$11)),$C45*IF($H45&lt;&gt;"",$H45,$E45)*INDEX(Summary!$C$6:$C$8,MATCH($P45,Summary!$B$6:$B$8,0)),0)</f>
         <v>34.18</v>
       </c>
@@ -25852,10 +25879,10 @@
       <c r="C46" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="21" t="n">
+      <c r="D46" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E46" s="21" t="n">
+      <c r="E46" s="27" t="n">
         <v>8.19</v>
       </c>
       <c r="F46" s="20" t="s">
@@ -25864,8 +25891,8 @@
       <c r="G46" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H46" s="22"/>
-      <c r="I46" s="23" t="n">
+      <c r="H46" s="28"/>
+      <c r="I46" s="29" t="n">
         <f aca="false">IF(AND($K46="Y",$F46&lt;&gt;"Y",OR($T46="",$T46=Summary!$C$11)),$C46*IF($H46&lt;&gt;"",$H46,($D46+$E46)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P46,Summary!$B$6:$B$8,0)),0)</f>
         <v>12.19</v>
       </c>
@@ -25900,11 +25927,11 @@
         <v>924</v>
       </c>
       <c r="T46" s="18"/>
-      <c r="U46" s="25" t="n">
+      <c r="U46" s="30" t="n">
         <f aca="false">IF(AND($K46="Y",$F46&lt;&gt;"Y",OR($T46="",$T46=Summary!$C$11)),$C46*IF($H46&lt;&gt;"",$H46,$D46)*INDEX(Summary!$C$6:$C$8,MATCH($P46,Summary!$B$6:$B$8,0)),0)</f>
         <v>8</v>
       </c>
-      <c r="V46" s="25" t="n">
+      <c r="V46" s="30" t="n">
         <f aca="false">IF(AND($K46="Y",$F46&lt;&gt;"Y",OR($T46="",$T46=Summary!$C$11)),$C46*IF($H46&lt;&gt;"",$H46,$E46)*INDEX(Summary!$C$6:$C$8,MATCH($P46,Summary!$B$6:$B$8,0)),0)</f>
         <v>16.38</v>
       </c>
@@ -25925,10 +25952,10 @@
       <c r="C47" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="21" t="n">
+      <c r="D47" s="27" t="n">
         <v>19.46</v>
       </c>
-      <c r="E47" s="21" t="n">
+      <c r="E47" s="27" t="n">
         <v>22.79</v>
       </c>
       <c r="F47" s="20" t="s">
@@ -25937,8 +25964,8 @@
       <c r="G47" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H47" s="22"/>
-      <c r="I47" s="23" t="n">
+      <c r="H47" s="28"/>
+      <c r="I47" s="29" t="n">
         <f aca="false">IF(AND($K47="Y",$F47&lt;&gt;"Y",OR($T47="",$T47=Summary!$C$11)),$C47*IF($H47&lt;&gt;"",$H47,($D47+$E47)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P47,Summary!$B$6:$B$8,0)),0)</f>
         <v>21.125</v>
       </c>
@@ -25973,11 +26000,11 @@
         <v>924</v>
       </c>
       <c r="T47" s="18"/>
-      <c r="U47" s="25" t="n">
+      <c r="U47" s="30" t="n">
         <f aca="false">IF(AND($K47="Y",$F47&lt;&gt;"Y",OR($T47="",$T47=Summary!$C$11)),$C47*IF($H47&lt;&gt;"",$H47,$D47)*INDEX(Summary!$C$6:$C$8,MATCH($P47,Summary!$B$6:$B$8,0)),0)</f>
         <v>19.46</v>
       </c>
-      <c r="V47" s="25" t="n">
+      <c r="V47" s="30" t="n">
         <f aca="false">IF(AND($K47="Y",$F47&lt;&gt;"Y",OR($T47="",$T47=Summary!$C$11)),$C47*IF($H47&lt;&gt;"",$H47,$E47)*INDEX(Summary!$C$6:$C$8,MATCH($P47,Summary!$B$6:$B$8,0)),0)</f>
         <v>22.79</v>
       </c>
@@ -25998,10 +26025,10 @@
       <c r="C48" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="21" t="n">
+      <c r="D48" s="27" t="n">
         <v>5.39</v>
       </c>
-      <c r="E48" s="21" t="n">
+      <c r="E48" s="27" t="n">
         <v>7.79</v>
       </c>
       <c r="F48" s="20" t="s">
@@ -26010,8 +26037,8 @@
       <c r="G48" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H48" s="22"/>
-      <c r="I48" s="23" t="n">
+      <c r="H48" s="28"/>
+      <c r="I48" s="29" t="n">
         <f aca="false">IF(AND($K48="Y",$F48&lt;&gt;"Y",OR($T48="",$T48=Summary!$C$11)),$C48*IF($H48&lt;&gt;"",$H48,($D48+$E48)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P48,Summary!$B$6:$B$8,0)),0)</f>
         <v>6.59</v>
       </c>
@@ -26046,11 +26073,11 @@
         <v>924</v>
       </c>
       <c r="T48" s="18"/>
-      <c r="U48" s="25" t="n">
+      <c r="U48" s="30" t="n">
         <f aca="false">IF(AND($K48="Y",$F48&lt;&gt;"Y",OR($T48="",$T48=Summary!$C$11)),$C48*IF($H48&lt;&gt;"",$H48,$D48)*INDEX(Summary!$C$6:$C$8,MATCH($P48,Summary!$B$6:$B$8,0)),0)</f>
         <v>5.39</v>
       </c>
-      <c r="V48" s="25" t="n">
+      <c r="V48" s="30" t="n">
         <f aca="false">IF(AND($K48="Y",$F48&lt;&gt;"Y",OR($T48="",$T48=Summary!$C$11)),$C48*IF($H48&lt;&gt;"",$H48,$E48)*INDEX(Summary!$C$6:$C$8,MATCH($P48,Summary!$B$6:$B$8,0)),0)</f>
         <v>7.79</v>
       </c>
@@ -26071,10 +26098,10 @@
       <c r="C49" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="21" t="n">
+      <c r="D49" s="27" t="n">
         <v>11.78</v>
       </c>
-      <c r="E49" s="21" t="n">
+      <c r="E49" s="27" t="n">
         <v>20</v>
       </c>
       <c r="F49" s="20" t="s">
@@ -26083,8 +26110,8 @@
       <c r="G49" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H49" s="22"/>
-      <c r="I49" s="23" t="n">
+      <c r="H49" s="28"/>
+      <c r="I49" s="29" t="n">
         <f aca="false">IF(AND($K49="Y",$F49&lt;&gt;"Y",OR($T49="",$T49=Summary!$C$11)),$C49*IF($H49&lt;&gt;"",$H49,($D49+$E49)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P49,Summary!$B$6:$B$8,0)),0)</f>
         <v>15.89</v>
       </c>
@@ -26119,11 +26146,11 @@
         <v>924</v>
       </c>
       <c r="T49" s="18"/>
-      <c r="U49" s="25" t="n">
+      <c r="U49" s="30" t="n">
         <f aca="false">IF(AND($K49="Y",$F49&lt;&gt;"Y",OR($T49="",$T49=Summary!$C$11)),$C49*IF($H49&lt;&gt;"",$H49,$D49)*INDEX(Summary!$C$6:$C$8,MATCH($P49,Summary!$B$6:$B$8,0)),0)</f>
         <v>11.78</v>
       </c>
-      <c r="V49" s="25" t="n">
+      <c r="V49" s="30" t="n">
         <f aca="false">IF(AND($K49="Y",$F49&lt;&gt;"Y",OR($T49="",$T49=Summary!$C$11)),$C49*IF($H49&lt;&gt;"",$H49,$E49)*INDEX(Summary!$C$6:$C$8,MATCH($P49,Summary!$B$6:$B$8,0)),0)</f>
         <v>20</v>
       </c>
@@ -26144,10 +26171,10 @@
       <c r="C50" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="21" t="n">
+      <c r="D50" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E50" s="21" t="n">
+      <c r="E50" s="27" t="n">
         <v>20</v>
       </c>
       <c r="F50" s="20" t="s">
@@ -26156,8 +26183,8 @@
       <c r="G50" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="22"/>
-      <c r="I50" s="23" t="n">
+      <c r="H50" s="28"/>
+      <c r="I50" s="29" t="n">
         <f aca="false">IF(AND($K50="Y",$F50&lt;&gt;"Y",OR($T50="",$T50=Summary!$C$11)),$C50*IF($H50&lt;&gt;"",$H50,($D50+$E50)/2)*INDEX(Summary!$C$6:$C$8,MATCH($P50,Summary!$B$6:$B$8,0)),0)</f>
         <v>15</v>
       </c>
@@ -26192,11 +26219,11 @@
         <v>924</v>
       </c>
       <c r="T50" s="18"/>
-      <c r="U50" s="25" t="n">
+      <c r="U50" s="30" t="n">
         <f aca="false">IF(AND($K50="Y",$F50&lt;&gt;"Y",OR($T50="",$T50=Summary!$C$11)),$C50*IF($H50&lt;&gt;"",$H50,$D50)*INDEX(Summary!$C$6:$C$8,MATCH($P50,Summary!$B$6:$B$8,0)),0)</f>
         <v>10</v>
       </c>
-      <c r="V50" s="25" t="n">
+      <c r="V50" s="30" t="n">
         <f aca="false">IF(AND($K50="Y",$F50&lt;&gt;"Y",OR($T50="",$T50=Summary!$C$11)),$C50*IF($H50&lt;&gt;"",$H50,$E50)*INDEX(Summary!$C$6:$C$8,MATCH($P50,Summary!$B$6:$B$8,0)),0)</f>
         <v>20</v>
       </c>
@@ -26208,58 +26235,64 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H51" s="14" t="s">
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="H51" s="32" t="s">
         <v>915</v>
       </c>
-      <c r="I51" s="14" t="n">
+      <c r="I51" s="32" t="n">
         <f aca="false">SUM(I5:I50)</f>
         <v>1576.15</v>
       </c>
-      <c r="U51" s="14" t="n">
+      <c r="U51" s="32" t="n">
         <f aca="false">SUM(U5:U50)</f>
         <v>1252.25</v>
       </c>
-      <c r="V51" s="14" t="n">
+      <c r="V51" s="32" t="n">
         <f aca="false">SUM(V5:V50)</f>
         <v>1900.05</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H52" s="14" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="H52" s="32" t="s">
         <v>1142</v>
       </c>
-      <c r="I52" s="14" t="n">
+      <c r="I52" s="32" t="n">
         <f aca="false">SUMIFS($I$5:$I$50,$J$5:$J$50,"Ordered")+SUMIFS($I$5:$I$50,$J$5:$J$50,"Done")</f>
         <v>0</v>
       </c>
-      <c r="U52" s="14" t="n">
+      <c r="U52" s="32" t="n">
         <f aca="false">SUMIFS($U$5:$U$50,$J$5:$J$50,"Ordered")+SUMIFS($U$5:$U$50,$J$5:$J$50,"Done")</f>
         <v>0</v>
       </c>
-      <c r="V52" s="14" t="n">
+      <c r="V52" s="32" t="n">
         <f aca="false">SUMIFS($V$5:$V$50,$J$5:$J$50,"Ordered")+SUMIFS($V$5:$V$50,$J$5:$J$50,"Done")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H53" s="14" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="H53" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="I53" s="14" t="n">
+      <c r="I53" s="32" t="n">
         <f aca="false">I51-I52</f>
         <v>1576.15</v>
       </c>
-      <c r="U53" s="14" t="n">
+      <c r="U53" s="32" t="n">
         <f aca="false">U51-U52</f>
         <v>1252.25</v>
       </c>
-      <c r="V53" s="14" t="n">
+      <c r="V53" s="32" t="n">
         <f aca="false">V51-V52</f>
         <v>1900.05</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H54" s="27" t="s">
+    <row r="54" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H54" s="33" t="s">
         <v>1143</v>
       </c>
     </row>
@@ -26373,80 +26406,85 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="120"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="34" t="s">
         <v>1144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="35" t="s">
         <v>1145</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="35" t="s">
         <v>1146</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="35" t="s">
         <v>1147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="35" t="s">
         <v>1148</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="35" t="s">
         <v>1149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="35" t="s">
         <v>1150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="35" t="s">
         <v>1151</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="35" t="s">
         <v>1152</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="35" t="s">
         <v>1153</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="35" t="s">
         <v>1154</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="35" t="s">
         <v>1155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="35" t="s">
         <v>1156</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="35" t="s">
         <v>1157</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="35" t="s">
+        <v>1158</v>
       </c>
     </row>
   </sheetData>
